--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D61AA6-0381-4A8A-A9F6-3915E10843E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD39F30-64DB-4AE9-A987-D4080FDCA65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -3219,18 +3219,18 @@
             <v>BERARDI</v>
           </cell>
           <cell r="AS120" t="str">
-            <v>SARTI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT120" t="str">
-            <v>SARTI</v>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="121">
           <cell r="AQ121" t="str">
-            <v>SARTI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR121" t="str">
-            <v>SARTI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS121" t="str">
             <v>BARBIERI</v>
@@ -3482,7 +3482,7 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR139" t="str">
-            <v>PAZZAGLIA</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS139" t="str">
             <v>MICHELOT.</v>
@@ -3622,7 +3622,7 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR149" t="str">
-            <v>PAZZAGLIA</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS149" t="str">
             <v>SARTI</v>
@@ -7138,10 +7138,10 @@
             <v>R</v>
           </cell>
           <cell r="DY3" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="DZ3" t="str">
-            <v>M</v>
+            <v>p</v>
           </cell>
           <cell r="EA3" t="str">
             <v>N</v>
@@ -7201,10 +7201,10 @@
             <v>P</v>
           </cell>
           <cell r="ET3" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="EU3" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="EV3" t="str">
             <v>r</v>
@@ -7213,10 +7213,10 @@
             <v>p</v>
           </cell>
           <cell r="EX3" t="str">
-            <v>m</v>
+            <v>r</v>
           </cell>
           <cell r="EY3" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="EZ3" t="str">
             <v>r</v>
@@ -11856,16 +11856,16 @@
             <v>R</v>
           </cell>
           <cell r="DL9" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="DM9" t="str">
-            <v>M/R</v>
+            <v>-</v>
           </cell>
           <cell r="DN9" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="DO9" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="DP9" t="str">
             <v>R</v>
@@ -13045,20 +13045,20 @@
           <cell r="DK10">
             <v>0</v>
           </cell>
-          <cell r="DL10">
-            <v>0</v>
-          </cell>
-          <cell r="DM10">
-            <v>0</v>
-          </cell>
-          <cell r="DN10">
-            <v>0</v>
-          </cell>
-          <cell r="DO10">
-            <v>0</v>
-          </cell>
-          <cell r="DP10">
-            <v>0</v>
+          <cell r="DL10" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="DM10" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="DN10" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="DO10" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="DP10" t="str">
+            <v>m</v>
           </cell>
           <cell r="DQ10">
             <v>0</v>
@@ -14236,7 +14236,7 @@
             <v>M</v>
           </cell>
           <cell r="DL12" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="DM12" t="str">
             <v>r</v>
@@ -19098,7 +19098,7 @@
             <v>p</v>
           </cell>
           <cell r="ET18" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="EU18" t="str">
             <v>r</v>
@@ -19110,10 +19110,10 @@
             <v>r</v>
           </cell>
           <cell r="EX18" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="EY18" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="EZ18" t="str">
             <v>P</v>
@@ -21382,13 +21382,13 @@
             <v>p</v>
           </cell>
           <cell r="DN21" t="str">
-            <v>m</v>
+            <v>N</v>
           </cell>
           <cell r="DO21" t="str">
-            <v>r</v>
+            <v>S</v>
           </cell>
           <cell r="DP21" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="DQ21" t="str">
             <v>r</v>
@@ -22577,8 +22577,8 @@
           <cell r="DO22">
             <v>0</v>
           </cell>
-          <cell r="DP22" t="str">
-            <v>r</v>
+          <cell r="DP22">
+            <v>0</v>
           </cell>
           <cell r="DQ22">
             <v>0</v>
@@ -23759,7 +23759,7 @@
             <v>p</v>
           </cell>
           <cell r="DM24" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="DN24" t="str">
             <v>m</v>
@@ -28511,14 +28511,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" customWidth="1"/>
-    <col min="3" max="3" width="4.42578125" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="16.28515625" customWidth="1"/>
-    <col min="8" max="257" width="3.42578125" customWidth="1"/>
-    <col min="258" max="388" width="4.140625" customWidth="1"/>
+    <col min="2" max="366" width="9.28515625" customWidth="1"/>
+    <col min="367" max="388" width="4.140625" customWidth="1"/>
     <col min="389" max="397" width="4.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -30656,11 +30650,11 @@
       </c>
       <c r="DV3" s="16" t="str">
         <f>[1]CARTELLINO!DY$3</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="DW3" s="16" t="str">
         <f>[1]CARTELLINO!DZ$3</f>
-        <v>M</v>
+        <v>p</v>
       </c>
       <c r="DX3" s="16" t="str">
         <f>[1]CARTELLINO!EA$3</f>
@@ -30740,11 +30734,11 @@
       </c>
       <c r="EQ3" s="16" t="str">
         <f>[1]CARTELLINO!ET$3</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="ER3" s="16" t="str">
         <f>[1]CARTELLINO!EU$3</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="ES3" s="16" t="str">
         <f>[1]CARTELLINO!EV$3</f>
@@ -30756,11 +30750,11 @@
       </c>
       <c r="EU3" s="16" t="str">
         <f>[1]CARTELLINO!EX$3</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="EV3" s="16" t="str">
         <f>[1]CARTELLINO!EY$3</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="EW3" s="16" t="str">
         <f>[1]CARTELLINO!EZ$3</f>
@@ -37795,19 +37789,19 @@
       </c>
       <c r="DI9" s="24" t="str">
         <f>[1]CARTELLINO!DL$9</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="DJ9" s="24" t="str">
         <f>[1]CARTELLINO!DM$9</f>
-        <v>M/R</v>
+        <v>-</v>
       </c>
       <c r="DK9" s="24" t="str">
         <f>[1]CARTELLINO!DN$9</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="DL9" s="24" t="str">
         <f>[1]CARTELLINO!DO$9</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="DM9" s="24" t="str">
         <f>[1]CARTELLINO!DP$9</f>
@@ -39387,25 +39381,25 @@
         <f>[1]CARTELLINO!DK$10</f>
         <v>0</v>
       </c>
-      <c r="DI10" s="46">
+      <c r="DI10" s="46" t="str">
         <f>[1]CARTELLINO!DL$10</f>
-        <v>0</v>
-      </c>
-      <c r="DJ10" s="46">
+        <v>m</v>
+      </c>
+      <c r="DJ10" s="46" t="str">
         <f>[1]CARTELLINO!DM$10</f>
-        <v>0</v>
-      </c>
-      <c r="DK10" s="46">
+        <v>m</v>
+      </c>
+      <c r="DK10" s="46" t="str">
         <f>[1]CARTELLINO!DN$10</f>
-        <v>0</v>
-      </c>
-      <c r="DL10" s="46">
+        <v>m</v>
+      </c>
+      <c r="DL10" s="46" t="str">
         <f>[1]CARTELLINO!DO$10</f>
-        <v>0</v>
-      </c>
-      <c r="DM10" s="46">
+        <v>m</v>
+      </c>
+      <c r="DM10" s="46" t="str">
         <f>[1]CARTELLINO!DP$10</f>
-        <v>0</v>
+        <v>m</v>
       </c>
       <c r="DN10" s="46">
         <f>[1]CARTELLINO!DQ$10</f>
@@ -41391,7 +41385,7 @@
       </c>
       <c r="DI12" s="25" t="str">
         <f>[1]CARTELLINO!DL$12</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="DJ12" s="25" t="str">
         <f>[1]CARTELLINO!DM$12</f>
@@ -48719,7 +48713,7 @@
       </c>
       <c r="EQ18" s="27" t="str">
         <f>[1]CARTELLINO!ET$18</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="ER18" s="27" t="str">
         <f>[1]CARTELLINO!EU$18</f>
@@ -48735,11 +48729,11 @@
       </c>
       <c r="EU18" s="27" t="str">
         <f>[1]CARTELLINO!EX$18</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="EV18" s="27" t="str">
         <f>[1]CARTELLINO!EY$18</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="EW18" s="27" t="str">
         <f>[1]CARTELLINO!EZ$18</f>
@@ -52187,15 +52181,15 @@
       </c>
       <c r="DK21" s="28" t="str">
         <f>[1]CARTELLINO!DN$21</f>
-        <v>m</v>
+        <v>N</v>
       </c>
       <c r="DL21" s="28" t="str">
         <f>[1]CARTELLINO!DO$21</f>
-        <v>r</v>
+        <v>S</v>
       </c>
       <c r="DM21" s="28" t="str">
         <f>[1]CARTELLINO!DP$21</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="DN21" s="28" t="str">
         <f>[1]CARTELLINO!DQ$21</f>
@@ -53787,9 +53781,9 @@
         <f>[1]CARTELLINO!DO$22</f>
         <v>0</v>
       </c>
-      <c r="DM22" s="46" t="str">
+      <c r="DM22" s="46">
         <f>[1]CARTELLINO!DP$22</f>
-        <v>r</v>
+        <v>0</v>
       </c>
       <c r="DN22" s="46">
         <f>[1]CARTELLINO!DQ$22</f>
@@ -55779,7 +55773,7 @@
       </c>
       <c r="DJ24" s="29" t="str">
         <f>[1]CARTELLINO!DM$24</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="DK24" s="29" t="str">
         <f>[1]CARTELLINO!DN$24</f>
@@ -62456,7 +62450,7 @@
         <v>BERARDI</v>
       </c>
       <c r="DK29" s="63" t="str">
-        <v>SARTI</v>
+        <v>BERARDI</v>
       </c>
       <c r="DL29" s="63" t="str">
         <v>BARBIERI</v>
@@ -63556,7 +63550,7 @@
         <v>BERARDI</v>
       </c>
       <c r="DK30" s="63" t="str">
-        <v>SARTI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="DL30" s="63" t="str">
         <v>BARBIERI</v>
@@ -63610,7 +63604,7 @@
         <v>BIANCHI</v>
       </c>
       <c r="EC30" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>BERARDI</v>
       </c>
       <c r="ED30" s="63" t="str">
         <v>MICHELOT.</v>
@@ -63640,7 +63634,7 @@
         <v>BIANCHI</v>
       </c>
       <c r="EM30" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>BERARDI</v>
       </c>
       <c r="EN30" s="63" t="str">
         <v>SARTI</v>
@@ -64653,7 +64647,7 @@
         <v>BERARDI</v>
       </c>
       <c r="DJ31" s="63" t="str">
-        <v>SARTI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="DK31" s="63" t="str">
         <v>BARBIERI</v>
@@ -65753,7 +65747,7 @@
         <v>BERARDI</v>
       </c>
       <c r="DJ32" s="63" t="str">
-        <v>SARTI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="DK32" s="63" t="str">
         <v>BARBIERI</v>

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD39F30-64DB-4AE9-A987-D4080FDCA65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA9C2ED-8A32-473D-83BA-0E3648B394D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3289,7 +3289,7 @@
             <v>SARTI</v>
           </cell>
           <cell r="AS125" t="str">
-            <v>BIANCHI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT125" t="str">
             <v>BIANCHI</v>
@@ -14251,7 +14251,7 @@
             <v>p</v>
           </cell>
           <cell r="DQ12" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="DR12" t="str">
             <v>r</v>
@@ -14440,22 +14440,22 @@
             <v>R</v>
           </cell>
           <cell r="GB12" t="str">
-            <v>r</v>
+            <v>-</v>
           </cell>
           <cell r="GC12" t="str">
             <v>r</v>
           </cell>
           <cell r="GD12" t="str">
-            <v>m</v>
+            <v>r</v>
           </cell>
           <cell r="GE12" t="str">
             <v>p</v>
           </cell>
           <cell r="GF12" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="GG12" t="str">
             <v>m</v>
-          </cell>
-          <cell r="GG12" t="str">
-            <v>p</v>
           </cell>
           <cell r="GH12" t="str">
             <v>m</v>
@@ -15629,8 +15629,8 @@
           <cell r="GA13" t="str">
             <v>f</v>
           </cell>
-          <cell r="GB13">
-            <v>0</v>
+          <cell r="GB13" t="str">
+            <v>f</v>
           </cell>
           <cell r="GC13">
             <v>0</v>
@@ -21394,7 +21394,7 @@
             <v>r</v>
           </cell>
           <cell r="DR21" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="DS21" t="str">
             <v>m</v>
@@ -21592,7 +21592,7 @@
             <v>m</v>
           </cell>
           <cell r="GF21" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="GG21" t="str">
             <v>r</v>
@@ -21724,7 +21724,7 @@
             <v>M</v>
           </cell>
           <cell r="HX21" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="HY21" t="str">
             <v>-</v>
@@ -23771,10 +23771,10 @@
             <v>r</v>
           </cell>
           <cell r="DQ24" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="DR24" t="str">
             <v>p</v>
-          </cell>
-          <cell r="DR24" t="str">
-            <v>m/R</v>
           </cell>
           <cell r="DS24" t="str">
             <v>p</v>
@@ -28517,431 +28517,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28951,7 +28951,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -41405,7 +41405,7 @@
       </c>
       <c r="DN12" s="25" t="str">
         <f>[1]CARTELLINO!DQ$12</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="DO12" s="25" t="str">
         <f>[1]CARTELLINO!DR$12</f>
@@ -41657,7 +41657,7 @@
       </c>
       <c r="FY12" s="25" t="str">
         <f>[1]CARTELLINO!GB$12</f>
-        <v>r</v>
+        <v>-</v>
       </c>
       <c r="FZ12" s="25" t="str">
         <f>[1]CARTELLINO!GC$12</f>
@@ -41665,7 +41665,7 @@
       </c>
       <c r="GA12" s="25" t="str">
         <f>[1]CARTELLINO!GD$12</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="GB12" s="25" t="str">
         <f>[1]CARTELLINO!GE$12</f>
@@ -41673,11 +41673,11 @@
       </c>
       <c r="GC12" s="25" t="str">
         <f>[1]CARTELLINO!GF$12</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="GD12" s="25" t="str">
         <f>[1]CARTELLINO!GG$12</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="GE12" s="25" t="str">
         <f>[1]CARTELLINO!GH$12</f>
@@ -43249,9 +43249,9 @@
         <f>[1]CARTELLINO!GA$13</f>
         <v>f</v>
       </c>
-      <c r="FY13" s="46">
+      <c r="FY13" s="46" t="str">
         <f>[1]CARTELLINO!GB$13</f>
-        <v>0</v>
+        <v>f</v>
       </c>
       <c r="FZ13" s="46">
         <f>[1]CARTELLINO!GC$13</f>
@@ -52197,7 +52197,7 @@
       </c>
       <c r="DO21" s="28" t="str">
         <f>[1]CARTELLINO!DR$21</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="DP21" s="28" t="str">
         <f>[1]CARTELLINO!DS$21</f>
@@ -52461,7 +52461,7 @@
       </c>
       <c r="GC21" s="28" t="str">
         <f>[1]CARTELLINO!GF$21</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="GD21" s="28" t="str">
         <f>[1]CARTELLINO!GG$21</f>
@@ -52637,7 +52637,7 @@
       </c>
       <c r="HU21" s="28" t="str">
         <f>[1]CARTELLINO!HX$21</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="HV21" s="28" t="str">
         <f>[1]CARTELLINO!HY$21</f>
@@ -55789,11 +55789,11 @@
       </c>
       <c r="DN24" s="29" t="str">
         <f>[1]CARTELLINO!DQ$24</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="DO24" s="29" t="str">
         <f>[1]CARTELLINO!DR$24</f>
-        <v>m/R</v>
+        <v>p</v>
       </c>
       <c r="DP24" s="29" t="str">
         <f>[1]CARTELLINO!DS$24</f>
@@ -64662,7 +64662,7 @@
         <v>SARTI</v>
       </c>
       <c r="DO31" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>BERARDI</v>
       </c>
       <c r="DP31" s="63" t="str">
         <v>BARBIERI</v>
@@ -66529,12 +66529,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71027,6 +71027,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71035,13 +71042,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA9C2ED-8A32-473D-83BA-0E3648B394D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79ED2D2-799A-4F23-A3CC-52E6D1FAE59F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="1350" yWindow="570" windowWidth="25665" windowHeight="14910" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -14617,19 +14617,19 @@
             <v>-</v>
           </cell>
           <cell r="II12" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="IJ12" t="str">
-            <v>M</v>
+            <v>R</v>
           </cell>
           <cell r="IK12" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="IL12" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="IM12" t="str">
-            <v>R</v>
+            <v>-</v>
           </cell>
           <cell r="IN12" t="str">
             <v>-</v>
@@ -15797,26 +15797,26 @@
           <cell r="IE13">
             <v>0</v>
           </cell>
-          <cell r="IF13">
-            <v>0</v>
-          </cell>
-          <cell r="IG13">
-            <v>0</v>
-          </cell>
-          <cell r="IH13">
-            <v>0</v>
-          </cell>
-          <cell r="II13">
-            <v>0</v>
-          </cell>
-          <cell r="IJ13">
-            <v>0</v>
-          </cell>
-          <cell r="IK13">
-            <v>0</v>
-          </cell>
-          <cell r="IL13">
-            <v>0</v>
+          <cell r="IF13" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="IG13" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="IH13" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="II13" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="IJ13" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="IK13" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="IL13" t="str">
+            <v>f</v>
           </cell>
           <cell r="IM13">
             <v>0</v>
@@ -28517,431 +28517,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28951,7 +28951,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -41893,23 +41893,23 @@
       </c>
       <c r="IF12" s="25" t="str">
         <f>[1]CARTELLINO!II$12</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="IG12" s="25" t="str">
         <f>[1]CARTELLINO!IJ$12</f>
-        <v>M</v>
+        <v>R</v>
       </c>
       <c r="IH12" s="25" t="str">
         <f>[1]CARTELLINO!IK$12</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="II12" s="25" t="str">
         <f>[1]CARTELLINO!IL$12</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="IJ12" s="25" t="str">
         <f>[1]CARTELLINO!IM$12</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="IK12" s="25" t="str">
         <f>[1]CARTELLINO!IN$12</f>
@@ -43473,33 +43473,33 @@
         <f>[1]CARTELLINO!IE$13</f>
         <v>0</v>
       </c>
-      <c r="IC13" s="46">
+      <c r="IC13" s="46" t="str">
         <f>[1]CARTELLINO!IF$13</f>
-        <v>0</v>
-      </c>
-      <c r="ID13" s="46">
+        <v>f</v>
+      </c>
+      <c r="ID13" s="46" t="str">
         <f>[1]CARTELLINO!IG$13</f>
-        <v>0</v>
-      </c>
-      <c r="IE13" s="46">
+        <v>f</v>
+      </c>
+      <c r="IE13" s="46" t="str">
         <f>[1]CARTELLINO!IH$13</f>
-        <v>0</v>
-      </c>
-      <c r="IF13" s="46">
+        <v>f</v>
+      </c>
+      <c r="IF13" s="46" t="str">
         <f>[1]CARTELLINO!II$13</f>
-        <v>0</v>
-      </c>
-      <c r="IG13" s="46">
+        <v>f</v>
+      </c>
+      <c r="IG13" s="46" t="str">
         <f>[1]CARTELLINO!IJ$13</f>
-        <v>0</v>
-      </c>
-      <c r="IH13" s="46">
+        <v>f</v>
+      </c>
+      <c r="IH13" s="46" t="str">
         <f>[1]CARTELLINO!IK$13</f>
-        <v>0</v>
-      </c>
-      <c r="II13" s="46">
+        <v>f</v>
+      </c>
+      <c r="II13" s="46" t="str">
         <f>[1]CARTELLINO!IL$13</f>
-        <v>0</v>
+        <v>f</v>
       </c>
       <c r="IJ13" s="46">
         <f>[1]CARTELLINO!IM$13</f>
@@ -66529,12 +66529,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71027,13 +71027,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71042,6 +71035,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79ED2D2-799A-4F23-A3CC-52E6D1FAE59F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5964D8-9D49-420B-BAEC-F146D73B16BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1350" yWindow="570" windowWidth="25665" windowHeight="14910" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3292,7 +3292,7 @@
             <v>BERARDI</v>
           </cell>
           <cell r="AT125" t="str">
-            <v>BIANCHI</v>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="126">
@@ -3306,7 +3306,7 @@
             <v>BARBIERI</v>
           </cell>
           <cell r="AT126" t="str">
-            <v>BARBIERI</v>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="127">
@@ -3432,7 +3432,7 @@
             <v>GHIOTTI</v>
           </cell>
           <cell r="AT135" t="str">
-            <v>GHIOTTI</v>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="136">
@@ -7204,13 +7204,13 @@
             <v>p</v>
           </cell>
           <cell r="EU3" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="EV3" t="str">
             <v>p</v>
           </cell>
-          <cell r="EV3" t="str">
+          <cell r="EW3" t="str">
             <v>r</v>
-          </cell>
-          <cell r="EW3" t="str">
-            <v>p</v>
           </cell>
           <cell r="EX3" t="str">
             <v>r</v>
@@ -19098,7 +19098,7 @@
             <v>p</v>
           </cell>
           <cell r="ET18" t="str">
-            <v>m</v>
+            <v>r</v>
           </cell>
           <cell r="EU18" t="str">
             <v>r</v>
@@ -19107,7 +19107,7 @@
             <v>r</v>
           </cell>
           <cell r="EW18" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="EX18" t="str">
             <v>m</v>
@@ -28517,431 +28517,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28951,7 +28951,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -30738,15 +30738,15 @@
       </c>
       <c r="ER3" s="16" t="str">
         <f>[1]CARTELLINO!EU$3</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="ES3" s="16" t="str">
         <f>[1]CARTELLINO!EV$3</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="ET3" s="16" t="str">
         <f>[1]CARTELLINO!EW$3</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="EU3" s="16" t="str">
         <f>[1]CARTELLINO!EX$3</f>
@@ -48713,7 +48713,7 @@
       </c>
       <c r="EQ18" s="27" t="str">
         <f>[1]CARTELLINO!ET$18</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="ER18" s="27" t="str">
         <f>[1]CARTELLINO!EU$18</f>
@@ -48725,7 +48725,7 @@
       </c>
       <c r="ET18" s="27" t="str">
         <f>[1]CARTELLINO!EW$18</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="EU18" s="27" t="str">
         <f>[1]CARTELLINO!EX$18</f>
@@ -65762,10 +65762,10 @@
         <v>SARTI</v>
       </c>
       <c r="DO32" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>BERARDI</v>
       </c>
       <c r="DP32" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>BERARDI</v>
       </c>
       <c r="DQ32" s="63" t="str">
         <v>MICHELOT.</v>
@@ -65792,7 +65792,7 @@
         <v>FABBRI</v>
       </c>
       <c r="DY32" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BERARDI</v>
       </c>
       <c r="DZ32" s="63" t="str">
         <v>BARBIERI</v>
@@ -66529,12 +66529,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71027,6 +71027,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71035,13 +71042,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5964D8-9D49-420B-BAEC-F146D73B16BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E841A09D-25AA-4B77-AD39-A7BAEC2B1574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3342,7 +3342,7 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR129" t="str">
-            <v>PAZZAGLIA</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS129" t="str">
             <v>FABBRI</v>
@@ -28517,431 +28517,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28951,7 +28951,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -63574,7 +63574,7 @@
         <v>MICHELOT.</v>
       </c>
       <c r="DS30" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>VOLPINI</v>
       </c>
       <c r="DT30" s="63" t="str">
         <v>FABBRI</v>
@@ -66529,12 +66529,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71027,13 +71027,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71042,6 +71035,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E841A09D-25AA-4B77-AD39-A7BAEC2B1574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{706F46F6-7BC1-4777-9042-19932DDC875E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="0" yWindow="45" windowWidth="28800" windowHeight="14910" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -26178,7 +26178,7 @@
             <v>R</v>
           </cell>
           <cell r="DZ27" t="str">
-            <v>P</v>
+            <v>M</v>
           </cell>
           <cell r="EA27" t="str">
             <v>M/R</v>
@@ -28517,431 +28517,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28951,7 +28951,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -59421,7 +59421,7 @@
       </c>
       <c r="DW27" s="30" t="str">
         <f>[1]CARTELLINO!DZ$27</f>
-        <v>P</v>
+        <v>M</v>
       </c>
       <c r="DX27" s="30" t="str">
         <f>[1]CARTELLINO!EA$27</f>
@@ -66529,12 +66529,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71027,6 +71027,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71035,13 +71042,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{706F46F6-7BC1-4777-9042-19932DDC875E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6779E01F-076A-4C66-BA8E-F98E4B178E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="45" windowWidth="28800" windowHeight="14910" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3376,12 +3376,12 @@
             <v>SARTI</v>
           </cell>
           <cell r="AT131" t="str">
-            <v>SARTI</v>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="132">
           <cell r="AQ132" t="str">
-            <v>SARTI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR132" t="str">
             <v>SARTI</v>
@@ -19047,10 +19047,10 @@
             <v>r</v>
           </cell>
           <cell r="EC18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="ED18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="EE18" t="str">
             <v>r</v>
@@ -20236,11 +20236,11 @@
           <cell r="EB19">
             <v>0</v>
           </cell>
-          <cell r="EC19" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="ED19" t="str">
-            <v>p</v>
+          <cell r="EC19">
+            <v>0</v>
+          </cell>
+          <cell r="ED19">
+            <v>0</v>
           </cell>
           <cell r="EE19">
             <v>0</v>
@@ -26202,7 +26202,7 @@
             <v>m</v>
           </cell>
           <cell r="EH27" t="str">
-            <v>m</v>
+            <v>-</v>
           </cell>
           <cell r="EI27" t="str">
             <v>r</v>
@@ -27391,8 +27391,8 @@
           <cell r="EG28">
             <v>0</v>
           </cell>
-          <cell r="EH28">
-            <v>0</v>
+          <cell r="EH28" t="str">
+            <v>c</v>
           </cell>
           <cell r="EI28">
             <v>0</v>
@@ -28517,431 +28517,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28951,7 +28951,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -48645,11 +48645,11 @@
       </c>
       <c r="DZ18" s="27" t="str">
         <f>[1]CARTELLINO!EC$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="EA18" s="27" t="str">
         <f>[1]CARTELLINO!ED$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="EB18" s="27" t="str">
         <f>[1]CARTELLINO!EE$18</f>
@@ -50237,13 +50237,13 @@
         <f>[1]CARTELLINO!EB$19</f>
         <v>0</v>
       </c>
-      <c r="DZ19" s="46" t="str">
+      <c r="DZ19" s="46">
         <f>[1]CARTELLINO!EC$19</f>
-        <v>p</v>
-      </c>
-      <c r="EA19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="EA19" s="46">
         <f>[1]CARTELLINO!ED$19</f>
-        <v>p</v>
+        <v>0</v>
       </c>
       <c r="EB19" s="46">
         <f>[1]CARTELLINO!EE$19</f>
@@ -59453,7 +59453,7 @@
       </c>
       <c r="EE27" s="30" t="str">
         <f>[1]CARTELLINO!EH$27</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="EF27" s="30" t="str">
         <f>[1]CARTELLINO!EI$27</f>
@@ -61045,9 +61045,9 @@
         <f>[1]CARTELLINO!EG$28</f>
         <v>0</v>
       </c>
-      <c r="EE28" s="62">
+      <c r="EE28" s="62" t="str">
         <f>[1]CARTELLINO!EH$28</f>
-        <v>0</v>
+        <v>c</v>
       </c>
       <c r="EF28" s="62">
         <f>[1]CARTELLINO!EI$28</f>
@@ -62483,7 +62483,7 @@
         <v>BERARDI</v>
       </c>
       <c r="DV29" s="63" t="str">
-        <v>SARTI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="DW29" s="63" t="str">
         <v>VOLPINI</v>
@@ -65780,7 +65780,7 @@
         <v>BERARDI</v>
       </c>
       <c r="DU32" s="63" t="str">
-        <v>SARTI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="DV32" s="63" t="str">
         <v>VOLPINI</v>
@@ -66529,12 +66529,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71027,13 +71027,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71042,6 +71035,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6779E01F-076A-4C66-BA8E-F98E4B178E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE497B6-B731-432D-AC95-00E11F798764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="0" yWindow="570" windowWidth="28800" windowHeight="14910" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3905,18 +3905,18 @@
             <v>VOLPINI</v>
           </cell>
           <cell r="AS169" t="str">
-            <v>BIANCHI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT169" t="str">
-            <v>BIANCHI</v>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="170">
           <cell r="AQ170" t="str">
-            <v>BIANCHI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR170" t="str">
-            <v>BIANCHI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS170" t="str">
             <v>PAZZAGLIA</v>
@@ -4059,18 +4059,18 @@
             <v>BARBIERI</v>
           </cell>
           <cell r="AS180" t="str">
-            <v>PAZZAGLIA</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT180" t="str">
-            <v>PAZZAGLIA</v>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="181">
           <cell r="AQ181" t="str">
-            <v>PAZZAGLIA</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR181" t="str">
-            <v>PAZZAGLIA</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS181" t="str">
             <v>GHIOTTI</v>
@@ -4101,18 +4101,18 @@
             <v>FABBRI</v>
           </cell>
           <cell r="AS183" t="str">
-            <v>BERARDI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT183" t="str">
-            <v>BERARDI</v>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="184">
           <cell r="AQ184" t="str">
-            <v>BERARDI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR184" t="str">
-            <v>BERARDI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS184" t="str">
             <v>BARBIERI</v>
@@ -7156,7 +7156,7 @@
             <v>P</v>
           </cell>
           <cell r="EE3" t="str">
-            <v>M/R</v>
+            <v>-</v>
           </cell>
           <cell r="EF3" t="str">
             <v>N</v>
@@ -7207,16 +7207,16 @@
             <v>m</v>
           </cell>
           <cell r="EV3" t="str">
-            <v>p</v>
+            <v>r</v>
           </cell>
           <cell r="EW3" t="str">
             <v>r</v>
           </cell>
           <cell r="EX3" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="EY3" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="EZ3" t="str">
             <v>r</v>
@@ -7273,19 +7273,19 @@
             <v>r</v>
           </cell>
           <cell r="FR3" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="FS3" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="FT3" t="str">
             <v>N</v>
           </cell>
-          <cell r="FS3" t="str">
+          <cell r="FU3" t="str">
             <v>S</v>
           </cell>
-          <cell r="FT3" t="str">
+          <cell r="FV3" t="str">
             <v>R</v>
-          </cell>
-          <cell r="FU3" t="str">
-            <v>M/R</v>
-          </cell>
-          <cell r="FV3" t="str">
-            <v>P</v>
           </cell>
           <cell r="FW3" t="str">
             <v>N</v>
@@ -8345,8 +8345,8 @@
           <cell r="ED4">
             <v>0</v>
           </cell>
-          <cell r="EE4">
-            <v>0</v>
+          <cell r="EE4" t="str">
+            <v>p</v>
           </cell>
           <cell r="EF4">
             <v>0</v>
@@ -16808,10 +16808,10 @@
             <v>p</v>
           </cell>
           <cell r="FX15" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="FY15" t="str">
             <v>m</v>
-          </cell>
-          <cell r="FY15" t="str">
-            <v>p</v>
           </cell>
           <cell r="FZ15" t="str">
             <v>r</v>
@@ -19113,7 +19113,7 @@
             <v>m</v>
           </cell>
           <cell r="EY18" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="EZ18" t="str">
             <v>P</v>
@@ -19170,7 +19170,7 @@
             <v>p</v>
           </cell>
           <cell r="FR18" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="FS18" t="str">
             <v>m/R</v>
@@ -21526,7 +21526,7 @@
             <v>P</v>
           </cell>
           <cell r="FJ21" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="FK21" t="str">
             <v>N</v>
@@ -21550,25 +21550,25 @@
             <v>m/R</v>
           </cell>
           <cell r="FR21" t="str">
-            <v>p</v>
+            <v>N</v>
           </cell>
           <cell r="FS21" t="str">
-            <v>p</v>
+            <v>S</v>
           </cell>
           <cell r="FT21" t="str">
-            <v>N</v>
+            <v>R</v>
           </cell>
           <cell r="FU21" t="str">
-            <v>S</v>
+            <v>M/R</v>
           </cell>
           <cell r="FV21" t="str">
-            <v>R</v>
+            <v>P</v>
           </cell>
           <cell r="FW21" t="str">
             <v>P</v>
           </cell>
           <cell r="FX21" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="FY21" t="str">
             <v>N</v>
@@ -23906,7 +23906,7 @@
             <v>p</v>
           </cell>
           <cell r="FJ24" t="str">
-            <v>m/R</v>
+            <v>m</v>
           </cell>
           <cell r="FK24" t="str">
             <v>p</v>
@@ -23948,10 +23948,10 @@
             <v>m</v>
           </cell>
           <cell r="FX24" t="str">
+            <v>m/R</v>
+          </cell>
+          <cell r="FY24" t="str">
             <v>p</v>
-          </cell>
-          <cell r="FY24" t="str">
-            <v>m</v>
           </cell>
           <cell r="FZ24" t="str">
             <v>r</v>
@@ -28517,431 +28517,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28951,7 +28951,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -30674,7 +30674,7 @@
       </c>
       <c r="EB3" s="16" t="str">
         <f>[1]CARTELLINO!EE$3</f>
-        <v>M/R</v>
+        <v>-</v>
       </c>
       <c r="EC3" s="16" t="str">
         <f>[1]CARTELLINO!EF$3</f>
@@ -30742,7 +30742,7 @@
       </c>
       <c r="ES3" s="16" t="str">
         <f>[1]CARTELLINO!EV$3</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="ET3" s="16" t="str">
         <f>[1]CARTELLINO!EW$3</f>
@@ -30750,11 +30750,11 @@
       </c>
       <c r="EU3" s="16" t="str">
         <f>[1]CARTELLINO!EX$3</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="EV3" s="16" t="str">
         <f>[1]CARTELLINO!EY$3</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="EW3" s="16" t="str">
         <f>[1]CARTELLINO!EZ$3</f>
@@ -30830,23 +30830,23 @@
       </c>
       <c r="FO3" s="16" t="str">
         <f>[1]CARTELLINO!FR$3</f>
-        <v>N</v>
+        <v>m</v>
       </c>
       <c r="FP3" s="16" t="str">
         <f>[1]CARTELLINO!FS$3</f>
-        <v>S</v>
+        <v>p</v>
       </c>
       <c r="FQ3" s="16" t="str">
         <f>[1]CARTELLINO!FT$3</f>
-        <v>R</v>
+        <v>N</v>
       </c>
       <c r="FR3" s="16" t="str">
         <f>[1]CARTELLINO!FU$3</f>
-        <v>M/R</v>
+        <v>S</v>
       </c>
       <c r="FS3" s="16" t="str">
         <f>[1]CARTELLINO!FV$3</f>
-        <v>P</v>
+        <v>R</v>
       </c>
       <c r="FT3" s="16" t="str">
         <f>[1]CARTELLINO!FW$3</f>
@@ -32266,9 +32266,9 @@
         <f>[1]CARTELLINO!ED$4</f>
         <v>0</v>
       </c>
-      <c r="EB4" s="43">
+      <c r="EB4" s="43" t="str">
         <f>[1]CARTELLINO!EE$4</f>
-        <v>0</v>
+        <v>p</v>
       </c>
       <c r="EC4" s="43">
         <f>[1]CARTELLINO!EF$4</f>
@@ -45237,11 +45237,11 @@
       </c>
       <c r="FU15" s="26" t="str">
         <f>[1]CARTELLINO!FX$15</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="FV15" s="26" t="str">
         <f>[1]CARTELLINO!FY$15</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="FW15" s="26" t="str">
         <f>[1]CARTELLINO!FZ$15</f>
@@ -48733,7 +48733,7 @@
       </c>
       <c r="EV18" s="27" t="str">
         <f>[1]CARTELLINO!EY$18</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="EW18" s="27" t="str">
         <f>[1]CARTELLINO!EZ$18</f>
@@ -48809,7 +48809,7 @@
       </c>
       <c r="FO18" s="27" t="str">
         <f>[1]CARTELLINO!FR$18</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="FP18" s="27" t="str">
         <f>[1]CARTELLINO!FS$18</f>
@@ -52373,7 +52373,7 @@
       </c>
       <c r="FG21" s="28" t="str">
         <f>[1]CARTELLINO!FJ$21</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="FH21" s="28" t="str">
         <f>[1]CARTELLINO!FK$21</f>
@@ -52405,23 +52405,23 @@
       </c>
       <c r="FO21" s="28" t="str">
         <f>[1]CARTELLINO!FR$21</f>
-        <v>p</v>
+        <v>N</v>
       </c>
       <c r="FP21" s="28" t="str">
         <f>[1]CARTELLINO!FS$21</f>
-        <v>p</v>
+        <v>S</v>
       </c>
       <c r="FQ21" s="28" t="str">
         <f>[1]CARTELLINO!FT$21</f>
-        <v>N</v>
+        <v>R</v>
       </c>
       <c r="FR21" s="28" t="str">
         <f>[1]CARTELLINO!FU$21</f>
-        <v>S</v>
+        <v>M/R</v>
       </c>
       <c r="FS21" s="28" t="str">
         <f>[1]CARTELLINO!FV$21</f>
-        <v>R</v>
+        <v>P</v>
       </c>
       <c r="FT21" s="28" t="str">
         <f>[1]CARTELLINO!FW$21</f>
@@ -52429,7 +52429,7 @@
       </c>
       <c r="FU21" s="28" t="str">
         <f>[1]CARTELLINO!FX$21</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="FV21" s="28" t="str">
         <f>[1]CARTELLINO!FY$21</f>
@@ -55969,7 +55969,7 @@
       </c>
       <c r="FG24" s="29" t="str">
         <f>[1]CARTELLINO!FJ$24</f>
-        <v>m/R</v>
+        <v>m</v>
       </c>
       <c r="FH24" s="29" t="str">
         <f>[1]CARTELLINO!FK$24</f>
@@ -56025,11 +56025,11 @@
       </c>
       <c r="FU24" s="29" t="str">
         <f>[1]CARTELLINO!FX$24</f>
-        <v>p</v>
+        <v>m/R</v>
       </c>
       <c r="FV24" s="29" t="str">
         <f>[1]CARTELLINO!FY$24</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="FW24" s="29" t="str">
         <f>[1]CARTELLINO!FZ$24</f>
@@ -62597,7 +62597,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="FH29" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>BERARDI</v>
       </c>
       <c r="FI29" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -62630,7 +62630,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="FS29" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>BERARDI</v>
       </c>
       <c r="FT29" s="63" t="str">
         <v>GHIOTTI</v>
@@ -62639,7 +62639,7 @@
         <v>FABBRI</v>
       </c>
       <c r="FV29" s="63" t="str">
-        <v>BERARDI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="FW29" s="63" t="str">
         <v>BARBIERI</v>
@@ -63697,7 +63697,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="FH30" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>BERARDI</v>
       </c>
       <c r="FI30" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -63730,7 +63730,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="FS30" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>BERARDI</v>
       </c>
       <c r="FT30" s="63" t="str">
         <v>GHIOTTI</v>
@@ -63739,7 +63739,7 @@
         <v>FABBRI</v>
       </c>
       <c r="FV30" s="63" t="str">
-        <v>BERARDI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="FW30" s="63" t="str">
         <v>BARBIERI</v>
@@ -64794,7 +64794,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="FG31" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>BERARDI</v>
       </c>
       <c r="FH31" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -64827,7 +64827,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="FR31" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>BERARDI</v>
       </c>
       <c r="FS31" s="63" t="str">
         <v>GHIOTTI</v>
@@ -64836,7 +64836,7 @@
         <v>FABBRI</v>
       </c>
       <c r="FU31" s="63" t="str">
-        <v>BERARDI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="FV31" s="63" t="str">
         <v>BARBIERI</v>
@@ -65894,7 +65894,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="FG32" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>BERARDI</v>
       </c>
       <c r="FH32" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -65927,7 +65927,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="FR32" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>BERARDI</v>
       </c>
       <c r="FS32" s="63" t="str">
         <v>GHIOTTI</v>
@@ -65936,7 +65936,7 @@
         <v>FABBRI</v>
       </c>
       <c r="FU32" s="63" t="str">
-        <v>BERARDI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="FV32" s="63" t="str">
         <v>BARBIERI</v>
@@ -66529,12 +66529,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71027,6 +71027,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71035,13 +71042,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE497B6-B731-432D-AC95-00E11F798764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4D7256-0C23-4672-A83E-3A30E03FDC05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="570" windowWidth="28800" windowHeight="14910" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -7156,7 +7156,7 @@
             <v>P</v>
           </cell>
           <cell r="EE3" t="str">
-            <v>-</v>
+            <v>/R</v>
           </cell>
           <cell r="EF3" t="str">
             <v>N</v>
@@ -11640,7 +11640,7 @@
             <v>-</v>
           </cell>
           <cell r="AR9" t="str">
-            <v>-</v>
+            <v>/R</v>
           </cell>
           <cell r="AS9" t="str">
             <v>N</v>
@@ -14218,7 +14218,7 @@
             <v>P</v>
           </cell>
           <cell r="DF12" t="str">
-            <v>-</v>
+            <v>/R</v>
           </cell>
           <cell r="DG12" t="str">
             <v>N</v>
@@ -18930,7 +18930,7 @@
             <v>P</v>
           </cell>
           <cell r="CP18" t="str">
-            <v>-</v>
+            <v>/R</v>
           </cell>
           <cell r="CQ18" t="str">
             <v>N</v>
@@ -30674,7 +30674,7 @@
       </c>
       <c r="EB3" s="16" t="str">
         <f>[1]CARTELLINO!EE$3</f>
-        <v>-</v>
+        <v>/R</v>
       </c>
       <c r="EC3" s="16" t="str">
         <f>[1]CARTELLINO!EF$3</f>
@@ -37501,7 +37501,7 @@
       </c>
       <c r="AO9" s="24" t="str">
         <f>[1]CARTELLINO!AR$9</f>
-        <v>-</v>
+        <v>/R</v>
       </c>
       <c r="AP9" s="24" t="str">
         <f>[1]CARTELLINO!AS$9</f>
@@ -41361,7 +41361,7 @@
       </c>
       <c r="DC12" s="25" t="str">
         <f>[1]CARTELLINO!DF$12</f>
-        <v>-</v>
+        <v>/R</v>
       </c>
       <c r="DD12" s="25" t="str">
         <f>[1]CARTELLINO!DG$12</f>
@@ -48489,7 +48489,7 @@
       </c>
       <c r="CM18" s="27" t="str">
         <f>[1]CARTELLINO!CP$18</f>
-        <v>-</v>
+        <v>/R</v>
       </c>
       <c r="CN18" s="27" t="str">
         <f>[1]CARTELLINO!CQ$18</f>

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4D7256-0C23-4672-A83E-3A30E03FDC05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FF7011A-90F8-46CC-87D0-6D758B3CF62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="0" yWindow="1290" windowWidth="28800" windowHeight="14910" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -11913,7 +11913,7 @@
             <v>p</v>
           </cell>
           <cell r="EE9" t="str">
-            <v>m</v>
+            <v>M</v>
           </cell>
           <cell r="EF9" t="str">
             <v>r</v>
@@ -28517,431 +28517,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28951,7 +28951,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -37865,7 +37865,7 @@
       </c>
       <c r="EB9" s="24" t="str">
         <f>[1]CARTELLINO!EE$9</f>
-        <v>m</v>
+        <v>M</v>
       </c>
       <c r="EC9" s="24" t="str">
         <f>[1]CARTELLINO!EF$9</f>
@@ -66529,12 +66529,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71027,13 +71027,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71042,6 +71035,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FF7011A-90F8-46CC-87D0-6D758B3CF62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919E017C-F58C-4F2E-87A9-7A883F433F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1290" windowWidth="28800" windowHeight="14910" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="0" yWindow="570" windowWidth="28800" windowHeight="14910" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3572,7 +3572,7 @@
             <v>FABBRI</v>
           </cell>
           <cell r="AT145" t="str">
-            <v>FABBRI</v>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="146">
@@ -3926,12 +3926,8 @@
           </cell>
         </row>
         <row r="171">
-          <cell r="AQ171" t="str">
-            <v>PAZZAGLIA</v>
-          </cell>
-          <cell r="AR171" t="str">
-            <v>PAZZAGLIA</v>
-          </cell>
+          <cell r="AQ171"/>
+          <cell r="AR171"/>
           <cell r="AS171" t="str">
             <v>SARTI</v>
           </cell>
@@ -4185,438 +4181,438 @@
             <v>GHIOTTI</v>
           </cell>
           <cell r="AS189" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT189" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="190">
           <cell r="AQ190" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR190" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS190" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT190" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="191">
           <cell r="AQ191" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR191" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS191" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT191" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="192">
           <cell r="AQ192" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR192" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS192" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT192" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="193">
           <cell r="AQ193" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR193" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS193" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT193" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="194">
           <cell r="AQ194" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR194" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS194" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT194" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="195">
           <cell r="AQ195" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR195" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS195" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT195" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="196">
           <cell r="AQ196" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR196" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS196" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT196" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="197">
           <cell r="AQ197" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR197" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS197" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT197" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="198">
           <cell r="AQ198" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR198" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS198" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT198" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="199">
           <cell r="AQ199" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR199" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS199" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AT199" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="200">
           <cell r="AQ200" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AR200" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AS200" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT200" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="201">
           <cell r="AQ201" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR201" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS201" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT201" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="202">
           <cell r="AQ202" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR202" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS202" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT202" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="203">
           <cell r="AQ203" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR203" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS203" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT203" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="204">
           <cell r="AQ204" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR204" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS204" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AT204" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="205">
           <cell r="AQ205" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AR205" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AS205" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT205" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="206">
           <cell r="AQ206" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR206" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS206" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT206" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="207">
           <cell r="AQ207" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR207" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS207" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT207" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="208">
           <cell r="AQ208" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR208" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS208" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT208" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="209">
           <cell r="AQ209" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR209" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS209" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AT209" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="210">
           <cell r="AQ210" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AR210" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AS210" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT210" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="211">
           <cell r="AQ211" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR211" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS211" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT211" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="212">
           <cell r="AQ212" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR212" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS212" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT212" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="213">
           <cell r="AQ213" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR213" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS213" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT213" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="214">
           <cell r="AQ214" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR214" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS214" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT214" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="215">
           <cell r="AQ215" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR215" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS215" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AT215" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="216">
           <cell r="AQ216" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AR216" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AS216" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT216" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="217">
           <cell r="AQ217" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR217" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS217" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT217" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="218">
           <cell r="AQ218" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR218" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS218" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT218" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="219">
           <cell r="AQ219" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR219" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS219" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT219" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="220">
           <cell r="AQ220" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR220" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS220" t="str">
             <v/>
@@ -7255,10 +7251,10 @@
             <v>M/R</v>
           </cell>
           <cell r="FL3" t="str">
-            <v>N</v>
+            <v>m</v>
           </cell>
           <cell r="FM3" t="str">
-            <v>S</v>
+            <v>M</v>
           </cell>
           <cell r="FN3" t="str">
             <v>p</v>
@@ -7360,7 +7356,7 @@
             <v>P</v>
           </cell>
           <cell r="GU3" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="GV3" t="str">
             <v>N</v>
@@ -7375,7 +7371,7 @@
             <v>P</v>
           </cell>
           <cell r="GZ3" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="HA3" t="str">
             <v>N</v>
@@ -7393,13 +7389,13 @@
             <v>m</v>
           </cell>
           <cell r="HF3" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="HG3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="HH3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="HI3" t="str">
             <v>N</v>
@@ -7417,37 +7413,37 @@
             <v>M</v>
           </cell>
           <cell r="HN3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="HO3" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="HP3" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="HQ3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="HR3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="HS3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="HT3" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="HU3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="HV3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="HW3" t="str">
             <v>-</v>
           </cell>
           <cell r="HX3" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="HY3" t="str">
             <v>-</v>
@@ -8633,8 +8629,8 @@
           <cell r="HV4">
             <v>0</v>
           </cell>
-          <cell r="HW4">
-            <v>0</v>
+          <cell r="HW4" t="str">
+            <v>ng</v>
           </cell>
           <cell r="HX4">
             <v>0</v>
@@ -9701,7 +9697,7 @@
             <v>P</v>
           </cell>
           <cell r="GI6" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="GJ6" t="str">
             <v>N</v>
@@ -9767,19 +9763,19 @@
             <v>P</v>
           </cell>
           <cell r="HE6" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="HF6" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="HG6" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="HH6" t="str">
             <v>P</v>
           </cell>
           <cell r="HI6" t="str">
-            <v>M</v>
+            <v>r</v>
           </cell>
           <cell r="HJ6" t="str">
             <v>N</v>
@@ -9806,25 +9802,25 @@
             <v>R</v>
           </cell>
           <cell r="HR6" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="HS6" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="HT6" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="HU6" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="HV6" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="HW6" t="str">
-            <v>P</v>
+            <v>p</v>
           </cell>
           <cell r="HX6" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="HY6" t="str">
             <v>P</v>
@@ -9842,7 +9838,7 @@
             <v>R</v>
           </cell>
           <cell r="ID6" t="str">
-            <v>P</v>
+            <v>r</v>
           </cell>
           <cell r="IE6" t="str">
             <v>M</v>
@@ -9935,19 +9931,19 @@
             <v>-</v>
           </cell>
           <cell r="JI6" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="JJ6" t="str">
-            <v>M</v>
+            <v>-</v>
           </cell>
           <cell r="JK6" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="JL6" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="JM6" t="str">
-            <v>R</v>
+            <v>-</v>
           </cell>
           <cell r="JN6" t="str">
             <v>-</v>
@@ -12084,19 +12080,19 @@
             <v>R</v>
           </cell>
           <cell r="GJ9" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="GK9" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="GL9" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="GM9" t="str">
             <v>P</v>
           </cell>
           <cell r="GN9" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="GO9" t="str">
             <v>N</v>
@@ -12111,7 +12107,7 @@
             <v>P</v>
           </cell>
           <cell r="GS9" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="GT9" t="str">
             <v>N</v>
@@ -12123,46 +12119,46 @@
             <v>R</v>
           </cell>
           <cell r="GW9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="GX9" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="GY9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="GZ9" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="HA9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="HB9" t="str">
             <v>-</v>
           </cell>
           <cell r="HC9" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="HD9" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="HE9" t="str">
             <v>p</v>
           </cell>
           <cell r="HF9" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="HG9" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="HH9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="HI9" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="HJ9" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="HK9" t="str">
             <v>P</v>
@@ -13330,8 +13326,8 @@
           <cell r="HB10" t="str">
             <v>p</v>
           </cell>
-          <cell r="HC10" t="str">
-            <v>p</v>
+          <cell r="HC10">
+            <v>0</v>
           </cell>
           <cell r="HD10">
             <v>0</v>
@@ -14452,10 +14448,10 @@
             <v>p</v>
           </cell>
           <cell r="GF12" t="str">
+            <v>m/R</v>
+          </cell>
+          <cell r="GG12" t="str">
             <v>p</v>
-          </cell>
-          <cell r="GG12" t="str">
-            <v>m</v>
           </cell>
           <cell r="GH12" t="str">
             <v>m</v>
@@ -14467,25 +14463,25 @@
             <v>p</v>
           </cell>
           <cell r="GK12" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="GL12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="GM12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="GN12" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="GO12" t="str">
-            <v>m</v>
+            <v>r</v>
           </cell>
           <cell r="GP12" t="str">
             <v>P</v>
           </cell>
           <cell r="GQ12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="GR12" t="str">
             <v>N</v>
@@ -14500,7 +14496,7 @@
             <v>P</v>
           </cell>
           <cell r="GV12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="GW12" t="str">
             <v>N</v>
@@ -14515,7 +14511,7 @@
             <v>P</v>
           </cell>
           <cell r="HA12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="HB12" t="str">
             <v>N</v>
@@ -14587,25 +14583,25 @@
             <v>R</v>
           </cell>
           <cell r="HY12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="HZ12" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="IA12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="IB12" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="IC12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="ID12" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="IE12" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="IF12" t="str">
             <v>-</v>
@@ -14629,7 +14625,7 @@
             <v>-</v>
           </cell>
           <cell r="IM12" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="IN12" t="str">
             <v>-</v>
@@ -15827,8 +15823,8 @@
           <cell r="IO13">
             <v>0</v>
           </cell>
-          <cell r="IP13">
-            <v>0</v>
+          <cell r="IP13" t="str">
+            <v>ng</v>
           </cell>
           <cell r="IQ13">
             <v>0</v>
@@ -16772,7 +16768,7 @@
             <v>R</v>
           </cell>
           <cell r="FL15" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="FM15" t="str">
             <v>P</v>
@@ -16817,7 +16813,7 @@
             <v>r</v>
           </cell>
           <cell r="GA15" t="str">
-            <v>p</v>
+            <v>r</v>
           </cell>
           <cell r="GB15" t="str">
             <v>P</v>
@@ -16838,7 +16834,7 @@
             <v>P</v>
           </cell>
           <cell r="GH15" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="GI15" t="str">
             <v>N</v>
@@ -16853,7 +16849,7 @@
             <v>P</v>
           </cell>
           <cell r="GM15" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="GN15" t="str">
             <v>N</v>
@@ -16868,7 +16864,7 @@
             <v>P</v>
           </cell>
           <cell r="GR15" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="GS15" t="str">
             <v>N</v>
@@ -16913,7 +16909,7 @@
             <v>P</v>
           </cell>
           <cell r="HG15" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="HH15" t="str">
             <v>N</v>
@@ -16925,25 +16921,25 @@
             <v>R</v>
           </cell>
           <cell r="HK15" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="HL15" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="HM15" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="HN15" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="HO15" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="HP15" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="HQ15" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="HR15" t="str">
             <v>-</v>
@@ -16961,52 +16957,52 @@
             <v>R</v>
           </cell>
           <cell r="HW15" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="HX15" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="HY15" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="HZ15" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="IA15" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="IB15" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="IC15" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="ID15" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="IE15" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="IF15" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="IG15" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="IH15" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="II15" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="IJ15" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="IK15" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="IL15" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="IM15" t="str">
             <v>P</v>
@@ -19209,7 +19205,7 @@
             <v>P</v>
           </cell>
           <cell r="GE18" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="GF18" t="str">
             <v>N</v>
@@ -19221,49 +19217,49 @@
             <v>R</v>
           </cell>
           <cell r="GI18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="GJ18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="GK18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="GL18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="GM18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="GN18" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="GO18" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="GP18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="GQ18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="GR18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="GS18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="GT18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="GU18" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="GV18" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="GW18" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="GX18" t="str">
             <v>N</v>
@@ -19278,7 +19274,7 @@
             <v>P</v>
           </cell>
           <cell r="HB18" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="HC18" t="str">
             <v>N</v>
@@ -19389,7 +19385,7 @@
             <v>R</v>
           </cell>
           <cell r="IM18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="IN18" t="str">
             <v>-</v>
@@ -19398,7 +19394,7 @@
             <v>-</v>
           </cell>
           <cell r="IP18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="IQ18" t="str">
             <v>-</v>
@@ -19422,46 +19418,46 @@
             <v>-</v>
           </cell>
           <cell r="IX18" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="IY18" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="IZ18" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="JA18" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="JB18" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="JC18" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="JD18" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="JE18" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="JF18" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="JG18" t="str">
             <v>R</v>
           </cell>
-          <cell r="IY18" t="str">
-            <v>-</v>
-          </cell>
-          <cell r="IZ18" t="str">
-            <v>-</v>
-          </cell>
-          <cell r="JA18" t="str">
-            <v>-</v>
-          </cell>
-          <cell r="JB18" t="str">
-            <v>-</v>
-          </cell>
-          <cell r="JC18" t="str">
-            <v>R</v>
-          </cell>
-          <cell r="JD18" t="str">
-            <v>-</v>
-          </cell>
-          <cell r="JE18" t="str">
-            <v>-</v>
-          </cell>
-          <cell r="JF18" t="str">
-            <v>-</v>
-          </cell>
-          <cell r="JG18" t="str">
-            <v>-</v>
-          </cell>
           <cell r="JH18" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="JI18" t="str">
-            <v>M</v>
+            <v>-</v>
           </cell>
           <cell r="JJ18" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="JK18" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="JL18" t="str">
             <v>R</v>
@@ -19527,31 +19523,31 @@
             <v>R</v>
           </cell>
           <cell r="KG18" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="KH18" t="str">
-            <v>M</v>
+            <v>-</v>
           </cell>
           <cell r="KI18" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="KJ18" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="KK18" t="str">
             <v>R</v>
           </cell>
           <cell r="KL18" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="KM18" t="str">
-            <v>M</v>
+            <v>-</v>
           </cell>
           <cell r="KN18" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="KO18" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="KP18" t="str">
             <v>R</v>
@@ -19569,7 +19565,7 @@
             <v>-</v>
           </cell>
           <cell r="KU18" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="KV18" t="str">
             <v>-</v>
@@ -19584,7 +19580,7 @@
             <v>-</v>
           </cell>
           <cell r="KZ18" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="LA18" t="str">
             <v>-</v>
@@ -19599,7 +19595,7 @@
             <v>-</v>
           </cell>
           <cell r="LE18" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="LF18" t="str">
             <v>-</v>
@@ -19611,11 +19607,11 @@
             <v>-</v>
           </cell>
           <cell r="LI18" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="LJ18" t="str">
             <v>R</v>
           </cell>
-          <cell r="LJ18" t="str">
-            <v>-</v>
-          </cell>
           <cell r="LK18" t="str">
             <v>-</v>
           </cell>
@@ -19626,7 +19622,7 @@
             <v>-</v>
           </cell>
           <cell r="LN18" t="str">
-            <v>R</v>
+            <v>-</v>
           </cell>
           <cell r="LO18" t="str">
             <v>-</v>
@@ -20599,62 +20595,62 @@
           <cell r="IS19">
             <v>0</v>
           </cell>
-          <cell r="IT19" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="IU19" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="IV19" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="IW19" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="IX19" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="IY19" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="IZ19" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="JA19" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="JB19" t="str">
-            <v>f</v>
+          <cell r="IT19">
+            <v>0</v>
+          </cell>
+          <cell r="IU19">
+            <v>0</v>
+          </cell>
+          <cell r="IV19">
+            <v>0</v>
+          </cell>
+          <cell r="IW19">
+            <v>0</v>
+          </cell>
+          <cell r="IX19">
+            <v>0</v>
+          </cell>
+          <cell r="IY19">
+            <v>0</v>
+          </cell>
+          <cell r="IZ19">
+            <v>0</v>
+          </cell>
+          <cell r="JA19">
+            <v>0</v>
+          </cell>
+          <cell r="JB19">
+            <v>0</v>
           </cell>
           <cell r="JC19" t="str">
             <v>f</v>
           </cell>
-          <cell r="JD19">
-            <v>0</v>
-          </cell>
-          <cell r="JE19">
-            <v>0</v>
-          </cell>
-          <cell r="JF19">
-            <v>0</v>
-          </cell>
-          <cell r="JG19">
-            <v>0</v>
-          </cell>
-          <cell r="JH19">
-            <v>0</v>
-          </cell>
-          <cell r="JI19">
-            <v>0</v>
-          </cell>
-          <cell r="JJ19">
-            <v>0</v>
-          </cell>
-          <cell r="JK19">
-            <v>0</v>
-          </cell>
-          <cell r="JL19">
-            <v>0</v>
+          <cell r="JD19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="JE19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="JF19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="JG19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="JH19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="JI19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="JJ19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="JK19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="JL19" t="str">
+            <v>f</v>
           </cell>
           <cell r="JM19">
             <v>0</v>
@@ -20716,77 +20712,77 @@
           <cell r="KF19">
             <v>0</v>
           </cell>
-          <cell r="KG19">
-            <v>0</v>
-          </cell>
-          <cell r="KH19">
-            <v>0</v>
-          </cell>
-          <cell r="KI19">
-            <v>0</v>
-          </cell>
-          <cell r="KJ19">
-            <v>0</v>
-          </cell>
-          <cell r="KK19">
-            <v>0</v>
-          </cell>
-          <cell r="KL19">
-            <v>0</v>
-          </cell>
-          <cell r="KM19">
-            <v>0</v>
-          </cell>
-          <cell r="KN19">
-            <v>0</v>
-          </cell>
-          <cell r="KO19">
-            <v>0</v>
-          </cell>
-          <cell r="KP19">
-            <v>0</v>
-          </cell>
-          <cell r="KQ19">
-            <v>0</v>
-          </cell>
-          <cell r="KR19">
-            <v>0</v>
-          </cell>
-          <cell r="KS19">
-            <v>0</v>
-          </cell>
-          <cell r="KT19">
-            <v>0</v>
-          </cell>
-          <cell r="KU19">
-            <v>0</v>
-          </cell>
-          <cell r="KV19">
-            <v>0</v>
-          </cell>
-          <cell r="KW19">
-            <v>0</v>
-          </cell>
-          <cell r="KX19">
-            <v>0</v>
-          </cell>
-          <cell r="KY19">
-            <v>0</v>
-          </cell>
-          <cell r="KZ19">
-            <v>0</v>
-          </cell>
-          <cell r="LA19">
-            <v>0</v>
-          </cell>
-          <cell r="LB19">
-            <v>0</v>
-          </cell>
-          <cell r="LC19">
-            <v>0</v>
-          </cell>
-          <cell r="LD19">
-            <v>0</v>
+          <cell r="KG19" t="str">
+            <v>k</v>
+          </cell>
+          <cell r="KH19" t="str">
+            <v>k</v>
+          </cell>
+          <cell r="KI19" t="str">
+            <v>k</v>
+          </cell>
+          <cell r="KJ19" t="str">
+            <v>k</v>
+          </cell>
+          <cell r="KK19" t="str">
+            <v>k</v>
+          </cell>
+          <cell r="KL19" t="str">
+            <v>k</v>
+          </cell>
+          <cell r="KM19" t="str">
+            <v>k</v>
+          </cell>
+          <cell r="KN19" t="str">
+            <v>k</v>
+          </cell>
+          <cell r="KO19" t="str">
+            <v>k</v>
+          </cell>
+          <cell r="KP19" t="str">
+            <v>k</v>
+          </cell>
+          <cell r="KQ19" t="str">
+            <v>k</v>
+          </cell>
+          <cell r="KR19" t="str">
+            <v>k</v>
+          </cell>
+          <cell r="KS19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="KT19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="KU19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="KV19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="KW19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="KX19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="KY19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="KZ19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="LA19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="LB19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="LC19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="LD19" t="str">
+            <v>f</v>
           </cell>
           <cell r="LE19" t="str">
             <v>f</v>
@@ -20809,14 +20805,14 @@
           <cell r="LK19" t="str">
             <v>f</v>
           </cell>
-          <cell r="LL19" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="LM19" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="LN19" t="str">
-            <v>f</v>
+          <cell r="LL19">
+            <v>0</v>
+          </cell>
+          <cell r="LM19">
+            <v>0</v>
+          </cell>
+          <cell r="LN19">
+            <v>0</v>
           </cell>
           <cell r="LO19">
             <v>0</v>
@@ -21592,7 +21588,7 @@
             <v>m</v>
           </cell>
           <cell r="GF21" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="GG21" t="str">
             <v>r</v>
@@ -21604,7 +21600,7 @@
             <v>P</v>
           </cell>
           <cell r="GJ21" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="GK21" t="str">
             <v>N</v>
@@ -21634,7 +21630,7 @@
             <v>P</v>
           </cell>
           <cell r="GT21" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="GU21" t="str">
             <v>N</v>
@@ -21649,7 +21645,7 @@
             <v>P</v>
           </cell>
           <cell r="GY21" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="GZ21" t="str">
             <v>N</v>
@@ -21712,13 +21708,13 @@
             <v>-</v>
           </cell>
           <cell r="HT21" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="HU21" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="HV21" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="HW21" t="str">
             <v>M</v>
@@ -21727,7 +21723,7 @@
             <v>r</v>
           </cell>
           <cell r="HY21" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="HZ21" t="str">
             <v>P</v>
@@ -21748,28 +21744,28 @@
             <v>P</v>
           </cell>
           <cell r="IF21" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="IG21" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="IH21" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="II21" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="IJ21" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="IK21" t="str">
-            <v>-</v>
+            <v>N</v>
           </cell>
           <cell r="IL21" t="str">
-            <v>-</v>
+            <v>S</v>
           </cell>
           <cell r="IM21" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="IN21" t="str">
             <v>-</v>
@@ -21790,61 +21786,61 @@
             <v>-</v>
           </cell>
           <cell r="IT21" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="IU21" t="str">
-            <v>M</v>
+            <v>-</v>
           </cell>
           <cell r="IV21" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="IW21" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="IX21" t="str">
             <v>R</v>
           </cell>
           <cell r="IY21" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="IZ21" t="str">
-            <v>M</v>
+            <v>-</v>
           </cell>
           <cell r="JA21" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="JB21" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="JC21" t="str">
             <v>R</v>
           </cell>
           <cell r="JD21" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="JE21" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="JF21" t="str">
-            <v>-</v>
+            <v>N</v>
           </cell>
           <cell r="JG21" t="str">
-            <v>-</v>
+            <v>S</v>
           </cell>
           <cell r="JH21" t="str">
             <v>R</v>
           </cell>
           <cell r="JI21" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="JJ21" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="JK21" t="str">
-            <v>-</v>
+            <v>N</v>
           </cell>
           <cell r="JL21" t="str">
-            <v>-</v>
+            <v>S</v>
           </cell>
           <cell r="JM21" t="str">
             <v>R</v>
@@ -22620,7 +22616,7 @@
             <v>0</v>
           </cell>
           <cell r="ED22" t="str">
-            <v>p</v>
+            <v>r</v>
           </cell>
           <cell r="EE22">
             <v>0</v>
@@ -22979,65 +22975,65 @@
           <cell r="IS22">
             <v>0</v>
           </cell>
-          <cell r="IT22">
-            <v>0</v>
-          </cell>
-          <cell r="IU22">
-            <v>0</v>
-          </cell>
-          <cell r="IV22">
-            <v>0</v>
-          </cell>
-          <cell r="IW22">
-            <v>0</v>
-          </cell>
-          <cell r="IX22">
-            <v>0</v>
-          </cell>
-          <cell r="IY22">
-            <v>0</v>
-          </cell>
-          <cell r="IZ22">
-            <v>0</v>
-          </cell>
-          <cell r="JA22">
-            <v>0</v>
-          </cell>
-          <cell r="JB22">
-            <v>0</v>
-          </cell>
-          <cell r="JC22">
-            <v>0</v>
-          </cell>
-          <cell r="JD22" t="str">
+          <cell r="IT22" t="str">
             <v>f</v>
           </cell>
-          <cell r="JE22" t="str">
+          <cell r="IU22" t="str">
             <v>f</v>
           </cell>
-          <cell r="JF22" t="str">
+          <cell r="IV22" t="str">
             <v>f</v>
           </cell>
-          <cell r="JG22" t="str">
+          <cell r="IW22" t="str">
             <v>f</v>
           </cell>
-          <cell r="JH22" t="str">
+          <cell r="IX22" t="str">
             <v>f</v>
           </cell>
-          <cell r="JI22" t="str">
+          <cell r="IY22" t="str">
             <v>f</v>
           </cell>
-          <cell r="JJ22" t="str">
+          <cell r="IZ22" t="str">
             <v>f</v>
           </cell>
-          <cell r="JK22" t="str">
+          <cell r="JA22" t="str">
             <v>f</v>
           </cell>
-          <cell r="JL22" t="str">
+          <cell r="JB22" t="str">
             <v>f</v>
           </cell>
-          <cell r="JM22" t="str">
+          <cell r="JC22" t="str">
             <v>f</v>
+          </cell>
+          <cell r="JD22">
+            <v>0</v>
+          </cell>
+          <cell r="JE22">
+            <v>0</v>
+          </cell>
+          <cell r="JF22">
+            <v>0</v>
+          </cell>
+          <cell r="JG22">
+            <v>0</v>
+          </cell>
+          <cell r="JH22">
+            <v>0</v>
+          </cell>
+          <cell r="JI22">
+            <v>0</v>
+          </cell>
+          <cell r="JJ22">
+            <v>0</v>
+          </cell>
+          <cell r="JK22">
+            <v>0</v>
+          </cell>
+          <cell r="JL22">
+            <v>0</v>
+          </cell>
+          <cell r="JM22">
+            <v>0</v>
           </cell>
           <cell r="JN22">
             <v>0</v>
@@ -23966,7 +23962,7 @@
             <v>m</v>
           </cell>
           <cell r="GD24" t="str">
-            <v>r</v>
+            <v>m/R</v>
           </cell>
           <cell r="GE24" t="str">
             <v>P</v>
@@ -23981,13 +23977,13 @@
             <v>S</v>
           </cell>
           <cell r="GI24" t="str">
-            <v>R</v>
+            <v>p</v>
           </cell>
           <cell r="GJ24" t="str">
-            <v>P</v>
+            <v>r</v>
           </cell>
           <cell r="GK24" t="str">
-            <v>M</v>
+            <v>r</v>
           </cell>
           <cell r="GL24" t="str">
             <v>N</v>
@@ -23999,28 +23995,28 @@
             <v>R</v>
           </cell>
           <cell r="GO24" t="str">
+            <v>r</v>
+          </cell>
+          <cell r="GP24" t="str">
+            <v>m/R</v>
+          </cell>
+          <cell r="GQ24" t="str">
             <v>p</v>
           </cell>
-          <cell r="GP24" t="str">
-            <v>-</v>
-          </cell>
-          <cell r="GQ24" t="str">
-            <v>-</v>
-          </cell>
           <cell r="GR24" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="GS24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="GT24" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="GU24" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="GV24" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="GW24" t="str">
             <v>P</v>
@@ -24128,28 +24124,28 @@
             <v>R</v>
           </cell>
           <cell r="IF24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="IG24" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="IH24" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="II24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="IJ24" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="IK24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="IL24" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="IM24" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="IN24" t="str">
             <v>P</v>
@@ -26262,7 +26258,7 @@
             <v>m</v>
           </cell>
           <cell r="FB27" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="FC27" t="str">
             <v>p</v>
@@ -26292,34 +26288,34 @@
             <v>R</v>
           </cell>
           <cell r="FL27" t="str">
-            <v>P</v>
+            <v>N</v>
           </cell>
           <cell r="FM27" t="str">
-            <v>M</v>
+            <v>S</v>
           </cell>
           <cell r="FN27" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="FO27" t="str">
             <v>-</v>
           </cell>
           <cell r="FP27" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="FQ27" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="FR27" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="FS27" t="str">
             <v>R</v>
           </cell>
-          <cell r="FQ27" t="str">
-            <v>-</v>
-          </cell>
-          <cell r="FR27" t="str">
-            <v>-</v>
-          </cell>
-          <cell r="FS27" t="str">
-            <v>-</v>
-          </cell>
           <cell r="FT27" t="str">
             <v>-</v>
           </cell>
           <cell r="FU27" t="str">
-            <v>R</v>
+            <v>-</v>
           </cell>
           <cell r="FV27" t="str">
             <v>M</v>
@@ -26355,7 +26351,7 @@
             <v>P</v>
           </cell>
           <cell r="GG27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="GH27" t="str">
             <v>N</v>
@@ -26370,7 +26366,7 @@
             <v>P</v>
           </cell>
           <cell r="GL27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="GM27" t="str">
             <v>N</v>
@@ -26403,25 +26399,25 @@
             <v>-</v>
           </cell>
           <cell r="GW27" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="GX27" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="GY27" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="GZ27" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="HA27" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="HB27" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="HC27" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="HD27" t="str">
             <v>N</v>
@@ -26436,34 +26432,34 @@
             <v>P</v>
           </cell>
           <cell r="HH27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="HI27" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="HJ27" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="HK27" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="HL27" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="HM27" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="HN27" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="HO27" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="HP27" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="HQ27" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="HR27" t="str">
             <v>P</v>
@@ -26481,7 +26477,7 @@
             <v>R</v>
           </cell>
           <cell r="HW27" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="HX27" t="str">
             <v>M</v>
@@ -26580,19 +26576,19 @@
             <v>-</v>
           </cell>
           <cell r="JD27" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="JE27" t="str">
-            <v>M</v>
+            <v>-</v>
           </cell>
           <cell r="JF27" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="JG27" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="JH27" t="str">
-            <v>R</v>
+            <v>-</v>
           </cell>
           <cell r="JI27" t="str">
             <v>-</v>
@@ -27487,8 +27483,8 @@
           <cell r="FM28">
             <v>0</v>
           </cell>
-          <cell r="FN28" t="str">
-            <v>f</v>
+          <cell r="FN28">
+            <v>0</v>
           </cell>
           <cell r="FO28" t="str">
             <v>f</v>
@@ -27670,8 +27666,8 @@
           <cell r="HV28">
             <v>0</v>
           </cell>
-          <cell r="HW28" t="str">
-            <v>ng</v>
+          <cell r="HW28">
+            <v>0</v>
           </cell>
           <cell r="HX28">
             <v>0</v>
@@ -28517,431 +28513,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28951,7 +28947,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -30806,11 +30802,11 @@
       </c>
       <c r="FI3" s="16" t="str">
         <f>[1]CARTELLINO!FL$3</f>
-        <v>N</v>
+        <v>m</v>
       </c>
       <c r="FJ3" s="16" t="str">
         <f>[1]CARTELLINO!FM$3</f>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="FK3" s="16" t="str">
         <f>[1]CARTELLINO!FN$3</f>
@@ -30946,7 +30942,7 @@
       </c>
       <c r="GR3" s="16" t="str">
         <f>[1]CARTELLINO!GU$3</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="GS3" s="16" t="str">
         <f>[1]CARTELLINO!GV$3</f>
@@ -30966,7 +30962,7 @@
       </c>
       <c r="GW3" s="16" t="str">
         <f>[1]CARTELLINO!GZ$3</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="GX3" s="16" t="str">
         <f>[1]CARTELLINO!HA$3</f>
@@ -30990,15 +30986,15 @@
       </c>
       <c r="HC3" s="16" t="str">
         <f>[1]CARTELLINO!HF$3</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="HD3" s="16" t="str">
         <f>[1]CARTELLINO!HG$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="HE3" s="16" t="str">
         <f>[1]CARTELLINO!HH$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="HF3" s="16" t="str">
         <f>[1]CARTELLINO!HI$3</f>
@@ -31022,39 +31018,39 @@
       </c>
       <c r="HK3" s="16" t="str">
         <f>[1]CARTELLINO!HN$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="HL3" s="16" t="str">
         <f>[1]CARTELLINO!HO$3</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="HM3" s="16" t="str">
         <f>[1]CARTELLINO!HP$3</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="HN3" s="16" t="str">
         <f>[1]CARTELLINO!HQ$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="HO3" s="16" t="str">
         <f>[1]CARTELLINO!HR$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="HP3" s="16" t="str">
         <f>[1]CARTELLINO!HS$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="HQ3" s="16" t="str">
         <f>[1]CARTELLINO!HT$3</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="HR3" s="16" t="str">
         <f>[1]CARTELLINO!HU$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="HS3" s="16" t="str">
         <f>[1]CARTELLINO!HV$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="HT3" s="16" t="str">
         <f>[1]CARTELLINO!HW$3</f>
@@ -31062,7 +31058,7 @@
       </c>
       <c r="HU3" s="16" t="str">
         <f>[1]CARTELLINO!HX$3</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="HV3" s="16" t="str">
         <f>[1]CARTELLINO!HY$3</f>
@@ -32650,9 +32646,9 @@
         <f>[1]CARTELLINO!HV$4</f>
         <v>0</v>
       </c>
-      <c r="HT4" s="43">
+      <c r="HT4" s="43" t="str">
         <f>[1]CARTELLINO!HW$4</f>
-        <v>0</v>
+        <v>ng</v>
       </c>
       <c r="HU4" s="43">
         <f>[1]CARTELLINO!HX$4</f>
@@ -34493,7 +34489,7 @@
       </c>
       <c r="GF6" s="22" t="str">
         <f>[1]CARTELLINO!GI$6</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="GG6" s="22" t="str">
         <f>[1]CARTELLINO!GJ$6</f>
@@ -34581,15 +34577,15 @@
       </c>
       <c r="HB6" s="22" t="str">
         <f>[1]CARTELLINO!HE$6</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="HC6" s="22" t="str">
         <f>[1]CARTELLINO!HF$6</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="HD6" s="22" t="str">
         <f>[1]CARTELLINO!HG$6</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="HE6" s="22" t="str">
         <f>[1]CARTELLINO!HH$6</f>
@@ -34597,7 +34593,7 @@
       </c>
       <c r="HF6" s="22" t="str">
         <f>[1]CARTELLINO!HI$6</f>
-        <v>M</v>
+        <v>r</v>
       </c>
       <c r="HG6" s="22" t="str">
         <f>[1]CARTELLINO!HJ$6</f>
@@ -34633,31 +34629,31 @@
       </c>
       <c r="HO6" s="22" t="str">
         <f>[1]CARTELLINO!HR$6</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="HP6" s="22" t="str">
         <f>[1]CARTELLINO!HS$6</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="HQ6" s="22" t="str">
         <f>[1]CARTELLINO!HT$6</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="HR6" s="22" t="str">
         <f>[1]CARTELLINO!HU$6</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="HS6" s="22" t="str">
         <f>[1]CARTELLINO!HV$6</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="HT6" s="22" t="str">
         <f>[1]CARTELLINO!HW$6</f>
-        <v>P</v>
+        <v>p</v>
       </c>
       <c r="HU6" s="22" t="str">
         <f>[1]CARTELLINO!HX$6</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="HV6" s="22" t="str">
         <f>[1]CARTELLINO!HY$6</f>
@@ -34681,7 +34677,7 @@
       </c>
       <c r="IA6" s="22" t="str">
         <f>[1]CARTELLINO!ID$6</f>
-        <v>P</v>
+        <v>r</v>
       </c>
       <c r="IB6" s="22" t="str">
         <f>[1]CARTELLINO!IE$6</f>
@@ -34805,23 +34801,23 @@
       </c>
       <c r="JF6" s="22" t="str">
         <f>[1]CARTELLINO!JI$6</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="JG6" s="22" t="str">
         <f>[1]CARTELLINO!JJ$6</f>
-        <v>M</v>
+        <v>-</v>
       </c>
       <c r="JH6" s="22" t="str">
         <f>[1]CARTELLINO!JK$6</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="JI6" s="22" t="str">
         <f>[1]CARTELLINO!JL$6</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="JJ6" s="22" t="str">
         <f>[1]CARTELLINO!JM$6</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="JK6" s="22" t="str">
         <f>[1]CARTELLINO!JN$6</f>
@@ -38093,15 +38089,15 @@
       </c>
       <c r="GG9" s="24" t="str">
         <f>[1]CARTELLINO!GJ$9</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="GH9" s="24" t="str">
         <f>[1]CARTELLINO!GK$9</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="GI9" s="24" t="str">
         <f>[1]CARTELLINO!GL$9</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="GJ9" s="24" t="str">
         <f>[1]CARTELLINO!GM$9</f>
@@ -38109,7 +38105,7 @@
       </c>
       <c r="GK9" s="24" t="str">
         <f>[1]CARTELLINO!GN$9</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="GL9" s="24" t="str">
         <f>[1]CARTELLINO!GO$9</f>
@@ -38129,7 +38125,7 @@
       </c>
       <c r="GP9" s="24" t="str">
         <f>[1]CARTELLINO!GS$9</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="GQ9" s="24" t="str">
         <f>[1]CARTELLINO!GT$9</f>
@@ -38145,23 +38141,23 @@
       </c>
       <c r="GT9" s="24" t="str">
         <f>[1]CARTELLINO!GW$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="GU9" s="24" t="str">
         <f>[1]CARTELLINO!GX$9</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="GV9" s="24" t="str">
         <f>[1]CARTELLINO!GY$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="GW9" s="24" t="str">
         <f>[1]CARTELLINO!GZ$9</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="GX9" s="24" t="str">
         <f>[1]CARTELLINO!HA$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="GY9" s="24" t="str">
         <f>[1]CARTELLINO!HB$9</f>
@@ -38169,11 +38165,11 @@
       </c>
       <c r="GZ9" s="24" t="str">
         <f>[1]CARTELLINO!HC$9</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="HA9" s="24" t="str">
         <f>[1]CARTELLINO!HD$9</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="HB9" s="24" t="str">
         <f>[1]CARTELLINO!HE$9</f>
@@ -38181,23 +38177,23 @@
       </c>
       <c r="HC9" s="24" t="str">
         <f>[1]CARTELLINO!HF$9</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="HD9" s="24" t="str">
         <f>[1]CARTELLINO!HG$9</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="HE9" s="24" t="str">
         <f>[1]CARTELLINO!HH$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="HF9" s="24" t="str">
         <f>[1]CARTELLINO!HI$9</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="HG9" s="24" t="str">
         <f>[1]CARTELLINO!HJ$9</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="HH9" s="24" t="str">
         <f>[1]CARTELLINO!HK$9</f>
@@ -39761,9 +39757,9 @@
         <f>[1]CARTELLINO!HB$10</f>
         <v>p</v>
       </c>
-      <c r="GZ10" s="46" t="str">
+      <c r="GZ10" s="46">
         <f>[1]CARTELLINO!HC$10</f>
-        <v>p</v>
+        <v>0</v>
       </c>
       <c r="HA10" s="46">
         <f>[1]CARTELLINO!HD$10</f>
@@ -41673,11 +41669,11 @@
       </c>
       <c r="GC12" s="25" t="str">
         <f>[1]CARTELLINO!GF$12</f>
-        <v>p</v>
+        <v>m/R</v>
       </c>
       <c r="GD12" s="25" t="str">
         <f>[1]CARTELLINO!GG$12</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="GE12" s="25" t="str">
         <f>[1]CARTELLINO!GH$12</f>
@@ -41693,23 +41689,23 @@
       </c>
       <c r="GH12" s="25" t="str">
         <f>[1]CARTELLINO!GK$12</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="GI12" s="25" t="str">
         <f>[1]CARTELLINO!GL$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="GJ12" s="25" t="str">
         <f>[1]CARTELLINO!GM$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="GK12" s="25" t="str">
         <f>[1]CARTELLINO!GN$12</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="GL12" s="25" t="str">
         <f>[1]CARTELLINO!GO$12</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="GM12" s="25" t="str">
         <f>[1]CARTELLINO!GP$12</f>
@@ -41717,7 +41713,7 @@
       </c>
       <c r="GN12" s="25" t="str">
         <f>[1]CARTELLINO!GQ$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="GO12" s="25" t="str">
         <f>[1]CARTELLINO!GR$12</f>
@@ -41737,7 +41733,7 @@
       </c>
       <c r="GS12" s="25" t="str">
         <f>[1]CARTELLINO!GV$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="GT12" s="25" t="str">
         <f>[1]CARTELLINO!GW$12</f>
@@ -41757,7 +41753,7 @@
       </c>
       <c r="GX12" s="25" t="str">
         <f>[1]CARTELLINO!HA$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="GY12" s="25" t="str">
         <f>[1]CARTELLINO!HB$12</f>
@@ -41853,31 +41849,31 @@
       </c>
       <c r="HV12" s="25" t="str">
         <f>[1]CARTELLINO!HY$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="HW12" s="25" t="str">
         <f>[1]CARTELLINO!HZ$12</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="HX12" s="25" t="str">
         <f>[1]CARTELLINO!IA$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="HY12" s="25" t="str">
         <f>[1]CARTELLINO!IB$12</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="HZ12" s="25" t="str">
         <f>[1]CARTELLINO!IC$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="IA12" s="25" t="str">
         <f>[1]CARTELLINO!ID$12</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="IB12" s="25" t="str">
         <f>[1]CARTELLINO!IE$12</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="IC12" s="25" t="str">
         <f>[1]CARTELLINO!IF$12</f>
@@ -41909,7 +41905,7 @@
       </c>
       <c r="IJ12" s="25" t="str">
         <f>[1]CARTELLINO!IM$12</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="IK12" s="25" t="str">
         <f>[1]CARTELLINO!IN$12</f>
@@ -43513,9 +43509,9 @@
         <f>[1]CARTELLINO!IO$13</f>
         <v>0</v>
       </c>
-      <c r="IM13" s="46">
+      <c r="IM13" s="46" t="str">
         <f>[1]CARTELLINO!IP$13</f>
-        <v>0</v>
+        <v>ng</v>
       </c>
       <c r="IN13" s="46">
         <f>[1]CARTELLINO!IQ$13</f>
@@ -45189,7 +45185,7 @@
       </c>
       <c r="FI15" s="26" t="str">
         <f>[1]CARTELLINO!FL$15</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="FJ15" s="26" t="str">
         <f>[1]CARTELLINO!FM$15</f>
@@ -45249,7 +45245,7 @@
       </c>
       <c r="FX15" s="26" t="str">
         <f>[1]CARTELLINO!GA$15</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="FY15" s="26" t="str">
         <f>[1]CARTELLINO!GB$15</f>
@@ -45277,7 +45273,7 @@
       </c>
       <c r="GE15" s="26" t="str">
         <f>[1]CARTELLINO!GH$15</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="GF15" s="26" t="str">
         <f>[1]CARTELLINO!GI$15</f>
@@ -45297,7 +45293,7 @@
       </c>
       <c r="GJ15" s="26" t="str">
         <f>[1]CARTELLINO!GM$15</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="GK15" s="26" t="str">
         <f>[1]CARTELLINO!GN$15</f>
@@ -45317,7 +45313,7 @@
       </c>
       <c r="GO15" s="26" t="str">
         <f>[1]CARTELLINO!GR$15</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="GP15" s="26" t="str">
         <f>[1]CARTELLINO!GS$15</f>
@@ -45377,7 +45373,7 @@
       </c>
       <c r="HD15" s="26" t="str">
         <f>[1]CARTELLINO!HG$15</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="HE15" s="26" t="str">
         <f>[1]CARTELLINO!HH$15</f>
@@ -45393,31 +45389,31 @@
       </c>
       <c r="HH15" s="26" t="str">
         <f>[1]CARTELLINO!HK$15</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="HI15" s="26" t="str">
         <f>[1]CARTELLINO!HL$15</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="HJ15" s="26" t="str">
         <f>[1]CARTELLINO!HM$15</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="HK15" s="26" t="str">
         <f>[1]CARTELLINO!HN$15</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="HL15" s="26" t="str">
         <f>[1]CARTELLINO!HO$15</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="HM15" s="26" t="str">
         <f>[1]CARTELLINO!HP$15</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="HN15" s="26" t="str">
         <f>[1]CARTELLINO!HQ$15</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="HO15" s="26" t="str">
         <f>[1]CARTELLINO!HR$15</f>
@@ -45441,67 +45437,67 @@
       </c>
       <c r="HT15" s="26" t="str">
         <f>[1]CARTELLINO!HW$15</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="HU15" s="26" t="str">
         <f>[1]CARTELLINO!HX$15</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="HV15" s="26" t="str">
         <f>[1]CARTELLINO!HY$15</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="HW15" s="26" t="str">
         <f>[1]CARTELLINO!HZ$15</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="HX15" s="26" t="str">
         <f>[1]CARTELLINO!IA$15</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="HY15" s="26" t="str">
         <f>[1]CARTELLINO!IB$15</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="HZ15" s="26" t="str">
         <f>[1]CARTELLINO!IC$15</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="IA15" s="26" t="str">
         <f>[1]CARTELLINO!ID$15</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="IB15" s="26" t="str">
         <f>[1]CARTELLINO!IE$15</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="IC15" s="26" t="str">
         <f>[1]CARTELLINO!IF$15</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="ID15" s="26" t="str">
         <f>[1]CARTELLINO!IG$15</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="IE15" s="26" t="str">
         <f>[1]CARTELLINO!IH$15</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="IF15" s="26" t="str">
         <f>[1]CARTELLINO!II$15</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="IG15" s="26" t="str">
         <f>[1]CARTELLINO!IJ$15</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="IH15" s="26" t="str">
         <f>[1]CARTELLINO!IK$15</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="II15" s="26" t="str">
         <f>[1]CARTELLINO!IL$15</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="IJ15" s="26" t="str">
         <f>[1]CARTELLINO!IM$15</f>
@@ -48861,7 +48857,7 @@
       </c>
       <c r="GB18" s="27" t="str">
         <f>[1]CARTELLINO!GE$18</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="GC18" s="27" t="str">
         <f>[1]CARTELLINO!GF$18</f>
@@ -48877,63 +48873,63 @@
       </c>
       <c r="GF18" s="27" t="str">
         <f>[1]CARTELLINO!GI$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="GG18" s="27" t="str">
         <f>[1]CARTELLINO!GJ$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="GH18" s="27" t="str">
         <f>[1]CARTELLINO!GK$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="GI18" s="27" t="str">
         <f>[1]CARTELLINO!GL$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="GJ18" s="27" t="str">
         <f>[1]CARTELLINO!GM$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="GK18" s="27" t="str">
         <f>[1]CARTELLINO!GN$18</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="GL18" s="27" t="str">
         <f>[1]CARTELLINO!GO$18</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="GM18" s="27" t="str">
         <f>[1]CARTELLINO!GP$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="GN18" s="27" t="str">
         <f>[1]CARTELLINO!GQ$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="GO18" s="27" t="str">
         <f>[1]CARTELLINO!GR$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="GP18" s="27" t="str">
         <f>[1]CARTELLINO!GS$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="GQ18" s="27" t="str">
         <f>[1]CARTELLINO!GT$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="GR18" s="27" t="str">
         <f>[1]CARTELLINO!GU$18</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="GS18" s="27" t="str">
         <f>[1]CARTELLINO!GV$18</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="GT18" s="27" t="str">
         <f>[1]CARTELLINO!GW$18</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="GU18" s="27" t="str">
         <f>[1]CARTELLINO!GX$18</f>
@@ -48953,7 +48949,7 @@
       </c>
       <c r="GY18" s="27" t="str">
         <f>[1]CARTELLINO!HB$18</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="GZ18" s="27" t="str">
         <f>[1]CARTELLINO!HC$18</f>
@@ -49101,7 +49097,7 @@
       </c>
       <c r="IJ18" s="27" t="str">
         <f>[1]CARTELLINO!IM$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="IK18" s="27" t="str">
         <f>[1]CARTELLINO!IN$18</f>
@@ -49113,7 +49109,7 @@
       </c>
       <c r="IM18" s="27" t="str">
         <f>[1]CARTELLINO!IP$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="IN18" s="27" t="str">
         <f>[1]CARTELLINO!IQ$18</f>
@@ -49145,7 +49141,7 @@
       </c>
       <c r="IU18" s="27" t="str">
         <f>[1]CARTELLINO!IX$18</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="IV18" s="27" t="str">
         <f>[1]CARTELLINO!IY$18</f>
@@ -49165,7 +49161,7 @@
       </c>
       <c r="IZ18" s="27" t="str">
         <f>[1]CARTELLINO!JC$18</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="JA18" s="27" t="str">
         <f>[1]CARTELLINO!JD$18</f>
@@ -49181,23 +49177,23 @@
       </c>
       <c r="JD18" s="27" t="str">
         <f>[1]CARTELLINO!JG$18</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="JE18" s="27" t="str">
         <f>[1]CARTELLINO!JH$18</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="JF18" s="27" t="str">
         <f>[1]CARTELLINO!JI$18</f>
-        <v>M</v>
+        <v>-</v>
       </c>
       <c r="JG18" s="27" t="str">
         <f>[1]CARTELLINO!JJ$18</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="JH18" s="27" t="str">
         <f>[1]CARTELLINO!JK$18</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="JI18" s="27" t="str">
         <f>[1]CARTELLINO!JL$18</f>
@@ -49285,19 +49281,19 @@
       </c>
       <c r="KD18" s="27" t="str">
         <f>[1]CARTELLINO!KG$18</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="KE18" s="27" t="str">
         <f>[1]CARTELLINO!KH$18</f>
-        <v>M</v>
+        <v>-</v>
       </c>
       <c r="KF18" s="27" t="str">
         <f>[1]CARTELLINO!KI$18</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="KG18" s="27" t="str">
         <f>[1]CARTELLINO!KJ$18</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="KH18" s="27" t="str">
         <f>[1]CARTELLINO!KK$18</f>
@@ -49305,19 +49301,19 @@
       </c>
       <c r="KI18" s="27" t="str">
         <f>[1]CARTELLINO!KL$18</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="KJ18" s="27" t="str">
         <f>[1]CARTELLINO!KM$18</f>
-        <v>M</v>
+        <v>-</v>
       </c>
       <c r="KK18" s="27" t="str">
         <f>[1]CARTELLINO!KN$18</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="KL18" s="27" t="str">
         <f>[1]CARTELLINO!KO$18</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="KM18" s="27" t="str">
         <f>[1]CARTELLINO!KP$18</f>
@@ -49341,7 +49337,7 @@
       </c>
       <c r="KR18" s="27" t="str">
         <f>[1]CARTELLINO!KU$18</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="KS18" s="27" t="str">
         <f>[1]CARTELLINO!KV$18</f>
@@ -49361,7 +49357,7 @@
       </c>
       <c r="KW18" s="27" t="str">
         <f>[1]CARTELLINO!KZ$18</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="KX18" s="27" t="str">
         <f>[1]CARTELLINO!LA$18</f>
@@ -49381,7 +49377,7 @@
       </c>
       <c r="LB18" s="27" t="str">
         <f>[1]CARTELLINO!LE$18</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="LC18" s="27" t="str">
         <f>[1]CARTELLINO!LF$18</f>
@@ -49397,11 +49393,11 @@
       </c>
       <c r="LF18" s="27" t="str">
         <f>[1]CARTELLINO!LI$18</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="LG18" s="27" t="str">
         <f>[1]CARTELLINO!LJ$18</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="LH18" s="27" t="str">
         <f>[1]CARTELLINO!LK$18</f>
@@ -49417,7 +49413,7 @@
       </c>
       <c r="LK18" s="27" t="str">
         <f>[1]CARTELLINO!LN$18</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="LL18" s="27" t="str">
         <f>[1]CARTELLINO!LO$18</f>
@@ -50721,81 +50717,81 @@
         <f>[1]CARTELLINO!IS$19</f>
         <v>0</v>
       </c>
-      <c r="IQ19" s="46" t="str">
+      <c r="IQ19" s="46">
         <f>[1]CARTELLINO!IT$19</f>
-        <v>f</v>
-      </c>
-      <c r="IR19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="IR19" s="46">
         <f>[1]CARTELLINO!IU$19</f>
-        <v>f</v>
-      </c>
-      <c r="IS19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="IS19" s="46">
         <f>[1]CARTELLINO!IV$19</f>
-        <v>f</v>
-      </c>
-      <c r="IT19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="IT19" s="46">
         <f>[1]CARTELLINO!IW$19</f>
-        <v>f</v>
-      </c>
-      <c r="IU19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="IU19" s="46">
         <f>[1]CARTELLINO!IX$19</f>
-        <v>f</v>
-      </c>
-      <c r="IV19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="IV19" s="46">
         <f>[1]CARTELLINO!IY$19</f>
-        <v>f</v>
-      </c>
-      <c r="IW19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="IW19" s="46">
         <f>[1]CARTELLINO!IZ$19</f>
-        <v>f</v>
-      </c>
-      <c r="IX19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="IX19" s="46">
         <f>[1]CARTELLINO!JA$19</f>
-        <v>f</v>
-      </c>
-      <c r="IY19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="IY19" s="46">
         <f>[1]CARTELLINO!JB$19</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="IZ19" s="46" t="str">
         <f>[1]CARTELLINO!JC$19</f>
         <v>f</v>
       </c>
-      <c r="JA19" s="46">
+      <c r="JA19" s="46" t="str">
         <f>[1]CARTELLINO!JD$19</f>
-        <v>0</v>
-      </c>
-      <c r="JB19" s="46">
+        <v>f</v>
+      </c>
+      <c r="JB19" s="46" t="str">
         <f>[1]CARTELLINO!JE$19</f>
-        <v>0</v>
-      </c>
-      <c r="JC19" s="46">
+        <v>f</v>
+      </c>
+      <c r="JC19" s="46" t="str">
         <f>[1]CARTELLINO!JF$19</f>
-        <v>0</v>
-      </c>
-      <c r="JD19" s="46">
+        <v>f</v>
+      </c>
+      <c r="JD19" s="46" t="str">
         <f>[1]CARTELLINO!JG$19</f>
-        <v>0</v>
-      </c>
-      <c r="JE19" s="46">
+        <v>f</v>
+      </c>
+      <c r="JE19" s="46" t="str">
         <f>[1]CARTELLINO!JH$19</f>
-        <v>0</v>
-      </c>
-      <c r="JF19" s="46">
+        <v>f</v>
+      </c>
+      <c r="JF19" s="46" t="str">
         <f>[1]CARTELLINO!JI$19</f>
-        <v>0</v>
-      </c>
-      <c r="JG19" s="46">
+        <v>f</v>
+      </c>
+      <c r="JG19" s="46" t="str">
         <f>[1]CARTELLINO!JJ$19</f>
-        <v>0</v>
-      </c>
-      <c r="JH19" s="46">
+        <v>f</v>
+      </c>
+      <c r="JH19" s="46" t="str">
         <f>[1]CARTELLINO!JK$19</f>
-        <v>0</v>
-      </c>
-      <c r="JI19" s="46">
+        <v>f</v>
+      </c>
+      <c r="JI19" s="46" t="str">
         <f>[1]CARTELLINO!JL$19</f>
-        <v>0</v>
+        <v>f</v>
       </c>
       <c r="JJ19" s="46">
         <f>[1]CARTELLINO!JM$19</f>
@@ -50877,101 +50873,101 @@
         <f>[1]CARTELLINO!KF$19</f>
         <v>0</v>
       </c>
-      <c r="KD19" s="46">
+      <c r="KD19" s="46" t="str">
         <f>[1]CARTELLINO!KG$19</f>
-        <v>0</v>
-      </c>
-      <c r="KE19" s="46">
+        <v>k</v>
+      </c>
+      <c r="KE19" s="46" t="str">
         <f>[1]CARTELLINO!KH$19</f>
-        <v>0</v>
-      </c>
-      <c r="KF19" s="46">
+        <v>k</v>
+      </c>
+      <c r="KF19" s="46" t="str">
         <f>[1]CARTELLINO!KI$19</f>
-        <v>0</v>
-      </c>
-      <c r="KG19" s="46">
+        <v>k</v>
+      </c>
+      <c r="KG19" s="46" t="str">
         <f>[1]CARTELLINO!KJ$19</f>
-        <v>0</v>
-      </c>
-      <c r="KH19" s="46">
+        <v>k</v>
+      </c>
+      <c r="KH19" s="46" t="str">
         <f>[1]CARTELLINO!KK$19</f>
-        <v>0</v>
-      </c>
-      <c r="KI19" s="46">
+        <v>k</v>
+      </c>
+      <c r="KI19" s="46" t="str">
         <f>[1]CARTELLINO!KL$19</f>
-        <v>0</v>
-      </c>
-      <c r="KJ19" s="46">
+        <v>k</v>
+      </c>
+      <c r="KJ19" s="46" t="str">
         <f>[1]CARTELLINO!KM$19</f>
-        <v>0</v>
-      </c>
-      <c r="KK19" s="46">
+        <v>k</v>
+      </c>
+      <c r="KK19" s="46" t="str">
         <f>[1]CARTELLINO!KN$19</f>
-        <v>0</v>
-      </c>
-      <c r="KL19" s="46">
+        <v>k</v>
+      </c>
+      <c r="KL19" s="46" t="str">
         <f>[1]CARTELLINO!KO$19</f>
-        <v>0</v>
-      </c>
-      <c r="KM19" s="46">
+        <v>k</v>
+      </c>
+      <c r="KM19" s="46" t="str">
         <f>[1]CARTELLINO!KP$19</f>
-        <v>0</v>
-      </c>
-      <c r="KN19" s="46">
+        <v>k</v>
+      </c>
+      <c r="KN19" s="46" t="str">
         <f>[1]CARTELLINO!KQ$19</f>
-        <v>0</v>
-      </c>
-      <c r="KO19" s="46">
+        <v>k</v>
+      </c>
+      <c r="KO19" s="46" t="str">
         <f>[1]CARTELLINO!KR$19</f>
-        <v>0</v>
-      </c>
-      <c r="KP19" s="46">
+        <v>k</v>
+      </c>
+      <c r="KP19" s="46" t="str">
         <f>[1]CARTELLINO!KS$19</f>
-        <v>0</v>
-      </c>
-      <c r="KQ19" s="46">
+        <v>f</v>
+      </c>
+      <c r="KQ19" s="46" t="str">
         <f>[1]CARTELLINO!KT$19</f>
-        <v>0</v>
-      </c>
-      <c r="KR19" s="46">
+        <v>f</v>
+      </c>
+      <c r="KR19" s="46" t="str">
         <f>[1]CARTELLINO!KU$19</f>
-        <v>0</v>
-      </c>
-      <c r="KS19" s="46">
+        <v>f</v>
+      </c>
+      <c r="KS19" s="46" t="str">
         <f>[1]CARTELLINO!KV$19</f>
-        <v>0</v>
-      </c>
-      <c r="KT19" s="46">
+        <v>f</v>
+      </c>
+      <c r="KT19" s="46" t="str">
         <f>[1]CARTELLINO!KW$19</f>
-        <v>0</v>
-      </c>
-      <c r="KU19" s="46">
+        <v>f</v>
+      </c>
+      <c r="KU19" s="46" t="str">
         <f>[1]CARTELLINO!KX$19</f>
-        <v>0</v>
-      </c>
-      <c r="KV19" s="46">
+        <v>f</v>
+      </c>
+      <c r="KV19" s="46" t="str">
         <f>[1]CARTELLINO!KY$19</f>
-        <v>0</v>
-      </c>
-      <c r="KW19" s="46">
+        <v>f</v>
+      </c>
+      <c r="KW19" s="46" t="str">
         <f>[1]CARTELLINO!KZ$19</f>
-        <v>0</v>
-      </c>
-      <c r="KX19" s="46">
+        <v>f</v>
+      </c>
+      <c r="KX19" s="46" t="str">
         <f>[1]CARTELLINO!LA$19</f>
-        <v>0</v>
-      </c>
-      <c r="KY19" s="46">
+        <v>f</v>
+      </c>
+      <c r="KY19" s="46" t="str">
         <f>[1]CARTELLINO!LB$19</f>
-        <v>0</v>
-      </c>
-      <c r="KZ19" s="46">
+        <v>f</v>
+      </c>
+      <c r="KZ19" s="46" t="str">
         <f>[1]CARTELLINO!LC$19</f>
-        <v>0</v>
-      </c>
-      <c r="LA19" s="46">
+        <v>f</v>
+      </c>
+      <c r="LA19" s="46" t="str">
         <f>[1]CARTELLINO!LD$19</f>
-        <v>0</v>
+        <v>f</v>
       </c>
       <c r="LB19" s="46" t="str">
         <f>[1]CARTELLINO!LE$19</f>
@@ -51001,17 +50997,17 @@
         <f>[1]CARTELLINO!LK$19</f>
         <v>f</v>
       </c>
-      <c r="LI19" s="46" t="str">
+      <c r="LI19" s="46">
         <f>[1]CARTELLINO!LL$19</f>
-        <v>f</v>
-      </c>
-      <c r="LJ19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="LJ19" s="46">
         <f>[1]CARTELLINO!LM$19</f>
-        <v>f</v>
-      </c>
-      <c r="LK19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="LK19" s="46">
         <f>[1]CARTELLINO!LN$19</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="LL19" s="46">
         <f>[1]CARTELLINO!LO$19</f>
@@ -52461,7 +52457,7 @@
       </c>
       <c r="GC21" s="28" t="str">
         <f>[1]CARTELLINO!GF$21</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="GD21" s="28" t="str">
         <f>[1]CARTELLINO!GG$21</f>
@@ -52477,7 +52473,7 @@
       </c>
       <c r="GG21" s="28" t="str">
         <f>[1]CARTELLINO!GJ$21</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="GH21" s="28" t="str">
         <f>[1]CARTELLINO!GK$21</f>
@@ -52517,7 +52513,7 @@
       </c>
       <c r="GQ21" s="28" t="str">
         <f>[1]CARTELLINO!GT$21</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="GR21" s="28" t="str">
         <f>[1]CARTELLINO!GU$21</f>
@@ -52537,7 +52533,7 @@
       </c>
       <c r="GV21" s="28" t="str">
         <f>[1]CARTELLINO!GY$21</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="GW21" s="28" t="str">
         <f>[1]CARTELLINO!GZ$21</f>
@@ -52621,15 +52617,15 @@
       </c>
       <c r="HQ21" s="28" t="str">
         <f>[1]CARTELLINO!HT$21</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="HR21" s="28" t="str">
         <f>[1]CARTELLINO!HU$21</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="HS21" s="28" t="str">
         <f>[1]CARTELLINO!HV$21</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="HT21" s="28" t="str">
         <f>[1]CARTELLINO!HW$21</f>
@@ -52641,7 +52637,7 @@
       </c>
       <c r="HV21" s="28" t="str">
         <f>[1]CARTELLINO!HY$21</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="HW21" s="28" t="str">
         <f>[1]CARTELLINO!HZ$21</f>
@@ -52669,35 +52665,35 @@
       </c>
       <c r="IC21" s="28" t="str">
         <f>[1]CARTELLINO!IF$21</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="ID21" s="28" t="str">
         <f>[1]CARTELLINO!IG$21</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="IE21" s="28" t="str">
         <f>[1]CARTELLINO!IH$21</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="IF21" s="28" t="str">
         <f>[1]CARTELLINO!II$21</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="IG21" s="28" t="str">
         <f>[1]CARTELLINO!IJ$21</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="IH21" s="28" t="str">
         <f>[1]CARTELLINO!IK$21</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="II21" s="28" t="str">
         <f>[1]CARTELLINO!IL$21</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="IJ21" s="28" t="str">
         <f>[1]CARTELLINO!IM$21</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="IK21" s="28" t="str">
         <f>[1]CARTELLINO!IN$21</f>
@@ -52725,19 +52721,19 @@
       </c>
       <c r="IQ21" s="28" t="str">
         <f>[1]CARTELLINO!IT$21</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="IR21" s="28" t="str">
         <f>[1]CARTELLINO!IU$21</f>
-        <v>M</v>
+        <v>-</v>
       </c>
       <c r="IS21" s="28" t="str">
         <f>[1]CARTELLINO!IV$21</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="IT21" s="28" t="str">
         <f>[1]CARTELLINO!IW$21</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="IU21" s="28" t="str">
         <f>[1]CARTELLINO!IX$21</f>
@@ -52745,19 +52741,19 @@
       </c>
       <c r="IV21" s="28" t="str">
         <f>[1]CARTELLINO!IY$21</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="IW21" s="28" t="str">
         <f>[1]CARTELLINO!IZ$21</f>
-        <v>M</v>
+        <v>-</v>
       </c>
       <c r="IX21" s="28" t="str">
         <f>[1]CARTELLINO!JA$21</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="IY21" s="28" t="str">
         <f>[1]CARTELLINO!JB$21</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="IZ21" s="28" t="str">
         <f>[1]CARTELLINO!JC$21</f>
@@ -52765,19 +52761,19 @@
       </c>
       <c r="JA21" s="28" t="str">
         <f>[1]CARTELLINO!JD$21</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="JB21" s="28" t="str">
         <f>[1]CARTELLINO!JE$21</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="JC21" s="28" t="str">
         <f>[1]CARTELLINO!JF$21</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="JD21" s="28" t="str">
         <f>[1]CARTELLINO!JG$21</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="JE21" s="28" t="str">
         <f>[1]CARTELLINO!JH$21</f>
@@ -52785,19 +52781,19 @@
       </c>
       <c r="JF21" s="28" t="str">
         <f>[1]CARTELLINO!JI$21</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="JG21" s="28" t="str">
         <f>[1]CARTELLINO!JJ$21</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="JH21" s="28" t="str">
         <f>[1]CARTELLINO!JK$21</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="JI21" s="28" t="str">
         <f>[1]CARTELLINO!JL$21</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="JJ21" s="28" t="str">
         <f>[1]CARTELLINO!JM$21</f>
@@ -53839,7 +53835,7 @@
       </c>
       <c r="EA22" s="46" t="str">
         <f>[1]CARTELLINO!ED$22</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="EB22" s="46">
         <f>[1]CARTELLINO!EE$22</f>
@@ -54317,85 +54313,85 @@
         <f>[1]CARTELLINO!IS$22</f>
         <v>0</v>
       </c>
-      <c r="IQ22" s="46">
+      <c r="IQ22" s="46" t="str">
         <f>[1]CARTELLINO!IT$22</f>
-        <v>0</v>
-      </c>
-      <c r="IR22" s="46">
+        <v>f</v>
+      </c>
+      <c r="IR22" s="46" t="str">
         <f>[1]CARTELLINO!IU$22</f>
-        <v>0</v>
-      </c>
-      <c r="IS22" s="46">
+        <v>f</v>
+      </c>
+      <c r="IS22" s="46" t="str">
         <f>[1]CARTELLINO!IV$22</f>
-        <v>0</v>
-      </c>
-      <c r="IT22" s="46">
+        <v>f</v>
+      </c>
+      <c r="IT22" s="46" t="str">
         <f>[1]CARTELLINO!IW$22</f>
-        <v>0</v>
-      </c>
-      <c r="IU22" s="46">
+        <v>f</v>
+      </c>
+      <c r="IU22" s="46" t="str">
         <f>[1]CARTELLINO!IX$22</f>
-        <v>0</v>
-      </c>
-      <c r="IV22" s="46">
+        <v>f</v>
+      </c>
+      <c r="IV22" s="46" t="str">
         <f>[1]CARTELLINO!IY$22</f>
-        <v>0</v>
-      </c>
-      <c r="IW22" s="46">
+        <v>f</v>
+      </c>
+      <c r="IW22" s="46" t="str">
         <f>[1]CARTELLINO!IZ$22</f>
-        <v>0</v>
-      </c>
-      <c r="IX22" s="46">
+        <v>f</v>
+      </c>
+      <c r="IX22" s="46" t="str">
         <f>[1]CARTELLINO!JA$22</f>
-        <v>0</v>
-      </c>
-      <c r="IY22" s="46">
+        <v>f</v>
+      </c>
+      <c r="IY22" s="46" t="str">
         <f>[1]CARTELLINO!JB$22</f>
-        <v>0</v>
-      </c>
-      <c r="IZ22" s="46">
+        <v>f</v>
+      </c>
+      <c r="IZ22" s="46" t="str">
         <f>[1]CARTELLINO!JC$22</f>
-        <v>0</v>
-      </c>
-      <c r="JA22" s="46" t="str">
+        <v>f</v>
+      </c>
+      <c r="JA22" s="46">
         <f>[1]CARTELLINO!JD$22</f>
-        <v>f</v>
-      </c>
-      <c r="JB22" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="JB22" s="46">
         <f>[1]CARTELLINO!JE$22</f>
-        <v>f</v>
-      </c>
-      <c r="JC22" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="JC22" s="46">
         <f>[1]CARTELLINO!JF$22</f>
-        <v>f</v>
-      </c>
-      <c r="JD22" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="JD22" s="46">
         <f>[1]CARTELLINO!JG$22</f>
-        <v>f</v>
-      </c>
-      <c r="JE22" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="JE22" s="46">
         <f>[1]CARTELLINO!JH$22</f>
-        <v>f</v>
-      </c>
-      <c r="JF22" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="JF22" s="46">
         <f>[1]CARTELLINO!JI$22</f>
-        <v>f</v>
-      </c>
-      <c r="JG22" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="JG22" s="46">
         <f>[1]CARTELLINO!JJ$22</f>
-        <v>f</v>
-      </c>
-      <c r="JH22" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="JH22" s="46">
         <f>[1]CARTELLINO!JK$22</f>
-        <v>f</v>
-      </c>
-      <c r="JI22" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="JI22" s="46">
         <f>[1]CARTELLINO!JL$22</f>
-        <v>f</v>
-      </c>
-      <c r="JJ22" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="JJ22" s="46">
         <f>[1]CARTELLINO!JM$22</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="JK22" s="46">
         <f>[1]CARTELLINO!JN$22</f>
@@ -56049,7 +56045,7 @@
       </c>
       <c r="GA24" s="29" t="str">
         <f>[1]CARTELLINO!GD$24</f>
-        <v>r</v>
+        <v>m/R</v>
       </c>
       <c r="GB24" s="29" t="str">
         <f>[1]CARTELLINO!GE$24</f>
@@ -56069,15 +56065,15 @@
       </c>
       <c r="GF24" s="29" t="str">
         <f>[1]CARTELLINO!GI$24</f>
-        <v>R</v>
+        <v>p</v>
       </c>
       <c r="GG24" s="29" t="str">
         <f>[1]CARTELLINO!GJ$24</f>
-        <v>P</v>
+        <v>r</v>
       </c>
       <c r="GH24" s="29" t="str">
         <f>[1]CARTELLINO!GK$24</f>
-        <v>M</v>
+        <v>r</v>
       </c>
       <c r="GI24" s="29" t="str">
         <f>[1]CARTELLINO!GL$24</f>
@@ -56093,35 +56089,35 @@
       </c>
       <c r="GL24" s="29" t="str">
         <f>[1]CARTELLINO!GO$24</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="GM24" s="29" t="str">
         <f>[1]CARTELLINO!GP$24</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="GN24" s="29" t="str">
         <f>[1]CARTELLINO!GQ$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="GO24" s="29" t="str">
         <f>[1]CARTELLINO!GR$24</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="GP24" s="29" t="str">
         <f>[1]CARTELLINO!GS$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="GQ24" s="29" t="str">
         <f>[1]CARTELLINO!GT$24</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="GR24" s="29" t="str">
         <f>[1]CARTELLINO!GU$24</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="GS24" s="29" t="str">
         <f>[1]CARTELLINO!GV$24</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="GT24" s="29" t="str">
         <f>[1]CARTELLINO!GW$24</f>
@@ -56265,35 +56261,35 @@
       </c>
       <c r="IC24" s="29" t="str">
         <f>[1]CARTELLINO!IF$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="ID24" s="29" t="str">
         <f>[1]CARTELLINO!IG$24</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="IE24" s="29" t="str">
         <f>[1]CARTELLINO!IH$24</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="IF24" s="29" t="str">
         <f>[1]CARTELLINO!II$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="IG24" s="29" t="str">
         <f>[1]CARTELLINO!IJ$24</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="IH24" s="29" t="str">
         <f>[1]CARTELLINO!IK$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="II24" s="29" t="str">
         <f>[1]CARTELLINO!IL$24</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="IJ24" s="29" t="str">
         <f>[1]CARTELLINO!IM$24</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="IK24" s="29" t="str">
         <f>[1]CARTELLINO!IN$24</f>
@@ -59533,7 +59529,7 @@
       </c>
       <c r="EY27" s="30" t="str">
         <f>[1]CARTELLINO!FB$27</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="EZ27" s="30" t="str">
         <f>[1]CARTELLINO!FC$27</f>
@@ -59573,15 +59569,15 @@
       </c>
       <c r="FI27" s="30" t="str">
         <f>[1]CARTELLINO!FL$27</f>
-        <v>P</v>
+        <v>N</v>
       </c>
       <c r="FJ27" s="30" t="str">
         <f>[1]CARTELLINO!FM$27</f>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="FK27" s="30" t="str">
         <f>[1]CARTELLINO!FN$27</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="FL27" s="30" t="str">
         <f>[1]CARTELLINO!FO$27</f>
@@ -59589,7 +59585,7 @@
       </c>
       <c r="FM27" s="30" t="str">
         <f>[1]CARTELLINO!FP$27</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="FN27" s="30" t="str">
         <f>[1]CARTELLINO!FQ$27</f>
@@ -59601,7 +59597,7 @@
       </c>
       <c r="FP27" s="30" t="str">
         <f>[1]CARTELLINO!FS$27</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="FQ27" s="30" t="str">
         <f>[1]CARTELLINO!FT$27</f>
@@ -59609,7 +59605,7 @@
       </c>
       <c r="FR27" s="30" t="str">
         <f>[1]CARTELLINO!FU$27</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="FS27" s="30" t="str">
         <f>[1]CARTELLINO!FV$27</f>
@@ -59657,7 +59653,7 @@
       </c>
       <c r="GD27" s="30" t="str">
         <f>[1]CARTELLINO!GG$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="GE27" s="30" t="str">
         <f>[1]CARTELLINO!GH$27</f>
@@ -59677,7 +59673,7 @@
       </c>
       <c r="GI27" s="30" t="str">
         <f>[1]CARTELLINO!GL$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="GJ27" s="30" t="str">
         <f>[1]CARTELLINO!GM$27</f>
@@ -59721,31 +59717,31 @@
       </c>
       <c r="GT27" s="30" t="str">
         <f>[1]CARTELLINO!GW$27</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="GU27" s="30" t="str">
         <f>[1]CARTELLINO!GX$27</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="GV27" s="30" t="str">
         <f>[1]CARTELLINO!GY$27</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="GW27" s="30" t="str">
         <f>[1]CARTELLINO!GZ$27</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="GX27" s="30" t="str">
         <f>[1]CARTELLINO!HA$27</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="GY27" s="30" t="str">
         <f>[1]CARTELLINO!HB$27</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="GZ27" s="30" t="str">
         <f>[1]CARTELLINO!HC$27</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="HA27" s="30" t="str">
         <f>[1]CARTELLINO!HD$27</f>
@@ -59765,43 +59761,43 @@
       </c>
       <c r="HE27" s="30" t="str">
         <f>[1]CARTELLINO!HH$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="HF27" s="30" t="str">
         <f>[1]CARTELLINO!HI$27</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="HG27" s="30" t="str">
         <f>[1]CARTELLINO!HJ$27</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="HH27" s="30" t="str">
         <f>[1]CARTELLINO!HK$27</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="HI27" s="30" t="str">
         <f>[1]CARTELLINO!HL$27</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="HJ27" s="30" t="str">
         <f>[1]CARTELLINO!HM$27</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="HK27" s="30" t="str">
         <f>[1]CARTELLINO!HN$27</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="HL27" s="30" t="str">
         <f>[1]CARTELLINO!HO$27</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="HM27" s="30" t="str">
         <f>[1]CARTELLINO!HP$27</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="HN27" s="30" t="str">
         <f>[1]CARTELLINO!HQ$27</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="HO27" s="30" t="str">
         <f>[1]CARTELLINO!HR$27</f>
@@ -59825,7 +59821,7 @@
       </c>
       <c r="HT27" s="30" t="str">
         <f>[1]CARTELLINO!HW$27</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="HU27" s="30" t="str">
         <f>[1]CARTELLINO!HX$27</f>
@@ -59957,23 +59953,23 @@
       </c>
       <c r="JA27" s="30" t="str">
         <f>[1]CARTELLINO!JD$27</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="JB27" s="30" t="str">
         <f>[1]CARTELLINO!JE$27</f>
-        <v>M</v>
+        <v>-</v>
       </c>
       <c r="JC27" s="30" t="str">
         <f>[1]CARTELLINO!JF$27</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="JD27" s="30" t="str">
         <f>[1]CARTELLINO!JG$27</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="JE27" s="30" t="str">
         <f>[1]CARTELLINO!JH$27</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="JF27" s="30" t="str">
         <f>[1]CARTELLINO!JI$27</f>
@@ -61173,9 +61169,9 @@
         <f>[1]CARTELLINO!FM$28</f>
         <v>0</v>
       </c>
-      <c r="FK28" s="62" t="str">
+      <c r="FK28" s="62">
         <f>[1]CARTELLINO!FN$28</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="FL28" s="62" t="str">
         <f>[1]CARTELLINO!FO$28</f>
@@ -61417,9 +61413,9 @@
         <f>[1]CARTELLINO!HV$28</f>
         <v>0</v>
       </c>
-      <c r="HT28" s="62" t="str">
+      <c r="HT28" s="62">
         <f>[1]CARTELLINO!HW$28</f>
-        <v>ng</v>
+        <v>0</v>
       </c>
       <c r="HU28" s="62">
         <f>[1]CARTELLINO!HX$28</f>
@@ -62599,8 +62595,8 @@
       <c r="FH29" s="63" t="str">
         <v>BERARDI</v>
       </c>
-      <c r="FI29" s="63" t="str">
-        <v>PAZZAGLIA</v>
+      <c r="FI29" s="63">
+        <v>0</v>
       </c>
       <c r="FJ29" s="63" t="str">
         <v>SARTI</v>
@@ -62657,97 +62653,97 @@
         <v>GHIOTTI</v>
       </c>
       <c r="GB29" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="GC29" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="GD29" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="GE29" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="GF29" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="GG29" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="GH29" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="GI29" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="GJ29" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="GK29" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="GL29" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="GM29" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="GN29" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="GO29" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="GP29" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="GQ29" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="GR29" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="GS29" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="GT29" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="GU29" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="GV29" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="GW29" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="GX29" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="GY29" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="GZ29" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="HA29" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="HB29" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="HC29" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="HD29" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="HE29" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="HF29" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="HG29" s="63" t="str">
         <v/>
@@ -63699,8 +63695,8 @@
       <c r="FH30" s="63" t="str">
         <v>BERARDI</v>
       </c>
-      <c r="FI30" s="63" t="str">
-        <v>PAZZAGLIA</v>
+      <c r="FI30" s="63">
+        <v>0</v>
       </c>
       <c r="FJ30" s="63" t="str">
         <v>SARTI</v>
@@ -63757,97 +63753,97 @@
         <v>GHIOTTI</v>
       </c>
       <c r="GB30" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="GC30" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="GD30" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="GE30" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="GF30" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="GG30" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="GH30" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="GI30" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="GJ30" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="GK30" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="GL30" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="GM30" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="GN30" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="GO30" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="GP30" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="GQ30" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="GR30" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="GS30" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="GT30" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="GU30" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="GV30" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="GW30" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="GX30" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="GY30" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="GZ30" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="HA30" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="HB30" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="HC30" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="HD30" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="HE30" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="HF30" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="HG30" s="63" t="str">
         <v/>
@@ -64854,97 +64850,97 @@
         <v>GHIOTTI</v>
       </c>
       <c r="GA31" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="GB31" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="GC31" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="GD31" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="GE31" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="GF31" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="GG31" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="GH31" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="GI31" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="GJ31" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="GK31" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="GL31" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="GM31" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="GN31" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="GO31" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="GP31" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="GQ31" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="GR31" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="GS31" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="GT31" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="GU31" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="GV31" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="GW31" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="GX31" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="GY31" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="GZ31" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="HA31" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="HB31" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="HC31" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="HD31" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="HE31" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="HF31" s="63" t="str">
         <v/>
@@ -65822,7 +65818,7 @@
         <v>BERARDI</v>
       </c>
       <c r="EI32" s="63" t="str">
-        <v>FABBRI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="EJ32" s="63" t="str">
         <v>BERARDI</v>
@@ -65954,97 +65950,97 @@
         <v>GHIOTTI</v>
       </c>
       <c r="GA32" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="GB32" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="GC32" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="GD32" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="GE32" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="GF32" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="GG32" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="GH32" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="GI32" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="GJ32" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="GK32" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="GL32" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="GM32" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="GN32" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="GO32" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="GP32" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="GQ32" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="GR32" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="GS32" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="GT32" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="GU32" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="GV32" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="GW32" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="GX32" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="GY32" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="GZ32" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="HA32" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="HB32" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="HC32" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="HD32" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="HE32" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="HF32" s="63" t="str">
         <v/>
@@ -66529,12 +66525,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71027,6 +71023,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71035,13 +71038,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919E017C-F58C-4F2E-87A9-7A883F433F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B5A5964-700A-4C0D-81D8-35110A9DA3E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="570" windowWidth="28800" windowHeight="14910" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3622,7 +3622,7 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR149" t="str">
-            <v>BERARDI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS149" t="str">
             <v>SARTI</v>
@@ -3926,8 +3926,12 @@
           </cell>
         </row>
         <row r="171">
-          <cell r="AQ171"/>
-          <cell r="AR171"/>
+          <cell r="AQ171" t="str">
+            <v>FABBRI</v>
+          </cell>
+          <cell r="AR171" t="str">
+            <v>FABBRI</v>
+          </cell>
           <cell r="AS171" t="str">
             <v>SARTI</v>
           </cell>
@@ -9934,19 +9938,19 @@
             <v>-</v>
           </cell>
           <cell r="JJ6" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="JK6" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="JL6" t="str">
-            <v>-</v>
+            <v>N</v>
           </cell>
           <cell r="JM6" t="str">
-            <v>-</v>
+            <v>S</v>
           </cell>
           <cell r="JN6" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="JO6" t="str">
             <v>-</v>
@@ -19463,19 +19467,19 @@
             <v>R</v>
           </cell>
           <cell r="JM18" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="JN18" t="str">
-            <v>M</v>
+            <v>-</v>
           </cell>
           <cell r="JO18" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="JP18" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="JQ18" t="str">
-            <v>R</v>
+            <v>-</v>
           </cell>
           <cell r="JR18" t="str">
             <v>P</v>
@@ -26594,29 +26598,29 @@
             <v>-</v>
           </cell>
           <cell r="JJ27" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="JK27" t="str">
-            <v>M</v>
+            <v>-</v>
           </cell>
           <cell r="JL27" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="JM27" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="JN27" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="JO27" t="str">
             <v>N</v>
           </cell>
-          <cell r="JM27" t="str">
+          <cell r="JP27" t="str">
             <v>S</v>
           </cell>
-          <cell r="JN27" t="str">
+          <cell r="JQ27" t="str">
             <v>R</v>
           </cell>
-          <cell r="JO27" t="str">
-            <v>-</v>
-          </cell>
-          <cell r="JP27" t="str">
-            <v>-</v>
-          </cell>
-          <cell r="JQ27" t="str">
-            <v>-</v>
-          </cell>
           <cell r="JR27" t="str">
             <v>-</v>
           </cell>
@@ -26630,7 +26634,7 @@
             <v>-</v>
           </cell>
           <cell r="JV27" t="str">
-            <v>P</v>
+            <v>R</v>
           </cell>
           <cell r="JW27" t="str">
             <v>M</v>
@@ -27807,14 +27811,14 @@
           <cell r="JQ28">
             <v>0</v>
           </cell>
-          <cell r="JR28">
-            <v>0</v>
-          </cell>
-          <cell r="JS28">
-            <v>0</v>
-          </cell>
-          <cell r="JT28">
-            <v>0</v>
+          <cell r="JR28" t="str">
+            <v>nl</v>
+          </cell>
+          <cell r="JS28" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="JT28" t="str">
+            <v>pn</v>
           </cell>
           <cell r="JU28">
             <v>0</v>
@@ -28513,431 +28517,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28947,7 +28951,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -34805,23 +34809,23 @@
       </c>
       <c r="JG6" s="22" t="str">
         <f>[1]CARTELLINO!JJ$6</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="JH6" s="22" t="str">
         <f>[1]CARTELLINO!JK$6</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="JI6" s="22" t="str">
         <f>[1]CARTELLINO!JL$6</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="JJ6" s="22" t="str">
         <f>[1]CARTELLINO!JM$6</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="JK6" s="22" t="str">
         <f>[1]CARTELLINO!JN$6</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="JL6" s="22" t="str">
         <f>[1]CARTELLINO!JO$6</f>
@@ -49201,23 +49205,23 @@
       </c>
       <c r="JJ18" s="27" t="str">
         <f>[1]CARTELLINO!JM$18</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="JK18" s="27" t="str">
         <f>[1]CARTELLINO!JN$18</f>
-        <v>M</v>
+        <v>-</v>
       </c>
       <c r="JL18" s="27" t="str">
         <f>[1]CARTELLINO!JO$18</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="JM18" s="27" t="str">
         <f>[1]CARTELLINO!JP$18</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="JN18" s="27" t="str">
         <f>[1]CARTELLINO!JQ$18</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="JO18" s="27" t="str">
         <f>[1]CARTELLINO!JR$18</f>
@@ -59977,35 +59981,35 @@
       </c>
       <c r="JG27" s="30" t="str">
         <f>[1]CARTELLINO!JJ$27</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="JH27" s="30" t="str">
         <f>[1]CARTELLINO!JK$27</f>
-        <v>M</v>
+        <v>-</v>
       </c>
       <c r="JI27" s="30" t="str">
         <f>[1]CARTELLINO!JL$27</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="JJ27" s="30" t="str">
         <f>[1]CARTELLINO!JM$27</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="JK27" s="30" t="str">
         <f>[1]CARTELLINO!JN$27</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="JL27" s="30" t="str">
         <f>[1]CARTELLINO!JO$27</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="JM27" s="30" t="str">
         <f>[1]CARTELLINO!JP$27</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="JN27" s="30" t="str">
         <f>[1]CARTELLINO!JQ$27</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="JO27" s="30" t="str">
         <f>[1]CARTELLINO!JR$27</f>
@@ -60025,7 +60029,7 @@
       </c>
       <c r="JS27" s="30" t="str">
         <f>[1]CARTELLINO!JV$27</f>
-        <v>P</v>
+        <v>R</v>
       </c>
       <c r="JT27" s="30" t="str">
         <f>[1]CARTELLINO!JW$27</f>
@@ -61601,17 +61605,17 @@
         <f>[1]CARTELLINO!JQ$28</f>
         <v>0</v>
       </c>
-      <c r="JO28" s="62">
+      <c r="JO28" s="62" t="str">
         <f>[1]CARTELLINO!JR$28</f>
-        <v>0</v>
-      </c>
-      <c r="JP28" s="62">
+        <v>nl</v>
+      </c>
+      <c r="JP28" s="62" t="str">
         <f>[1]CARTELLINO!JS$28</f>
-        <v>0</v>
-      </c>
-      <c r="JQ28" s="62">
+        <v>p</v>
+      </c>
+      <c r="JQ28" s="62" t="str">
         <f>[1]CARTELLINO!JT$28</f>
-        <v>0</v>
+        <v>pn</v>
       </c>
       <c r="JR28" s="62">
         <f>[1]CARTELLINO!JU$28</f>
@@ -62595,8 +62599,8 @@
       <c r="FH29" s="63" t="str">
         <v>BERARDI</v>
       </c>
-      <c r="FI29" s="63">
-        <v>0</v>
+      <c r="FI29" s="63" t="str">
+        <v>FABBRI</v>
       </c>
       <c r="FJ29" s="63" t="str">
         <v>SARTI</v>
@@ -63630,7 +63634,7 @@
         <v>BIANCHI</v>
       </c>
       <c r="EM30" s="63" t="str">
-        <v>BERARDI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="EN30" s="63" t="str">
         <v>SARTI</v>
@@ -63695,8 +63699,8 @@
       <c r="FH30" s="63" t="str">
         <v>BERARDI</v>
       </c>
-      <c r="FI30" s="63">
-        <v>0</v>
+      <c r="FI30" s="63" t="str">
+        <v>FABBRI</v>
       </c>
       <c r="FJ30" s="63" t="str">
         <v>SARTI</v>
@@ -66525,12 +66529,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71023,13 +71027,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71038,6 +71035,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B5A5964-700A-4C0D-81D8-35110A9DA3E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5614CD86-5239-47A8-9B85-4C6901A6890F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="570" windowWidth="28800" windowHeight="14910" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3650,7 +3650,7 @@
             <v>GHIOTTI</v>
           </cell>
           <cell r="AR151" t="str">
-            <v>FABBRI</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS151" t="str">
             <v>MICHELOT.</v>
@@ -7213,7 +7213,7 @@
             <v>r</v>
           </cell>
           <cell r="EX3" t="str">
-            <v>p</v>
+            <v>-</v>
           </cell>
           <cell r="EY3" t="str">
             <v>m</v>
@@ -8402,8 +8402,8 @@
           <cell r="EW4">
             <v>0</v>
           </cell>
-          <cell r="EX4">
-            <v>0</v>
+          <cell r="EX4" t="str">
+            <v>p</v>
           </cell>
           <cell r="EY4">
             <v>0</v>
@@ -28517,431 +28517,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28951,7 +28951,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -30750,7 +30750,7 @@
       </c>
       <c r="EU3" s="16" t="str">
         <f>[1]CARTELLINO!EX$3</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="EV3" s="16" t="str">
         <f>[1]CARTELLINO!EY$3</f>
@@ -32342,9 +32342,9 @@
         <f>[1]CARTELLINO!EW$4</f>
         <v>0</v>
       </c>
-      <c r="EU4" s="43">
+      <c r="EU4" s="43" t="str">
         <f>[1]CARTELLINO!EX$4</f>
-        <v>0</v>
+        <v>p</v>
       </c>
       <c r="EV4" s="43">
         <f>[1]CARTELLINO!EY$4</f>
@@ -63640,7 +63640,7 @@
         <v>SARTI</v>
       </c>
       <c r="EO30" s="63" t="str">
-        <v>FABBRI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="EP30" s="63" t="str">
         <v>MICHELOT.</v>
@@ -66529,12 +66529,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71027,6 +71027,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71035,13 +71042,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5614CD86-5239-47A8-9B85-4C6901A6890F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0E2A5A-53A7-4C10-9E58-86AC815A1BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="570" windowWidth="28800" windowHeight="14910" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7225,7 +7225,7 @@
             <v>p</v>
           </cell>
           <cell r="FB3" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="FC3" t="str">
             <v>m</v>
@@ -7249,13 +7249,13 @@
             <v>R</v>
           </cell>
           <cell r="FJ3" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="FK3" t="str">
             <v>M/R</v>
           </cell>
           <cell r="FL3" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="FM3" t="str">
             <v>M</v>
@@ -7273,7 +7273,7 @@
             <v>r</v>
           </cell>
           <cell r="FR3" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="FS3" t="str">
             <v>p</v>
@@ -7285,7 +7285,7 @@
             <v>S</v>
           </cell>
           <cell r="FV3" t="str">
-            <v>R</v>
+            <v>p</v>
           </cell>
           <cell r="FW3" t="str">
             <v>N</v>
@@ -9557,7 +9557,7 @@
             <v>r</v>
           </cell>
           <cell r="EM6" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="EN6" t="str">
             <v>m</v>
@@ -9623,7 +9623,7 @@
             <v>m</v>
           </cell>
           <cell r="FI6" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="FJ6" t="str">
             <v>p</v>
@@ -11970,10 +11970,10 @@
             <v>M</v>
           </cell>
           <cell r="EX9" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="EY9" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="EZ9" t="str">
             <v>R</v>
@@ -13159,8 +13159,8 @@
           <cell r="EW10">
             <v>0</v>
           </cell>
-          <cell r="EX10">
-            <v>0</v>
+          <cell r="EX10" t="str">
+            <v>pn</v>
           </cell>
           <cell r="EY10">
             <v>0</v>
@@ -16772,7 +16772,7 @@
             <v>R</v>
           </cell>
           <cell r="FL15" t="str">
-            <v>P</v>
+            <v>p</v>
           </cell>
           <cell r="FM15" t="str">
             <v>P</v>
@@ -16964,7 +16964,7 @@
             <v>m</v>
           </cell>
           <cell r="HX15" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="HY15" t="str">
             <v>r</v>
@@ -19077,7 +19077,7 @@
             <v>p</v>
           </cell>
           <cell r="EM18" t="str">
-            <v>m</v>
+            <v>-</v>
           </cell>
           <cell r="EN18" t="str">
             <v>r</v>
@@ -19110,10 +19110,10 @@
             <v>p</v>
           </cell>
           <cell r="EX18" t="str">
-            <v>m</v>
+            <v>N</v>
           </cell>
           <cell r="EY18" t="str">
-            <v>p</v>
+            <v>S</v>
           </cell>
           <cell r="EZ18" t="str">
             <v>P</v>
@@ -19170,7 +19170,7 @@
             <v>p</v>
           </cell>
           <cell r="FR18" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="FS18" t="str">
             <v>m/R</v>
@@ -19344,7 +19344,7 @@
             <v>R</v>
           </cell>
           <cell r="HX18" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="HY18" t="str">
             <v>M</v>
@@ -20266,8 +20266,8 @@
           <cell r="EL19">
             <v>0</v>
           </cell>
-          <cell r="EM19">
-            <v>0</v>
+          <cell r="EM19" t="str">
+            <v>p</v>
           </cell>
           <cell r="EN19">
             <v>0</v>
@@ -20321,7 +20321,7 @@
             <v>0</v>
           </cell>
           <cell r="FE19" t="str">
-            <v>f</v>
+            <v>p</v>
           </cell>
           <cell r="FF19" t="str">
             <v>f</v>
@@ -20533,8 +20533,8 @@
           <cell r="HW19">
             <v>0</v>
           </cell>
-          <cell r="HX19">
-            <v>0</v>
+          <cell r="HX19" t="str">
+            <v>p</v>
           </cell>
           <cell r="HY19">
             <v>0</v>
@@ -20626,17 +20626,17 @@
           <cell r="JB19">
             <v>0</v>
           </cell>
-          <cell r="JC19" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="JD19" t="str">
-            <v>f</v>
+          <cell r="JC19">
+            <v>7</v>
+          </cell>
+          <cell r="JD19">
+            <v>7</v>
           </cell>
           <cell r="JE19" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="JF19" t="str">
-            <v>f</v>
+            <v>pn</v>
+          </cell>
+          <cell r="JF19">
+            <v>0</v>
           </cell>
           <cell r="JG19" t="str">
             <v>f</v>
@@ -20753,10 +20753,10 @@
             <v>k</v>
           </cell>
           <cell r="KS19" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="KT19" t="str">
-            <v>f</v>
+            <v>pn</v>
+          </cell>
+          <cell r="KT19">
+            <v>0</v>
           </cell>
           <cell r="KU19" t="str">
             <v>f</v>
@@ -23855,7 +23855,7 @@
             <v>P</v>
           </cell>
           <cell r="ES24" t="str">
-            <v>M/R</v>
+            <v>m/R</v>
           </cell>
           <cell r="ET24" t="str">
             <v>N</v>
@@ -23903,10 +23903,10 @@
             <v>p</v>
           </cell>
           <cell r="FI24" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="FJ24" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="FK24" t="str">
             <v>p</v>
@@ -26235,7 +26235,7 @@
             <v>p</v>
           </cell>
           <cell r="ES27" t="str">
-            <v>m</v>
+            <v>M</v>
           </cell>
           <cell r="ET27" t="str">
             <v>m/R</v>
@@ -28517,431 +28517,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28951,7 +28951,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -30766,7 +30766,7 @@
       </c>
       <c r="EY3" s="16" t="str">
         <f>[1]CARTELLINO!FB$3</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="EZ3" s="16" t="str">
         <f>[1]CARTELLINO!FC$3</f>
@@ -30798,7 +30798,7 @@
       </c>
       <c r="FG3" s="16" t="str">
         <f>[1]CARTELLINO!FJ$3</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="FH3" s="16" t="str">
         <f>[1]CARTELLINO!FK$3</f>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="FI3" s="16" t="str">
         <f>[1]CARTELLINO!FL$3</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="FJ3" s="16" t="str">
         <f>[1]CARTELLINO!FM$3</f>
@@ -30830,7 +30830,7 @@
       </c>
       <c r="FO3" s="16" t="str">
         <f>[1]CARTELLINO!FR$3</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="FP3" s="16" t="str">
         <f>[1]CARTELLINO!FS$3</f>
@@ -30846,7 +30846,7 @@
       </c>
       <c r="FS3" s="16" t="str">
         <f>[1]CARTELLINO!FV$3</f>
-        <v>R</v>
+        <v>p</v>
       </c>
       <c r="FT3" s="16" t="str">
         <f>[1]CARTELLINO!FW$3</f>
@@ -34301,7 +34301,7 @@
       </c>
       <c r="EJ6" s="22" t="str">
         <f>[1]CARTELLINO!EM$6</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="EK6" s="22" t="str">
         <f>[1]CARTELLINO!EN$6</f>
@@ -34389,7 +34389,7 @@
       </c>
       <c r="FF6" s="22" t="str">
         <f>[1]CARTELLINO!FI$6</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="FG6" s="22" t="str">
         <f>[1]CARTELLINO!FJ$6</f>
@@ -37941,11 +37941,11 @@
       </c>
       <c r="EU9" s="24" t="str">
         <f>[1]CARTELLINO!EX$9</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="EV9" s="24" t="str">
         <f>[1]CARTELLINO!EY$9</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="EW9" s="24" t="str">
         <f>[1]CARTELLINO!EZ$9</f>
@@ -39533,9 +39533,9 @@
         <f>[1]CARTELLINO!EW$10</f>
         <v>0</v>
       </c>
-      <c r="EU10" s="46">
+      <c r="EU10" s="46" t="str">
         <f>[1]CARTELLINO!EX$10</f>
-        <v>0</v>
+        <v>pn</v>
       </c>
       <c r="EV10" s="46">
         <f>[1]CARTELLINO!EY$10</f>
@@ -45189,7 +45189,7 @@
       </c>
       <c r="FI15" s="26" t="str">
         <f>[1]CARTELLINO!FL$15</f>
-        <v>P</v>
+        <v>p</v>
       </c>
       <c r="FJ15" s="26" t="str">
         <f>[1]CARTELLINO!FM$15</f>
@@ -45445,7 +45445,7 @@
       </c>
       <c r="HU15" s="26" t="str">
         <f>[1]CARTELLINO!HX$15</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="HV15" s="26" t="str">
         <f>[1]CARTELLINO!HY$15</f>
@@ -48685,7 +48685,7 @@
       </c>
       <c r="EJ18" s="27" t="str">
         <f>[1]CARTELLINO!EM$18</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="EK18" s="27" t="str">
         <f>[1]CARTELLINO!EN$18</f>
@@ -48729,11 +48729,11 @@
       </c>
       <c r="EU18" s="27" t="str">
         <f>[1]CARTELLINO!EX$18</f>
-        <v>m</v>
+        <v>N</v>
       </c>
       <c r="EV18" s="27" t="str">
         <f>[1]CARTELLINO!EY$18</f>
-        <v>p</v>
+        <v>S</v>
       </c>
       <c r="EW18" s="27" t="str">
         <f>[1]CARTELLINO!EZ$18</f>
@@ -48809,7 +48809,7 @@
       </c>
       <c r="FO18" s="27" t="str">
         <f>[1]CARTELLINO!FR$18</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="FP18" s="27" t="str">
         <f>[1]CARTELLINO!FS$18</f>
@@ -49041,7 +49041,7 @@
       </c>
       <c r="HU18" s="27" t="str">
         <f>[1]CARTELLINO!HX$18</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="HV18" s="27" t="str">
         <f>[1]CARTELLINO!HY$18</f>
@@ -50277,9 +50277,9 @@
         <f>[1]CARTELLINO!EL$19</f>
         <v>0</v>
       </c>
-      <c r="EJ19" s="46">
+      <c r="EJ19" s="46" t="str">
         <f>[1]CARTELLINO!EM$19</f>
-        <v>0</v>
+        <v>p</v>
       </c>
       <c r="EK19" s="46">
         <f>[1]CARTELLINO!EN$19</f>
@@ -50351,7 +50351,7 @@
       </c>
       <c r="FB19" s="46" t="str">
         <f>[1]CARTELLINO!FE$19</f>
-        <v>f</v>
+        <v>p</v>
       </c>
       <c r="FC19" s="46" t="str">
         <f>[1]CARTELLINO!FF$19</f>
@@ -50633,9 +50633,9 @@
         <f>[1]CARTELLINO!HW$19</f>
         <v>0</v>
       </c>
-      <c r="HU19" s="46">
+      <c r="HU19" s="46" t="str">
         <f>[1]CARTELLINO!HX$19</f>
-        <v>0</v>
+        <v>p</v>
       </c>
       <c r="HV19" s="46">
         <f>[1]CARTELLINO!HY$19</f>
@@ -50757,21 +50757,21 @@
         <f>[1]CARTELLINO!JB$19</f>
         <v>0</v>
       </c>
-      <c r="IZ19" s="46" t="str">
+      <c r="IZ19" s="46">
         <f>[1]CARTELLINO!JC$19</f>
-        <v>f</v>
-      </c>
-      <c r="JA19" s="46" t="str">
+        <v>7</v>
+      </c>
+      <c r="JA19" s="46">
         <f>[1]CARTELLINO!JD$19</f>
-        <v>f</v>
+        <v>7</v>
       </c>
       <c r="JB19" s="46" t="str">
         <f>[1]CARTELLINO!JE$19</f>
-        <v>f</v>
-      </c>
-      <c r="JC19" s="46" t="str">
+        <v>pn</v>
+      </c>
+      <c r="JC19" s="46">
         <f>[1]CARTELLINO!JF$19</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="JD19" s="46" t="str">
         <f>[1]CARTELLINO!JG$19</f>
@@ -50927,11 +50927,11 @@
       </c>
       <c r="KP19" s="46" t="str">
         <f>[1]CARTELLINO!KS$19</f>
-        <v>f</v>
-      </c>
-      <c r="KQ19" s="46" t="str">
+        <v>pn</v>
+      </c>
+      <c r="KQ19" s="46">
         <f>[1]CARTELLINO!KT$19</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="KR19" s="46" t="str">
         <f>[1]CARTELLINO!KU$19</f>
@@ -55901,7 +55901,7 @@
       </c>
       <c r="EP24" s="29" t="str">
         <f>[1]CARTELLINO!ES$24</f>
-        <v>M/R</v>
+        <v>m/R</v>
       </c>
       <c r="EQ24" s="29" t="str">
         <f>[1]CARTELLINO!ET$24</f>
@@ -55965,11 +55965,11 @@
       </c>
       <c r="FF24" s="29" t="str">
         <f>[1]CARTELLINO!FI$24</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="FG24" s="29" t="str">
         <f>[1]CARTELLINO!FJ$24</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="FH24" s="29" t="str">
         <f>[1]CARTELLINO!FK$24</f>
@@ -59497,7 +59497,7 @@
       </c>
       <c r="EP27" s="30" t="str">
         <f>[1]CARTELLINO!ES$27</f>
-        <v>m</v>
+        <v>M</v>
       </c>
       <c r="EQ27" s="30" t="str">
         <f>[1]CARTELLINO!ET$27</f>
@@ -66529,12 +66529,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71027,13 +71027,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71042,6 +71035,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0E2A5A-53A7-4C10-9E58-86AC815A1BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CDAD65D-F581-4092-B996-B61DED18AAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="0" yWindow="795" windowWidth="28800" windowHeight="15405" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3751,7 +3751,7 @@
             <v>BIANCHI</v>
           </cell>
           <cell r="AS158" t="str">
-            <v>VOLPINI</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT158" t="str">
             <v>VOLPINI</v>
@@ -9593,7 +9593,7 @@
             <v>p</v>
           </cell>
           <cell r="EY6" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="EZ6" t="str">
             <v>m</v>
@@ -9641,7 +9641,7 @@
             <v>P</v>
           </cell>
           <cell r="FO6" t="str">
-            <v>M</v>
+            <v>-</v>
           </cell>
           <cell r="FP6" t="str">
             <v>N</v>
@@ -10831,7 +10831,7 @@
             <v>0</v>
           </cell>
           <cell r="FO7">
-            <v>0</v>
+            <v>7</v>
           </cell>
           <cell r="FP7">
             <v>0</v>
@@ -14353,7 +14353,7 @@
             <v>P</v>
           </cell>
           <cell r="EY12" t="str">
-            <v>M/R</v>
+            <v>P</v>
           </cell>
           <cell r="EZ12" t="str">
             <v>N</v>
@@ -22120,10 +22120,10 @@
             <v>R</v>
           </cell>
           <cell r="MZ21" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="NA21" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="NB21" t="str">
             <v>-</v>
@@ -26880,10 +26880,10 @@
             <v>R</v>
           </cell>
           <cell r="MZ27" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="NA27" t="str">
-            <v>M</v>
+            <v>-</v>
           </cell>
           <cell r="NB27" t="str">
             <v>N</v>
@@ -27752,13 +27752,13 @@
             <v>f</v>
           </cell>
           <cell r="IX28" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="IY28" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="IZ28" t="str">
-            <v>f</v>
+            <v>pn</v>
+          </cell>
+          <cell r="IY28">
+            <v>0</v>
+          </cell>
+          <cell r="IZ28">
+            <v>0</v>
           </cell>
           <cell r="JA28">
             <v>0</v>
@@ -28069,11 +28069,11 @@
           <cell r="MY28" t="str">
             <v>f</v>
           </cell>
-          <cell r="MZ28">
-            <v>0</v>
-          </cell>
-          <cell r="NA28">
-            <v>0</v>
+          <cell r="MZ28" t="str">
+            <v>nl</v>
+          </cell>
+          <cell r="NA28" t="str">
+            <v>p</v>
           </cell>
           <cell r="NB28">
             <v>0</v>
@@ -28517,431 +28517,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28951,7 +28951,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -34349,7 +34349,7 @@
       </c>
       <c r="EV6" s="22" t="str">
         <f>[1]CARTELLINO!EY$6</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="EW6" s="22" t="str">
         <f>[1]CARTELLINO!EZ$6</f>
@@ -34413,7 +34413,7 @@
       </c>
       <c r="FL6" s="22" t="str">
         <f>[1]CARTELLINO!FO$6</f>
-        <v>M</v>
+        <v>-</v>
       </c>
       <c r="FM6" s="22" t="str">
         <f>[1]CARTELLINO!FP$6</f>
@@ -36007,7 +36007,7 @@
       </c>
       <c r="FL7" s="46">
         <f>[1]CARTELLINO!FO$7</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="FM7" s="46">
         <f>[1]CARTELLINO!FP$7</f>
@@ -41541,7 +41541,7 @@
       </c>
       <c r="EV12" s="25" t="str">
         <f>[1]CARTELLINO!EY$12</f>
-        <v>M/R</v>
+        <v>P</v>
       </c>
       <c r="EW12" s="25" t="str">
         <f>[1]CARTELLINO!EZ$12</f>
@@ -53165,11 +53165,11 @@
       </c>
       <c r="MW21" s="28" t="str">
         <f>[1]CARTELLINO!MZ$21</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="MX21" s="28" t="str">
         <f>[1]CARTELLINO!NA$21</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="MY21" s="28" t="str">
         <f>[1]CARTELLINO!NB$21</f>
@@ -60357,11 +60357,11 @@
       </c>
       <c r="MW27" s="30" t="str">
         <f>[1]CARTELLINO!MZ$27</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="MX27" s="30" t="str">
         <f>[1]CARTELLINO!NA$27</f>
-        <v>M</v>
+        <v>-</v>
       </c>
       <c r="MY27" s="30" t="str">
         <f>[1]CARTELLINO!NB$27</f>
@@ -61527,15 +61527,15 @@
       </c>
       <c r="IU28" s="62" t="str">
         <f>[1]CARTELLINO!IX$28</f>
-        <v>f</v>
-      </c>
-      <c r="IV28" s="62" t="str">
+        <v>pn</v>
+      </c>
+      <c r="IV28" s="62">
         <f>[1]CARTELLINO!IY$28</f>
-        <v>f</v>
-      </c>
-      <c r="IW28" s="62" t="str">
+        <v>0</v>
+      </c>
+      <c r="IW28" s="62">
         <f>[1]CARTELLINO!IZ$28</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="IX28" s="62">
         <f>[1]CARTELLINO!JA$28</f>
@@ -61949,13 +61949,13 @@
         <f>[1]CARTELLINO!MY$28</f>
         <v>f</v>
       </c>
-      <c r="MW28" s="62">
+      <c r="MW28" s="62" t="str">
         <f>[1]CARTELLINO!MZ$28</f>
-        <v>0</v>
-      </c>
-      <c r="MX28" s="62">
+        <v>nl</v>
+      </c>
+      <c r="MX28" s="62" t="str">
         <f>[1]CARTELLINO!NA$28</f>
-        <v>0</v>
+        <v>p</v>
       </c>
       <c r="MY28" s="62">
         <f>[1]CARTELLINO!NB$28</f>
@@ -64761,7 +64761,7 @@
         <v>BIANCHI</v>
       </c>
       <c r="EV31" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="EW31" s="63" t="str">
         <v>BERARDI</v>
@@ -66529,12 +66529,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71027,6 +71027,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71035,13 +71042,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CDAD65D-F581-4092-B996-B61DED18AAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A3D684-8C58-4F84-B2B7-EBD9B732B12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="795" windowWidth="28800" windowHeight="15405" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3748,7 +3748,7 @@
             <v>BIANCHI</v>
           </cell>
           <cell r="AR158" t="str">
-            <v>BIANCHI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS158" t="str">
             <v>BARBIERI</v>
@@ -7225,7 +7225,7 @@
             <v>p</v>
           </cell>
           <cell r="FB3" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="FC3" t="str">
             <v>m</v>
@@ -7234,7 +7234,7 @@
             <v>r</v>
           </cell>
           <cell r="FE3" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="FF3" t="str">
             <v>M/R</v>
@@ -8415,7 +8415,7 @@
             <v>0</v>
           </cell>
           <cell r="FB4">
-            <v>0</v>
+            <v>2</v>
           </cell>
           <cell r="FC4">
             <v>0</v>
@@ -9611,7 +9611,7 @@
             <v>p</v>
           </cell>
           <cell r="FE6" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="FF6" t="str">
             <v>r</v>
@@ -17357,10 +17357,10 @@
             <v>-</v>
           </cell>
           <cell r="MY15" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="MZ15" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="NA15" t="str">
             <v>-</v>
@@ -22973,8 +22973,8 @@
           <cell r="IQ22">
             <v>0</v>
           </cell>
-          <cell r="IR22">
-            <v>0</v>
+          <cell r="IR22" t="str">
+            <v>p</v>
           </cell>
           <cell r="IS22">
             <v>0</v>
@@ -24497,16 +24497,16 @@
             <v>R</v>
           </cell>
           <cell r="MY24" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="MZ24" t="str">
-            <v>M</v>
+            <v>-</v>
           </cell>
           <cell r="NA24" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="NB24" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="NC24" t="str">
             <v>R</v>
@@ -25287,8 +25287,8 @@
           <cell r="HU25">
             <v>0</v>
           </cell>
-          <cell r="HV25">
-            <v>0</v>
+          <cell r="HV25" t="str">
+            <v>f</v>
           </cell>
           <cell r="HW25" t="str">
             <v>ng</v>
@@ -25686,14 +25686,14 @@
           <cell r="MX25">
             <v>0</v>
           </cell>
-          <cell r="MY25">
-            <v>0</v>
-          </cell>
-          <cell r="MZ25">
-            <v>0</v>
-          </cell>
-          <cell r="NA25">
-            <v>0</v>
+          <cell r="MY25" t="str">
+            <v>nl</v>
+          </cell>
+          <cell r="MZ25" t="str">
+            <v>nl</v>
+          </cell>
+          <cell r="NA25" t="str">
+            <v>pn</v>
           </cell>
           <cell r="NB25">
             <v>0</v>
@@ -28517,431 +28517,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28951,7 +28951,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -30766,7 +30766,7 @@
       </c>
       <c r="EY3" s="16" t="str">
         <f>[1]CARTELLINO!FB$3</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="EZ3" s="16" t="str">
         <f>[1]CARTELLINO!FC$3</f>
@@ -30778,7 +30778,7 @@
       </c>
       <c r="FB3" s="16" t="str">
         <f>[1]CARTELLINO!FE$3</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="FC3" s="16" t="str">
         <f>[1]CARTELLINO!FF$3</f>
@@ -32360,7 +32360,7 @@
       </c>
       <c r="EY4" s="43">
         <f>[1]CARTELLINO!FB$4</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="EZ4" s="43">
         <f>[1]CARTELLINO!FC$4</f>
@@ -34373,7 +34373,7 @@
       </c>
       <c r="FB6" s="22" t="str">
         <f>[1]CARTELLINO!FE$6</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="FC6" s="22" t="str">
         <f>[1]CARTELLINO!FF$6</f>
@@ -45969,11 +45969,11 @@
       </c>
       <c r="MV15" s="26" t="str">
         <f>[1]CARTELLINO!MY$15</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="MW15" s="26" t="str">
         <f>[1]CARTELLINO!MZ$15</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="MX15" s="26" t="str">
         <f>[1]CARTELLINO!NA$15</f>
@@ -54309,9 +54309,9 @@
         <f>[1]CARTELLINO!IQ$22</f>
         <v>0</v>
       </c>
-      <c r="IO22" s="46">
+      <c r="IO22" s="46" t="str">
         <f>[1]CARTELLINO!IR$22</f>
-        <v>0</v>
+        <v>p</v>
       </c>
       <c r="IP22" s="46">
         <f>[1]CARTELLINO!IS$22</f>
@@ -56757,19 +56757,19 @@
       </c>
       <c r="MV24" s="29" t="str">
         <f>[1]CARTELLINO!MY$24</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="MW24" s="29" t="str">
         <f>[1]CARTELLINO!MZ$24</f>
-        <v>M</v>
+        <v>-</v>
       </c>
       <c r="MX24" s="29" t="str">
         <f>[1]CARTELLINO!NA$24</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="MY24" s="29" t="str">
         <f>[1]CARTELLINO!NB$24</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="MZ24" s="29" t="str">
         <f>[1]CARTELLINO!NC$24</f>
@@ -57817,9 +57817,9 @@
         <f>[1]CARTELLINO!HU$25</f>
         <v>0</v>
       </c>
-      <c r="HS25" s="46">
+      <c r="HS25" s="46" t="str">
         <f>[1]CARTELLINO!HV$25</f>
-        <v>0</v>
+        <v>f</v>
       </c>
       <c r="HT25" s="46" t="str">
         <f>[1]CARTELLINO!HW$25</f>
@@ -58349,17 +58349,17 @@
         <f>[1]CARTELLINO!MX$25</f>
         <v>0</v>
       </c>
-      <c r="MV25" s="46">
+      <c r="MV25" s="46" t="str">
         <f>[1]CARTELLINO!MY$25</f>
-        <v>0</v>
-      </c>
-      <c r="MW25" s="46">
+        <v>nl</v>
+      </c>
+      <c r="MW25" s="46" t="str">
         <f>[1]CARTELLINO!MZ$25</f>
-        <v>0</v>
-      </c>
-      <c r="MX25" s="46">
+        <v>nl</v>
+      </c>
+      <c r="MX25" s="46" t="str">
         <f>[1]CARTELLINO!NA$25</f>
-        <v>0</v>
+        <v>pn</v>
       </c>
       <c r="MY25" s="46">
         <f>[1]CARTELLINO!NB$25</f>
@@ -63661,7 +63661,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="EV30" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="EW30" s="63" t="str">
         <v>VOLPINI</v>
@@ -66529,12 +66529,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71027,13 +71027,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71042,6 +71035,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A3D684-8C58-4F84-B2B7-EBD9B732B12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C2E5108-0C27-41D0-B022-7BE6F972D596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="0" yWindow="795" windowWidth="28800" windowHeight="15405" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3835,18 +3835,18 @@
             <v>VOLPINI</v>
           </cell>
           <cell r="AS164" t="str">
-            <v>BERARDI</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT164" t="str">
-            <v>BERARDI</v>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="165">
           <cell r="AQ165" t="str">
-            <v>BERARDI</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR165" t="str">
-            <v>BERARDI</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS165" t="str">
             <v>PAZZAGLIA</v>
@@ -7285,16 +7285,16 @@
             <v>S</v>
           </cell>
           <cell r="FV3" t="str">
+            <v>R</v>
+          </cell>
+          <cell r="FW3" t="str">
             <v>p</v>
           </cell>
-          <cell r="FW3" t="str">
-            <v>N</v>
-          </cell>
           <cell r="FX3" t="str">
-            <v>S</v>
+            <v>r</v>
           </cell>
           <cell r="FY3" t="str">
-            <v>R</v>
+            <v>m</v>
           </cell>
           <cell r="FZ3" t="str">
             <v>P</v>
@@ -16751,16 +16751,16 @@
             <v>r</v>
           </cell>
           <cell r="FE15" t="str">
-            <v>p</v>
+            <v>M/R</v>
           </cell>
           <cell r="FF15" t="str">
-            <v>m</v>
+            <v>N</v>
           </cell>
           <cell r="FG15" t="str">
-            <v>-</v>
+            <v>S</v>
           </cell>
           <cell r="FH15" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="FI15" t="str">
             <v>-</v>
@@ -16769,10 +16769,10 @@
             <v>-</v>
           </cell>
           <cell r="FK15" t="str">
-            <v>R</v>
+            <v>-</v>
           </cell>
           <cell r="FL15" t="str">
-            <v>p</v>
+            <v>-</v>
           </cell>
           <cell r="FM15" t="str">
             <v>P</v>
@@ -16805,19 +16805,19 @@
             <v>m/R</v>
           </cell>
           <cell r="FW15" t="str">
-            <v>p</v>
+            <v>N</v>
           </cell>
           <cell r="FX15" t="str">
-            <v>p</v>
+            <v>S</v>
           </cell>
           <cell r="FY15" t="str">
-            <v>m</v>
+            <v>R</v>
           </cell>
           <cell r="FZ15" t="str">
             <v>r</v>
           </cell>
           <cell r="GA15" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="GB15" t="str">
             <v>P</v>
@@ -17946,11 +17946,11 @@
           <cell r="FF16">
             <v>0</v>
           </cell>
-          <cell r="FG16" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="FH16" t="str">
-            <v>f</v>
+          <cell r="FG16">
+            <v>0</v>
+          </cell>
+          <cell r="FH16">
+            <v>0</v>
           </cell>
           <cell r="FI16" t="str">
             <v>f</v>
@@ -17959,7 +17959,7 @@
             <v>f</v>
           </cell>
           <cell r="FK16" t="str">
-            <v>f</v>
+            <v>pn</v>
           </cell>
           <cell r="FL16">
             <v>0</v>
@@ -21511,16 +21511,16 @@
             <v>P</v>
           </cell>
           <cell r="FE21" t="str">
-            <v>M/R</v>
+            <v>p</v>
           </cell>
           <cell r="FF21" t="str">
-            <v>N</v>
+            <v>m</v>
           </cell>
           <cell r="FG21" t="str">
-            <v>S</v>
+            <v>m</v>
           </cell>
           <cell r="FH21" t="str">
-            <v>R</v>
+            <v>r</v>
           </cell>
           <cell r="FI21" t="str">
             <v>P</v>
@@ -25287,8 +25287,8 @@
           <cell r="HU25">
             <v>0</v>
           </cell>
-          <cell r="HV25" t="str">
-            <v>f</v>
+          <cell r="HV25">
+            <v>0</v>
           </cell>
           <cell r="HW25" t="str">
             <v>ng</v>
@@ -28517,431 +28517,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28951,7 +28951,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -30846,19 +30846,19 @@
       </c>
       <c r="FS3" s="16" t="str">
         <f>[1]CARTELLINO!FV$3</f>
-        <v>p</v>
+        <v>R</v>
       </c>
       <c r="FT3" s="16" t="str">
         <f>[1]CARTELLINO!FW$3</f>
-        <v>N</v>
+        <v>p</v>
       </c>
       <c r="FU3" s="16" t="str">
         <f>[1]CARTELLINO!FX$3</f>
-        <v>S</v>
+        <v>r</v>
       </c>
       <c r="FV3" s="16" t="str">
         <f>[1]CARTELLINO!FY$3</f>
-        <v>R</v>
+        <v>m</v>
       </c>
       <c r="FW3" s="16" t="str">
         <f>[1]CARTELLINO!FZ$3</f>
@@ -45161,19 +45161,19 @@
       </c>
       <c r="FB15" s="26" t="str">
         <f>[1]CARTELLINO!FE$15</f>
-        <v>p</v>
+        <v>M/R</v>
       </c>
       <c r="FC15" s="26" t="str">
         <f>[1]CARTELLINO!FF$15</f>
-        <v>m</v>
+        <v>N</v>
       </c>
       <c r="FD15" s="26" t="str">
         <f>[1]CARTELLINO!FG$15</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="FE15" s="26" t="str">
         <f>[1]CARTELLINO!FH$15</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="FF15" s="26" t="str">
         <f>[1]CARTELLINO!FI$15</f>
@@ -45185,11 +45185,11 @@
       </c>
       <c r="FH15" s="26" t="str">
         <f>[1]CARTELLINO!FK$15</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="FI15" s="26" t="str">
         <f>[1]CARTELLINO!FL$15</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="FJ15" s="26" t="str">
         <f>[1]CARTELLINO!FM$15</f>
@@ -45233,15 +45233,15 @@
       </c>
       <c r="FT15" s="26" t="str">
         <f>[1]CARTELLINO!FW$15</f>
-        <v>p</v>
+        <v>N</v>
       </c>
       <c r="FU15" s="26" t="str">
         <f>[1]CARTELLINO!FX$15</f>
-        <v>p</v>
+        <v>S</v>
       </c>
       <c r="FV15" s="26" t="str">
         <f>[1]CARTELLINO!FY$15</f>
-        <v>m</v>
+        <v>R</v>
       </c>
       <c r="FW15" s="26" t="str">
         <f>[1]CARTELLINO!FZ$15</f>
@@ -45249,7 +45249,7 @@
       </c>
       <c r="FX15" s="26" t="str">
         <f>[1]CARTELLINO!GA$15</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="FY15" s="26" t="str">
         <f>[1]CARTELLINO!GB$15</f>
@@ -46761,13 +46761,13 @@
         <f>[1]CARTELLINO!FF$16</f>
         <v>0</v>
       </c>
-      <c r="FD16" s="46" t="str">
+      <c r="FD16" s="46">
         <f>[1]CARTELLINO!FG$16</f>
-        <v>f</v>
-      </c>
-      <c r="FE16" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="FE16" s="46">
         <f>[1]CARTELLINO!FH$16</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="FF16" s="46" t="str">
         <f>[1]CARTELLINO!FI$16</f>
@@ -46779,7 +46779,7 @@
       </c>
       <c r="FH16" s="46" t="str">
         <f>[1]CARTELLINO!FK$16</f>
-        <v>f</v>
+        <v>pn</v>
       </c>
       <c r="FI16" s="46">
         <f>[1]CARTELLINO!FL$16</f>
@@ -52353,19 +52353,19 @@
       </c>
       <c r="FB21" s="28" t="str">
         <f>[1]CARTELLINO!FE$21</f>
-        <v>M/R</v>
+        <v>p</v>
       </c>
       <c r="FC21" s="28" t="str">
         <f>[1]CARTELLINO!FF$21</f>
-        <v>N</v>
+        <v>m</v>
       </c>
       <c r="FD21" s="28" t="str">
         <f>[1]CARTELLINO!FG$21</f>
-        <v>S</v>
+        <v>m</v>
       </c>
       <c r="FE21" s="28" t="str">
         <f>[1]CARTELLINO!FH$21</f>
-        <v>R</v>
+        <v>r</v>
       </c>
       <c r="FF21" s="28" t="str">
         <f>[1]CARTELLINO!FI$21</f>
@@ -57817,9 +57817,9 @@
         <f>[1]CARTELLINO!HU$25</f>
         <v>0</v>
       </c>
-      <c r="HS25" s="46" t="str">
+      <c r="HS25" s="46">
         <f>[1]CARTELLINO!HV$25</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="HT25" s="46" t="str">
         <f>[1]CARTELLINO!HW$25</f>
@@ -62582,7 +62582,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="FC29" s="63" t="str">
-        <v>BERARDI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="FD29" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -63682,7 +63682,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="FC30" s="63" t="str">
-        <v>BERARDI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="FD30" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -64779,7 +64779,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="FB31" s="63" t="str">
-        <v>BERARDI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="FC31" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -65879,7 +65879,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="FB32" s="63" t="str">
-        <v>BERARDI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="FC32" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -66529,12 +66529,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71027,6 +71027,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71035,13 +71042,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C2E5108-0C27-41D0-B022-7BE6F972D596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31FACA02-DE6B-499E-8CE8-5E8E62101259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="795" windowWidth="28800" windowHeight="15405" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7417,7 +7417,7 @@
             <v>M</v>
           </cell>
           <cell r="HN3" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="HO3" t="str">
             <v>r</v>
@@ -21517,7 +21517,7 @@
             <v>m</v>
           </cell>
           <cell r="FG21" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="FH21" t="str">
             <v>r</v>
@@ -23897,7 +23897,7 @@
             <v>R</v>
           </cell>
           <cell r="FG24" t="str">
-            <v>m</v>
+            <v>r</v>
           </cell>
           <cell r="FH24" t="str">
             <v>p</v>
@@ -23912,7 +23912,7 @@
             <v>p</v>
           </cell>
           <cell r="FL24" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="FM24" t="str">
             <v>r</v>
@@ -26262,7 +26262,7 @@
             <v>m</v>
           </cell>
           <cell r="FB27" t="str">
-            <v>m</v>
+            <v>r</v>
           </cell>
           <cell r="FC27" t="str">
             <v>p</v>
@@ -26277,7 +26277,7 @@
             <v>p</v>
           </cell>
           <cell r="FG27" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="FH27" t="str">
             <v>M/R</v>
@@ -26454,7 +26454,7 @@
             <v>p</v>
           </cell>
           <cell r="HN27" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="HO27" t="str">
             <v>p</v>
@@ -28517,431 +28517,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28951,7 +28951,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -31022,7 +31022,7 @@
       </c>
       <c r="HK3" s="16" t="str">
         <f>[1]CARTELLINO!HN$3</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="HL3" s="16" t="str">
         <f>[1]CARTELLINO!HO$3</f>
@@ -52361,7 +52361,7 @@
       </c>
       <c r="FD21" s="28" t="str">
         <f>[1]CARTELLINO!FG$21</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="FE21" s="28" t="str">
         <f>[1]CARTELLINO!FH$21</f>
@@ -55957,7 +55957,7 @@
       </c>
       <c r="FD24" s="29" t="str">
         <f>[1]CARTELLINO!FG$24</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="FE24" s="29" t="str">
         <f>[1]CARTELLINO!FH$24</f>
@@ -55977,7 +55977,7 @@
       </c>
       <c r="FI24" s="29" t="str">
         <f>[1]CARTELLINO!FL$24</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="FJ24" s="29" t="str">
         <f>[1]CARTELLINO!FM$24</f>
@@ -59533,7 +59533,7 @@
       </c>
       <c r="EY27" s="30" t="str">
         <f>[1]CARTELLINO!FB$27</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="EZ27" s="30" t="str">
         <f>[1]CARTELLINO!FC$27</f>
@@ -59553,7 +59553,7 @@
       </c>
       <c r="FD27" s="30" t="str">
         <f>[1]CARTELLINO!FG$27</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="FE27" s="30" t="str">
         <f>[1]CARTELLINO!FH$27</f>
@@ -59789,7 +59789,7 @@
       </c>
       <c r="HK27" s="30" t="str">
         <f>[1]CARTELLINO!HN$27</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="HL27" s="30" t="str">
         <f>[1]CARTELLINO!HO$27</f>
@@ -66529,12 +66529,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71027,13 +71027,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71042,6 +71035,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31FACA02-DE6B-499E-8CE8-5E8E62101259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C780F1-3EDB-4345-8F43-95F82A3E3EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="795" windowWidth="28800" windowHeight="15405" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="0" yWindow="75" windowWidth="28800" windowHeight="15405" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -7225,7 +7225,7 @@
             <v>p</v>
           </cell>
           <cell r="FB3" t="str">
-            <v>m</v>
+            <v>M</v>
           </cell>
           <cell r="FC3" t="str">
             <v>m</v>
@@ -7387,10 +7387,10 @@
             <v>R</v>
           </cell>
           <cell r="HD3" t="str">
-            <v>p</v>
+            <v>r</v>
           </cell>
           <cell r="HE3" t="str">
-            <v>m</v>
+            <v>-</v>
           </cell>
           <cell r="HF3" t="str">
             <v>m/R</v>
@@ -7417,16 +7417,16 @@
             <v>M</v>
           </cell>
           <cell r="HN3" t="str">
-            <v>p</v>
+            <v>N</v>
           </cell>
           <cell r="HO3" t="str">
-            <v>r</v>
+            <v>S</v>
           </cell>
           <cell r="HP3" t="str">
-            <v>r</v>
+            <v>R</v>
           </cell>
           <cell r="HQ3" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="HR3" t="str">
             <v>p</v>
@@ -8579,8 +8579,8 @@
           <cell r="HD4">
             <v>0</v>
           </cell>
-          <cell r="HE4">
-            <v>0</v>
+          <cell r="HE4" t="str">
+            <v>nl</v>
           </cell>
           <cell r="HF4">
             <v>0</v>
@@ -14638,7 +14638,7 @@
             <v>-</v>
           </cell>
           <cell r="IP12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="IQ12" t="str">
             <v>-</v>
@@ -14983,13 +14983,13 @@
             <v>-</v>
           </cell>
           <cell r="NA12" t="str">
-            <v>-</v>
+            <v>N</v>
           </cell>
           <cell r="NB12" t="str">
-            <v>-</v>
+            <v>S</v>
           </cell>
           <cell r="NC12" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="ND12" t="str">
             <v>-</v>
@@ -15827,8 +15827,8 @@
           <cell r="IO13">
             <v>0</v>
           </cell>
-          <cell r="IP13" t="str">
-            <v>ng</v>
+          <cell r="IP13">
+            <v>0</v>
           </cell>
           <cell r="IQ13">
             <v>0</v>
@@ -16961,7 +16961,7 @@
             <v>R</v>
           </cell>
           <cell r="HW15" t="str">
-            <v>m</v>
+            <v>-</v>
           </cell>
           <cell r="HX15" t="str">
             <v>P</v>
@@ -16982,7 +16982,7 @@
             <v>m</v>
           </cell>
           <cell r="ID15" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="IE15" t="str">
             <v>r</v>
@@ -17102,7 +17102,7 @@
             <v>P</v>
           </cell>
           <cell r="JR15" t="str">
-            <v>M</v>
+            <v>-</v>
           </cell>
           <cell r="JS15" t="str">
             <v>N</v>
@@ -18150,8 +18150,8 @@
           <cell r="HV16" t="str">
             <v>f</v>
           </cell>
-          <cell r="HW16">
-            <v>0</v>
+          <cell r="HW16" t="str">
+            <v>ng</v>
           </cell>
           <cell r="HX16">
             <v>0</v>
@@ -18291,8 +18291,8 @@
           <cell r="JQ16">
             <v>0</v>
           </cell>
-          <cell r="JR16">
-            <v>0</v>
+          <cell r="JR16" t="str">
+            <v>ng</v>
           </cell>
           <cell r="JS16">
             <v>0</v>
@@ -18496,7 +18496,7 @@
             <v>f</v>
           </cell>
           <cell r="MH16" t="str">
-            <v>f</v>
+            <v>nl</v>
           </cell>
           <cell r="MI16" t="str">
             <v>f</v>
@@ -19434,7 +19434,7 @@
             <v>-</v>
           </cell>
           <cell r="JB18" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JC18" t="str">
             <v>-</v>
@@ -21721,7 +21721,7 @@
             <v>p</v>
           </cell>
           <cell r="HW21" t="str">
-            <v>M</v>
+            <v>m</v>
           </cell>
           <cell r="HX21" t="str">
             <v>r</v>
@@ -21778,7 +21778,7 @@
             <v>-</v>
           </cell>
           <cell r="IP21" t="str">
-            <v>p</v>
+            <v>-</v>
           </cell>
           <cell r="IQ21" t="str">
             <v>-</v>
@@ -22967,8 +22967,8 @@
           <cell r="IO22">
             <v>0</v>
           </cell>
-          <cell r="IP22">
-            <v>0</v>
+          <cell r="IP22" t="str">
+            <v>ng</v>
           </cell>
           <cell r="IQ22">
             <v>0</v>
@@ -24044,10 +24044,10 @@
             <v>M</v>
           </cell>
           <cell r="HD24" t="str">
-            <v>-</v>
+            <v>N</v>
           </cell>
           <cell r="HE24" t="str">
-            <v>-</v>
+            <v>S</v>
           </cell>
           <cell r="HF24" t="str">
             <v>R</v>
@@ -24074,16 +24074,16 @@
             <v>-</v>
           </cell>
           <cell r="HN24" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="HO24" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="HP24" t="str">
             <v>R</v>
           </cell>
           <cell r="HQ24" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="HR24" t="str">
             <v>M</v>
@@ -24101,7 +24101,7 @@
             <v>P</v>
           </cell>
           <cell r="HW24" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="HX24" t="str">
             <v>N</v>
@@ -25233,14 +25233,14 @@
           <cell r="HC25">
             <v>0</v>
           </cell>
-          <cell r="HD25" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="HE25" t="str">
-            <v>nl</v>
-          </cell>
-          <cell r="HF25" t="str">
-            <v>f</v>
+          <cell r="HD25">
+            <v>0</v>
+          </cell>
+          <cell r="HE25">
+            <v>0</v>
+          </cell>
+          <cell r="HF25">
+            <v>0</v>
           </cell>
           <cell r="HG25" t="str">
             <v>f</v>
@@ -25263,17 +25263,17 @@
           <cell r="HM25" t="str">
             <v>f</v>
           </cell>
-          <cell r="HN25">
-            <v>0</v>
-          </cell>
-          <cell r="HO25">
-            <v>0</v>
-          </cell>
-          <cell r="HP25">
-            <v>0</v>
-          </cell>
-          <cell r="HQ25">
-            <v>0</v>
+          <cell r="HN25" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="HO25" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="HP25" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="HQ25" t="str">
+            <v>f</v>
           </cell>
           <cell r="HR25">
             <v>0</v>
@@ -25290,8 +25290,8 @@
           <cell r="HV25">
             <v>0</v>
           </cell>
-          <cell r="HW25" t="str">
-            <v>ng</v>
+          <cell r="HW25">
+            <v>0</v>
           </cell>
           <cell r="HX25">
             <v>0</v>
@@ -26424,13 +26424,13 @@
             <v>m/R</v>
           </cell>
           <cell r="HD27" t="str">
-            <v>N</v>
+            <v>p</v>
           </cell>
           <cell r="HE27" t="str">
-            <v>S</v>
+            <v>m</v>
           </cell>
           <cell r="HF27" t="str">
-            <v>R</v>
+            <v>r</v>
           </cell>
           <cell r="HG27" t="str">
             <v>P</v>
@@ -26826,7 +26826,7 @@
             <v>-</v>
           </cell>
           <cell r="MH27" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="MI27" t="str">
             <v>-</v>
@@ -30766,7 +30766,7 @@
       </c>
       <c r="EY3" s="16" t="str">
         <f>[1]CARTELLINO!FB$3</f>
-        <v>m</v>
+        <v>M</v>
       </c>
       <c r="EZ3" s="16" t="str">
         <f>[1]CARTELLINO!FC$3</f>
@@ -30982,11 +30982,11 @@
       </c>
       <c r="HA3" s="16" t="str">
         <f>[1]CARTELLINO!HD$3</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="HB3" s="16" t="str">
         <f>[1]CARTELLINO!HE$3</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="HC3" s="16" t="str">
         <f>[1]CARTELLINO!HF$3</f>
@@ -31022,19 +31022,19 @@
       </c>
       <c r="HK3" s="16" t="str">
         <f>[1]CARTELLINO!HN$3</f>
-        <v>p</v>
+        <v>N</v>
       </c>
       <c r="HL3" s="16" t="str">
         <f>[1]CARTELLINO!HO$3</f>
-        <v>r</v>
+        <v>S</v>
       </c>
       <c r="HM3" s="16" t="str">
         <f>[1]CARTELLINO!HP$3</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="HN3" s="16" t="str">
         <f>[1]CARTELLINO!HQ$3</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="HO3" s="16" t="str">
         <f>[1]CARTELLINO!HR$3</f>
@@ -32578,9 +32578,9 @@
         <f>[1]CARTELLINO!HD$4</f>
         <v>0</v>
       </c>
-      <c r="HB4" s="43">
+      <c r="HB4" s="43" t="str">
         <f>[1]CARTELLINO!HE$4</f>
-        <v>0</v>
+        <v>nl</v>
       </c>
       <c r="HC4" s="43">
         <f>[1]CARTELLINO!HF$4</f>
@@ -41921,7 +41921,7 @@
       </c>
       <c r="IM12" s="25" t="str">
         <f>[1]CARTELLINO!IP$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="IN12" s="25" t="str">
         <f>[1]CARTELLINO!IQ$12</f>
@@ -42381,15 +42381,15 @@
       </c>
       <c r="MX12" s="25" t="str">
         <f>[1]CARTELLINO!NA$12</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="MY12" s="25" t="str">
         <f>[1]CARTELLINO!NB$12</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="MZ12" s="25" t="str">
         <f>[1]CARTELLINO!NC$12</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="NA12" s="25" t="str">
         <f>[1]CARTELLINO!ND$12</f>
@@ -43513,9 +43513,9 @@
         <f>[1]CARTELLINO!IO$13</f>
         <v>0</v>
       </c>
-      <c r="IM13" s="46" t="str">
+      <c r="IM13" s="46">
         <f>[1]CARTELLINO!IP$13</f>
-        <v>ng</v>
+        <v>0</v>
       </c>
       <c r="IN13" s="46">
         <f>[1]CARTELLINO!IQ$13</f>
@@ -45441,7 +45441,7 @@
       </c>
       <c r="HT15" s="26" t="str">
         <f>[1]CARTELLINO!HW$15</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="HU15" s="26" t="str">
         <f>[1]CARTELLINO!HX$15</f>
@@ -45469,7 +45469,7 @@
       </c>
       <c r="IA15" s="26" t="str">
         <f>[1]CARTELLINO!ID$15</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="IB15" s="26" t="str">
         <f>[1]CARTELLINO!IE$15</f>
@@ -45629,7 +45629,7 @@
       </c>
       <c r="JO15" s="26" t="str">
         <f>[1]CARTELLINO!JR$15</f>
-        <v>M</v>
+        <v>-</v>
       </c>
       <c r="JP15" s="26" t="str">
         <f>[1]CARTELLINO!JS$15</f>
@@ -47033,9 +47033,9 @@
         <f>[1]CARTELLINO!HV$16</f>
         <v>f</v>
       </c>
-      <c r="HT16" s="46">
+      <c r="HT16" s="46" t="str">
         <f>[1]CARTELLINO!HW$16</f>
-        <v>0</v>
+        <v>ng</v>
       </c>
       <c r="HU16" s="46">
         <f>[1]CARTELLINO!HX$16</f>
@@ -47221,9 +47221,9 @@
         <f>[1]CARTELLINO!JQ$16</f>
         <v>0</v>
       </c>
-      <c r="JO16" s="46">
+      <c r="JO16" s="46" t="str">
         <f>[1]CARTELLINO!JR$16</f>
-        <v>0</v>
+        <v>ng</v>
       </c>
       <c r="JP16" s="46">
         <f>[1]CARTELLINO!JS$16</f>
@@ -47495,7 +47495,7 @@
       </c>
       <c r="ME16" s="46" t="str">
         <f>[1]CARTELLINO!MH$16</f>
-        <v>f</v>
+        <v>nl</v>
       </c>
       <c r="MF16" s="46" t="str">
         <f>[1]CARTELLINO!MI$16</f>
@@ -49161,7 +49161,7 @@
       </c>
       <c r="IY18" s="27" t="str">
         <f>[1]CARTELLINO!JB$18</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="IZ18" s="27" t="str">
         <f>[1]CARTELLINO!JC$18</f>
@@ -52633,7 +52633,7 @@
       </c>
       <c r="HT21" s="28" t="str">
         <f>[1]CARTELLINO!HW$21</f>
-        <v>M</v>
+        <v>m</v>
       </c>
       <c r="HU21" s="28" t="str">
         <f>[1]CARTELLINO!HX$21</f>
@@ -52709,7 +52709,7 @@
       </c>
       <c r="IM21" s="28" t="str">
         <f>[1]CARTELLINO!IP$21</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="IN21" s="28" t="str">
         <f>[1]CARTELLINO!IQ$21</f>
@@ -54301,9 +54301,9 @@
         <f>[1]CARTELLINO!IO$22</f>
         <v>0</v>
       </c>
-      <c r="IM22" s="46">
+      <c r="IM22" s="46" t="str">
         <f>[1]CARTELLINO!IP$22</f>
-        <v>0</v>
+        <v>ng</v>
       </c>
       <c r="IN22" s="46">
         <f>[1]CARTELLINO!IQ$22</f>
@@ -56153,11 +56153,11 @@
       </c>
       <c r="HA24" s="29" t="str">
         <f>[1]CARTELLINO!HD$24</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="HB24" s="29" t="str">
         <f>[1]CARTELLINO!HE$24</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="HC24" s="29" t="str">
         <f>[1]CARTELLINO!HF$24</f>
@@ -56193,11 +56193,11 @@
       </c>
       <c r="HK24" s="29" t="str">
         <f>[1]CARTELLINO!HN$24</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="HL24" s="29" t="str">
         <f>[1]CARTELLINO!HO$24</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="HM24" s="29" t="str">
         <f>[1]CARTELLINO!HP$24</f>
@@ -56205,7 +56205,7 @@
       </c>
       <c r="HN24" s="29" t="str">
         <f>[1]CARTELLINO!HQ$24</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="HO24" s="29" t="str">
         <f>[1]CARTELLINO!HR$24</f>
@@ -56229,7 +56229,7 @@
       </c>
       <c r="HT24" s="29" t="str">
         <f>[1]CARTELLINO!HW$24</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="HU24" s="29" t="str">
         <f>[1]CARTELLINO!HX$24</f>
@@ -57745,17 +57745,17 @@
         <f>[1]CARTELLINO!HC$25</f>
         <v>0</v>
       </c>
-      <c r="HA25" s="46" t="str">
+      <c r="HA25" s="46">
         <f>[1]CARTELLINO!HD$25</f>
-        <v>f</v>
-      </c>
-      <c r="HB25" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="HB25" s="46">
         <f>[1]CARTELLINO!HE$25</f>
-        <v>nl</v>
-      </c>
-      <c r="HC25" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="HC25" s="46">
         <f>[1]CARTELLINO!HF$25</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="HD25" s="46" t="str">
         <f>[1]CARTELLINO!HG$25</f>
@@ -57785,21 +57785,21 @@
         <f>[1]CARTELLINO!HM$25</f>
         <v>f</v>
       </c>
-      <c r="HK25" s="46">
+      <c r="HK25" s="46" t="str">
         <f>[1]CARTELLINO!HN$25</f>
-        <v>0</v>
-      </c>
-      <c r="HL25" s="46">
+        <v>f</v>
+      </c>
+      <c r="HL25" s="46" t="str">
         <f>[1]CARTELLINO!HO$25</f>
-        <v>0</v>
-      </c>
-      <c r="HM25" s="46">
+        <v>f</v>
+      </c>
+      <c r="HM25" s="46" t="str">
         <f>[1]CARTELLINO!HP$25</f>
-        <v>0</v>
-      </c>
-      <c r="HN25" s="46">
+        <v>f</v>
+      </c>
+      <c r="HN25" s="46" t="str">
         <f>[1]CARTELLINO!HQ$25</f>
-        <v>0</v>
+        <v>f</v>
       </c>
       <c r="HO25" s="46">
         <f>[1]CARTELLINO!HR$25</f>
@@ -57821,9 +57821,9 @@
         <f>[1]CARTELLINO!HV$25</f>
         <v>0</v>
       </c>
-      <c r="HT25" s="46" t="str">
+      <c r="HT25" s="46">
         <f>[1]CARTELLINO!HW$25</f>
-        <v>ng</v>
+        <v>0</v>
       </c>
       <c r="HU25" s="46">
         <f>[1]CARTELLINO!HX$25</f>
@@ -59749,15 +59749,15 @@
       </c>
       <c r="HA27" s="30" t="str">
         <f>[1]CARTELLINO!HD$27</f>
-        <v>N</v>
+        <v>p</v>
       </c>
       <c r="HB27" s="30" t="str">
         <f>[1]CARTELLINO!HE$27</f>
-        <v>S</v>
+        <v>m</v>
       </c>
       <c r="HC27" s="30" t="str">
         <f>[1]CARTELLINO!HF$27</f>
-        <v>R</v>
+        <v>r</v>
       </c>
       <c r="HD27" s="30" t="str">
         <f>[1]CARTELLINO!HG$27</f>
@@ -60285,7 +60285,7 @@
       </c>
       <c r="ME27" s="30" t="str">
         <f>[1]CARTELLINO!MH$27</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="MF27" s="30" t="str">
         <f>[1]CARTELLINO!MI$27</f>

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C780F1-3EDB-4345-8F43-95F82A3E3EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{799C00DA-41C2-4493-B57F-634A9EEB8302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="75" windowWidth="28800" windowHeight="15405" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="28800" windowHeight="15405" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1644,6 +1644,9 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="8">
+          <cell r="R8" t="str">
+            <v>MAT/R</v>
+          </cell>
           <cell r="AQ8" t="str">
             <v>GHIOTTI</v>
           </cell>
@@ -3860,7 +3863,7 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR166" t="str">
-            <v>PAZZAGLIA</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS166" t="str">
             <v>SARTI</v>
@@ -28517,431 +28520,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28951,7 +28954,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -63685,7 +63688,7 @@
         <v>GHIOTTI</v>
       </c>
       <c r="FD30" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>BERARDI</v>
       </c>
       <c r="FE30" s="63" t="str">
         <v>SARTI</v>
@@ -66529,12 +66532,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71027,6 +71030,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71035,13 +71045,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{799C00DA-41C2-4493-B57F-634A9EEB8302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA05E16B-BEBA-4917-AE75-A2B25FCEF175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="28800" windowHeight="15405" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1644,9 +1644,6 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="8">
-          <cell r="R8" t="str">
-            <v>MAT/R</v>
-          </cell>
           <cell r="AQ8" t="str">
             <v>GHIOTTI</v>
           </cell>
@@ -7267,7 +7264,7 @@
             <v>p</v>
           </cell>
           <cell r="FO3" t="str">
-            <v>m/R</v>
+            <v>M/R</v>
           </cell>
           <cell r="FP3" t="str">
             <v>p</v>
@@ -9965,7 +9962,7 @@
             <v>-</v>
           </cell>
           <cell r="JR6" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="JS6" t="str">
             <v>-</v>
@@ -12258,10 +12255,10 @@
             <v>R</v>
           </cell>
           <cell r="IO9" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="IP9" t="str">
-            <v>M</v>
+            <v>p</v>
           </cell>
           <cell r="IQ9" t="str">
             <v>N</v>
@@ -12288,19 +12285,19 @@
             <v>-</v>
           </cell>
           <cell r="IY9" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="IZ9" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="JA9" t="str">
-            <v>-</v>
+            <v>N</v>
           </cell>
           <cell r="JB9" t="str">
-            <v>-</v>
+            <v>S</v>
           </cell>
           <cell r="JC9" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="JD9" t="str">
             <v>-</v>
@@ -13165,8 +13162,8 @@
           <cell r="EX10" t="str">
             <v>pn</v>
           </cell>
-          <cell r="EY10">
-            <v>0</v>
+          <cell r="EY10" t="str">
+            <v>x</v>
           </cell>
           <cell r="EZ10">
             <v>0</v>
@@ -14641,7 +14638,7 @@
             <v>-</v>
           </cell>
           <cell r="IP12" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="IQ12" t="str">
             <v>-</v>
@@ -16931,13 +16928,13 @@
             <v>m</v>
           </cell>
           <cell r="HL15" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="HM15" t="str">
+            <v>r</v>
+          </cell>
+          <cell r="HN15" t="str">
             <v>p</v>
-          </cell>
-          <cell r="HM15" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="HN15" t="str">
-            <v>r</v>
           </cell>
           <cell r="HO15" t="str">
             <v>m</v>
@@ -17117,7 +17114,7 @@
             <v>R</v>
           </cell>
           <cell r="JV15" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="JW15" t="str">
             <v>-</v>
@@ -17964,8 +17961,8 @@
           <cell r="FK16" t="str">
             <v>pn</v>
           </cell>
-          <cell r="FL16">
-            <v>0</v>
+          <cell r="FL16" t="str">
+            <v>x</v>
           </cell>
           <cell r="FM16">
             <v>0</v>
@@ -19398,10 +19395,10 @@
             <v>-</v>
           </cell>
           <cell r="IO18" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="IP18" t="str">
-            <v>m</v>
+            <v>M</v>
           </cell>
           <cell r="IQ18" t="str">
             <v>-</v>
@@ -19413,19 +19410,19 @@
             <v>-</v>
           </cell>
           <cell r="IT18" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="IU18" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="IV18" t="str">
-            <v>-</v>
+            <v>N</v>
           </cell>
           <cell r="IW18" t="str">
-            <v>-</v>
+            <v>S</v>
           </cell>
           <cell r="IX18" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="IY18" t="str">
             <v>-</v>
@@ -20638,8 +20635,8 @@
           <cell r="JE19" t="str">
             <v>pn</v>
           </cell>
-          <cell r="JF19">
-            <v>0</v>
+          <cell r="JF19" t="str">
+            <v>x</v>
           </cell>
           <cell r="JG19" t="str">
             <v>f</v>
@@ -20758,8 +20755,8 @@
           <cell r="KS19" t="str">
             <v>pn</v>
           </cell>
-          <cell r="KT19">
-            <v>0</v>
+          <cell r="KT19" t="str">
+            <v>x</v>
           </cell>
           <cell r="KU19" t="str">
             <v>f</v>
@@ -20771,7 +20768,7 @@
             <v>f</v>
           </cell>
           <cell r="KX19" t="str">
-            <v>f</v>
+            <v>nl</v>
           </cell>
           <cell r="KY19" t="str">
             <v>f</v>
@@ -24251,10 +24248,10 @@
             <v>-</v>
           </cell>
           <cell r="JT24" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="JU24" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="JV24" t="str">
             <v>-</v>
@@ -25698,8 +25695,8 @@
           <cell r="NA25" t="str">
             <v>pn</v>
           </cell>
-          <cell r="NB25">
-            <v>0</v>
+          <cell r="NB25" t="str">
+            <v>x</v>
           </cell>
           <cell r="NC25">
             <v>0</v>
@@ -26451,10 +26448,10 @@
             <v>p</v>
           </cell>
           <cell r="HL27" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="HM27" t="str">
             <v>m</v>
-          </cell>
-          <cell r="HM27" t="str">
-            <v>p</v>
           </cell>
           <cell r="HN27" t="str">
             <v>m</v>
@@ -26595,25 +26592,25 @@
             <v>-</v>
           </cell>
           <cell r="JH27" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="JI27" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="JJ27" t="str">
-            <v>-</v>
+            <v>N</v>
           </cell>
           <cell r="JK27" t="str">
-            <v>-</v>
+            <v>S</v>
           </cell>
           <cell r="JL27" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="JM27" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="JN27" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="JO27" t="str">
             <v>N</v>
@@ -27757,8 +27754,8 @@
           <cell r="IX28" t="str">
             <v>pn</v>
           </cell>
-          <cell r="IY28">
-            <v>0</v>
+          <cell r="IY28" t="str">
+            <v>x</v>
           </cell>
           <cell r="IZ28">
             <v>0</v>
@@ -27823,8 +27820,8 @@
           <cell r="JT28" t="str">
             <v>pn</v>
           </cell>
-          <cell r="JU28">
-            <v>0</v>
+          <cell r="JU28" t="str">
+            <v>x</v>
           </cell>
           <cell r="JV28">
             <v>0</v>
@@ -28520,431 +28517,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28954,7 +28951,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -30821,7 +30818,7 @@
       </c>
       <c r="FL3" s="16" t="str">
         <f>[1]CARTELLINO!FO$3</f>
-        <v>m/R</v>
+        <v>M/R</v>
       </c>
       <c r="FM3" s="16" t="str">
         <f>[1]CARTELLINO!FP$3</f>
@@ -34844,7 +34841,7 @@
       </c>
       <c r="JO6" s="22" t="str">
         <f>[1]CARTELLINO!JR$6</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="JP6" s="22" t="str">
         <f>[1]CARTELLINO!JS$6</f>
@@ -38324,11 +38321,11 @@
       </c>
       <c r="IL9" s="24" t="str">
         <f>[1]CARTELLINO!IO$9</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="IM9" s="24" t="str">
         <f>[1]CARTELLINO!IP$9</f>
-        <v>M</v>
+        <v>p</v>
       </c>
       <c r="IN9" s="24" t="str">
         <f>[1]CARTELLINO!IQ$9</f>
@@ -38364,23 +38361,23 @@
       </c>
       <c r="IV9" s="24" t="str">
         <f>[1]CARTELLINO!IY$9</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="IW9" s="24" t="str">
         <f>[1]CARTELLINO!IZ$9</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="IX9" s="24" t="str">
         <f>[1]CARTELLINO!JA$9</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="IY9" s="24" t="str">
         <f>[1]CARTELLINO!JB$9</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="IZ9" s="24" t="str">
         <f>[1]CARTELLINO!JC$9</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="JA9" s="24" t="str">
         <f>[1]CARTELLINO!JD$9</f>
@@ -39540,9 +39537,9 @@
         <f>[1]CARTELLINO!EX$10</f>
         <v>pn</v>
       </c>
-      <c r="EV10" s="46">
+      <c r="EV10" s="46" t="str">
         <f>[1]CARTELLINO!EY$10</f>
-        <v>0</v>
+        <v>x</v>
       </c>
       <c r="EW10" s="46">
         <f>[1]CARTELLINO!EZ$10</f>
@@ -41924,7 +41921,7 @@
       </c>
       <c r="IM12" s="25" t="str">
         <f>[1]CARTELLINO!IP$12</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="IN12" s="25" t="str">
         <f>[1]CARTELLINO!IQ$12</f>
@@ -45400,15 +45397,15 @@
       </c>
       <c r="HI15" s="26" t="str">
         <f>[1]CARTELLINO!HL$15</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="HJ15" s="26" t="str">
         <f>[1]CARTELLINO!HM$15</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="HK15" s="26" t="str">
         <f>[1]CARTELLINO!HN$15</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="HL15" s="26" t="str">
         <f>[1]CARTELLINO!HO$15</f>
@@ -45648,7 +45645,7 @@
       </c>
       <c r="JS15" s="26" t="str">
         <f>[1]CARTELLINO!JV$15</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="JT15" s="26" t="str">
         <f>[1]CARTELLINO!JW$15</f>
@@ -46784,9 +46781,9 @@
         <f>[1]CARTELLINO!FK$16</f>
         <v>pn</v>
       </c>
-      <c r="FI16" s="46">
+      <c r="FI16" s="46" t="str">
         <f>[1]CARTELLINO!FL$16</f>
-        <v>0</v>
+        <v>x</v>
       </c>
       <c r="FJ16" s="46">
         <f>[1]CARTELLINO!FM$16</f>
@@ -49112,11 +49109,11 @@
       </c>
       <c r="IL18" s="27" t="str">
         <f>[1]CARTELLINO!IO$18</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="IM18" s="27" t="str">
         <f>[1]CARTELLINO!IP$18</f>
-        <v>m</v>
+        <v>M</v>
       </c>
       <c r="IN18" s="27" t="str">
         <f>[1]CARTELLINO!IQ$18</f>
@@ -49132,23 +49129,23 @@
       </c>
       <c r="IQ18" s="27" t="str">
         <f>[1]CARTELLINO!IT$18</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="IR18" s="27" t="str">
         <f>[1]CARTELLINO!IU$18</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="IS18" s="27" t="str">
         <f>[1]CARTELLINO!IV$18</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="IT18" s="27" t="str">
         <f>[1]CARTELLINO!IW$18</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="IU18" s="27" t="str">
         <f>[1]CARTELLINO!IX$18</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="IV18" s="27" t="str">
         <f>[1]CARTELLINO!IY$18</f>
@@ -50772,9 +50769,9 @@
         <f>[1]CARTELLINO!JE$19</f>
         <v>pn</v>
       </c>
-      <c r="JC19" s="46">
+      <c r="JC19" s="46" t="str">
         <f>[1]CARTELLINO!JF$19</f>
-        <v>0</v>
+        <v>x</v>
       </c>
       <c r="JD19" s="46" t="str">
         <f>[1]CARTELLINO!JG$19</f>
@@ -50932,9 +50929,9 @@
         <f>[1]CARTELLINO!KS$19</f>
         <v>pn</v>
       </c>
-      <c r="KQ19" s="46">
+      <c r="KQ19" s="46" t="str">
         <f>[1]CARTELLINO!KT$19</f>
-        <v>0</v>
+        <v>x</v>
       </c>
       <c r="KR19" s="46" t="str">
         <f>[1]CARTELLINO!KU$19</f>
@@ -50950,7 +50947,7 @@
       </c>
       <c r="KU19" s="46" t="str">
         <f>[1]CARTELLINO!KX$19</f>
-        <v>f</v>
+        <v>nl</v>
       </c>
       <c r="KV19" s="46" t="str">
         <f>[1]CARTELLINO!KY$19</f>
@@ -56428,11 +56425,11 @@
       </c>
       <c r="JQ24" s="29" t="str">
         <f>[1]CARTELLINO!JT$24</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="JR24" s="29" t="str">
         <f>[1]CARTELLINO!JU$24</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="JS24" s="29" t="str">
         <f>[1]CARTELLINO!JV$24</f>
@@ -58364,9 +58361,9 @@
         <f>[1]CARTELLINO!NA$25</f>
         <v>pn</v>
       </c>
-      <c r="MY25" s="46">
+      <c r="MY25" s="46" t="str">
         <f>[1]CARTELLINO!NB$25</f>
-        <v>0</v>
+        <v>x</v>
       </c>
       <c r="MZ25" s="46">
         <f>[1]CARTELLINO!NC$25</f>
@@ -59784,11 +59781,11 @@
       </c>
       <c r="HI27" s="30" t="str">
         <f>[1]CARTELLINO!HL$27</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="HJ27" s="30" t="str">
         <f>[1]CARTELLINO!HM$27</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="HK27" s="30" t="str">
         <f>[1]CARTELLINO!HN$27</f>
@@ -59976,31 +59973,31 @@
       </c>
       <c r="JE27" s="30" t="str">
         <f>[1]CARTELLINO!JH$27</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="JF27" s="30" t="str">
         <f>[1]CARTELLINO!JI$27</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="JG27" s="30" t="str">
         <f>[1]CARTELLINO!JJ$27</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="JH27" s="30" t="str">
         <f>[1]CARTELLINO!JK$27</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="JI27" s="30" t="str">
         <f>[1]CARTELLINO!JL$27</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="JJ27" s="30" t="str">
         <f>[1]CARTELLINO!JM$27</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="JK27" s="30" t="str">
         <f>[1]CARTELLINO!JN$27</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="JL27" s="30" t="str">
         <f>[1]CARTELLINO!JO$27</f>
@@ -61532,9 +61529,9 @@
         <f>[1]CARTELLINO!IX$28</f>
         <v>pn</v>
       </c>
-      <c r="IV28" s="62">
+      <c r="IV28" s="62" t="str">
         <f>[1]CARTELLINO!IY$28</f>
-        <v>0</v>
+        <v>x</v>
       </c>
       <c r="IW28" s="62">
         <f>[1]CARTELLINO!IZ$28</f>
@@ -61620,9 +61617,9 @@
         <f>[1]CARTELLINO!JT$28</f>
         <v>pn</v>
       </c>
-      <c r="JR28" s="62">
+      <c r="JR28" s="62" t="str">
         <f>[1]CARTELLINO!JU$28</f>
-        <v>0</v>
+        <v>x</v>
       </c>
       <c r="JS28" s="62">
         <f>[1]CARTELLINO!JV$28</f>
@@ -66532,12 +66529,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71030,13 +71027,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71045,6 +71035,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA05E16B-BEBA-4917-AE75-A2B25FCEF175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793388EF-081C-4926-86E6-79C1DF999539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3927,7 +3927,7 @@
         </row>
         <row r="171">
           <cell r="AQ171" t="str">
-            <v>FABBRI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR171" t="str">
             <v>FABBRI</v>
@@ -7399,7 +7399,7 @@
             <v>p</v>
           </cell>
           <cell r="HH3" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="HI3" t="str">
             <v>N</v>
@@ -12156,7 +12156,7 @@
             <v>r</v>
           </cell>
           <cell r="HH9" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="HI9" t="str">
             <v>M</v>
@@ -28517,431 +28517,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28951,7 +28951,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -30998,7 +30998,7 @@
       </c>
       <c r="HE3" s="16" t="str">
         <f>[1]CARTELLINO!HH$3</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="HF3" s="16" t="str">
         <f>[1]CARTELLINO!HI$3</f>
@@ -38189,7 +38189,7 @@
       </c>
       <c r="HE9" s="24" t="str">
         <f>[1]CARTELLINO!HH$9</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="HF9" s="24" t="str">
         <f>[1]CARTELLINO!HI$9</f>
@@ -62600,7 +62600,7 @@
         <v>BERARDI</v>
       </c>
       <c r="FI29" s="63" t="str">
-        <v>FABBRI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="FJ29" s="63" t="str">
         <v>SARTI</v>
@@ -66529,12 +66529,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71027,6 +71027,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71035,13 +71042,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793388EF-081C-4926-86E6-79C1DF999539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0BDB220-20B1-44EC-9B71-C2E1B78A5899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="0" yWindow="75" windowWidth="28800" windowHeight="15405" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3933,7 +3933,7 @@
             <v>FABBRI</v>
           </cell>
           <cell r="AS171" t="str">
-            <v>SARTI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT171" t="str">
             <v>SARTI</v>
@@ -4549,18 +4549,18 @@
             <v>FABBRI</v>
           </cell>
           <cell r="AS215" t="str">
-            <v>SARTI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT215" t="str">
-            <v>SARTI</v>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="216">
           <cell r="AQ216" t="str">
-            <v>SARTI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR216" t="str">
-            <v>SARTI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS216" t="str">
             <v>BARBIERI</v>
@@ -4619,438 +4619,438 @@
             <v>FABBRI</v>
           </cell>
           <cell r="AS220" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AT220" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="221">
           <cell r="AQ221" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AR221" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AS221" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT221" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="222">
           <cell r="AQ222" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR222" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS222" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT222" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="223">
           <cell r="AQ223" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR223" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS223" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT223" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="224">
           <cell r="AQ224" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR224" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS224" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT224" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="225">
           <cell r="AQ225" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR225" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS225" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT225" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="226">
           <cell r="AQ226" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR226" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS226" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT226" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="227">
           <cell r="AQ227" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR227" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS227" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT227" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="228">
           <cell r="AQ228" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR228" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS228" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AT228" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="229">
           <cell r="AQ229" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AR229" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AS229" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT229" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="230">
           <cell r="AQ230" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR230" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS230" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT230" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="231">
           <cell r="AQ231" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR231" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS231" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT231" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="232">
           <cell r="AQ232" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR232" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS232" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT232" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="233">
           <cell r="AQ233" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR233" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS233" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT233" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="234">
           <cell r="AQ234" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR234" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS234" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT234" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="235">
           <cell r="AQ235" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR235" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS235" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT235" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="236">
           <cell r="AQ236" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR236" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS236" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT236" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="237">
           <cell r="AQ237" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR237" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS237" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT237" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="238">
           <cell r="AQ238" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR238" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS238" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT238" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="239">
           <cell r="AQ239" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR239" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS239" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT239" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="240">
           <cell r="AQ240" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR240" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS240" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT240" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="241">
           <cell r="AQ241" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR241" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS241" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT241" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="242">
           <cell r="AQ242" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR242" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS242" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT242" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="243">
           <cell r="AQ243" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR243" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS243" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AT243" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="244">
           <cell r="AQ244" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AR244" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AS244" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT244" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="245">
           <cell r="AQ245" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR245" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS245" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT245" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="246">
           <cell r="AQ246" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR246" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS246" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT246" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="247">
           <cell r="AQ247" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR247" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS247" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT247" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="248">
           <cell r="AQ248" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR248" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS248" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AT248" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="249">
           <cell r="AQ249" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AR249" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AS249" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT249" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="250">
           <cell r="AQ250" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR250" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS250" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT250" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="251">
           <cell r="AQ251" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR251" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS251" t="str">
             <v/>
@@ -7414,7 +7414,7 @@
             <v>P</v>
           </cell>
           <cell r="HM3" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="HN3" t="str">
             <v>N</v>
@@ -7441,7 +7441,7 @@
             <v>p</v>
           </cell>
           <cell r="HV3" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="HW3" t="str">
             <v>-</v>
@@ -7489,7 +7489,7 @@
             <v>P</v>
           </cell>
           <cell r="IL3" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="IM3" t="str">
             <v>N</v>
@@ -9776,25 +9776,25 @@
             <v>m</v>
           </cell>
           <cell r="HH6" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="HI6" t="str">
             <v>r</v>
           </cell>
           <cell r="HJ6" t="str">
-            <v>N</v>
+            <v>r</v>
           </cell>
           <cell r="HK6" t="str">
-            <v>S</v>
+            <v>P</v>
           </cell>
           <cell r="HL6" t="str">
-            <v>R</v>
+            <v>M</v>
           </cell>
           <cell r="HM6" t="str">
             <v>P</v>
           </cell>
           <cell r="HN6" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="HO6" t="str">
             <v>N</v>
@@ -9830,7 +9830,7 @@
             <v>P</v>
           </cell>
           <cell r="HZ6" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="IA6" t="str">
             <v>N</v>
@@ -9845,7 +9845,7 @@
             <v>r</v>
           </cell>
           <cell r="IE6" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="IF6" t="str">
             <v>N</v>
@@ -12024,7 +12024,7 @@
             <v>R</v>
           </cell>
           <cell r="FP9" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="FQ9" t="str">
             <v>M+N</v>
@@ -12144,7 +12144,7 @@
             <v>r</v>
           </cell>
           <cell r="HD9" t="str">
-            <v>m/R</v>
+            <v>m</v>
           </cell>
           <cell r="HE9" t="str">
             <v>p</v>
@@ -12156,19 +12156,19 @@
             <v>r</v>
           </cell>
           <cell r="HH9" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="HI9" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="HJ9" t="str">
-            <v>r</v>
+            <v>N</v>
           </cell>
           <cell r="HK9" t="str">
-            <v>P</v>
+            <v>S</v>
           </cell>
           <cell r="HL9" t="str">
-            <v>M</v>
+            <v>R</v>
           </cell>
           <cell r="HM9" t="str">
             <v>N</v>
@@ -12183,7 +12183,7 @@
             <v>P</v>
           </cell>
           <cell r="HQ9" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="HR9" t="str">
             <v>N</v>
@@ -12228,7 +12228,7 @@
             <v>-</v>
           </cell>
           <cell r="IF9" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="IG9" t="str">
             <v>N</v>
@@ -12243,7 +12243,7 @@
             <v>P</v>
           </cell>
           <cell r="IK9" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="IL9" t="str">
             <v>N</v>
@@ -14545,7 +14545,7 @@
             <v>P</v>
           </cell>
           <cell r="HK12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="HL12" t="str">
             <v>N</v>
@@ -14560,7 +14560,7 @@
             <v>P</v>
           </cell>
           <cell r="HP12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="HQ12" t="str">
             <v>N</v>
@@ -14596,7 +14596,7 @@
             <v>p</v>
           </cell>
           <cell r="IB12" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="IC12" t="str">
             <v>p</v>
@@ -14629,10 +14629,10 @@
             <v>-</v>
           </cell>
           <cell r="IM12" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="IN12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="IO12" t="str">
             <v>-</v>
@@ -16928,10 +16928,10 @@
             <v>m</v>
           </cell>
           <cell r="HL15" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="HM15" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="HN15" t="str">
             <v>p</v>
@@ -16979,10 +16979,10 @@
             <v>p</v>
           </cell>
           <cell r="IC15" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="ID15" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="IE15" t="str">
             <v>r</v>
@@ -16994,10 +16994,10 @@
             <v>p</v>
           </cell>
           <cell r="IH15" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="II15" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="IJ15" t="str">
             <v>p</v>
@@ -19302,7 +19302,7 @@
             <v>P</v>
           </cell>
           <cell r="HJ18" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="HK18" t="str">
             <v>N</v>
@@ -19317,7 +19317,7 @@
             <v>P</v>
           </cell>
           <cell r="HO18" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="HP18" t="str">
             <v>N</v>
@@ -19332,7 +19332,7 @@
             <v>P</v>
           </cell>
           <cell r="HT18" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="HU18" t="str">
             <v>N</v>
@@ -19347,7 +19347,7 @@
             <v>-</v>
           </cell>
           <cell r="HY18" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="HZ18" t="str">
             <v>N</v>
@@ -19362,7 +19362,7 @@
             <v>P</v>
           </cell>
           <cell r="ID18" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="IE18" t="str">
             <v>N</v>
@@ -21664,7 +21664,7 @@
             <v>P</v>
           </cell>
           <cell r="HD21" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="HE21" t="str">
             <v>N</v>
@@ -21715,7 +21715,7 @@
             <v>p</v>
           </cell>
           <cell r="HU21" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="HV21" t="str">
             <v>p</v>
@@ -21733,7 +21733,7 @@
             <v>P</v>
           </cell>
           <cell r="IA21" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="IB21" t="str">
             <v>N</v>
@@ -21760,7 +21760,7 @@
             <v>P</v>
           </cell>
           <cell r="IJ21" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="IK21" t="str">
             <v>N</v>
@@ -23924,7 +23924,7 @@
             <v>p</v>
           </cell>
           <cell r="FP24" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="FQ24" t="str">
             <v>P</v>
@@ -24086,7 +24086,7 @@
             <v>-</v>
           </cell>
           <cell r="HR24" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="HS24" t="str">
             <v>N</v>
@@ -24101,7 +24101,7 @@
             <v>P</v>
           </cell>
           <cell r="HW24" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="HX24" t="str">
             <v>N</v>
@@ -24131,10 +24131,10 @@
             <v>p</v>
           </cell>
           <cell r="IG24" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="IH24" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="II24" t="str">
             <v>p</v>
@@ -26469,7 +26469,7 @@
             <v>P</v>
           </cell>
           <cell r="HS27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="HT27" t="str">
             <v>N</v>
@@ -26484,7 +26484,7 @@
             <v>P</v>
           </cell>
           <cell r="HX27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="HY27" t="str">
             <v>N</v>
@@ -26514,7 +26514,7 @@
             <v>P</v>
           </cell>
           <cell r="IH27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="II27" t="str">
             <v>N</v>
@@ -28517,431 +28517,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28951,7 +28951,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -31018,7 +31018,7 @@
       </c>
       <c r="HJ3" s="16" t="str">
         <f>[1]CARTELLINO!HM$3</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="HK3" s="16" t="str">
         <f>[1]CARTELLINO!HN$3</f>
@@ -31054,7 +31054,7 @@
       </c>
       <c r="HS3" s="16" t="str">
         <f>[1]CARTELLINO!HV$3</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="HT3" s="16" t="str">
         <f>[1]CARTELLINO!HW$3</f>
@@ -31118,7 +31118,7 @@
       </c>
       <c r="II3" s="16" t="str">
         <f>[1]CARTELLINO!IL$3</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="IJ3" s="16" t="str">
         <f>[1]CARTELLINO!IM$3</f>
@@ -34593,7 +34593,7 @@
       </c>
       <c r="HE6" s="22" t="str">
         <f>[1]CARTELLINO!HH$6</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="HF6" s="22" t="str">
         <f>[1]CARTELLINO!HI$6</f>
@@ -34601,15 +34601,15 @@
       </c>
       <c r="HG6" s="22" t="str">
         <f>[1]CARTELLINO!HJ$6</f>
-        <v>N</v>
+        <v>r</v>
       </c>
       <c r="HH6" s="22" t="str">
         <f>[1]CARTELLINO!HK$6</f>
-        <v>S</v>
+        <v>P</v>
       </c>
       <c r="HI6" s="22" t="str">
         <f>[1]CARTELLINO!HL$6</f>
-        <v>R</v>
+        <v>M</v>
       </c>
       <c r="HJ6" s="22" t="str">
         <f>[1]CARTELLINO!HM$6</f>
@@ -34617,7 +34617,7 @@
       </c>
       <c r="HK6" s="22" t="str">
         <f>[1]CARTELLINO!HN$6</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="HL6" s="22" t="str">
         <f>[1]CARTELLINO!HO$6</f>
@@ -34665,7 +34665,7 @@
       </c>
       <c r="HW6" s="22" t="str">
         <f>[1]CARTELLINO!HZ$6</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="HX6" s="22" t="str">
         <f>[1]CARTELLINO!IA$6</f>
@@ -34685,7 +34685,7 @@
       </c>
       <c r="IB6" s="22" t="str">
         <f>[1]CARTELLINO!IE$6</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="IC6" s="22" t="str">
         <f>[1]CARTELLINO!IF$6</f>
@@ -38013,7 +38013,7 @@
       </c>
       <c r="FM9" s="24" t="str">
         <f>[1]CARTELLINO!FP$9</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="FN9" s="24" t="str">
         <f>[1]CARTELLINO!FQ$9</f>
@@ -38173,7 +38173,7 @@
       </c>
       <c r="HA9" s="24" t="str">
         <f>[1]CARTELLINO!HD$9</f>
-        <v>m/R</v>
+        <v>m</v>
       </c>
       <c r="HB9" s="24" t="str">
         <f>[1]CARTELLINO!HE$9</f>
@@ -38189,23 +38189,23 @@
       </c>
       <c r="HE9" s="24" t="str">
         <f>[1]CARTELLINO!HH$9</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="HF9" s="24" t="str">
         <f>[1]CARTELLINO!HI$9</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="HG9" s="24" t="str">
         <f>[1]CARTELLINO!HJ$9</f>
-        <v>r</v>
+        <v>N</v>
       </c>
       <c r="HH9" s="24" t="str">
         <f>[1]CARTELLINO!HK$9</f>
-        <v>P</v>
+        <v>S</v>
       </c>
       <c r="HI9" s="24" t="str">
         <f>[1]CARTELLINO!HL$9</f>
-        <v>M</v>
+        <v>R</v>
       </c>
       <c r="HJ9" s="24" t="str">
         <f>[1]CARTELLINO!HM$9</f>
@@ -38225,7 +38225,7 @@
       </c>
       <c r="HN9" s="24" t="str">
         <f>[1]CARTELLINO!HQ$9</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="HO9" s="24" t="str">
         <f>[1]CARTELLINO!HR$9</f>
@@ -38285,7 +38285,7 @@
       </c>
       <c r="IC9" s="24" t="str">
         <f>[1]CARTELLINO!IF$9</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="ID9" s="24" t="str">
         <f>[1]CARTELLINO!IG$9</f>
@@ -38305,7 +38305,7 @@
       </c>
       <c r="IH9" s="24" t="str">
         <f>[1]CARTELLINO!IK$9</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="II9" s="24" t="str">
         <f>[1]CARTELLINO!IL$9</f>
@@ -41797,7 +41797,7 @@
       </c>
       <c r="HH12" s="25" t="str">
         <f>[1]CARTELLINO!HK$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="HI12" s="25" t="str">
         <f>[1]CARTELLINO!HL$12</f>
@@ -41817,7 +41817,7 @@
       </c>
       <c r="HM12" s="25" t="str">
         <f>[1]CARTELLINO!HP$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="HN12" s="25" t="str">
         <f>[1]CARTELLINO!HQ$12</f>
@@ -41865,7 +41865,7 @@
       </c>
       <c r="HY12" s="25" t="str">
         <f>[1]CARTELLINO!IB$12</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="HZ12" s="25" t="str">
         <f>[1]CARTELLINO!IC$12</f>
@@ -41909,11 +41909,11 @@
       </c>
       <c r="IJ12" s="25" t="str">
         <f>[1]CARTELLINO!IM$12</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="IK12" s="25" t="str">
         <f>[1]CARTELLINO!IN$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="IL12" s="25" t="str">
         <f>[1]CARTELLINO!IO$12</f>
@@ -45397,11 +45397,11 @@
       </c>
       <c r="HI15" s="26" t="str">
         <f>[1]CARTELLINO!HL$15</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="HJ15" s="26" t="str">
         <f>[1]CARTELLINO!HM$15</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="HK15" s="26" t="str">
         <f>[1]CARTELLINO!HN$15</f>
@@ -45465,11 +45465,11 @@
       </c>
       <c r="HZ15" s="26" t="str">
         <f>[1]CARTELLINO!IC$15</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="IA15" s="26" t="str">
         <f>[1]CARTELLINO!ID$15</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="IB15" s="26" t="str">
         <f>[1]CARTELLINO!IE$15</f>
@@ -45485,11 +45485,11 @@
       </c>
       <c r="IE15" s="26" t="str">
         <f>[1]CARTELLINO!IH$15</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="IF15" s="26" t="str">
         <f>[1]CARTELLINO!II$15</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="IG15" s="26" t="str">
         <f>[1]CARTELLINO!IJ$15</f>
@@ -48985,7 +48985,7 @@
       </c>
       <c r="HG18" s="27" t="str">
         <f>[1]CARTELLINO!HJ$18</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="HH18" s="27" t="str">
         <f>[1]CARTELLINO!HK$18</f>
@@ -49005,7 +49005,7 @@
       </c>
       <c r="HL18" s="27" t="str">
         <f>[1]CARTELLINO!HO$18</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="HM18" s="27" t="str">
         <f>[1]CARTELLINO!HP$18</f>
@@ -49025,7 +49025,7 @@
       </c>
       <c r="HQ18" s="27" t="str">
         <f>[1]CARTELLINO!HT$18</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="HR18" s="27" t="str">
         <f>[1]CARTELLINO!HU$18</f>
@@ -49045,7 +49045,7 @@
       </c>
       <c r="HV18" s="27" t="str">
         <f>[1]CARTELLINO!HY$18</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="HW18" s="27" t="str">
         <f>[1]CARTELLINO!HZ$18</f>
@@ -49065,7 +49065,7 @@
       </c>
       <c r="IA18" s="27" t="str">
         <f>[1]CARTELLINO!ID$18</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="IB18" s="27" t="str">
         <f>[1]CARTELLINO!IE$18</f>
@@ -52557,7 +52557,7 @@
       </c>
       <c r="HA21" s="28" t="str">
         <f>[1]CARTELLINO!HD$21</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="HB21" s="28" t="str">
         <f>[1]CARTELLINO!HE$21</f>
@@ -52625,7 +52625,7 @@
       </c>
       <c r="HR21" s="28" t="str">
         <f>[1]CARTELLINO!HU$21</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="HS21" s="28" t="str">
         <f>[1]CARTELLINO!HV$21</f>
@@ -52649,7 +52649,7 @@
       </c>
       <c r="HX21" s="28" t="str">
         <f>[1]CARTELLINO!IA$21</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="HY21" s="28" t="str">
         <f>[1]CARTELLINO!IB$21</f>
@@ -52685,7 +52685,7 @@
       </c>
       <c r="IG21" s="28" t="str">
         <f>[1]CARTELLINO!IJ$21</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="IH21" s="28" t="str">
         <f>[1]CARTELLINO!IK$21</f>
@@ -55993,7 +55993,7 @@
       </c>
       <c r="FM24" s="29" t="str">
         <f>[1]CARTELLINO!FP$24</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="FN24" s="29" t="str">
         <f>[1]CARTELLINO!FQ$24</f>
@@ -56209,7 +56209,7 @@
       </c>
       <c r="HO24" s="29" t="str">
         <f>[1]CARTELLINO!HR$24</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="HP24" s="29" t="str">
         <f>[1]CARTELLINO!HS$24</f>
@@ -56229,7 +56229,7 @@
       </c>
       <c r="HT24" s="29" t="str">
         <f>[1]CARTELLINO!HW$24</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="HU24" s="29" t="str">
         <f>[1]CARTELLINO!HX$24</f>
@@ -56269,11 +56269,11 @@
       </c>
       <c r="ID24" s="29" t="str">
         <f>[1]CARTELLINO!IG$24</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="IE24" s="29" t="str">
         <f>[1]CARTELLINO!IH$24</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="IF24" s="29" t="str">
         <f>[1]CARTELLINO!II$24</f>
@@ -59809,7 +59809,7 @@
       </c>
       <c r="HP27" s="30" t="str">
         <f>[1]CARTELLINO!HS$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="HQ27" s="30" t="str">
         <f>[1]CARTELLINO!HT$27</f>
@@ -59829,7 +59829,7 @@
       </c>
       <c r="HU27" s="30" t="str">
         <f>[1]CARTELLINO!HX$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="HV27" s="30" t="str">
         <f>[1]CARTELLINO!HY$27</f>
@@ -59869,7 +59869,7 @@
       </c>
       <c r="IE27" s="30" t="str">
         <f>[1]CARTELLINO!IH$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="IF27" s="30" t="str">
         <f>[1]CARTELLINO!II$27</f>
@@ -62735,7 +62735,7 @@
         <v>FABBRI</v>
       </c>
       <c r="HB29" s="63" t="str">
-        <v>SARTI</v>
+        <v>BERARDI</v>
       </c>
       <c r="HC29" s="63" t="str">
         <v>BARBIERI</v>
@@ -62750,97 +62750,97 @@
         <v>FABBRI</v>
       </c>
       <c r="HG29" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="HH29" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="HI29" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="HJ29" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="HK29" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="HL29" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="HM29" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="HN29" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="HO29" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="HP29" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="HQ29" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="HR29" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="HS29" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="HT29" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="HU29" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="HV29" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="HW29" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="HX29" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="HY29" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="HZ29" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="IA29" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="IB29" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="IC29" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="ID29" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="IE29" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="IF29" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="IG29" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="IH29" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="II29" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="IJ29" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IK29" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="IL29" s="63" t="str">
         <v/>
@@ -63835,7 +63835,7 @@
         <v>FABBRI</v>
       </c>
       <c r="HB30" s="63" t="str">
-        <v>SARTI</v>
+        <v>BERARDI</v>
       </c>
       <c r="HC30" s="63" t="str">
         <v>BARBIERI</v>
@@ -63850,97 +63850,97 @@
         <v>FABBRI</v>
       </c>
       <c r="HG30" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="HH30" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="HI30" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="HJ30" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="HK30" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="HL30" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="HM30" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="HN30" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="HO30" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="HP30" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="HQ30" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="HR30" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="HS30" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="HT30" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="HU30" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="HV30" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="HW30" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="HX30" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="HY30" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="HZ30" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="IA30" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="IB30" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="IC30" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="ID30" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="IE30" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="IF30" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="IG30" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="IH30" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="II30" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="IJ30" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IK30" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="IL30" s="63" t="str">
         <v/>
@@ -64800,7 +64800,7 @@
         <v>PAZZAGLIA</v>
       </c>
       <c r="FI31" s="63" t="str">
-        <v>SARTI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="FJ31" s="63" t="str">
         <v>BARBIERI</v>
@@ -64932,7 +64932,7 @@
         <v>FABBRI</v>
       </c>
       <c r="HA31" s="63" t="str">
-        <v>SARTI</v>
+        <v>BERARDI</v>
       </c>
       <c r="HB31" s="63" t="str">
         <v>BARBIERI</v>
@@ -64947,97 +64947,97 @@
         <v>FABBRI</v>
       </c>
       <c r="HF31" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="HG31" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="HH31" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="HI31" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="HJ31" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="HK31" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="HL31" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="HM31" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="HN31" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="HO31" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="HP31" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="HQ31" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="HR31" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="HS31" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="HT31" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="HU31" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="HV31" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="HW31" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="HX31" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="HY31" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="HZ31" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="IA31" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="IB31" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="IC31" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="ID31" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="IE31" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="IF31" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="IG31" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="IH31" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="II31" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IJ31" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="IK31" s="63" t="str">
         <v/>
@@ -66032,7 +66032,7 @@
         <v>FABBRI</v>
       </c>
       <c r="HA32" s="63" t="str">
-        <v>SARTI</v>
+        <v>BERARDI</v>
       </c>
       <c r="HB32" s="63" t="str">
         <v>BARBIERI</v>
@@ -66047,97 +66047,97 @@
         <v>FABBRI</v>
       </c>
       <c r="HF32" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="HG32" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="HH32" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="HI32" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="HJ32" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="HK32" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="HL32" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="HM32" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="HN32" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="HO32" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="HP32" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="HQ32" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="HR32" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="HS32" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="HT32" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="HU32" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="HV32" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="HW32" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="HX32" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="HY32" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="HZ32" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="IA32" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="IB32" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="IC32" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="ID32" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="IE32" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="IF32" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="IG32" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="IH32" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="II32" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IJ32" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="IK32" s="63" t="str">
         <v/>
@@ -66529,12 +66529,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71027,13 +71027,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71042,6 +71035,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0BDB220-20B1-44EC-9B71-C2E1B78A5899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3435D7F5-9BFA-430A-B2A6-676A38958CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="75" windowWidth="28800" windowHeight="15405" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7789,7 +7789,7 @@
             <v>-</v>
           </cell>
           <cell r="MH3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="MI3" t="str">
             <v>-</v>
@@ -8774,8 +8774,8 @@
           <cell r="JQ4">
             <v>0</v>
           </cell>
-          <cell r="JR4">
-            <v>0</v>
+          <cell r="JR4" t="str">
+            <v>ng</v>
           </cell>
           <cell r="JS4">
             <v>0</v>
@@ -9962,7 +9962,7 @@
             <v>-</v>
           </cell>
           <cell r="JR6" t="str">
-            <v>M</v>
+            <v>p</v>
           </cell>
           <cell r="JS6" t="str">
             <v>-</v>
@@ -10217,10 +10217,10 @@
             <v>-</v>
           </cell>
           <cell r="MY6" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="MZ6" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NA6" t="str">
             <v>-</v>
@@ -14638,7 +14638,7 @@
             <v>-</v>
           </cell>
           <cell r="IP12" t="str">
-            <v>m</v>
+            <v>-</v>
           </cell>
           <cell r="IQ12" t="str">
             <v>-</v>
@@ -14818,7 +14818,7 @@
             <v>-</v>
           </cell>
           <cell r="KX12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KY12" t="str">
             <v>-</v>
@@ -14977,10 +14977,10 @@
             <v>-</v>
           </cell>
           <cell r="MY12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="MZ12" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NA12" t="str">
             <v>N</v>
@@ -15827,8 +15827,8 @@
           <cell r="IO13">
             <v>0</v>
           </cell>
-          <cell r="IP13">
-            <v>0</v>
+          <cell r="IP13" t="str">
+            <v>ng</v>
           </cell>
           <cell r="IQ13">
             <v>0</v>
@@ -17009,19 +17009,19 @@
             <v>r</v>
           </cell>
           <cell r="IM15" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="IN15" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="IO15" t="str">
             <v>P</v>
           </cell>
-          <cell r="IN15" t="str">
+          <cell r="IP15" t="str">
             <v>M</v>
           </cell>
-          <cell r="IO15" t="str">
-            <v>N</v>
-          </cell>
-          <cell r="IP15" t="str">
-            <v>S</v>
-          </cell>
           <cell r="IQ15" t="str">
-            <v>R</v>
+            <v>-</v>
           </cell>
           <cell r="IR15" t="str">
             <v>P</v>
@@ -17102,7 +17102,7 @@
             <v>P</v>
           </cell>
           <cell r="JR15" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="JS15" t="str">
             <v>N</v>
@@ -18291,8 +18291,8 @@
           <cell r="JQ16">
             <v>0</v>
           </cell>
-          <cell r="JR16" t="str">
-            <v>ng</v>
+          <cell r="JR16">
+            <v>0</v>
           </cell>
           <cell r="JS16">
             <v>0</v>
@@ -19389,19 +19389,19 @@
             <v>R</v>
           </cell>
           <cell r="IM18" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="IN18" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="IO18" t="str">
-            <v>P</v>
+            <v>N</v>
           </cell>
           <cell r="IP18" t="str">
-            <v>M</v>
+            <v>S</v>
           </cell>
           <cell r="IQ18" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="IR18" t="str">
             <v>-</v>
@@ -21778,7 +21778,7 @@
             <v>-</v>
           </cell>
           <cell r="IP21" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="IQ21" t="str">
             <v>-</v>
@@ -21958,7 +21958,7 @@
             <v>-</v>
           </cell>
           <cell r="KX21" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KY21" t="str">
             <v>-</v>
@@ -22967,8 +22967,8 @@
           <cell r="IO22">
             <v>0</v>
           </cell>
-          <cell r="IP22" t="str">
-            <v>ng</v>
+          <cell r="IP22">
+            <v>0</v>
           </cell>
           <cell r="IQ22">
             <v>0</v>
@@ -24242,7 +24242,7 @@
             <v>-</v>
           </cell>
           <cell r="JR24" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="JS24" t="str">
             <v>-</v>
@@ -28517,431 +28517,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28951,7 +28951,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -31518,7 +31518,7 @@
       </c>
       <c r="ME3" s="16" t="str">
         <f>[1]CARTELLINO!MH$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="MF3" s="16" t="str">
         <f>[1]CARTELLINO!MI$3</f>
@@ -32838,9 +32838,9 @@
         <f>[1]CARTELLINO!JQ$4</f>
         <v>0</v>
       </c>
-      <c r="JO4" s="43">
+      <c r="JO4" s="43" t="str">
         <f>[1]CARTELLINO!JR$4</f>
-        <v>0</v>
+        <v>ng</v>
       </c>
       <c r="JP4" s="43">
         <f>[1]CARTELLINO!JS$4</f>
@@ -34841,7 +34841,7 @@
       </c>
       <c r="JO6" s="22" t="str">
         <f>[1]CARTELLINO!JR$6</f>
-        <v>M</v>
+        <v>p</v>
       </c>
       <c r="JP6" s="22" t="str">
         <f>[1]CARTELLINO!JS$6</f>
@@ -35181,11 +35181,11 @@
       </c>
       <c r="MV6" s="22" t="str">
         <f>[1]CARTELLINO!MY$6</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="MW6" s="22" t="str">
         <f>[1]CARTELLINO!MZ$6</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="MX6" s="22" t="str">
         <f>[1]CARTELLINO!NA$6</f>
@@ -41921,7 +41921,7 @@
       </c>
       <c r="IM12" s="25" t="str">
         <f>[1]CARTELLINO!IP$12</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="IN12" s="25" t="str">
         <f>[1]CARTELLINO!IQ$12</f>
@@ -42161,7 +42161,7 @@
       </c>
       <c r="KU12" s="25" t="str">
         <f>[1]CARTELLINO!KX$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KV12" s="25" t="str">
         <f>[1]CARTELLINO!KY$12</f>
@@ -42373,11 +42373,11 @@
       </c>
       <c r="MV12" s="25" t="str">
         <f>[1]CARTELLINO!MY$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="MW12" s="25" t="str">
         <f>[1]CARTELLINO!MZ$12</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="MX12" s="25" t="str">
         <f>[1]CARTELLINO!NA$12</f>
@@ -43513,9 +43513,9 @@
         <f>[1]CARTELLINO!IO$13</f>
         <v>0</v>
       </c>
-      <c r="IM13" s="46">
+      <c r="IM13" s="46" t="str">
         <f>[1]CARTELLINO!IP$13</f>
-        <v>0</v>
+        <v>ng</v>
       </c>
       <c r="IN13" s="46">
         <f>[1]CARTELLINO!IQ$13</f>
@@ -45505,23 +45505,23 @@
       </c>
       <c r="IJ15" s="26" t="str">
         <f>[1]CARTELLINO!IM$15</f>
-        <v>P</v>
+        <v>p</v>
       </c>
       <c r="IK15" s="26" t="str">
         <f>[1]CARTELLINO!IN$15</f>
-        <v>M</v>
+        <v>-</v>
       </c>
       <c r="IL15" s="26" t="str">
         <f>[1]CARTELLINO!IO$15</f>
-        <v>N</v>
+        <v>P</v>
       </c>
       <c r="IM15" s="26" t="str">
         <f>[1]CARTELLINO!IP$15</f>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="IN15" s="26" t="str">
         <f>[1]CARTELLINO!IQ$15</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="IO15" s="26" t="str">
         <f>[1]CARTELLINO!IR$15</f>
@@ -45629,7 +45629,7 @@
       </c>
       <c r="JO15" s="26" t="str">
         <f>[1]CARTELLINO!JR$15</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="JP15" s="26" t="str">
         <f>[1]CARTELLINO!JS$15</f>
@@ -47221,9 +47221,9 @@
         <f>[1]CARTELLINO!JQ$16</f>
         <v>0</v>
       </c>
-      <c r="JO16" s="46" t="str">
+      <c r="JO16" s="46">
         <f>[1]CARTELLINO!JR$16</f>
-        <v>ng</v>
+        <v>0</v>
       </c>
       <c r="JP16" s="46">
         <f>[1]CARTELLINO!JS$16</f>
@@ -49101,23 +49101,23 @@
       </c>
       <c r="IJ18" s="27" t="str">
         <f>[1]CARTELLINO!IM$18</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="IK18" s="27" t="str">
         <f>[1]CARTELLINO!IN$18</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="IL18" s="27" t="str">
         <f>[1]CARTELLINO!IO$18</f>
-        <v>P</v>
+        <v>N</v>
       </c>
       <c r="IM18" s="27" t="str">
         <f>[1]CARTELLINO!IP$18</f>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="IN18" s="27" t="str">
         <f>[1]CARTELLINO!IQ$18</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="IO18" s="27" t="str">
         <f>[1]CARTELLINO!IR$18</f>
@@ -52709,7 +52709,7 @@
       </c>
       <c r="IM21" s="28" t="str">
         <f>[1]CARTELLINO!IP$21</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="IN21" s="28" t="str">
         <f>[1]CARTELLINO!IQ$21</f>
@@ -52949,7 +52949,7 @@
       </c>
       <c r="KU21" s="28" t="str">
         <f>[1]CARTELLINO!KX$21</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KV21" s="28" t="str">
         <f>[1]CARTELLINO!KY$21</f>
@@ -54301,9 +54301,9 @@
         <f>[1]CARTELLINO!IO$22</f>
         <v>0</v>
       </c>
-      <c r="IM22" s="46" t="str">
+      <c r="IM22" s="46">
         <f>[1]CARTELLINO!IP$22</f>
-        <v>ng</v>
+        <v>0</v>
       </c>
       <c r="IN22" s="46">
         <f>[1]CARTELLINO!IQ$22</f>
@@ -56417,7 +56417,7 @@
       </c>
       <c r="JO24" s="29" t="str">
         <f>[1]CARTELLINO!JR$24</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="JP24" s="29" t="str">
         <f>[1]CARTELLINO!JS$24</f>
@@ -66529,12 +66529,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71027,6 +71027,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71035,13 +71042,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3435D7F5-9BFA-430A-B2A6-676A38958CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527E6B6D-B68D-43A2-974D-7F3A12DF1B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="75" windowWidth="28800" windowHeight="15405" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1627,6 +1627,7 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="TURNI"/>
+      <sheetName val="stampe mensili"/>
       <sheetName val="CONTEGGI ORARI"/>
       <sheetName val="Foglio3"/>
       <sheetName val="Foglio4"/>
@@ -4451,18 +4452,18 @@
             <v>VOLPINI</v>
           </cell>
           <cell r="AS208" t="str">
-            <v>FABBRI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT208" t="str">
-            <v>FABBRI</v>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="209">
           <cell r="AQ209" t="str">
-            <v>FABBRI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR209" t="str">
-            <v>FABBRI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS209" t="str">
             <v>SARTI</v>
@@ -4885,18 +4886,18 @@
             <v>BERARDI</v>
           </cell>
           <cell r="AS239" t="str">
-            <v>VOLPINI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT239" t="str">
-            <v>VOLPINI</v>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="240">
           <cell r="AQ240" t="str">
-            <v>VOLPINI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR240" t="str">
-            <v>VOLPINI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS240" t="str">
             <v>GHIOTTI</v>
@@ -5053,872 +5054,872 @@
             <v>VOLPINI</v>
           </cell>
           <cell r="AS251" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT251" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="252">
           <cell r="AQ252" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR252" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS252" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT252" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="253">
           <cell r="AQ253" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR253" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS253" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT253" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="254">
           <cell r="AQ254" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR254" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS254" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT254" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="255">
           <cell r="AQ255" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR255" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS255" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT255" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="256">
           <cell r="AQ256" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR256" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS256" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT256" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="257">
           <cell r="AQ257" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR257" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS257" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT257" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="258">
           <cell r="AQ258" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR258" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS258" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AT258" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="259">
           <cell r="AQ259" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AR259" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AS259" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT259" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="260">
           <cell r="AQ260" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR260" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS260" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT260" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="261">
           <cell r="AQ261" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR261" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS261" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT261" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="262">
           <cell r="AQ262" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR262" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS262" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT262" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="263">
           <cell r="AQ263" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR263" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS263" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AT263" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="264">
           <cell r="AQ264" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AR264" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AS264" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT264" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="265">
           <cell r="AQ265" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR265" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS265" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT265" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="266">
           <cell r="AQ266" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR266" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS266" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT266" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="267">
           <cell r="AQ267" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR267" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS267" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT267" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="268">
           <cell r="AQ268" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR268" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS268" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT268" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="269">
           <cell r="AQ269" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR269" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS269" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT269" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="270">
           <cell r="AQ270" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR270" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS270" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT270" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="271">
           <cell r="AQ271" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR271" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS271" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT271" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="272">
           <cell r="AQ272" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR272" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS272" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT272" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="273">
           <cell r="AQ273" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR273" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS273" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AT273" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="274">
           <cell r="AQ274" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AR274" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AS274" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT274" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="275">
           <cell r="AQ275" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR275" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS275" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT275" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="276">
           <cell r="AQ276" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR276" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS276" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT276" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="277">
           <cell r="AQ277" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR277" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS277" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT277" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="278">
           <cell r="AQ278" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR278" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS278" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT278" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="279">
           <cell r="AQ279" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR279" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS279" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AT279" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="280">
           <cell r="AQ280" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AR280" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AS280" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT280" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="281">
           <cell r="AQ281" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR281" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS281" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT281" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="282">
           <cell r="AQ282" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR282" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS282" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT282" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="283">
           <cell r="AQ283" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR283" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS283" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT283" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="284">
           <cell r="AQ284" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR284" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS284" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT284" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="285">
           <cell r="AQ285" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR285" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS285" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT285" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="286">
           <cell r="AQ286" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR286" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS286" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT286" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="287">
           <cell r="AQ287" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR287" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS287" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT287" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="288">
           <cell r="AQ288" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR288" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS288" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT288" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="289">
           <cell r="AQ289" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR289" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS289" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT289" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="290">
           <cell r="AQ290" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR290" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS290" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT290" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="291">
           <cell r="AQ291" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR291" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS291" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT291" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="292">
           <cell r="AQ292" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR292" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS292" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT292" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="293">
           <cell r="AQ293" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR293" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS293" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT293" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="294">
           <cell r="AQ294" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR294" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS294" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AT294" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="295">
           <cell r="AQ295" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AR295" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AS295" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT295" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="296">
           <cell r="AQ296" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR296" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS296" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT296" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="297">
           <cell r="AQ297" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR297" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS297" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT297" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="298">
           <cell r="AQ298" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR298" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS298" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT298" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="299">
           <cell r="AQ299" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR299" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS299" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AT299" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="300">
           <cell r="AQ300" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AR300" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AS300" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT300" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="301">
           <cell r="AQ301" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR301" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS301" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT301" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="302">
           <cell r="AQ302" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR302" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS302" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT302" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="303">
           <cell r="AQ303" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR303" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS303" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT303" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="304">
           <cell r="AQ304" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR304" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS304" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AT304" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="305">
           <cell r="AQ305" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AR305" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AS305" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT305" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="306">
           <cell r="AQ306" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR306" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS306" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT306" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="307">
           <cell r="AQ307" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR307" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS307" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT307" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="308">
           <cell r="AQ308" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR308" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS308" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT308" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="309">
           <cell r="AQ309" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR309" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS309" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AT309" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="310">
           <cell r="AQ310" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AR310" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AS310" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT310" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="311">
           <cell r="AQ311" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR311" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS311" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT311" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="312">
           <cell r="AQ312" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR312" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS312" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT312" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="313">
           <cell r="AQ313" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR313" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS313" t="str">
             <v/>
@@ -6763,7 +6764,8 @@
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
-      <sheetData sheetId="10">
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11">
         <row r="3">
           <cell r="E3" t="str">
             <v>P</v>
@@ -7501,10 +7503,10 @@
             <v>R</v>
           </cell>
           <cell r="IP3" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="IQ3" t="str">
-            <v>M</v>
+            <v>p</v>
           </cell>
           <cell r="IR3" t="str">
             <v>N</v>
@@ -7519,7 +7521,7 @@
             <v>P</v>
           </cell>
           <cell r="IV3" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="IW3" t="str">
             <v>N</v>
@@ -7534,7 +7536,7 @@
             <v>P</v>
           </cell>
           <cell r="JA3" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JB3" t="str">
             <v>N</v>
@@ -7549,7 +7551,7 @@
             <v>P</v>
           </cell>
           <cell r="JF3" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JG3" t="str">
             <v>N</v>
@@ -7576,94 +7578,94 @@
             <v>R</v>
           </cell>
           <cell r="JO3" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JP3" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JQ3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="JR3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JS3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="JT3" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JU3" t="str">
-            <v>-</v>
+            <v>M/R</v>
           </cell>
           <cell r="JV3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JW3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="JX3" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JY3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JZ3" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="KA3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KB3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KC3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KD3" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KE3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KF3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KG3" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KH3" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KI3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KJ3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KK3" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KL3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KM3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KN3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KO3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KP3" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KQ3" t="str">
             <v>P</v>
           </cell>
           <cell r="KR3" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KS3" t="str">
             <v>N</v>
@@ -7678,7 +7680,7 @@
             <v>P</v>
           </cell>
           <cell r="KW3" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KX3" t="str">
             <v>N</v>
@@ -8774,8 +8776,8 @@
           <cell r="JQ4">
             <v>0</v>
           </cell>
-          <cell r="JR4" t="str">
-            <v>ng</v>
+          <cell r="JR4">
+            <v>0</v>
           </cell>
           <cell r="JS4">
             <v>0</v>
@@ -9890,7 +9892,7 @@
             <v>P</v>
           </cell>
           <cell r="IT6" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="IU6" t="str">
             <v>N</v>
@@ -9905,7 +9907,7 @@
             <v>P</v>
           </cell>
           <cell r="IY6" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="IZ6" t="str">
             <v>N</v>
@@ -9920,7 +9922,7 @@
             <v>P</v>
           </cell>
           <cell r="JD6" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JE6" t="str">
             <v>N</v>
@@ -9932,16 +9934,16 @@
             <v>R</v>
           </cell>
           <cell r="JH6" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="JI6" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="JJ6" t="str">
             <v>P</v>
           </cell>
           <cell r="JK6" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JL6" t="str">
             <v>N</v>
@@ -9953,73 +9955,73 @@
             <v>R</v>
           </cell>
           <cell r="JO6" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="JP6" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="JQ6" t="str">
+            <v>r</v>
+          </cell>
+          <cell r="JR6" t="str">
             <v>-</v>
           </cell>
-          <cell r="JP6" t="str">
-            <v>-</v>
-          </cell>
-          <cell r="JQ6" t="str">
-            <v>-</v>
-          </cell>
-          <cell r="JR6" t="str">
+          <cell r="JS6" t="str">
             <v>p</v>
           </cell>
-          <cell r="JS6" t="str">
-            <v>-</v>
-          </cell>
           <cell r="JT6" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JU6" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="JV6" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JW6" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JX6" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="JY6" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="JZ6" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KA6" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KB6" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KC6" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KD6" t="str">
-            <v>-</v>
+            <v>M/R</v>
           </cell>
           <cell r="KE6" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="KF6" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KG6" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KH6" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KI6" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KJ6" t="str">
-            <v>P</v>
+            <v>r</v>
           </cell>
           <cell r="KK6" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KL6" t="str">
             <v>N</v>
@@ -10049,7 +10051,7 @@
             <v>P</v>
           </cell>
           <cell r="KU6" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KV6" t="str">
             <v>N</v>
@@ -11151,8 +11153,8 @@
           <cell r="JQ7">
             <v>0</v>
           </cell>
-          <cell r="JR7">
-            <v>0</v>
+          <cell r="JR7" t="str">
+            <v>ng</v>
           </cell>
           <cell r="JS7">
             <v>0</v>
@@ -12270,25 +12272,25 @@
             <v>R</v>
           </cell>
           <cell r="IT9" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="IU9" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="IV9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="IW9" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="IX9" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="IY9" t="str">
-            <v>P</v>
+            <v>r</v>
           </cell>
           <cell r="IZ9" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JA9" t="str">
             <v>N</v>
@@ -12300,43 +12302,43 @@
             <v>R</v>
           </cell>
           <cell r="JD9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JE9" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="JF9" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="JG9" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JH9" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JI9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JJ9" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="JK9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JL9" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="JM9" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JN9" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="JO9" t="str">
             <v>P</v>
           </cell>
           <cell r="JP9" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JQ9" t="str">
             <v>N</v>
@@ -12381,7 +12383,7 @@
             <v>P</v>
           </cell>
           <cell r="KE9" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KF9" t="str">
             <v>N</v>
@@ -12396,7 +12398,7 @@
             <v>P</v>
           </cell>
           <cell r="KJ9" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KK9" t="str">
             <v>N</v>
@@ -12411,7 +12413,7 @@
             <v>P</v>
           </cell>
           <cell r="KO9" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KP9" t="str">
             <v>N</v>
@@ -12426,7 +12428,7 @@
             <v>P</v>
           </cell>
           <cell r="KT9" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KU9" t="str">
             <v>N</v>
@@ -14596,7 +14598,7 @@
             <v>p</v>
           </cell>
           <cell r="IB12" t="str">
-            <v>m/R</v>
+            <v>m</v>
           </cell>
           <cell r="IC12" t="str">
             <v>p</v>
@@ -14635,31 +14637,31 @@
             <v>p</v>
           </cell>
           <cell r="IO12" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="IP12" t="str">
             <v>-</v>
           </cell>
           <cell r="IQ12" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="IR12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="IS12" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="IT12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="IU12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="IV12" t="str">
             <v>P</v>
           </cell>
           <cell r="IW12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="IX12" t="str">
             <v>N</v>
@@ -14704,7 +14706,7 @@
             <v>P</v>
           </cell>
           <cell r="JL12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JM12" t="str">
             <v>N</v>
@@ -14719,7 +14721,7 @@
             <v>P</v>
           </cell>
           <cell r="JQ12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JR12" t="str">
             <v>N</v>
@@ -14734,7 +14736,7 @@
             <v>P</v>
           </cell>
           <cell r="JV12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JW12" t="str">
             <v>N</v>
@@ -14761,10 +14763,10 @@
             <v>R</v>
           </cell>
           <cell r="KE12" t="str">
-            <v>P</v>
+            <v>r</v>
           </cell>
           <cell r="KF12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KG12" t="str">
             <v>N</v>
@@ -14776,46 +14778,46 @@
             <v>R</v>
           </cell>
           <cell r="KJ12" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="KK12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KL12" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KM12" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KN12" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KO12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KP12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KQ12" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KR12" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KS12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KT12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KU12" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KV12" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KW12" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KX12" t="str">
             <v>p</v>
@@ -17012,16 +17014,16 @@
             <v>p</v>
           </cell>
           <cell r="IN15" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="IO15" t="str">
             <v>P</v>
           </cell>
           <cell r="IP15" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="IQ15" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="IR15" t="str">
             <v>P</v>
@@ -17042,7 +17044,7 @@
             <v>P</v>
           </cell>
           <cell r="IX15" t="str">
-            <v>M</v>
+            <v>p</v>
           </cell>
           <cell r="IY15" t="str">
             <v>N</v>
@@ -17057,7 +17059,7 @@
             <v>P</v>
           </cell>
           <cell r="JC15" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JD15" t="str">
             <v>N</v>
@@ -17072,7 +17074,7 @@
             <v>P</v>
           </cell>
           <cell r="JH15" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JI15" t="str">
             <v>N</v>
@@ -17102,7 +17104,7 @@
             <v>P</v>
           </cell>
           <cell r="JR15" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JS15" t="str">
             <v>N</v>
@@ -17117,85 +17119,85 @@
             <v>P</v>
           </cell>
           <cell r="JW15" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JX15" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JY15" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JZ15" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KA15" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="KB15" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KC15" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KD15" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KE15" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KF15" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KG15" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="KH15" t="str">
-            <v>-</v>
+            <v>M/R</v>
           </cell>
           <cell r="KI15" t="str">
-            <v>-</v>
+            <v>N</v>
           </cell>
           <cell r="KJ15" t="str">
-            <v>-</v>
+            <v>S</v>
           </cell>
           <cell r="KK15" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="KL15" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="KM15" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KN15" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KO15" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KP15" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="KQ15" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KR15" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KS15" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KT15" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KU15" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KV15" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KW15" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KX15" t="str">
             <v>P</v>
@@ -19392,7 +19394,7 @@
             <v>P</v>
           </cell>
           <cell r="IN18" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="IO18" t="str">
             <v>N</v>
@@ -19404,10 +19406,10 @@
             <v>R</v>
           </cell>
           <cell r="IR18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="IS18" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="IT18" t="str">
             <v>P</v>
@@ -19425,13 +19427,13 @@
             <v>R</v>
           </cell>
           <cell r="IY18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="IZ18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JA18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="JB18" t="str">
             <v>r</v>
@@ -19467,25 +19469,25 @@
             <v>R</v>
           </cell>
           <cell r="JM18" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="JN18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JO18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="JP18" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JQ18" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JR18" t="str">
             <v>P</v>
           </cell>
           <cell r="JS18" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JT18" t="str">
             <v>N</v>
@@ -19500,7 +19502,7 @@
             <v>P</v>
           </cell>
           <cell r="JX18" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JY18" t="str">
             <v>N</v>
@@ -19515,7 +19517,7 @@
             <v>P</v>
           </cell>
           <cell r="KC18" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KD18" t="str">
             <v>N</v>
@@ -21772,22 +21774,22 @@
             <v>R</v>
           </cell>
           <cell r="IN21" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="IO21" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="IP21" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="IQ21" t="str">
             <v>m</v>
-          </cell>
-          <cell r="IQ21" t="str">
-            <v>-</v>
           </cell>
           <cell r="IR21" t="str">
             <v>-</v>
           </cell>
           <cell r="IS21" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="IT21" t="str">
             <v>-</v>
@@ -21823,7 +21825,7 @@
             <v>P</v>
           </cell>
           <cell r="JE21" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JF21" t="str">
             <v>N</v>
@@ -21853,7 +21855,7 @@
             <v>P</v>
           </cell>
           <cell r="JO21" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JP21" t="str">
             <v>N</v>
@@ -21868,7 +21870,7 @@
             <v>P</v>
           </cell>
           <cell r="JT21" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JU21" t="str">
             <v>N</v>
@@ -21895,67 +21897,67 @@
             <v>R</v>
           </cell>
           <cell r="KC21" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="KD21" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KE21" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KF21" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KG21" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="KH21" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KI21" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KJ21" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KK21" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KL21" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KM21" t="str">
-            <v>-</v>
+            <v>M/R</v>
           </cell>
           <cell r="KN21" t="str">
-            <v>-</v>
+            <v>N</v>
           </cell>
           <cell r="KO21" t="str">
-            <v>-</v>
+            <v>S</v>
           </cell>
           <cell r="KP21" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="KQ21" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KR21" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KS21" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KT21" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KU21" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KV21" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="KW21" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KX21" t="str">
             <v>m</v>
@@ -24023,10 +24025,10 @@
             <v>r</v>
           </cell>
           <cell r="GW24" t="str">
-            <v>P</v>
+            <v>m/R</v>
           </cell>
           <cell r="GX24" t="str">
-            <v>M</v>
+            <v>p</v>
           </cell>
           <cell r="GY24" t="str">
             <v>N</v>
@@ -24116,7 +24118,7 @@
             <v>P</v>
           </cell>
           <cell r="IB24" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="IC24" t="str">
             <v>N</v>
@@ -24155,7 +24157,7 @@
             <v>P</v>
           </cell>
           <cell r="IO24" t="str">
-            <v>M</v>
+            <v>p</v>
           </cell>
           <cell r="IP24" t="str">
             <v>N</v>
@@ -24167,34 +24169,34 @@
             <v>R</v>
           </cell>
           <cell r="IS24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="IT24" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="IU24" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="IV24" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="IW24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="IX24" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="IY24" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="IZ24" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JA24" t="str">
             <v>P</v>
           </cell>
           <cell r="JB24" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JC24" t="str">
             <v>N</v>
@@ -24209,76 +24211,76 @@
             <v>P</v>
           </cell>
           <cell r="JG24" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JH24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JI24" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JJ24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JK24" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="JL24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JM24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JN24" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JO24" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JP24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JQ24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JR24" t="str">
             <v>m</v>
           </cell>
           <cell r="JS24" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JT24" t="str">
             <v>P</v>
           </cell>
           <cell r="JU24" t="str">
-            <v>M</v>
+            <v>p</v>
           </cell>
           <cell r="JV24" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="JW24" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JX24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JY24" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="JZ24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KA24" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KB24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KC24" t="str">
-            <v>P</v>
+            <v>r</v>
           </cell>
           <cell r="KD24" t="str">
-            <v>M</v>
+            <v>r</v>
           </cell>
           <cell r="KE24" t="str">
             <v>N</v>
@@ -24293,7 +24295,7 @@
             <v>P</v>
           </cell>
           <cell r="KI24" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KJ24" t="str">
             <v>N</v>
@@ -24308,7 +24310,7 @@
             <v>P</v>
           </cell>
           <cell r="KN24" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KO24" t="str">
             <v>N</v>
@@ -24323,7 +24325,7 @@
             <v>P</v>
           </cell>
           <cell r="KS24" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KT24" t="str">
             <v>N</v>
@@ -26403,10 +26405,10 @@
             <v>-</v>
           </cell>
           <cell r="GW27" t="str">
-            <v>m/R</v>
+            <v>P</v>
           </cell>
           <cell r="GX27" t="str">
-            <v>p</v>
+            <v>M</v>
           </cell>
           <cell r="GY27" t="str">
             <v>m</v>
@@ -26544,7 +26546,7 @@
             <v>P</v>
           </cell>
           <cell r="IR27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="IS27" t="str">
             <v>N</v>
@@ -26571,31 +26573,31 @@
             <v>R</v>
           </cell>
           <cell r="JA27" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JB27" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="JC27" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JD27" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="JE27" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JF27" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JG27" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JH27" t="str">
             <v>P</v>
           </cell>
           <cell r="JI27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JJ27" t="str">
             <v>N</v>
@@ -26610,7 +26612,7 @@
             <v>P</v>
           </cell>
           <cell r="JN27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JO27" t="str">
             <v>N</v>
@@ -26637,7 +26639,7 @@
             <v>R</v>
           </cell>
           <cell r="JW27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JX27" t="str">
             <v>N</v>
@@ -26652,7 +26654,7 @@
             <v>P</v>
           </cell>
           <cell r="KB27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KC27" t="str">
             <v>N</v>
@@ -26682,7 +26684,7 @@
             <v>P</v>
           </cell>
           <cell r="KL27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KM27" t="str">
             <v>N</v>
@@ -26697,7 +26699,7 @@
             <v>P</v>
           </cell>
           <cell r="KQ27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KR27" t="str">
             <v>N</v>
@@ -28182,9 +28184,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
       <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -28517,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28951,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -31134,11 +31136,11 @@
       </c>
       <c r="IM3" s="16" t="str">
         <f>[1]CARTELLINO!IP$3</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="IN3" s="16" t="str">
         <f>[1]CARTELLINO!IQ$3</f>
-        <v>M</v>
+        <v>p</v>
       </c>
       <c r="IO3" s="16" t="str">
         <f>[1]CARTELLINO!IR$3</f>
@@ -31158,7 +31160,7 @@
       </c>
       <c r="IS3" s="16" t="str">
         <f>[1]CARTELLINO!IV$3</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="IT3" s="16" t="str">
         <f>[1]CARTELLINO!IW$3</f>
@@ -31178,7 +31180,7 @@
       </c>
       <c r="IX3" s="16" t="str">
         <f>[1]CARTELLINO!JA$3</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="IY3" s="16" t="str">
         <f>[1]CARTELLINO!JB$3</f>
@@ -31198,7 +31200,7 @@
       </c>
       <c r="JC3" s="16" t="str">
         <f>[1]CARTELLINO!JF$3</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="JD3" s="16" t="str">
         <f>[1]CARTELLINO!JG$3</f>
@@ -31234,115 +31236,115 @@
       </c>
       <c r="JL3" s="16" t="str">
         <f>[1]CARTELLINO!JO$3</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JM3" s="16" t="str">
         <f>[1]CARTELLINO!JP$3</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JN3" s="16" t="str">
         <f>[1]CARTELLINO!JQ$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="JO3" s="16" t="str">
         <f>[1]CARTELLINO!JR$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JP3" s="16" t="str">
         <f>[1]CARTELLINO!JS$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="JQ3" s="16" t="str">
         <f>[1]CARTELLINO!JT$3</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JR3" s="16" t="str">
         <f>[1]CARTELLINO!JU$3</f>
-        <v>-</v>
+        <v>M/R</v>
       </c>
       <c r="JS3" s="16" t="str">
         <f>[1]CARTELLINO!JV$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JT3" s="16" t="str">
         <f>[1]CARTELLINO!JW$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="JU3" s="16" t="str">
         <f>[1]CARTELLINO!JX$3</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JV3" s="16" t="str">
         <f>[1]CARTELLINO!JY$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JW3" s="16" t="str">
         <f>[1]CARTELLINO!JZ$3</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="JX3" s="16" t="str">
         <f>[1]CARTELLINO!KA$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JY3" s="16" t="str">
         <f>[1]CARTELLINO!KB$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="JZ3" s="16" t="str">
         <f>[1]CARTELLINO!KC$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KA3" s="16" t="str">
         <f>[1]CARTELLINO!KD$3</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KB3" s="16" t="str">
         <f>[1]CARTELLINO!KE$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KC3" s="16" t="str">
         <f>[1]CARTELLINO!KF$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KD3" s="16" t="str">
         <f>[1]CARTELLINO!KG$3</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KE3" s="16" t="str">
         <f>[1]CARTELLINO!KH$3</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KF3" s="16" t="str">
         <f>[1]CARTELLINO!KI$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KG3" s="16" t="str">
         <f>[1]CARTELLINO!KJ$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KH3" s="16" t="str">
         <f>[1]CARTELLINO!KK$3</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KI3" s="16" t="str">
         <f>[1]CARTELLINO!KL$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KJ3" s="16" t="str">
         <f>[1]CARTELLINO!KM$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KK3" s="16" t="str">
         <f>[1]CARTELLINO!KN$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KL3" s="16" t="str">
         <f>[1]CARTELLINO!KO$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KM3" s="16" t="str">
         <f>[1]CARTELLINO!KP$3</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KN3" s="16" t="str">
         <f>[1]CARTELLINO!KQ$3</f>
@@ -31350,7 +31352,7 @@
       </c>
       <c r="KO3" s="16" t="str">
         <f>[1]CARTELLINO!KR$3</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KP3" s="16" t="str">
         <f>[1]CARTELLINO!KS$3</f>
@@ -31370,7 +31372,7 @@
       </c>
       <c r="KT3" s="16" t="str">
         <f>[1]CARTELLINO!KW$3</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KU3" s="16" t="str">
         <f>[1]CARTELLINO!KX$3</f>
@@ -32838,9 +32840,9 @@
         <f>[1]CARTELLINO!JQ$4</f>
         <v>0</v>
       </c>
-      <c r="JO4" s="43" t="str">
+      <c r="JO4" s="43">
         <f>[1]CARTELLINO!JR$4</f>
-        <v>ng</v>
+        <v>0</v>
       </c>
       <c r="JP4" s="43">
         <f>[1]CARTELLINO!JS$4</f>
@@ -34745,7 +34747,7 @@
       </c>
       <c r="IQ6" s="22" t="str">
         <f>[1]CARTELLINO!IT$6</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="IR6" s="22" t="str">
         <f>[1]CARTELLINO!IU$6</f>
@@ -34765,7 +34767,7 @@
       </c>
       <c r="IV6" s="22" t="str">
         <f>[1]CARTELLINO!IY$6</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="IW6" s="22" t="str">
         <f>[1]CARTELLINO!IZ$6</f>
@@ -34785,7 +34787,7 @@
       </c>
       <c r="JA6" s="22" t="str">
         <f>[1]CARTELLINO!JD$6</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="JB6" s="22" t="str">
         <f>[1]CARTELLINO!JE$6</f>
@@ -34801,11 +34803,11 @@
       </c>
       <c r="JE6" s="22" t="str">
         <f>[1]CARTELLINO!JH$6</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="JF6" s="22" t="str">
         <f>[1]CARTELLINO!JI$6</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="JG6" s="22" t="str">
         <f>[1]CARTELLINO!JJ$6</f>
@@ -34813,7 +34815,7 @@
       </c>
       <c r="JH6" s="22" t="str">
         <f>[1]CARTELLINO!JK$6</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="JI6" s="22" t="str">
         <f>[1]CARTELLINO!JL$6</f>
@@ -34829,95 +34831,95 @@
       </c>
       <c r="JL6" s="22" t="str">
         <f>[1]CARTELLINO!JO$6</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JM6" s="22" t="str">
         <f>[1]CARTELLINO!JP$6</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="JN6" s="22" t="str">
         <f>[1]CARTELLINO!JQ$6</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JO6" s="22" t="str">
         <f>[1]CARTELLINO!JR$6</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="JP6" s="22" t="str">
         <f>[1]CARTELLINO!JS$6</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JQ6" s="22" t="str">
         <f>[1]CARTELLINO!JT$6</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JR6" s="22" t="str">
         <f>[1]CARTELLINO!JU$6</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="JS6" s="22" t="str">
         <f>[1]CARTELLINO!JV$6</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JT6" s="22" t="str">
         <f>[1]CARTELLINO!JW$6</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JU6" s="22" t="str">
         <f>[1]CARTELLINO!JX$6</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="JV6" s="22" t="str">
         <f>[1]CARTELLINO!JY$6</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="JW6" s="22" t="str">
         <f>[1]CARTELLINO!JZ$6</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JX6" s="22" t="str">
         <f>[1]CARTELLINO!KA$6</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JY6" s="22" t="str">
         <f>[1]CARTELLINO!KB$6</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="JZ6" s="22" t="str">
         <f>[1]CARTELLINO!KC$6</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KA6" s="22" t="str">
         <f>[1]CARTELLINO!KD$6</f>
-        <v>-</v>
+        <v>M/R</v>
       </c>
       <c r="KB6" s="22" t="str">
         <f>[1]CARTELLINO!KE$6</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="KC6" s="22" t="str">
         <f>[1]CARTELLINO!KF$6</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KD6" s="22" t="str">
         <f>[1]CARTELLINO!KG$6</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KE6" s="22" t="str">
         <f>[1]CARTELLINO!KH$6</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KF6" s="22" t="str">
         <f>[1]CARTELLINO!KI$6</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KG6" s="22" t="str">
         <f>[1]CARTELLINO!KJ$6</f>
-        <v>P</v>
+        <v>r</v>
       </c>
       <c r="KH6" s="22" t="str">
         <f>[1]CARTELLINO!KK$6</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KI6" s="22" t="str">
         <f>[1]CARTELLINO!KL$6</f>
@@ -34957,7 +34959,7 @@
       </c>
       <c r="KR6" s="22" t="str">
         <f>[1]CARTELLINO!KU$6</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KS6" s="22" t="str">
         <f>[1]CARTELLINO!KV$6</f>
@@ -36433,9 +36435,9 @@
         <f>[1]CARTELLINO!JQ$7</f>
         <v>0</v>
       </c>
-      <c r="JO7" s="46">
+      <c r="JO7" s="46" t="str">
         <f>[1]CARTELLINO!JR$7</f>
-        <v>0</v>
+        <v>ng</v>
       </c>
       <c r="JP7" s="46">
         <f>[1]CARTELLINO!JS$7</f>
@@ -38341,31 +38343,31 @@
       </c>
       <c r="IQ9" s="24" t="str">
         <f>[1]CARTELLINO!IT$9</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="IR9" s="24" t="str">
         <f>[1]CARTELLINO!IU$9</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="IS9" s="24" t="str">
         <f>[1]CARTELLINO!IV$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="IT9" s="24" t="str">
         <f>[1]CARTELLINO!IW$9</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="IU9" s="24" t="str">
         <f>[1]CARTELLINO!IX$9</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="IV9" s="24" t="str">
         <f>[1]CARTELLINO!IY$9</f>
-        <v>P</v>
+        <v>r</v>
       </c>
       <c r="IW9" s="24" t="str">
         <f>[1]CARTELLINO!IZ$9</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="IX9" s="24" t="str">
         <f>[1]CARTELLINO!JA$9</f>
@@ -38381,47 +38383,47 @@
       </c>
       <c r="JA9" s="24" t="str">
         <f>[1]CARTELLINO!JD$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JB9" s="24" t="str">
         <f>[1]CARTELLINO!JE$9</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="JC9" s="24" t="str">
         <f>[1]CARTELLINO!JF$9</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="JD9" s="24" t="str">
         <f>[1]CARTELLINO!JG$9</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JE9" s="24" t="str">
         <f>[1]CARTELLINO!JH$9</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JF9" s="24" t="str">
         <f>[1]CARTELLINO!JI$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JG9" s="24" t="str">
         <f>[1]CARTELLINO!JJ$9</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="JH9" s="24" t="str">
         <f>[1]CARTELLINO!JK$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JI9" s="24" t="str">
         <f>[1]CARTELLINO!JL$9</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="JJ9" s="24" t="str">
         <f>[1]CARTELLINO!JM$9</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JK9" s="24" t="str">
         <f>[1]CARTELLINO!JN$9</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="JL9" s="24" t="str">
         <f>[1]CARTELLINO!JO$9</f>
@@ -38429,7 +38431,7 @@
       </c>
       <c r="JM9" s="24" t="str">
         <f>[1]CARTELLINO!JP$9</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="JN9" s="24" t="str">
         <f>[1]CARTELLINO!JQ$9</f>
@@ -38489,7 +38491,7 @@
       </c>
       <c r="KB9" s="24" t="str">
         <f>[1]CARTELLINO!KE$9</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KC9" s="24" t="str">
         <f>[1]CARTELLINO!KF$9</f>
@@ -38509,7 +38511,7 @@
       </c>
       <c r="KG9" s="24" t="str">
         <f>[1]CARTELLINO!KJ$9</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KH9" s="24" t="str">
         <f>[1]CARTELLINO!KK$9</f>
@@ -38529,7 +38531,7 @@
       </c>
       <c r="KL9" s="24" t="str">
         <f>[1]CARTELLINO!KO$9</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KM9" s="24" t="str">
         <f>[1]CARTELLINO!KP$9</f>
@@ -38549,7 +38551,7 @@
       </c>
       <c r="KQ9" s="24" t="str">
         <f>[1]CARTELLINO!KT$9</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KR9" s="24" t="str">
         <f>[1]CARTELLINO!KU$9</f>
@@ -41865,7 +41867,7 @@
       </c>
       <c r="HY12" s="25" t="str">
         <f>[1]CARTELLINO!IB$12</f>
-        <v>m/R</v>
+        <v>m</v>
       </c>
       <c r="HZ12" s="25" t="str">
         <f>[1]CARTELLINO!IC$12</f>
@@ -41917,7 +41919,7 @@
       </c>
       <c r="IL12" s="25" t="str">
         <f>[1]CARTELLINO!IO$12</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="IM12" s="25" t="str">
         <f>[1]CARTELLINO!IP$12</f>
@@ -41925,23 +41927,23 @@
       </c>
       <c r="IN12" s="25" t="str">
         <f>[1]CARTELLINO!IQ$12</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="IO12" s="25" t="str">
         <f>[1]CARTELLINO!IR$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="IP12" s="25" t="str">
         <f>[1]CARTELLINO!IS$12</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="IQ12" s="25" t="str">
         <f>[1]CARTELLINO!IT$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="IR12" s="25" t="str">
         <f>[1]CARTELLINO!IU$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="IS12" s="25" t="str">
         <f>[1]CARTELLINO!IV$12</f>
@@ -41949,7 +41951,7 @@
       </c>
       <c r="IT12" s="25" t="str">
         <f>[1]CARTELLINO!IW$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="IU12" s="25" t="str">
         <f>[1]CARTELLINO!IX$12</f>
@@ -42009,7 +42011,7 @@
       </c>
       <c r="JI12" s="25" t="str">
         <f>[1]CARTELLINO!JL$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="JJ12" s="25" t="str">
         <f>[1]CARTELLINO!JM$12</f>
@@ -42029,7 +42031,7 @@
       </c>
       <c r="JN12" s="25" t="str">
         <f>[1]CARTELLINO!JQ$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="JO12" s="25" t="str">
         <f>[1]CARTELLINO!JR$12</f>
@@ -42049,7 +42051,7 @@
       </c>
       <c r="JS12" s="25" t="str">
         <f>[1]CARTELLINO!JV$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="JT12" s="25" t="str">
         <f>[1]CARTELLINO!JW$12</f>
@@ -42085,11 +42087,11 @@
       </c>
       <c r="KB12" s="25" t="str">
         <f>[1]CARTELLINO!KE$12</f>
-        <v>P</v>
+        <v>r</v>
       </c>
       <c r="KC12" s="25" t="str">
         <f>[1]CARTELLINO!KF$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KD12" s="25" t="str">
         <f>[1]CARTELLINO!KG$12</f>
@@ -42105,59 +42107,59 @@
       </c>
       <c r="KG12" s="25" t="str">
         <f>[1]CARTELLINO!KJ$12</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="KH12" s="25" t="str">
         <f>[1]CARTELLINO!KK$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KI12" s="25" t="str">
         <f>[1]CARTELLINO!KL$12</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KJ12" s="25" t="str">
         <f>[1]CARTELLINO!KM$12</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KK12" s="25" t="str">
         <f>[1]CARTELLINO!KN$12</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KL12" s="25" t="str">
         <f>[1]CARTELLINO!KO$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KM12" s="25" t="str">
         <f>[1]CARTELLINO!KP$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KN12" s="25" t="str">
         <f>[1]CARTELLINO!KQ$12</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KO12" s="25" t="str">
         <f>[1]CARTELLINO!KR$12</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KP12" s="25" t="str">
         <f>[1]CARTELLINO!KS$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KQ12" s="25" t="str">
         <f>[1]CARTELLINO!KT$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KR12" s="25" t="str">
         <f>[1]CARTELLINO!KU$12</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KS12" s="25" t="str">
         <f>[1]CARTELLINO!KV$12</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KT12" s="25" t="str">
         <f>[1]CARTELLINO!KW$12</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KU12" s="25" t="str">
         <f>[1]CARTELLINO!KX$12</f>
@@ -45509,7 +45511,7 @@
       </c>
       <c r="IK15" s="26" t="str">
         <f>[1]CARTELLINO!IN$15</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="IL15" s="26" t="str">
         <f>[1]CARTELLINO!IO$15</f>
@@ -45517,11 +45519,11 @@
       </c>
       <c r="IM15" s="26" t="str">
         <f>[1]CARTELLINO!IP$15</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="IN15" s="26" t="str">
         <f>[1]CARTELLINO!IQ$15</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="IO15" s="26" t="str">
         <f>[1]CARTELLINO!IR$15</f>
@@ -45549,7 +45551,7 @@
       </c>
       <c r="IU15" s="26" t="str">
         <f>[1]CARTELLINO!IX$15</f>
-        <v>M</v>
+        <v>p</v>
       </c>
       <c r="IV15" s="26" t="str">
         <f>[1]CARTELLINO!IY$15</f>
@@ -45569,7 +45571,7 @@
       </c>
       <c r="IZ15" s="26" t="str">
         <f>[1]CARTELLINO!JC$15</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="JA15" s="26" t="str">
         <f>[1]CARTELLINO!JD$15</f>
@@ -45589,7 +45591,7 @@
       </c>
       <c r="JE15" s="26" t="str">
         <f>[1]CARTELLINO!JH$15</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="JF15" s="26" t="str">
         <f>[1]CARTELLINO!JI$15</f>
@@ -45629,7 +45631,7 @@
       </c>
       <c r="JO15" s="26" t="str">
         <f>[1]CARTELLINO!JR$15</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="JP15" s="26" t="str">
         <f>[1]CARTELLINO!JS$15</f>
@@ -45649,111 +45651,111 @@
       </c>
       <c r="JT15" s="26" t="str">
         <f>[1]CARTELLINO!JW$15</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JU15" s="26" t="str">
         <f>[1]CARTELLINO!JX$15</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JV15" s="26" t="str">
         <f>[1]CARTELLINO!JY$15</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JW15" s="26" t="str">
         <f>[1]CARTELLINO!JZ$15</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="JX15" s="26" t="str">
         <f>[1]CARTELLINO!KA$15</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="JY15" s="26" t="str">
         <f>[1]CARTELLINO!KB$15</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JZ15" s="26" t="str">
         <f>[1]CARTELLINO!KC$15</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KA15" s="26" t="str">
         <f>[1]CARTELLINO!KD$15</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KB15" s="26" t="str">
         <f>[1]CARTELLINO!KE$15</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KC15" s="26" t="str">
         <f>[1]CARTELLINO!KF$15</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KD15" s="26" t="str">
         <f>[1]CARTELLINO!KG$15</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="KE15" s="26" t="str">
         <f>[1]CARTELLINO!KH$15</f>
-        <v>-</v>
+        <v>M/R</v>
       </c>
       <c r="KF15" s="26" t="str">
         <f>[1]CARTELLINO!KI$15</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="KG15" s="26" t="str">
         <f>[1]CARTELLINO!KJ$15</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="KH15" s="26" t="str">
         <f>[1]CARTELLINO!KK$15</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="KI15" s="26" t="str">
         <f>[1]CARTELLINO!KL$15</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="KJ15" s="26" t="str">
         <f>[1]CARTELLINO!KM$15</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KK15" s="26" t="str">
         <f>[1]CARTELLINO!KN$15</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KL15" s="26" t="str">
         <f>[1]CARTELLINO!KO$15</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KM15" s="26" t="str">
         <f>[1]CARTELLINO!KP$15</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="KN15" s="26" t="str">
         <f>[1]CARTELLINO!KQ$15</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KO15" s="26" t="str">
         <f>[1]CARTELLINO!KR$15</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KP15" s="26" t="str">
         <f>[1]CARTELLINO!KS$15</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KQ15" s="26" t="str">
         <f>[1]CARTELLINO!KT$15</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KR15" s="26" t="str">
         <f>[1]CARTELLINO!KU$15</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KS15" s="26" t="str">
         <f>[1]CARTELLINO!KV$15</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KT15" s="26" t="str">
         <f>[1]CARTELLINO!KW$15</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KU15" s="26" t="str">
         <f>[1]CARTELLINO!KX$15</f>
@@ -49105,7 +49107,7 @@
       </c>
       <c r="IK18" s="27" t="str">
         <f>[1]CARTELLINO!IN$18</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="IL18" s="27" t="str">
         <f>[1]CARTELLINO!IO$18</f>
@@ -49121,11 +49123,11 @@
       </c>
       <c r="IO18" s="27" t="str">
         <f>[1]CARTELLINO!IR$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="IP18" s="27" t="str">
         <f>[1]CARTELLINO!IS$18</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="IQ18" s="27" t="str">
         <f>[1]CARTELLINO!IT$18</f>
@@ -49149,15 +49151,15 @@
       </c>
       <c r="IV18" s="27" t="str">
         <f>[1]CARTELLINO!IY$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="IW18" s="27" t="str">
         <f>[1]CARTELLINO!IZ$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="IX18" s="27" t="str">
         <f>[1]CARTELLINO!JA$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="IY18" s="27" t="str">
         <f>[1]CARTELLINO!JB$18</f>
@@ -49205,23 +49207,23 @@
       </c>
       <c r="JJ18" s="27" t="str">
         <f>[1]CARTELLINO!JM$18</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="JK18" s="27" t="str">
         <f>[1]CARTELLINO!JN$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JL18" s="27" t="str">
         <f>[1]CARTELLINO!JO$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="JM18" s="27" t="str">
         <f>[1]CARTELLINO!JP$18</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JN18" s="27" t="str">
         <f>[1]CARTELLINO!JQ$18</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JO18" s="27" t="str">
         <f>[1]CARTELLINO!JR$18</f>
@@ -49229,7 +49231,7 @@
       </c>
       <c r="JP18" s="27" t="str">
         <f>[1]CARTELLINO!JS$18</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="JQ18" s="27" t="str">
         <f>[1]CARTELLINO!JT$18</f>
@@ -49249,7 +49251,7 @@
       </c>
       <c r="JU18" s="27" t="str">
         <f>[1]CARTELLINO!JX$18</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="JV18" s="27" t="str">
         <f>[1]CARTELLINO!JY$18</f>
@@ -49269,7 +49271,7 @@
       </c>
       <c r="JZ18" s="27" t="str">
         <f>[1]CARTELLINO!KC$18</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KA18" s="27" t="str">
         <f>[1]CARTELLINO!KD$18</f>
@@ -52701,19 +52703,19 @@
       </c>
       <c r="IK21" s="28" t="str">
         <f>[1]CARTELLINO!IN$21</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="IL21" s="28" t="str">
         <f>[1]CARTELLINO!IO$21</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="IM21" s="28" t="str">
         <f>[1]CARTELLINO!IP$21</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="IN21" s="28" t="str">
         <f>[1]CARTELLINO!IQ$21</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="IO21" s="28" t="str">
         <f>[1]CARTELLINO!IR$21</f>
@@ -52721,7 +52723,7 @@
       </c>
       <c r="IP21" s="28" t="str">
         <f>[1]CARTELLINO!IS$21</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="IQ21" s="28" t="str">
         <f>[1]CARTELLINO!IT$21</f>
@@ -52769,7 +52771,7 @@
       </c>
       <c r="JB21" s="28" t="str">
         <f>[1]CARTELLINO!JE$21</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="JC21" s="28" t="str">
         <f>[1]CARTELLINO!JF$21</f>
@@ -52809,7 +52811,7 @@
       </c>
       <c r="JL21" s="28" t="str">
         <f>[1]CARTELLINO!JO$21</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="JM21" s="28" t="str">
         <f>[1]CARTELLINO!JP$21</f>
@@ -52829,7 +52831,7 @@
       </c>
       <c r="JQ21" s="28" t="str">
         <f>[1]CARTELLINO!JT$21</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="JR21" s="28" t="str">
         <f>[1]CARTELLINO!JU$21</f>
@@ -52865,87 +52867,87 @@
       </c>
       <c r="JZ21" s="28" t="str">
         <f>[1]CARTELLINO!KC$21</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="KA21" s="28" t="str">
         <f>[1]CARTELLINO!KD$21</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KB21" s="28" t="str">
         <f>[1]CARTELLINO!KE$21</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KC21" s="28" t="str">
         <f>[1]CARTELLINO!KF$21</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KD21" s="28" t="str">
         <f>[1]CARTELLINO!KG$21</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="KE21" s="28" t="str">
         <f>[1]CARTELLINO!KH$21</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KF21" s="28" t="str">
         <f>[1]CARTELLINO!KI$21</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KG21" s="28" t="str">
         <f>[1]CARTELLINO!KJ$21</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KH21" s="28" t="str">
         <f>[1]CARTELLINO!KK$21</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KI21" s="28" t="str">
         <f>[1]CARTELLINO!KL$21</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KJ21" s="28" t="str">
         <f>[1]CARTELLINO!KM$21</f>
-        <v>-</v>
+        <v>M/R</v>
       </c>
       <c r="KK21" s="28" t="str">
         <f>[1]CARTELLINO!KN$21</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="KL21" s="28" t="str">
         <f>[1]CARTELLINO!KO$21</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="KM21" s="28" t="str">
         <f>[1]CARTELLINO!KP$21</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="KN21" s="28" t="str">
         <f>[1]CARTELLINO!KQ$21</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KO21" s="28" t="str">
         <f>[1]CARTELLINO!KR$21</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KP21" s="28" t="str">
         <f>[1]CARTELLINO!KS$21</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KQ21" s="28" t="str">
         <f>[1]CARTELLINO!KT$21</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KR21" s="28" t="str">
         <f>[1]CARTELLINO!KU$21</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KS21" s="28" t="str">
         <f>[1]CARTELLINO!KV$21</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="KT21" s="28" t="str">
         <f>[1]CARTELLINO!KW$21</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KU21" s="28" t="str">
         <f>[1]CARTELLINO!KX$21</f>
@@ -56125,11 +56127,11 @@
       </c>
       <c r="GT24" s="29" t="str">
         <f>[1]CARTELLINO!GW$24</f>
-        <v>P</v>
+        <v>m/R</v>
       </c>
       <c r="GU24" s="29" t="str">
         <f>[1]CARTELLINO!GX$24</f>
-        <v>M</v>
+        <v>p</v>
       </c>
       <c r="GV24" s="29" t="str">
         <f>[1]CARTELLINO!GY$24</f>
@@ -56249,7 +56251,7 @@
       </c>
       <c r="HY24" s="29" t="str">
         <f>[1]CARTELLINO!IB$24</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="HZ24" s="29" t="str">
         <f>[1]CARTELLINO!IC$24</f>
@@ -56301,7 +56303,7 @@
       </c>
       <c r="IL24" s="29" t="str">
         <f>[1]CARTELLINO!IO$24</f>
-        <v>M</v>
+        <v>p</v>
       </c>
       <c r="IM24" s="29" t="str">
         <f>[1]CARTELLINO!IP$24</f>
@@ -56317,35 +56319,35 @@
       </c>
       <c r="IP24" s="29" t="str">
         <f>[1]CARTELLINO!IS$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="IQ24" s="29" t="str">
         <f>[1]CARTELLINO!IT$24</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="IR24" s="29" t="str">
         <f>[1]CARTELLINO!IU$24</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="IS24" s="29" t="str">
         <f>[1]CARTELLINO!IV$24</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="IT24" s="29" t="str">
         <f>[1]CARTELLINO!IW$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="IU24" s="29" t="str">
         <f>[1]CARTELLINO!IX$24</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="IV24" s="29" t="str">
         <f>[1]CARTELLINO!IY$24</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="IW24" s="29" t="str">
         <f>[1]CARTELLINO!IZ$24</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="IX24" s="29" t="str">
         <f>[1]CARTELLINO!JA$24</f>
@@ -56353,7 +56355,7 @@
       </c>
       <c r="IY24" s="29" t="str">
         <f>[1]CARTELLINO!JB$24</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="IZ24" s="29" t="str">
         <f>[1]CARTELLINO!JC$24</f>
@@ -56373,47 +56375,47 @@
       </c>
       <c r="JD24" s="29" t="str">
         <f>[1]CARTELLINO!JG$24</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="JE24" s="29" t="str">
         <f>[1]CARTELLINO!JH$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JF24" s="29" t="str">
         <f>[1]CARTELLINO!JI$24</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JG24" s="29" t="str">
         <f>[1]CARTELLINO!JJ$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JH24" s="29" t="str">
         <f>[1]CARTELLINO!JK$24</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="JI24" s="29" t="str">
         <f>[1]CARTELLINO!JL$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JJ24" s="29" t="str">
         <f>[1]CARTELLINO!JM$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JK24" s="29" t="str">
         <f>[1]CARTELLINO!JN$24</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JL24" s="29" t="str">
         <f>[1]CARTELLINO!JO$24</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JM24" s="29" t="str">
         <f>[1]CARTELLINO!JP$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JN24" s="29" t="str">
         <f>[1]CARTELLINO!JQ$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JO24" s="29" t="str">
         <f>[1]CARTELLINO!JR$24</f>
@@ -56421,7 +56423,7 @@
       </c>
       <c r="JP24" s="29" t="str">
         <f>[1]CARTELLINO!JS$24</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JQ24" s="29" t="str">
         <f>[1]CARTELLINO!JT$24</f>
@@ -56429,43 +56431,43 @@
       </c>
       <c r="JR24" s="29" t="str">
         <f>[1]CARTELLINO!JU$24</f>
-        <v>M</v>
+        <v>p</v>
       </c>
       <c r="JS24" s="29" t="str">
         <f>[1]CARTELLINO!JV$24</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="JT24" s="29" t="str">
         <f>[1]CARTELLINO!JW$24</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JU24" s="29" t="str">
         <f>[1]CARTELLINO!JX$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JV24" s="29" t="str">
         <f>[1]CARTELLINO!JY$24</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="JW24" s="29" t="str">
         <f>[1]CARTELLINO!JZ$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JX24" s="29" t="str">
         <f>[1]CARTELLINO!KA$24</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="JY24" s="29" t="str">
         <f>[1]CARTELLINO!KB$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JZ24" s="29" t="str">
         <f>[1]CARTELLINO!KC$24</f>
-        <v>P</v>
+        <v>r</v>
       </c>
       <c r="KA24" s="29" t="str">
         <f>[1]CARTELLINO!KD$24</f>
-        <v>M</v>
+        <v>r</v>
       </c>
       <c r="KB24" s="29" t="str">
         <f>[1]CARTELLINO!KE$24</f>
@@ -56485,7 +56487,7 @@
       </c>
       <c r="KF24" s="29" t="str">
         <f>[1]CARTELLINO!KI$24</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KG24" s="29" t="str">
         <f>[1]CARTELLINO!KJ$24</f>
@@ -56505,7 +56507,7 @@
       </c>
       <c r="KK24" s="29" t="str">
         <f>[1]CARTELLINO!KN$24</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KL24" s="29" t="str">
         <f>[1]CARTELLINO!KO$24</f>
@@ -56525,7 +56527,7 @@
       </c>
       <c r="KP24" s="29" t="str">
         <f>[1]CARTELLINO!KS$24</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KQ24" s="29" t="str">
         <f>[1]CARTELLINO!KT$24</f>
@@ -59721,11 +59723,11 @@
       </c>
       <c r="GT27" s="30" t="str">
         <f>[1]CARTELLINO!GW$27</f>
-        <v>m/R</v>
+        <v>P</v>
       </c>
       <c r="GU27" s="30" t="str">
         <f>[1]CARTELLINO!GX$27</f>
-        <v>p</v>
+        <v>M</v>
       </c>
       <c r="GV27" s="30" t="str">
         <f>[1]CARTELLINO!GY$27</f>
@@ -59909,7 +59911,7 @@
       </c>
       <c r="IO27" s="30" t="str">
         <f>[1]CARTELLINO!IR$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="IP27" s="30" t="str">
         <f>[1]CARTELLINO!IS$27</f>
@@ -59945,31 +59947,31 @@
       </c>
       <c r="IX27" s="30" t="str">
         <f>[1]CARTELLINO!JA$27</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="IY27" s="30" t="str">
         <f>[1]CARTELLINO!JB$27</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="IZ27" s="30" t="str">
         <f>[1]CARTELLINO!JC$27</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JA27" s="30" t="str">
         <f>[1]CARTELLINO!JD$27</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="JB27" s="30" t="str">
         <f>[1]CARTELLINO!JE$27</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JC27" s="30" t="str">
         <f>[1]CARTELLINO!JF$27</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JD27" s="30" t="str">
         <f>[1]CARTELLINO!JG$27</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JE27" s="30" t="str">
         <f>[1]CARTELLINO!JH$27</f>
@@ -59977,7 +59979,7 @@
       </c>
       <c r="JF27" s="30" t="str">
         <f>[1]CARTELLINO!JI$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="JG27" s="30" t="str">
         <f>[1]CARTELLINO!JJ$27</f>
@@ -59997,7 +59999,7 @@
       </c>
       <c r="JK27" s="30" t="str">
         <f>[1]CARTELLINO!JN$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="JL27" s="30" t="str">
         <f>[1]CARTELLINO!JO$27</f>
@@ -60033,7 +60035,7 @@
       </c>
       <c r="JT27" s="30" t="str">
         <f>[1]CARTELLINO!JW$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="JU27" s="30" t="str">
         <f>[1]CARTELLINO!JX$27</f>
@@ -60053,7 +60055,7 @@
       </c>
       <c r="JY27" s="30" t="str">
         <f>[1]CARTELLINO!KB$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="JZ27" s="30" t="str">
         <f>[1]CARTELLINO!KC$27</f>
@@ -60093,7 +60095,7 @@
       </c>
       <c r="KI27" s="30" t="str">
         <f>[1]CARTELLINO!KL$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KJ27" s="30" t="str">
         <f>[1]CARTELLINO!KM$27</f>
@@ -60113,7 +60115,7 @@
       </c>
       <c r="KN27" s="30" t="str">
         <f>[1]CARTELLINO!KQ$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KO27" s="30" t="str">
         <f>[1]CARTELLINO!KR$27</f>
@@ -62714,7 +62716,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="GU29" s="63" t="str">
-        <v>FABBRI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="GV29" s="63" t="str">
         <v>SARTI</v>
@@ -62807,7 +62809,7 @@
         <v>BERARDI</v>
       </c>
       <c r="HZ29" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="IA29" s="63" t="str">
         <v>GHIOTTI</v>
@@ -62843,190 +62845,190 @@
         <v>VOLPINI</v>
       </c>
       <c r="IL29" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="IM29" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="IN29" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="IO29" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="IP29" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="IQ29" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="IR29" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="IS29" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="IT29" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IU29" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="IV29" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="IW29" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="IX29" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="IY29" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IZ29" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="JA29" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="JB29" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="JC29" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="JD29" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="JE29" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="JF29" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="JG29" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="JH29" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="JI29" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="JJ29" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="JK29" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="JL29" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="JM29" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="JN29" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="JO29" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="JP29" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="JQ29" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="JR29" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="JS29" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="JT29" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="JU29" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="JV29" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="JW29" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="JX29" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="JY29" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="JZ29" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="KA29" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="KB29" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="KC29" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="KD29" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="KE29" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="KF29" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="KG29" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="KH29" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="KI29" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="KJ29" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="KK29" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="KL29" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="KM29" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="KN29" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="KO29" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="KP29" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="KQ29" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="KR29" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="KS29" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="KT29" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="KU29" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="KV29" s="63" t="str">
         <v/>
@@ -63814,7 +63816,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="GU30" s="63" t="str">
-        <v>FABBRI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="GV30" s="63" t="str">
         <v>SARTI</v>
@@ -63907,7 +63909,7 @@
         <v>BERARDI</v>
       </c>
       <c r="HZ30" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="IA30" s="63" t="str">
         <v>GHIOTTI</v>
@@ -63943,190 +63945,190 @@
         <v>VOLPINI</v>
       </c>
       <c r="IL30" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="IM30" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="IN30" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="IO30" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="IP30" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="IQ30" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="IR30" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="IS30" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="IT30" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IU30" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="IV30" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="IW30" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="IX30" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="IY30" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IZ30" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="JA30" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="JB30" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="JC30" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="JD30" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="JE30" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="JF30" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="JG30" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="JH30" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="JI30" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="JJ30" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="JK30" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="JL30" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="JM30" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="JN30" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="JO30" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="JP30" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="JQ30" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="JR30" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="JS30" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="JT30" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="JU30" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="JV30" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="JW30" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="JX30" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="JY30" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="JZ30" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="KA30" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="KB30" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="KC30" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="KD30" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="KE30" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="KF30" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="KG30" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="KH30" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="KI30" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="KJ30" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="KK30" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="KL30" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="KM30" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="KN30" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="KO30" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="KP30" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="KQ30" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="KR30" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="KS30" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="KT30" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="KU30" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="KV30" s="63" t="str">
         <v/>
@@ -64911,7 +64913,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="GT31" s="63" t="str">
-        <v>FABBRI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="GU31" s="63" t="str">
         <v>SARTI</v>
@@ -65004,7 +65006,7 @@
         <v>BERARDI</v>
       </c>
       <c r="HY31" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="HZ31" s="63" t="str">
         <v>GHIOTTI</v>
@@ -65040,190 +65042,190 @@
         <v>VOLPINI</v>
       </c>
       <c r="IK31" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="IL31" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="IM31" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="IN31" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="IO31" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="IP31" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="IQ31" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="IR31" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="IS31" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IT31" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="IU31" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="IV31" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="IW31" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="IX31" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IY31" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="IZ31" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="JA31" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="JB31" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="JC31" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="JD31" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="JE31" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="JF31" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="JG31" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="JH31" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="JI31" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="JJ31" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="JK31" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="JL31" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="JM31" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="JN31" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="JO31" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="JP31" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="JQ31" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="JR31" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="JS31" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="JT31" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="JU31" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="JV31" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="JW31" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="JX31" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="JY31" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="JZ31" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="KA31" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="KB31" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="KC31" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="KD31" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="KE31" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="KF31" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="KG31" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="KH31" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="KI31" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="KJ31" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="KK31" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="KL31" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="KM31" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="KN31" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="KO31" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="KP31" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="KQ31" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="KR31" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="KS31" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="KT31" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="KU31" s="63" t="str">
         <v/>
@@ -66011,7 +66013,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="GT32" s="63" t="str">
-        <v>FABBRI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="GU32" s="63" t="str">
         <v>SARTI</v>
@@ -66104,7 +66106,7 @@
         <v>BERARDI</v>
       </c>
       <c r="HY32" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="HZ32" s="63" t="str">
         <v>GHIOTTI</v>
@@ -66140,190 +66142,190 @@
         <v>VOLPINI</v>
       </c>
       <c r="IK32" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="IL32" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="IM32" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="IN32" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="IO32" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="IP32" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="IQ32" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="IR32" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="IS32" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IT32" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="IU32" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="IV32" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="IW32" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="IX32" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IY32" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="IZ32" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="JA32" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="JB32" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="JC32" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="JD32" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="JE32" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="JF32" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="JG32" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="JH32" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="JI32" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="JJ32" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="JK32" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="JL32" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="JM32" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="JN32" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="JO32" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="JP32" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="JQ32" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="JR32" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="JS32" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="JT32" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="JU32" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="JV32" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="JW32" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="JX32" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="JY32" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="JZ32" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="KA32" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="KB32" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="KC32" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="KD32" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="KE32" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="KF32" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="KG32" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="KH32" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="KI32" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="KJ32" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="KK32" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="KL32" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="KM32" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="KN32" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="KO32" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="KP32" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="KQ32" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="KR32" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="KS32" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="KT32" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="KU32" s="63" t="str">
         <v/>
@@ -66529,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71027,13 +71029,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71042,6 +71037,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527E6B6D-B68D-43A2-974D-7F3A12DF1B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B645BFB-4477-4B86-A72B-3E13CD30E3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="75" windowWidth="28800" windowHeight="15405" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="0" yWindow="390" windowWidth="28800" windowHeight="15405" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -10168,7 +10168,7 @@
             <v>-</v>
           </cell>
           <cell r="MH6" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="MI6" t="str">
             <v>-</v>
@@ -10240,13 +10240,13 @@
             <v>-</v>
           </cell>
           <cell r="NF6" t="str">
-            <v>-</v>
+            <v>N</v>
           </cell>
           <cell r="NG6" t="str">
-            <v>-</v>
+            <v>S</v>
           </cell>
           <cell r="NH6" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="NI6" t="str">
             <v>P</v>
@@ -12548,7 +12548,7 @@
             <v>R</v>
           </cell>
           <cell r="MH9" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="MI9" t="str">
             <v>M</v>
@@ -13737,8 +13737,8 @@
           <cell r="MG10">
             <v>0</v>
           </cell>
-          <cell r="MH10" t="str">
-            <v>ng</v>
+          <cell r="MH10">
+            <v>0</v>
           </cell>
           <cell r="MI10">
             <v>0</v>
@@ -14457,7 +14457,7 @@
             <v>m/R</v>
           </cell>
           <cell r="GG12" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="GH12" t="str">
             <v>m</v>
@@ -14979,10 +14979,10 @@
             <v>-</v>
           </cell>
           <cell r="MY12" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="MZ12" t="str">
-            <v>m</v>
+            <v>M</v>
           </cell>
           <cell r="NA12" t="str">
             <v>N</v>
@@ -16837,7 +16837,7 @@
             <v>R</v>
           </cell>
           <cell r="GG15" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="GH15" t="str">
             <v>M/R</v>
@@ -17359,10 +17359,10 @@
             <v>-</v>
           </cell>
           <cell r="MY15" t="str">
-            <v>P</v>
+            <v>p</v>
           </cell>
           <cell r="MZ15" t="str">
-            <v>M</v>
+            <v>m</v>
           </cell>
           <cell r="NA15" t="str">
             <v>-</v>
@@ -18026,8 +18026,8 @@
           <cell r="GF16">
             <v>0</v>
           </cell>
-          <cell r="GG16">
-            <v>0</v>
+          <cell r="GG16" t="str">
+            <v>p</v>
           </cell>
           <cell r="GH16">
             <v>0</v>
@@ -24439,16 +24439,16 @@
             <v>R</v>
           </cell>
           <cell r="ME24" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="MF24" t="str">
-            <v>M</v>
+            <v>-</v>
           </cell>
           <cell r="MG24" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="MH24" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="MI24" t="str">
             <v>R</v>
@@ -24520,10 +24520,10 @@
             <v>M</v>
           </cell>
           <cell r="NF24" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="NG24" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="NH24" t="str">
             <v>R</v>
@@ -25628,20 +25628,20 @@
           <cell r="MD25">
             <v>0</v>
           </cell>
-          <cell r="ME25">
-            <v>0</v>
-          </cell>
-          <cell r="MF25">
-            <v>0</v>
-          </cell>
-          <cell r="MG25">
-            <v>0</v>
-          </cell>
-          <cell r="MH25">
-            <v>0</v>
-          </cell>
-          <cell r="MI25">
-            <v>0</v>
+          <cell r="ME25" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="MF25" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="MG25" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="MH25" t="str">
+            <v>nl</v>
+          </cell>
+          <cell r="MI25" t="str">
+            <v>f</v>
           </cell>
           <cell r="MJ25">
             <v>0</v>
@@ -25709,26 +25709,26 @@
           <cell r="NE25">
             <v>0</v>
           </cell>
-          <cell r="NF25">
-            <v>0</v>
-          </cell>
-          <cell r="NG25">
-            <v>0</v>
-          </cell>
-          <cell r="NH25">
-            <v>0</v>
-          </cell>
-          <cell r="NI25">
-            <v>0</v>
-          </cell>
-          <cell r="NJ25">
-            <v>0</v>
-          </cell>
-          <cell r="NK25">
-            <v>0</v>
-          </cell>
-          <cell r="NL25">
-            <v>0</v>
+          <cell r="NF25" t="str">
+            <v>nl</v>
+          </cell>
+          <cell r="NG25" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="NH25" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="NI25" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="NJ25" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="NK25" t="str">
+            <v>nl</v>
+          </cell>
+          <cell r="NL25" t="str">
+            <v>f</v>
           </cell>
           <cell r="NM25">
             <v>0</v>
@@ -26819,19 +26819,19 @@
             <v>-</v>
           </cell>
           <cell r="ME27" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="MF27" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="MG27" t="str">
-            <v>-</v>
+            <v>N</v>
           </cell>
           <cell r="MH27" t="str">
-            <v>m</v>
+            <v>S</v>
           </cell>
           <cell r="MI27" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="MJ27" t="str">
             <v>-</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -35115,7 +35115,7 @@
       </c>
       <c r="ME6" s="22" t="str">
         <f>[1]CARTELLINO!MH$6</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="MF6" s="22" t="str">
         <f>[1]CARTELLINO!MI$6</f>
@@ -35211,15 +35211,15 @@
       </c>
       <c r="NC6" s="22" t="str">
         <f>[1]CARTELLINO!NF$6</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="ND6" s="22" t="str">
         <f>[1]CARTELLINO!NG$6</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="NE6" s="22" t="str">
         <f>[1]CARTELLINO!NH$6</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="NF6" s="22" t="str">
         <f>[1]CARTELLINO!NI$6</f>
@@ -38711,7 +38711,7 @@
       </c>
       <c r="ME9" s="24" t="str">
         <f>[1]CARTELLINO!MH$9</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="MF9" s="24" t="str">
         <f>[1]CARTELLINO!MI$9</f>
@@ -40303,9 +40303,9 @@
         <f>[1]CARTELLINO!MG$10</f>
         <v>0</v>
       </c>
-      <c r="ME10" s="46" t="str">
+      <c r="ME10" s="46">
         <f>[1]CARTELLINO!MH$10</f>
-        <v>ng</v>
+        <v>0</v>
       </c>
       <c r="MF10" s="46">
         <f>[1]CARTELLINO!MI$10</f>
@@ -41679,7 +41679,7 @@
       </c>
       <c r="GD12" s="25" t="str">
         <f>[1]CARTELLINO!GG$12</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="GE12" s="25" t="str">
         <f>[1]CARTELLINO!GH$12</f>
@@ -42375,11 +42375,11 @@
       </c>
       <c r="MV12" s="25" t="str">
         <f>[1]CARTELLINO!MY$12</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="MW12" s="25" t="str">
         <f>[1]CARTELLINO!MZ$12</f>
-        <v>m</v>
+        <v>M</v>
       </c>
       <c r="MX12" s="25" t="str">
         <f>[1]CARTELLINO!NA$12</f>
@@ -45275,7 +45275,7 @@
       </c>
       <c r="GD15" s="26" t="str">
         <f>[1]CARTELLINO!GG$15</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="GE15" s="26" t="str">
         <f>[1]CARTELLINO!GH$15</f>
@@ -45971,11 +45971,11 @@
       </c>
       <c r="MV15" s="26" t="str">
         <f>[1]CARTELLINO!MY$15</f>
-        <v>P</v>
+        <v>p</v>
       </c>
       <c r="MW15" s="26" t="str">
         <f>[1]CARTELLINO!MZ$15</f>
-        <v>M</v>
+        <v>m</v>
       </c>
       <c r="MX15" s="26" t="str">
         <f>[1]CARTELLINO!NA$15</f>
@@ -46867,9 +46867,9 @@
         <f>[1]CARTELLINO!GF$16</f>
         <v>0</v>
       </c>
-      <c r="GD16" s="46">
+      <c r="GD16" s="46" t="str">
         <f>[1]CARTELLINO!GG$16</f>
-        <v>0</v>
+        <v>p</v>
       </c>
       <c r="GE16" s="46">
         <f>[1]CARTELLINO!GH$16</f>
@@ -56679,19 +56679,19 @@
       </c>
       <c r="MB24" s="29" t="str">
         <f>[1]CARTELLINO!ME$24</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="MC24" s="29" t="str">
         <f>[1]CARTELLINO!MF$24</f>
-        <v>M</v>
+        <v>-</v>
       </c>
       <c r="MD24" s="29" t="str">
         <f>[1]CARTELLINO!MG$24</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="ME24" s="29" t="str">
         <f>[1]CARTELLINO!MH$24</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="MF24" s="29" t="str">
         <f>[1]CARTELLINO!MI$24</f>
@@ -56787,11 +56787,11 @@
       </c>
       <c r="NC24" s="29" t="str">
         <f>[1]CARTELLINO!NF$24</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="ND24" s="29" t="str">
         <f>[1]CARTELLINO!NG$24</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="NE24" s="29" t="str">
         <f>[1]CARTELLINO!NH$24</f>
@@ -58271,25 +58271,25 @@
         <f>[1]CARTELLINO!MD$25</f>
         <v>0</v>
       </c>
-      <c r="MB25" s="46">
+      <c r="MB25" s="46" t="str">
         <f>[1]CARTELLINO!ME$25</f>
-        <v>0</v>
-      </c>
-      <c r="MC25" s="46">
+        <v>f</v>
+      </c>
+      <c r="MC25" s="46" t="str">
         <f>[1]CARTELLINO!MF$25</f>
-        <v>0</v>
-      </c>
-      <c r="MD25" s="46">
+        <v>f</v>
+      </c>
+      <c r="MD25" s="46" t="str">
         <f>[1]CARTELLINO!MG$25</f>
-        <v>0</v>
-      </c>
-      <c r="ME25" s="46">
+        <v>f</v>
+      </c>
+      <c r="ME25" s="46" t="str">
         <f>[1]CARTELLINO!MH$25</f>
-        <v>0</v>
-      </c>
-      <c r="MF25" s="46">
+        <v>nl</v>
+      </c>
+      <c r="MF25" s="46" t="str">
         <f>[1]CARTELLINO!MI$25</f>
-        <v>0</v>
+        <v>f</v>
       </c>
       <c r="MG25" s="46">
         <f>[1]CARTELLINO!MJ$25</f>
@@ -58379,33 +58379,33 @@
         <f>[1]CARTELLINO!NE$25</f>
         <v>0</v>
       </c>
-      <c r="NC25" s="46">
+      <c r="NC25" s="46" t="str">
         <f>[1]CARTELLINO!NF$25</f>
-        <v>0</v>
-      </c>
-      <c r="ND25" s="46">
+        <v>nl</v>
+      </c>
+      <c r="ND25" s="46" t="str">
         <f>[1]CARTELLINO!NG$25</f>
-        <v>0</v>
-      </c>
-      <c r="NE25" s="46">
+        <v>f</v>
+      </c>
+      <c r="NE25" s="46" t="str">
         <f>[1]CARTELLINO!NH$25</f>
-        <v>0</v>
-      </c>
-      <c r="NF25" s="46">
+        <v>f</v>
+      </c>
+      <c r="NF25" s="46" t="str">
         <f>[1]CARTELLINO!NI$25</f>
-        <v>0</v>
-      </c>
-      <c r="NG25" s="46">
+        <v>f</v>
+      </c>
+      <c r="NG25" s="46" t="str">
         <f>[1]CARTELLINO!NJ$25</f>
-        <v>0</v>
-      </c>
-      <c r="NH25" s="46">
+        <v>f</v>
+      </c>
+      <c r="NH25" s="46" t="str">
         <f>[1]CARTELLINO!NK$25</f>
-        <v>0</v>
-      </c>
-      <c r="NI25" s="46">
+        <v>nl</v>
+      </c>
+      <c r="NI25" s="46" t="str">
         <f>[1]CARTELLINO!NL$25</f>
-        <v>0</v>
+        <v>f</v>
       </c>
       <c r="NJ25" s="46">
         <f>[1]CARTELLINO!NM$25</f>
@@ -60275,23 +60275,23 @@
       </c>
       <c r="MB27" s="30" t="str">
         <f>[1]CARTELLINO!ME$27</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="MC27" s="30" t="str">
         <f>[1]CARTELLINO!MF$27</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="MD27" s="30" t="str">
         <f>[1]CARTELLINO!MG$27</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="ME27" s="30" t="str">
         <f>[1]CARTELLINO!MH$27</f>
-        <v>m</v>
+        <v>S</v>
       </c>
       <c r="MF27" s="30" t="str">
         <f>[1]CARTELLINO!MI$27</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="MG27" s="30" t="str">
         <f>[1]CARTELLINO!MJ$27</f>
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,6 +71029,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71037,13 +71044,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B645BFB-4477-4B86-A72B-3E13CD30E3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA5B5C0-5D7A-4C02-BDC4-45129FE74484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="390" windowWidth="28800" windowHeight="15405" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="0" yWindow="75" windowWidth="28800" windowHeight="15405" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -12137,7 +12137,7 @@
             <v>m</v>
           </cell>
           <cell r="HA9" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="HB9" t="str">
             <v>-</v>
@@ -26417,7 +26417,7 @@
             <v>p</v>
           </cell>
           <cell r="HA27" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="HB27" t="str">
             <v>r</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -38163,7 +38163,7 @@
       </c>
       <c r="GX9" s="24" t="str">
         <f>[1]CARTELLINO!HA$9</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="GY9" s="24" t="str">
         <f>[1]CARTELLINO!HB$9</f>
@@ -59739,7 +59739,7 @@
       </c>
       <c r="GX27" s="30" t="str">
         <f>[1]CARTELLINO!HA$27</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="GY27" s="30" t="str">
         <f>[1]CARTELLINO!HB$27</f>
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,13 +71029,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71044,6 +71037,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA5B5C0-5D7A-4C02-BDC4-45129FE74484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92EE9F5E-BC1B-4AA7-A197-DFF0A0EC000E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="75" windowWidth="28800" windowHeight="15405" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4329,12 +4329,12 @@
             <v>SARTI</v>
           </cell>
           <cell r="AT199" t="str">
-            <v>SARTI</v>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="200">
           <cell r="AQ200" t="str">
-            <v>SARTI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR200" t="str">
             <v>SARTI</v>
@@ -7467,10 +7467,10 @@
             <v>R</v>
           </cell>
           <cell r="ID3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="IE3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="IF3" t="str">
             <v>P</v>
@@ -8656,11 +8656,11 @@
           <cell r="IC4" t="str">
             <v>f</v>
           </cell>
-          <cell r="ID4" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="IE4" t="str">
-            <v>f</v>
+          <cell r="ID4">
+            <v>0</v>
+          </cell>
+          <cell r="IE4">
+            <v>0</v>
           </cell>
           <cell r="IF4">
             <v>0</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -31088,11 +31088,11 @@
       </c>
       <c r="IA3" s="16" t="str">
         <f>[1]CARTELLINO!ID$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="IB3" s="16" t="str">
         <f>[1]CARTELLINO!IE$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="IC3" s="16" t="str">
         <f>[1]CARTELLINO!IF$3</f>
@@ -32680,13 +32680,13 @@
         <f>[1]CARTELLINO!IC$4</f>
         <v>f</v>
       </c>
-      <c r="IA4" s="43" t="str">
+      <c r="IA4" s="43">
         <f>[1]CARTELLINO!ID$4</f>
-        <v>f</v>
-      </c>
-      <c r="IB4" s="43" t="str">
+        <v>0</v>
+      </c>
+      <c r="IB4" s="43">
         <f>[1]CARTELLINO!IE$4</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="IC4" s="43">
         <f>[1]CARTELLINO!IF$4</f>
@@ -62689,7 +62689,7 @@
         <v>GHIOTTI</v>
       </c>
       <c r="GL29" s="63" t="str">
-        <v>SARTI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="GM29" s="63" t="str">
         <v>MICHELOT.</v>
@@ -65986,7 +65986,7 @@
         <v>GHIOTTI</v>
       </c>
       <c r="GK32" s="63" t="str">
-        <v>SARTI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="GL32" s="63" t="str">
         <v>MICHELOT.</v>
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,6 +71029,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71037,13 +71044,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92EE9F5E-BC1B-4AA7-A197-DFF0A0EC000E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{424E6C4F-9423-49A2-A395-3B119757C023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="75" windowWidth="28800" windowHeight="15405" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4225,7 +4225,7 @@
             <v>VOLPINI</v>
           </cell>
           <cell r="AR192" t="str">
-            <v>VOLPINI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS192" t="str">
             <v>FABBRI</v>
@@ -4295,7 +4295,7 @@
             <v>VOLPINI</v>
           </cell>
           <cell r="AR197" t="str">
-            <v>VOLPINI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS197" t="str">
             <v>FABBRI</v>
@@ -4578,18 +4578,18 @@
             <v>BARBIERI</v>
           </cell>
           <cell r="AS217" t="str">
-            <v>PAZZAGLIA</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT217" t="str">
-            <v>PAZZAGLIA</v>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="218">
           <cell r="AQ218" t="str">
-            <v>PAZZAGLIA</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR218" t="str">
-            <v>PAZZAGLIA</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS218" t="str">
             <v>GHIOTTI</v>
@@ -4900,18 +4900,18 @@
             <v>BIANCHI</v>
           </cell>
           <cell r="AS240" t="str">
-            <v>GHIOTTI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT240" t="str">
-            <v>GHIOTTI</v>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="241">
           <cell r="AQ241" t="str">
-            <v>GHIOTTI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR241" t="str">
-            <v>GHIOTTI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS241" t="str">
             <v>MICHELOT.</v>
@@ -4928,18 +4928,18 @@
             <v>MICHELOT.</v>
           </cell>
           <cell r="AS242" t="str">
-            <v>BARBIERI</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT242" t="str">
-            <v>BARBIERI</v>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="243">
           <cell r="AQ243" t="str">
-            <v>BARBIERI</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR243" t="str">
-            <v>BARBIERI</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS243" t="str">
             <v>SARTI</v>
@@ -5278,18 +5278,18 @@
             <v>GHIOTTI</v>
           </cell>
           <cell r="AS267" t="str">
-            <v>BARBIERI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT267" t="str">
-            <v>BARBIERI</v>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="268">
           <cell r="AQ268" t="str">
-            <v>BARBIERI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR268" t="str">
-            <v>BARBIERI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS268" t="str">
             <v>BERARDI</v>
@@ -5306,18 +5306,18 @@
             <v>BERARDI</v>
           </cell>
           <cell r="AS269" t="str">
-            <v>PAZZAGLIA</v>
+            <v>SARTI</v>
           </cell>
           <cell r="AT269" t="str">
-            <v>PAZZAGLIA</v>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="270">
           <cell r="AQ270" t="str">
-            <v>PAZZAGLIA</v>
+            <v>SARTI</v>
           </cell>
           <cell r="AR270" t="str">
-            <v>PAZZAGLIA</v>
+            <v>SARTI</v>
           </cell>
           <cell r="AS270" t="str">
             <v>BIANCHI</v>
@@ -5362,32 +5362,32 @@
             <v>FABBRI</v>
           </cell>
           <cell r="AS273" t="str">
-            <v>SARTI</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT273" t="str">
-            <v>SARTI</v>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="274">
           <cell r="AQ274" t="str">
-            <v>SARTI</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR274" t="str">
-            <v>SARTI</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS274" t="str">
-            <v>BARBIERI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT274" t="str">
-            <v>BARBIERI</v>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="275">
           <cell r="AQ275" t="str">
-            <v>BARBIERI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR275" t="str">
-            <v>BARBIERI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS275" t="str">
             <v>VOLPINI</v>
@@ -5446,32 +5446,32 @@
             <v>BERARDI</v>
           </cell>
           <cell r="AS279" t="str">
-            <v>SARTI</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT279" t="str">
-            <v>SARTI</v>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="280">
           <cell r="AQ280" t="str">
+            <v>BARBIERI</v>
+          </cell>
+          <cell r="AR280" t="str">
+            <v>BARBIERI</v>
+          </cell>
+          <cell r="AS280" t="str">
             <v>SARTI</v>
           </cell>
-          <cell r="AR280" t="str">
+          <cell r="AT280" t="str">
             <v>SARTI</v>
-          </cell>
-          <cell r="AS280" t="str">
-            <v>VOLPINI</v>
-          </cell>
-          <cell r="AT280" t="str">
-            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="281">
           <cell r="AQ281" t="str">
-            <v>VOLPINI</v>
+            <v>SARTI</v>
           </cell>
           <cell r="AR281" t="str">
-            <v>VOLPINI</v>
+            <v>SARTI</v>
           </cell>
           <cell r="AS281" t="str">
             <v>GHIOTTI</v>
@@ -5670,18 +5670,18 @@
             <v>SARTI</v>
           </cell>
           <cell r="AS295" t="str">
-            <v>VOLPINI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT295" t="str">
-            <v>VOLPINI</v>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="296">
           <cell r="AQ296" t="str">
-            <v>VOLPINI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR296" t="str">
-            <v>VOLPINI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS296" t="str">
             <v>BERARDI</v>
@@ -7395,7 +7395,7 @@
             <v>-</v>
           </cell>
           <cell r="HF3" t="str">
-            <v>m/R</v>
+            <v>m</v>
           </cell>
           <cell r="HG3" t="str">
             <v>p</v>
@@ -7440,37 +7440,37 @@
             <v>r</v>
           </cell>
           <cell r="HU3" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="HV3" t="str">
-            <v>m/R</v>
+            <v>M/R</v>
           </cell>
           <cell r="HW3" t="str">
             <v>-</v>
           </cell>
           <cell r="HX3" t="str">
+            <v>P</v>
+          </cell>
+          <cell r="HY3" t="str">
             <v>r</v>
           </cell>
-          <cell r="HY3" t="str">
-            <v>-</v>
-          </cell>
           <cell r="HZ3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="IA3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="IB3" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="IC3" t="str">
-            <v>R</v>
+            <v>r</v>
           </cell>
           <cell r="ID3" t="str">
             <v>m</v>
           </cell>
           <cell r="IE3" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="IF3" t="str">
             <v>P</v>
@@ -7539,52 +7539,52 @@
             <v>M/R</v>
           </cell>
           <cell r="JB3" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="JC3" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="JD3" t="str">
             <v>R</v>
           </cell>
           <cell r="JE3" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="JF3" t="str">
-            <v>M/R</v>
+            <v>-</v>
           </cell>
           <cell r="JG3" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="JH3" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="JI3" t="str">
             <v>R</v>
           </cell>
           <cell r="JJ3" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="JK3" t="str">
-            <v>-</v>
+            <v>M/R</v>
           </cell>
           <cell r="JL3" t="str">
-            <v>-</v>
+            <v>N</v>
           </cell>
           <cell r="JM3" t="str">
-            <v>-</v>
+            <v>S</v>
           </cell>
           <cell r="JN3" t="str">
             <v>R</v>
           </cell>
           <cell r="JO3" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="JP3" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="JQ3" t="str">
             <v>r</v>
-          </cell>
-          <cell r="JP3" t="str">
-            <v>r</v>
-          </cell>
-          <cell r="JQ3" t="str">
-            <v>m</v>
           </cell>
           <cell r="JR3" t="str">
             <v>p</v>
@@ -7626,31 +7626,31 @@
             <v>r</v>
           </cell>
           <cell r="KE3" t="str">
+            <v>P</v>
+          </cell>
+          <cell r="KF3" t="str">
+            <v>M/R</v>
+          </cell>
+          <cell r="KG3" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="KH3" t="str">
+            <v>S</v>
+          </cell>
+          <cell r="KI3" t="str">
+            <v>R</v>
+          </cell>
+          <cell r="KJ3" t="str">
+            <v>P</v>
+          </cell>
+          <cell r="KK3" t="str">
             <v>p</v>
           </cell>
-          <cell r="KF3" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="KG3" t="str">
+          <cell r="KL3" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="KM3" t="str">
             <v>r</v>
-          </cell>
-          <cell r="KH3" t="str">
-            <v>r</v>
-          </cell>
-          <cell r="KI3" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="KJ3" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="KK3" t="str">
-            <v>r</v>
-          </cell>
-          <cell r="KL3" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="KM3" t="str">
-            <v>m</v>
           </cell>
           <cell r="KN3" t="str">
             <v>p</v>
@@ -7722,16 +7722,16 @@
             <v>R</v>
           </cell>
           <cell r="LK3" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="LL3" t="str">
-            <v>M</v>
+            <v>-</v>
           </cell>
           <cell r="LM3" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="LN3" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="LO3" t="str">
             <v>R</v>
@@ -7779,7 +7779,7 @@
             <v>-</v>
           </cell>
           <cell r="MD3" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="ME3" t="str">
             <v>-</v>
@@ -7815,10 +7815,10 @@
             <v>M</v>
           </cell>
           <cell r="MP3" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="MQ3" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="MR3" t="str">
             <v>R</v>
@@ -7839,7 +7839,7 @@
             <v>R</v>
           </cell>
           <cell r="MX3" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="MY3" t="str">
             <v>M</v>
@@ -8641,291 +8641,291 @@
           <cell r="HX4">
             <v>0</v>
           </cell>
-          <cell r="HY4" t="str">
+          <cell r="HY4">
+            <v>0</v>
+          </cell>
+          <cell r="HZ4">
+            <v>0</v>
+          </cell>
+          <cell r="IA4">
+            <v>0</v>
+          </cell>
+          <cell r="IB4">
+            <v>0</v>
+          </cell>
+          <cell r="IC4">
+            <v>0</v>
+          </cell>
+          <cell r="ID4">
+            <v>0</v>
+          </cell>
+          <cell r="IE4">
+            <v>0</v>
+          </cell>
+          <cell r="IF4">
+            <v>0</v>
+          </cell>
+          <cell r="IG4">
+            <v>0</v>
+          </cell>
+          <cell r="IH4">
+            <v>0</v>
+          </cell>
+          <cell r="II4">
+            <v>0</v>
+          </cell>
+          <cell r="IJ4">
+            <v>0</v>
+          </cell>
+          <cell r="IK4">
+            <v>0</v>
+          </cell>
+          <cell r="IL4">
+            <v>0</v>
+          </cell>
+          <cell r="IM4">
+            <v>0</v>
+          </cell>
+          <cell r="IN4">
+            <v>0</v>
+          </cell>
+          <cell r="IO4">
+            <v>0</v>
+          </cell>
+          <cell r="IP4">
+            <v>0</v>
+          </cell>
+          <cell r="IQ4">
+            <v>0</v>
+          </cell>
+          <cell r="IR4">
+            <v>0</v>
+          </cell>
+          <cell r="IS4">
+            <v>0</v>
+          </cell>
+          <cell r="IT4">
+            <v>0</v>
+          </cell>
+          <cell r="IU4">
+            <v>0</v>
+          </cell>
+          <cell r="IV4">
+            <v>0</v>
+          </cell>
+          <cell r="IW4">
+            <v>0</v>
+          </cell>
+          <cell r="IX4">
+            <v>0</v>
+          </cell>
+          <cell r="IY4">
+            <v>0</v>
+          </cell>
+          <cell r="IZ4">
+            <v>0</v>
+          </cell>
+          <cell r="JA4">
+            <v>0</v>
+          </cell>
+          <cell r="JB4" t="str">
+            <v>pn</v>
+          </cell>
+          <cell r="JC4" t="str">
+            <v>x</v>
+          </cell>
+          <cell r="JD4">
+            <v>0</v>
+          </cell>
+          <cell r="JE4" t="str">
             <v>f</v>
           </cell>
-          <cell r="HZ4" t="str">
+          <cell r="JF4" t="str">
             <v>f</v>
           </cell>
-          <cell r="IA4" t="str">
+          <cell r="JG4" t="str">
             <v>f</v>
           </cell>
-          <cell r="IB4" t="str">
+          <cell r="JH4" t="str">
             <v>f</v>
           </cell>
-          <cell r="IC4" t="str">
+          <cell r="JI4" t="str">
             <v>f</v>
           </cell>
-          <cell r="ID4">
-            <v>0</v>
-          </cell>
-          <cell r="IE4">
-            <v>0</v>
-          </cell>
-          <cell r="IF4">
-            <v>0</v>
-          </cell>
-          <cell r="IG4">
-            <v>0</v>
-          </cell>
-          <cell r="IH4">
-            <v>0</v>
-          </cell>
-          <cell r="II4">
-            <v>0</v>
-          </cell>
-          <cell r="IJ4">
-            <v>0</v>
-          </cell>
-          <cell r="IK4">
-            <v>0</v>
-          </cell>
-          <cell r="IL4">
-            <v>0</v>
-          </cell>
-          <cell r="IM4">
-            <v>0</v>
-          </cell>
-          <cell r="IN4">
-            <v>0</v>
-          </cell>
-          <cell r="IO4">
-            <v>0</v>
-          </cell>
-          <cell r="IP4">
-            <v>0</v>
-          </cell>
-          <cell r="IQ4">
-            <v>0</v>
-          </cell>
-          <cell r="IR4">
-            <v>0</v>
-          </cell>
-          <cell r="IS4">
-            <v>0</v>
-          </cell>
-          <cell r="IT4">
-            <v>0</v>
-          </cell>
-          <cell r="IU4">
-            <v>0</v>
-          </cell>
-          <cell r="IV4">
-            <v>0</v>
-          </cell>
-          <cell r="IW4">
-            <v>0</v>
-          </cell>
-          <cell r="IX4">
-            <v>0</v>
-          </cell>
-          <cell r="IY4">
-            <v>0</v>
-          </cell>
-          <cell r="IZ4">
-            <v>0</v>
-          </cell>
-          <cell r="JA4">
-            <v>0</v>
-          </cell>
-          <cell r="JB4">
-            <v>0</v>
-          </cell>
-          <cell r="JC4">
-            <v>0</v>
-          </cell>
-          <cell r="JD4">
-            <v>0</v>
-          </cell>
-          <cell r="JE4">
-            <v>0</v>
-          </cell>
-          <cell r="JF4">
-            <v>0</v>
-          </cell>
-          <cell r="JG4">
-            <v>0</v>
-          </cell>
-          <cell r="JH4">
-            <v>0</v>
-          </cell>
-          <cell r="JI4">
-            <v>0</v>
-          </cell>
-          <cell r="JJ4" t="str">
+          <cell r="JJ4">
+            <v>0</v>
+          </cell>
+          <cell r="JK4">
+            <v>0</v>
+          </cell>
+          <cell r="JL4">
+            <v>0</v>
+          </cell>
+          <cell r="JM4">
+            <v>0</v>
+          </cell>
+          <cell r="JN4">
+            <v>0</v>
+          </cell>
+          <cell r="JO4">
+            <v>0</v>
+          </cell>
+          <cell r="JP4">
+            <v>0</v>
+          </cell>
+          <cell r="JQ4">
+            <v>0</v>
+          </cell>
+          <cell r="JR4">
+            <v>0</v>
+          </cell>
+          <cell r="JS4">
+            <v>0</v>
+          </cell>
+          <cell r="JT4">
+            <v>0</v>
+          </cell>
+          <cell r="JU4">
+            <v>0</v>
+          </cell>
+          <cell r="JV4">
+            <v>0</v>
+          </cell>
+          <cell r="JW4">
+            <v>0</v>
+          </cell>
+          <cell r="JX4">
+            <v>0</v>
+          </cell>
+          <cell r="JY4">
+            <v>0</v>
+          </cell>
+          <cell r="JZ4">
+            <v>0</v>
+          </cell>
+          <cell r="KA4">
+            <v>0</v>
+          </cell>
+          <cell r="KB4">
+            <v>0</v>
+          </cell>
+          <cell r="KC4">
+            <v>0</v>
+          </cell>
+          <cell r="KD4">
+            <v>0</v>
+          </cell>
+          <cell r="KE4">
+            <v>0</v>
+          </cell>
+          <cell r="KF4">
+            <v>0</v>
+          </cell>
+          <cell r="KG4">
+            <v>0</v>
+          </cell>
+          <cell r="KH4">
+            <v>0</v>
+          </cell>
+          <cell r="KI4">
+            <v>0</v>
+          </cell>
+          <cell r="KJ4">
+            <v>0</v>
+          </cell>
+          <cell r="KK4">
+            <v>0</v>
+          </cell>
+          <cell r="KL4">
+            <v>0</v>
+          </cell>
+          <cell r="KM4">
+            <v>0</v>
+          </cell>
+          <cell r="KN4">
+            <v>0</v>
+          </cell>
+          <cell r="KO4">
+            <v>0</v>
+          </cell>
+          <cell r="KP4">
+            <v>0</v>
+          </cell>
+          <cell r="KQ4">
+            <v>0</v>
+          </cell>
+          <cell r="KR4">
+            <v>0</v>
+          </cell>
+          <cell r="KS4">
+            <v>0</v>
+          </cell>
+          <cell r="KT4">
+            <v>0</v>
+          </cell>
+          <cell r="KU4">
+            <v>0</v>
+          </cell>
+          <cell r="KV4">
+            <v>0</v>
+          </cell>
+          <cell r="KW4">
+            <v>0</v>
+          </cell>
+          <cell r="KX4">
+            <v>0</v>
+          </cell>
+          <cell r="KY4">
+            <v>0</v>
+          </cell>
+          <cell r="KZ4">
+            <v>0</v>
+          </cell>
+          <cell r="LA4">
+            <v>0</v>
+          </cell>
+          <cell r="LB4">
+            <v>0</v>
+          </cell>
+          <cell r="LC4">
+            <v>0</v>
+          </cell>
+          <cell r="LD4">
+            <v>0</v>
+          </cell>
+          <cell r="LE4">
+            <v>0</v>
+          </cell>
+          <cell r="LF4">
+            <v>0</v>
+          </cell>
+          <cell r="LG4">
+            <v>0</v>
+          </cell>
+          <cell r="LH4">
+            <v>0</v>
+          </cell>
+          <cell r="LI4">
+            <v>0</v>
+          </cell>
+          <cell r="LJ4">
+            <v>0</v>
+          </cell>
+          <cell r="LK4" t="str">
             <v>f</v>
           </cell>
-          <cell r="JK4" t="str">
+          <cell r="LL4" t="str">
             <v>f</v>
           </cell>
-          <cell r="JL4" t="str">
+          <cell r="LM4" t="str">
             <v>f</v>
           </cell>
-          <cell r="JM4" t="str">
+          <cell r="LN4" t="str">
             <v>f</v>
           </cell>
-          <cell r="JN4" t="str">
+          <cell r="LO4" t="str">
             <v>f</v>
           </cell>
-          <cell r="JO4">
-            <v>0</v>
-          </cell>
-          <cell r="JP4">
-            <v>0</v>
-          </cell>
-          <cell r="JQ4">
-            <v>0</v>
-          </cell>
-          <cell r="JR4">
-            <v>0</v>
-          </cell>
-          <cell r="JS4">
-            <v>0</v>
-          </cell>
-          <cell r="JT4">
-            <v>0</v>
-          </cell>
-          <cell r="JU4">
-            <v>0</v>
-          </cell>
-          <cell r="JV4">
-            <v>0</v>
-          </cell>
-          <cell r="JW4">
-            <v>0</v>
-          </cell>
-          <cell r="JX4">
-            <v>0</v>
-          </cell>
-          <cell r="JY4">
-            <v>0</v>
-          </cell>
-          <cell r="JZ4">
-            <v>0</v>
-          </cell>
-          <cell r="KA4">
-            <v>0</v>
-          </cell>
-          <cell r="KB4">
-            <v>0</v>
-          </cell>
-          <cell r="KC4">
-            <v>0</v>
-          </cell>
-          <cell r="KD4">
-            <v>0</v>
-          </cell>
-          <cell r="KE4">
-            <v>0</v>
-          </cell>
-          <cell r="KF4">
-            <v>0</v>
-          </cell>
-          <cell r="KG4">
-            <v>0</v>
-          </cell>
-          <cell r="KH4">
-            <v>0</v>
-          </cell>
-          <cell r="KI4">
-            <v>0</v>
-          </cell>
-          <cell r="KJ4">
-            <v>0</v>
-          </cell>
-          <cell r="KK4">
-            <v>0</v>
-          </cell>
-          <cell r="KL4">
-            <v>0</v>
-          </cell>
-          <cell r="KM4">
-            <v>0</v>
-          </cell>
-          <cell r="KN4">
-            <v>0</v>
-          </cell>
-          <cell r="KO4">
-            <v>0</v>
-          </cell>
-          <cell r="KP4">
-            <v>0</v>
-          </cell>
-          <cell r="KQ4">
-            <v>0</v>
-          </cell>
-          <cell r="KR4">
-            <v>0</v>
-          </cell>
-          <cell r="KS4">
-            <v>0</v>
-          </cell>
-          <cell r="KT4">
-            <v>0</v>
-          </cell>
-          <cell r="KU4">
-            <v>0</v>
-          </cell>
-          <cell r="KV4">
-            <v>0</v>
-          </cell>
-          <cell r="KW4">
-            <v>0</v>
-          </cell>
-          <cell r="KX4">
-            <v>0</v>
-          </cell>
-          <cell r="KY4">
-            <v>0</v>
-          </cell>
-          <cell r="KZ4">
-            <v>0</v>
-          </cell>
-          <cell r="LA4">
-            <v>0</v>
-          </cell>
-          <cell r="LB4">
-            <v>0</v>
-          </cell>
-          <cell r="LC4">
-            <v>0</v>
-          </cell>
-          <cell r="LD4">
-            <v>0</v>
-          </cell>
-          <cell r="LE4">
-            <v>0</v>
-          </cell>
-          <cell r="LF4">
-            <v>0</v>
-          </cell>
-          <cell r="LG4">
-            <v>0</v>
-          </cell>
-          <cell r="LH4">
-            <v>0</v>
-          </cell>
-          <cell r="LI4">
-            <v>0</v>
-          </cell>
-          <cell r="LJ4">
-            <v>0</v>
-          </cell>
-          <cell r="LK4">
-            <v>0</v>
-          </cell>
-          <cell r="LL4">
-            <v>0</v>
-          </cell>
-          <cell r="LM4">
-            <v>0</v>
-          </cell>
-          <cell r="LN4">
-            <v>0</v>
-          </cell>
-          <cell r="LO4">
-            <v>0</v>
-          </cell>
           <cell r="LP4">
             <v>0</v>
           </cell>
@@ -8956,20 +8956,20 @@
           <cell r="LY4">
             <v>0</v>
           </cell>
-          <cell r="LZ4">
-            <v>0</v>
-          </cell>
-          <cell r="MA4">
-            <v>0</v>
-          </cell>
-          <cell r="MB4">
-            <v>0</v>
-          </cell>
-          <cell r="MC4">
-            <v>0</v>
-          </cell>
-          <cell r="MD4">
-            <v>0</v>
+          <cell r="LZ4" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="MA4" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="MB4" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="MC4" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="MD4" t="str">
+            <v>f</v>
           </cell>
           <cell r="ME4">
             <v>0</v>
@@ -9004,14 +9004,14 @@
           <cell r="MO4">
             <v>0</v>
           </cell>
-          <cell r="MP4">
-            <v>0</v>
-          </cell>
-          <cell r="MQ4">
-            <v>0</v>
-          </cell>
-          <cell r="MR4">
-            <v>0</v>
+          <cell r="MP4" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="MQ4" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="MR4" t="str">
+            <v>f</v>
           </cell>
           <cell r="MS4" t="str">
             <v>f</v>
@@ -9028,8 +9028,8 @@
           <cell r="MW4" t="str">
             <v>f</v>
           </cell>
-          <cell r="MX4">
-            <v>0</v>
+          <cell r="MX4" t="str">
+            <v>f</v>
           </cell>
           <cell r="MY4">
             <v>0</v>
@@ -9811,16 +9811,16 @@
             <v>m</v>
           </cell>
           <cell r="HS6" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="HT6" t="str">
+            <v>S</v>
+          </cell>
+          <cell r="HU6" t="str">
+            <v>R</v>
+          </cell>
+          <cell r="HV6" t="str">
             <v>p</v>
-          </cell>
-          <cell r="HT6" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="HU6" t="str">
-            <v>r</v>
-          </cell>
-          <cell r="HV6" t="str">
-            <v>r</v>
           </cell>
           <cell r="HW6" t="str">
             <v>p</v>
@@ -9844,16 +9844,16 @@
             <v>R</v>
           </cell>
           <cell r="ID6" t="str">
-            <v>r</v>
+            <v>-</v>
           </cell>
           <cell r="IE6" t="str">
-            <v>M/R</v>
+            <v>-</v>
           </cell>
           <cell r="IF6" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="IG6" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="IH6" t="str">
             <v>R</v>
@@ -9889,7 +9889,7 @@
             <v>R</v>
           </cell>
           <cell r="IS6" t="str">
-            <v>P</v>
+            <v>r</v>
           </cell>
           <cell r="IT6" t="str">
             <v>M/R</v>
@@ -9922,7 +9922,7 @@
             <v>P</v>
           </cell>
           <cell r="JD6" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="JE6" t="str">
             <v>N</v>
@@ -9937,37 +9937,37 @@
             <v>m</v>
           </cell>
           <cell r="JI6" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="JJ6" t="str">
+            <v>m/R</v>
+          </cell>
+          <cell r="JK6" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="JL6" t="str">
+            <v>r</v>
+          </cell>
+          <cell r="JM6" t="str">
+            <v>r</v>
+          </cell>
+          <cell r="JN6" t="str">
+            <v>r</v>
+          </cell>
+          <cell r="JO6" t="str">
             <v>P</v>
           </cell>
-          <cell r="JK6" t="str">
+          <cell r="JP6" t="str">
             <v>M/R</v>
           </cell>
-          <cell r="JL6" t="str">
-            <v>N</v>
-          </cell>
-          <cell r="JM6" t="str">
-            <v>S</v>
-          </cell>
-          <cell r="JN6" t="str">
-            <v>R</v>
-          </cell>
-          <cell r="JO6" t="str">
+          <cell r="JQ6" t="str">
             <v>p</v>
-          </cell>
-          <cell r="JP6" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="JQ6" t="str">
-            <v>r</v>
           </cell>
           <cell r="JR6" t="str">
             <v>-</v>
           </cell>
           <cell r="JS6" t="str">
-            <v>p</v>
+            <v>r</v>
           </cell>
           <cell r="JT6" t="str">
             <v>p</v>
@@ -10003,7 +10003,7 @@
             <v>M/R</v>
           </cell>
           <cell r="KE6" t="str">
-            <v>P</v>
+            <v>p</v>
           </cell>
           <cell r="KF6" t="str">
             <v>m</v>
@@ -10018,7 +10018,7 @@
             <v>r</v>
           </cell>
           <cell r="KJ6" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="KK6" t="str">
             <v>M/R</v>
@@ -10192,13 +10192,13 @@
             <v>-</v>
           </cell>
           <cell r="MP6" t="str">
-            <v>-</v>
+            <v>N</v>
           </cell>
           <cell r="MQ6" t="str">
-            <v>-</v>
+            <v>S</v>
           </cell>
           <cell r="MR6" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="MS6" t="str">
             <v>P</v>
@@ -10216,7 +10216,7 @@
             <v>R</v>
           </cell>
           <cell r="MX6" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="MY6" t="str">
             <v>m</v>
@@ -11033,20 +11033,20 @@
           <cell r="IC7">
             <v>0</v>
           </cell>
-          <cell r="ID7">
-            <v>0</v>
-          </cell>
-          <cell r="IE7">
-            <v>0</v>
-          </cell>
-          <cell r="IF7">
-            <v>0</v>
-          </cell>
-          <cell r="IG7">
-            <v>0</v>
-          </cell>
-          <cell r="IH7">
-            <v>0</v>
+          <cell r="ID7" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="IE7" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="IF7" t="str">
+            <v>pn</v>
+          </cell>
+          <cell r="IG7" t="str">
+            <v>x</v>
+          </cell>
+          <cell r="IH7" t="str">
+            <v>f</v>
           </cell>
           <cell r="II7" t="str">
             <v>f</v>
@@ -12197,10 +12197,10 @@
             <v>R</v>
           </cell>
           <cell r="HU9" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="HV9" t="str">
-            <v>M</v>
+            <v>-</v>
           </cell>
           <cell r="HW9" t="str">
             <v>N</v>
@@ -12260,7 +12260,7 @@
             <v>m</v>
           </cell>
           <cell r="IP9" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="IQ9" t="str">
             <v>N</v>
@@ -12308,22 +12308,22 @@
             <v>m</v>
           </cell>
           <cell r="JF9" t="str">
+            <v>M/R</v>
+          </cell>
+          <cell r="JG9" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="JH9" t="str">
+            <v>S</v>
+          </cell>
+          <cell r="JI9" t="str">
+            <v>R</v>
+          </cell>
+          <cell r="JJ9" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="JK9" t="str">
             <v>m</v>
-          </cell>
-          <cell r="JG9" t="str">
-            <v>r</v>
-          </cell>
-          <cell r="JH9" t="str">
-            <v>r</v>
-          </cell>
-          <cell r="JI9" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="JJ9" t="str">
-            <v>m/R</v>
-          </cell>
-          <cell r="JK9" t="str">
-            <v>p</v>
           </cell>
           <cell r="JL9" t="str">
             <v>m</v>
@@ -12332,28 +12332,28 @@
             <v>r</v>
           </cell>
           <cell r="JN9" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="JO9" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="JP9" t="str">
+            <v>P</v>
+          </cell>
+          <cell r="JQ9" t="str">
+            <v>m/R</v>
+          </cell>
+          <cell r="JR9" t="str">
             <v>m</v>
           </cell>
-          <cell r="JO9" t="str">
-            <v>P</v>
-          </cell>
-          <cell r="JP9" t="str">
-            <v>M/R</v>
-          </cell>
-          <cell r="JQ9" t="str">
-            <v>N</v>
-          </cell>
-          <cell r="JR9" t="str">
-            <v>S</v>
-          </cell>
           <cell r="JS9" t="str">
-            <v>R</v>
+            <v>p</v>
           </cell>
           <cell r="JT9" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JU9" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JV9" t="str">
             <v>N</v>
@@ -13162,10 +13162,10 @@
             <v>0</v>
           </cell>
           <cell r="EX10" t="str">
-            <v>pn</v>
+            <v>f</v>
           </cell>
           <cell r="EY10" t="str">
-            <v>x</v>
+            <v>f</v>
           </cell>
           <cell r="EZ10">
             <v>0</v>
@@ -13386,11 +13386,11 @@
           <cell r="HT10">
             <v>0</v>
           </cell>
-          <cell r="HU10">
-            <v>0</v>
-          </cell>
-          <cell r="HV10">
-            <v>0</v>
+          <cell r="HU10" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="HV10" t="str">
+            <v>p</v>
           </cell>
           <cell r="HW10">
             <v>0</v>
@@ -13521,11 +13521,11 @@
           <cell r="JM10">
             <v>0</v>
           </cell>
-          <cell r="JN10">
-            <v>0</v>
-          </cell>
-          <cell r="JO10">
-            <v>0</v>
+          <cell r="JN10" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="JO10" t="str">
+            <v>p</v>
           </cell>
           <cell r="JP10">
             <v>0</v>
@@ -13539,11 +13539,11 @@
           <cell r="JS10">
             <v>0</v>
           </cell>
-          <cell r="JT10" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="JU10" t="str">
-            <v>p</v>
+          <cell r="JT10">
+            <v>0</v>
+          </cell>
+          <cell r="JU10">
+            <v>0</v>
           </cell>
           <cell r="JV10">
             <v>0</v>
@@ -14472,7 +14472,7 @@
             <v>m/R</v>
           </cell>
           <cell r="GL12" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="GM12" t="str">
             <v>p</v>
@@ -14532,7 +14532,7 @@
             <v>P</v>
           </cell>
           <cell r="HF12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="HG12" t="str">
             <v>N</v>
@@ -14595,19 +14595,19 @@
             <v>m</v>
           </cell>
           <cell r="IA12" t="str">
+            <v>r</v>
+          </cell>
+          <cell r="IB12" t="str">
             <v>p</v>
           </cell>
-          <cell r="IB12" t="str">
+          <cell r="IC12" t="str">
+            <v>m/R</v>
+          </cell>
+          <cell r="ID12" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="IE12" t="str">
             <v>m</v>
-          </cell>
-          <cell r="IC12" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="ID12" t="str">
-            <v>P</v>
-          </cell>
-          <cell r="IE12" t="str">
-            <v>r</v>
           </cell>
           <cell r="IF12" t="str">
             <v>-</v>
@@ -14673,25 +14673,25 @@
             <v>R</v>
           </cell>
           <cell r="JA12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JB12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JC12" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="JD12" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="JE12" t="str">
-            <v>R</v>
+            <v>p</v>
           </cell>
           <cell r="JF12" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JG12" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JH12" t="str">
             <v>N</v>
@@ -14718,10 +14718,10 @@
             <v>R</v>
           </cell>
           <cell r="JP12" t="str">
-            <v>P</v>
+            <v>r</v>
           </cell>
           <cell r="JQ12" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="JR12" t="str">
             <v>N</v>
@@ -14763,31 +14763,31 @@
             <v>R</v>
           </cell>
           <cell r="KE12" t="str">
-            <v>r</v>
+            <v>-</v>
           </cell>
           <cell r="KF12" t="str">
-            <v>M/R</v>
+            <v>-</v>
           </cell>
           <cell r="KG12" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="KH12" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="KI12" t="str">
             <v>R</v>
           </cell>
           <cell r="KJ12" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="KK12" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="KL12" t="str">
             <v>p</v>
           </cell>
-          <cell r="KL12" t="str">
+          <cell r="KM12" t="str">
             <v>m</v>
-          </cell>
-          <cell r="KM12" t="str">
-            <v>r</v>
           </cell>
           <cell r="KN12" t="str">
             <v>r</v>
@@ -15862,116 +15862,116 @@
           <cell r="IZ13">
             <v>0</v>
           </cell>
-          <cell r="JA13" t="str">
+          <cell r="JA13">
+            <v>0</v>
+          </cell>
+          <cell r="JB13">
+            <v>0</v>
+          </cell>
+          <cell r="JC13">
+            <v>0</v>
+          </cell>
+          <cell r="JD13">
+            <v>0</v>
+          </cell>
+          <cell r="JE13">
+            <v>0</v>
+          </cell>
+          <cell r="JF13">
+            <v>0</v>
+          </cell>
+          <cell r="JG13">
+            <v>0</v>
+          </cell>
+          <cell r="JH13">
+            <v>0</v>
+          </cell>
+          <cell r="JI13">
+            <v>0</v>
+          </cell>
+          <cell r="JJ13">
+            <v>0</v>
+          </cell>
+          <cell r="JK13">
+            <v>0</v>
+          </cell>
+          <cell r="JL13">
+            <v>0</v>
+          </cell>
+          <cell r="JM13">
+            <v>0</v>
+          </cell>
+          <cell r="JN13">
+            <v>0</v>
+          </cell>
+          <cell r="JO13">
+            <v>0</v>
+          </cell>
+          <cell r="JP13">
+            <v>0</v>
+          </cell>
+          <cell r="JQ13">
+            <v>0</v>
+          </cell>
+          <cell r="JR13">
+            <v>0</v>
+          </cell>
+          <cell r="JS13">
+            <v>0</v>
+          </cell>
+          <cell r="JT13">
+            <v>0</v>
+          </cell>
+          <cell r="JU13">
+            <v>0</v>
+          </cell>
+          <cell r="JV13">
+            <v>0</v>
+          </cell>
+          <cell r="JW13">
+            <v>0</v>
+          </cell>
+          <cell r="JX13">
+            <v>0</v>
+          </cell>
+          <cell r="JY13">
+            <v>0</v>
+          </cell>
+          <cell r="JZ13">
+            <v>0</v>
+          </cell>
+          <cell r="KA13">
+            <v>0</v>
+          </cell>
+          <cell r="KB13">
+            <v>0</v>
+          </cell>
+          <cell r="KC13">
+            <v>0</v>
+          </cell>
+          <cell r="KD13">
+            <v>0</v>
+          </cell>
+          <cell r="KE13" t="str">
             <v>f</v>
           </cell>
-          <cell r="JB13" t="str">
+          <cell r="KF13" t="str">
             <v>f</v>
           </cell>
-          <cell r="JC13" t="str">
+          <cell r="KG13" t="str">
             <v>f</v>
           </cell>
-          <cell r="JD13" t="str">
+          <cell r="KH13" t="str">
             <v>f</v>
           </cell>
-          <cell r="JE13" t="str">
+          <cell r="KI13" t="str">
             <v>f</v>
           </cell>
-          <cell r="JF13" t="str">
+          <cell r="KJ13" t="str">
             <v>f</v>
           </cell>
-          <cell r="JG13" t="str">
+          <cell r="KK13" t="str">
             <v>f</v>
-          </cell>
-          <cell r="JH13">
-            <v>0</v>
-          </cell>
-          <cell r="JI13">
-            <v>0</v>
-          </cell>
-          <cell r="JJ13">
-            <v>0</v>
-          </cell>
-          <cell r="JK13">
-            <v>0</v>
-          </cell>
-          <cell r="JL13">
-            <v>0</v>
-          </cell>
-          <cell r="JM13">
-            <v>0</v>
-          </cell>
-          <cell r="JN13">
-            <v>0</v>
-          </cell>
-          <cell r="JO13">
-            <v>0</v>
-          </cell>
-          <cell r="JP13">
-            <v>0</v>
-          </cell>
-          <cell r="JQ13">
-            <v>0</v>
-          </cell>
-          <cell r="JR13">
-            <v>0</v>
-          </cell>
-          <cell r="JS13">
-            <v>0</v>
-          </cell>
-          <cell r="JT13">
-            <v>0</v>
-          </cell>
-          <cell r="JU13">
-            <v>0</v>
-          </cell>
-          <cell r="JV13">
-            <v>0</v>
-          </cell>
-          <cell r="JW13">
-            <v>0</v>
-          </cell>
-          <cell r="JX13">
-            <v>0</v>
-          </cell>
-          <cell r="JY13">
-            <v>0</v>
-          </cell>
-          <cell r="JZ13">
-            <v>0</v>
-          </cell>
-          <cell r="KA13">
-            <v>0</v>
-          </cell>
-          <cell r="KB13">
-            <v>0</v>
-          </cell>
-          <cell r="KC13">
-            <v>0</v>
-          </cell>
-          <cell r="KD13">
-            <v>0</v>
-          </cell>
-          <cell r="KE13">
-            <v>0</v>
-          </cell>
-          <cell r="KF13">
-            <v>0</v>
-          </cell>
-          <cell r="KG13">
-            <v>0</v>
-          </cell>
-          <cell r="KH13">
-            <v>0</v>
-          </cell>
-          <cell r="KI13">
-            <v>0</v>
-          </cell>
-          <cell r="KJ13">
-            <v>0</v>
-          </cell>
-          <cell r="KK13">
-            <v>0</v>
           </cell>
           <cell r="KL13">
             <v>0</v>
@@ -16966,37 +16966,37 @@
             <v>-</v>
           </cell>
           <cell r="HX15" t="str">
-            <v>P</v>
+            <v>r</v>
           </cell>
           <cell r="HY15" t="str">
             <v>r</v>
           </cell>
           <cell r="HZ15" t="str">
+            <v>r</v>
+          </cell>
+          <cell r="IA15" t="str">
             <v>p</v>
           </cell>
-          <cell r="IA15" t="str">
+          <cell r="IB15" t="str">
             <v>m</v>
           </cell>
-          <cell r="IB15" t="str">
+          <cell r="IC15" t="str">
             <v>p</v>
           </cell>
-          <cell r="IC15" t="str">
-            <v>m/R</v>
-          </cell>
           <cell r="ID15" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="IE15" t="str">
-            <v>r</v>
+            <v>M/R</v>
           </cell>
           <cell r="IF15" t="str">
-            <v>r</v>
+            <v>N</v>
           </cell>
           <cell r="IG15" t="str">
-            <v>p</v>
+            <v>S</v>
           </cell>
           <cell r="IH15" t="str">
-            <v>m</v>
+            <v>R</v>
           </cell>
           <cell r="II15" t="str">
             <v>m/R</v>
@@ -19232,7 +19232,7 @@
             <v>p</v>
           </cell>
           <cell r="GL18" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="GM18" t="str">
             <v>m</v>
@@ -19427,7 +19427,7 @@
             <v>R</v>
           </cell>
           <cell r="IY18" t="str">
-            <v>p</v>
+            <v>r</v>
           </cell>
           <cell r="IZ18" t="str">
             <v>p</v>
@@ -19436,7 +19436,7 @@
             <v>m</v>
           </cell>
           <cell r="JB18" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="JC18" t="str">
             <v>-</v>
@@ -21720,7 +21720,7 @@
             <v>m/R</v>
           </cell>
           <cell r="HV21" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="HW21" t="str">
             <v>m</v>
@@ -21747,16 +21747,16 @@
             <v>R</v>
           </cell>
           <cell r="IE21" t="str">
-            <v>P</v>
+            <v>r</v>
           </cell>
           <cell r="IF21" t="str">
             <v>m</v>
           </cell>
           <cell r="IG21" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="IH21" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="II21" t="str">
             <v>P</v>
@@ -21774,7 +21774,7 @@
             <v>R</v>
           </cell>
           <cell r="IN21" t="str">
-            <v>p</v>
+            <v>r</v>
           </cell>
           <cell r="IO21" t="str">
             <v>m/R</v>
@@ -24091,16 +24091,16 @@
             <v>M/R</v>
           </cell>
           <cell r="HS24" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="HT24" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="HU24" t="str">
             <v>R</v>
           </cell>
           <cell r="HV24" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="HW24" t="str">
             <v>M/R</v>
@@ -24169,7 +24169,7 @@
             <v>R</v>
           </cell>
           <cell r="IS24" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="IT24" t="str">
             <v>m</v>
@@ -24193,7 +24193,7 @@
             <v>r</v>
           </cell>
           <cell r="JA24" t="str">
-            <v>P</v>
+            <v>r</v>
           </cell>
           <cell r="JB24" t="str">
             <v>M/R</v>
@@ -24217,13 +24217,13 @@
             <v>p</v>
           </cell>
           <cell r="JI24" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="JJ24" t="str">
             <v>r</v>
           </cell>
-          <cell r="JJ24" t="str">
-            <v>p</v>
-          </cell>
           <cell r="JK24" t="str">
-            <v>m</v>
+            <v>r</v>
           </cell>
           <cell r="JL24" t="str">
             <v>p</v>
@@ -24232,7 +24232,7 @@
             <v>p</v>
           </cell>
           <cell r="JN24" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="JO24" t="str">
             <v>r</v>
@@ -24241,13 +24241,13 @@
             <v>p</v>
           </cell>
           <cell r="JQ24" t="str">
-            <v>p</v>
+            <v>N</v>
           </cell>
           <cell r="JR24" t="str">
-            <v>m</v>
+            <v>S</v>
           </cell>
           <cell r="JS24" t="str">
-            <v>r</v>
+            <v>R</v>
           </cell>
           <cell r="JT24" t="str">
             <v>P</v>
@@ -25280,17 +25280,17 @@
           <cell r="HR25">
             <v>0</v>
           </cell>
-          <cell r="HS25">
-            <v>0</v>
-          </cell>
-          <cell r="HT25">
-            <v>0</v>
-          </cell>
-          <cell r="HU25">
-            <v>0</v>
-          </cell>
-          <cell r="HV25">
-            <v>0</v>
+          <cell r="HS25" t="str">
+            <v>pn</v>
+          </cell>
+          <cell r="HT25" t="str">
+            <v>x</v>
+          </cell>
+          <cell r="HU25" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="HV25" t="str">
+            <v>f</v>
           </cell>
           <cell r="HW25">
             <v>0</v>
@@ -26573,22 +26573,22 @@
             <v>R</v>
           </cell>
           <cell r="JA27" t="str">
+            <v>P</v>
+          </cell>
+          <cell r="JB27" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="JC27" t="str">
+            <v>S</v>
+          </cell>
+          <cell r="JD27" t="str">
+            <v>R</v>
+          </cell>
+          <cell r="JE27" t="str">
+            <v>P</v>
+          </cell>
+          <cell r="JF27" t="str">
             <v>p</v>
-          </cell>
-          <cell r="JB27" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="JC27" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="JD27" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="JE27" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="JF27" t="str">
-            <v>r</v>
           </cell>
           <cell r="JG27" t="str">
             <v>r</v>
@@ -26759,16 +26759,16 @@
             <v>-</v>
           </cell>
           <cell r="LK27" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="LL27" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="LM27" t="str">
-            <v>-</v>
+            <v>N</v>
           </cell>
           <cell r="LN27" t="str">
-            <v>-</v>
+            <v>S</v>
           </cell>
           <cell r="LO27" t="str">
             <v>-</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -30992,7 +30992,7 @@
       </c>
       <c r="HC3" s="16" t="str">
         <f>[1]CARTELLINO!HF$3</f>
-        <v>m/R</v>
+        <v>m</v>
       </c>
       <c r="HD3" s="16" t="str">
         <f>[1]CARTELLINO!HG$3</f>
@@ -31052,11 +31052,11 @@
       </c>
       <c r="HR3" s="16" t="str">
         <f>[1]CARTELLINO!HU$3</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="HS3" s="16" t="str">
         <f>[1]CARTELLINO!HV$3</f>
-        <v>m/R</v>
+        <v>M/R</v>
       </c>
       <c r="HT3" s="16" t="str">
         <f>[1]CARTELLINO!HW$3</f>
@@ -31064,27 +31064,27 @@
       </c>
       <c r="HU3" s="16" t="str">
         <f>[1]CARTELLINO!HX$3</f>
-        <v>r</v>
+        <v>P</v>
       </c>
       <c r="HV3" s="16" t="str">
         <f>[1]CARTELLINO!HY$3</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="HW3" s="16" t="str">
         <f>[1]CARTELLINO!HZ$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="HX3" s="16" t="str">
         <f>[1]CARTELLINO!IA$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="HY3" s="16" t="str">
         <f>[1]CARTELLINO!IB$3</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="HZ3" s="16" t="str">
         <f>[1]CARTELLINO!IC$3</f>
-        <v>R</v>
+        <v>r</v>
       </c>
       <c r="IA3" s="16" t="str">
         <f>[1]CARTELLINO!ID$3</f>
@@ -31092,7 +31092,7 @@
       </c>
       <c r="IB3" s="16" t="str">
         <f>[1]CARTELLINO!IE$3</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="IC3" s="16" t="str">
         <f>[1]CARTELLINO!IF$3</f>
@@ -31184,11 +31184,11 @@
       </c>
       <c r="IY3" s="16" t="str">
         <f>[1]CARTELLINO!JB$3</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="IZ3" s="16" t="str">
         <f>[1]CARTELLINO!JC$3</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="JA3" s="16" t="str">
         <f>[1]CARTELLINO!JD$3</f>
@@ -31196,19 +31196,19 @@
       </c>
       <c r="JB3" s="16" t="str">
         <f>[1]CARTELLINO!JE$3</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="JC3" s="16" t="str">
         <f>[1]CARTELLINO!JF$3</f>
-        <v>M/R</v>
+        <v>-</v>
       </c>
       <c r="JD3" s="16" t="str">
         <f>[1]CARTELLINO!JG$3</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="JE3" s="16" t="str">
         <f>[1]CARTELLINO!JH$3</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="JF3" s="16" t="str">
         <f>[1]CARTELLINO!JI$3</f>
@@ -31216,19 +31216,19 @@
       </c>
       <c r="JG3" s="16" t="str">
         <f>[1]CARTELLINO!JJ$3</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="JH3" s="16" t="str">
         <f>[1]CARTELLINO!JK$3</f>
-        <v>-</v>
+        <v>M/R</v>
       </c>
       <c r="JI3" s="16" t="str">
         <f>[1]CARTELLINO!JL$3</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="JJ3" s="16" t="str">
         <f>[1]CARTELLINO!JM$3</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="JK3" s="16" t="str">
         <f>[1]CARTELLINO!JN$3</f>
@@ -31236,15 +31236,15 @@
       </c>
       <c r="JL3" s="16" t="str">
         <f>[1]CARTELLINO!JO$3</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="JM3" s="16" t="str">
         <f>[1]CARTELLINO!JP$3</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="JN3" s="16" t="str">
         <f>[1]CARTELLINO!JQ$3</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="JO3" s="16" t="str">
         <f>[1]CARTELLINO!JR$3</f>
@@ -31300,39 +31300,39 @@
       </c>
       <c r="KB3" s="16" t="str">
         <f>[1]CARTELLINO!KE$3</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="KC3" s="16" t="str">
         <f>[1]CARTELLINO!KF$3</f>
-        <v>p</v>
+        <v>M/R</v>
       </c>
       <c r="KD3" s="16" t="str">
         <f>[1]CARTELLINO!KG$3</f>
-        <v>r</v>
+        <v>N</v>
       </c>
       <c r="KE3" s="16" t="str">
         <f>[1]CARTELLINO!KH$3</f>
-        <v>r</v>
+        <v>S</v>
       </c>
       <c r="KF3" s="16" t="str">
         <f>[1]CARTELLINO!KI$3</f>
-        <v>p</v>
+        <v>R</v>
       </c>
       <c r="KG3" s="16" t="str">
         <f>[1]CARTELLINO!KJ$3</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="KH3" s="16" t="str">
         <f>[1]CARTELLINO!KK$3</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="KI3" s="16" t="str">
         <f>[1]CARTELLINO!KL$3</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="KJ3" s="16" t="str">
         <f>[1]CARTELLINO!KM$3</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="KK3" s="16" t="str">
         <f>[1]CARTELLINO!KN$3</f>
@@ -31428,19 +31428,19 @@
       </c>
       <c r="LH3" s="16" t="str">
         <f>[1]CARTELLINO!LK$3</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="LI3" s="16" t="str">
         <f>[1]CARTELLINO!LL$3</f>
-        <v>M</v>
+        <v>-</v>
       </c>
       <c r="LJ3" s="16" t="str">
         <f>[1]CARTELLINO!LM$3</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="LK3" s="16" t="str">
         <f>[1]CARTELLINO!LN$3</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="LL3" s="16" t="str">
         <f>[1]CARTELLINO!LO$3</f>
@@ -31504,7 +31504,7 @@
       </c>
       <c r="MA3" s="16" t="str">
         <f>[1]CARTELLINO!MD$3</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="MB3" s="16" t="str">
         <f>[1]CARTELLINO!ME$3</f>
@@ -31552,11 +31552,11 @@
       </c>
       <c r="MM3" s="16" t="str">
         <f>[1]CARTELLINO!MP$3</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="MN3" s="16" t="str">
         <f>[1]CARTELLINO!MQ$3</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="MO3" s="16" t="str">
         <f>[1]CARTELLINO!MR$3</f>
@@ -31584,7 +31584,7 @@
       </c>
       <c r="MU3" s="16" t="str">
         <f>[1]CARTELLINO!MX$3</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="MV3" s="16" t="str">
         <f>[1]CARTELLINO!MY$3</f>
@@ -32660,25 +32660,25 @@
         <f>[1]CARTELLINO!HX$4</f>
         <v>0</v>
       </c>
-      <c r="HV4" s="43" t="str">
+      <c r="HV4" s="43">
         <f>[1]CARTELLINO!HY$4</f>
-        <v>f</v>
-      </c>
-      <c r="HW4" s="43" t="str">
+        <v>0</v>
+      </c>
+      <c r="HW4" s="43">
         <f>[1]CARTELLINO!HZ$4</f>
-        <v>f</v>
-      </c>
-      <c r="HX4" s="43" t="str">
+        <v>0</v>
+      </c>
+      <c r="HX4" s="43">
         <f>[1]CARTELLINO!IA$4</f>
-        <v>f</v>
-      </c>
-      <c r="HY4" s="43" t="str">
+        <v>0</v>
+      </c>
+      <c r="HY4" s="43">
         <f>[1]CARTELLINO!IB$4</f>
-        <v>f</v>
-      </c>
-      <c r="HZ4" s="43" t="str">
+        <v>0</v>
+      </c>
+      <c r="HZ4" s="43">
         <f>[1]CARTELLINO!IC$4</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="IA4" s="43">
         <f>[1]CARTELLINO!ID$4</f>
@@ -32776,57 +32776,57 @@
         <f>[1]CARTELLINO!JA$4</f>
         <v>0</v>
       </c>
-      <c r="IY4" s="43">
+      <c r="IY4" s="43" t="str">
         <f>[1]CARTELLINO!JB$4</f>
-        <v>0</v>
-      </c>
-      <c r="IZ4" s="43">
+        <v>pn</v>
+      </c>
+      <c r="IZ4" s="43" t="str">
         <f>[1]CARTELLINO!JC$4</f>
-        <v>0</v>
+        <v>x</v>
       </c>
       <c r="JA4" s="43">
         <f>[1]CARTELLINO!JD$4</f>
         <v>0</v>
       </c>
-      <c r="JB4" s="43">
+      <c r="JB4" s="43" t="str">
         <f>[1]CARTELLINO!JE$4</f>
-        <v>0</v>
-      </c>
-      <c r="JC4" s="43">
+        <v>f</v>
+      </c>
+      <c r="JC4" s="43" t="str">
         <f>[1]CARTELLINO!JF$4</f>
-        <v>0</v>
-      </c>
-      <c r="JD4" s="43">
+        <v>f</v>
+      </c>
+      <c r="JD4" s="43" t="str">
         <f>[1]CARTELLINO!JG$4</f>
-        <v>0</v>
-      </c>
-      <c r="JE4" s="43">
+        <v>f</v>
+      </c>
+      <c r="JE4" s="43" t="str">
         <f>[1]CARTELLINO!JH$4</f>
-        <v>0</v>
-      </c>
-      <c r="JF4" s="43">
+        <v>f</v>
+      </c>
+      <c r="JF4" s="43" t="str">
         <f>[1]CARTELLINO!JI$4</f>
-        <v>0</v>
-      </c>
-      <c r="JG4" s="43" t="str">
+        <v>f</v>
+      </c>
+      <c r="JG4" s="43">
         <f>[1]CARTELLINO!JJ$4</f>
-        <v>f</v>
-      </c>
-      <c r="JH4" s="43" t="str">
+        <v>0</v>
+      </c>
+      <c r="JH4" s="43">
         <f>[1]CARTELLINO!JK$4</f>
-        <v>f</v>
-      </c>
-      <c r="JI4" s="43" t="str">
+        <v>0</v>
+      </c>
+      <c r="JI4" s="43">
         <f>[1]CARTELLINO!JL$4</f>
-        <v>f</v>
-      </c>
-      <c r="JJ4" s="43" t="str">
+        <v>0</v>
+      </c>
+      <c r="JJ4" s="43">
         <f>[1]CARTELLINO!JM$4</f>
-        <v>f</v>
-      </c>
-      <c r="JK4" s="43" t="str">
+        <v>0</v>
+      </c>
+      <c r="JK4" s="43">
         <f>[1]CARTELLINO!JN$4</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="JL4" s="43">
         <f>[1]CARTELLINO!JO$4</f>
@@ -33020,25 +33020,25 @@
         <f>[1]CARTELLINO!LJ$4</f>
         <v>0</v>
       </c>
-      <c r="LH4" s="43">
+      <c r="LH4" s="43" t="str">
         <f>[1]CARTELLINO!LK$4</f>
-        <v>0</v>
-      </c>
-      <c r="LI4" s="43">
+        <v>f</v>
+      </c>
+      <c r="LI4" s="43" t="str">
         <f>[1]CARTELLINO!LL$4</f>
-        <v>0</v>
-      </c>
-      <c r="LJ4" s="43">
+        <v>f</v>
+      </c>
+      <c r="LJ4" s="43" t="str">
         <f>[1]CARTELLINO!LM$4</f>
-        <v>0</v>
-      </c>
-      <c r="LK4" s="43">
+        <v>f</v>
+      </c>
+      <c r="LK4" s="43" t="str">
         <f>[1]CARTELLINO!LN$4</f>
-        <v>0</v>
-      </c>
-      <c r="LL4" s="43">
+        <v>f</v>
+      </c>
+      <c r="LL4" s="43" t="str">
         <f>[1]CARTELLINO!LO$4</f>
-        <v>0</v>
+        <v>f</v>
       </c>
       <c r="LM4" s="43">
         <f>[1]CARTELLINO!LP$4</f>
@@ -33080,25 +33080,25 @@
         <f>[1]CARTELLINO!LY$4</f>
         <v>0</v>
       </c>
-      <c r="LW4" s="43">
+      <c r="LW4" s="43" t="str">
         <f>[1]CARTELLINO!LZ$4</f>
-        <v>0</v>
-      </c>
-      <c r="LX4" s="43">
+        <v>f</v>
+      </c>
+      <c r="LX4" s="43" t="str">
         <f>[1]CARTELLINO!MA$4</f>
-        <v>0</v>
-      </c>
-      <c r="LY4" s="43">
+        <v>f</v>
+      </c>
+      <c r="LY4" s="43" t="str">
         <f>[1]CARTELLINO!MB$4</f>
-        <v>0</v>
-      </c>
-      <c r="LZ4" s="43">
+        <v>f</v>
+      </c>
+      <c r="LZ4" s="43" t="str">
         <f>[1]CARTELLINO!MC$4</f>
-        <v>0</v>
-      </c>
-      <c r="MA4" s="43">
+        <v>f</v>
+      </c>
+      <c r="MA4" s="43" t="str">
         <f>[1]CARTELLINO!MD$4</f>
-        <v>0</v>
+        <v>f</v>
       </c>
       <c r="MB4" s="43">
         <f>[1]CARTELLINO!ME$4</f>
@@ -33144,17 +33144,17 @@
         <f>[1]CARTELLINO!MO$4</f>
         <v>0</v>
       </c>
-      <c r="MM4" s="43">
+      <c r="MM4" s="43" t="str">
         <f>[1]CARTELLINO!MP$4</f>
-        <v>0</v>
-      </c>
-      <c r="MN4" s="43">
+        <v>f</v>
+      </c>
+      <c r="MN4" s="43" t="str">
         <f>[1]CARTELLINO!MQ$4</f>
-        <v>0</v>
-      </c>
-      <c r="MO4" s="43">
+        <v>f</v>
+      </c>
+      <c r="MO4" s="43" t="str">
         <f>[1]CARTELLINO!MR$4</f>
-        <v>0</v>
+        <v>f</v>
       </c>
       <c r="MP4" s="43" t="str">
         <f>[1]CARTELLINO!MS$4</f>
@@ -33176,9 +33176,9 @@
         <f>[1]CARTELLINO!MW$4</f>
         <v>f</v>
       </c>
-      <c r="MU4" s="43">
+      <c r="MU4" s="43" t="str">
         <f>[1]CARTELLINO!MX$4</f>
-        <v>0</v>
+        <v>f</v>
       </c>
       <c r="MV4" s="43">
         <f>[1]CARTELLINO!MY$4</f>
@@ -34639,19 +34639,19 @@
       </c>
       <c r="HP6" s="22" t="str">
         <f>[1]CARTELLINO!HS$6</f>
-        <v>p</v>
+        <v>N</v>
       </c>
       <c r="HQ6" s="22" t="str">
         <f>[1]CARTELLINO!HT$6</f>
-        <v>m</v>
+        <v>S</v>
       </c>
       <c r="HR6" s="22" t="str">
         <f>[1]CARTELLINO!HU$6</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="HS6" s="22" t="str">
         <f>[1]CARTELLINO!HV$6</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="HT6" s="22" t="str">
         <f>[1]CARTELLINO!HW$6</f>
@@ -34683,19 +34683,19 @@
       </c>
       <c r="IA6" s="22" t="str">
         <f>[1]CARTELLINO!ID$6</f>
-        <v>r</v>
+        <v>-</v>
       </c>
       <c r="IB6" s="22" t="str">
         <f>[1]CARTELLINO!IE$6</f>
-        <v>M/R</v>
+        <v>-</v>
       </c>
       <c r="IC6" s="22" t="str">
         <f>[1]CARTELLINO!IF$6</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="ID6" s="22" t="str">
         <f>[1]CARTELLINO!IG$6</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="IE6" s="22" t="str">
         <f>[1]CARTELLINO!IH$6</f>
@@ -34743,7 +34743,7 @@
       </c>
       <c r="IP6" s="22" t="str">
         <f>[1]CARTELLINO!IS$6</f>
-        <v>P</v>
+        <v>r</v>
       </c>
       <c r="IQ6" s="22" t="str">
         <f>[1]CARTELLINO!IT$6</f>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="JA6" s="22" t="str">
         <f>[1]CARTELLINO!JD$6</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="JB6" s="22" t="str">
         <f>[1]CARTELLINO!JE$6</f>
@@ -34807,39 +34807,39 @@
       </c>
       <c r="JF6" s="22" t="str">
         <f>[1]CARTELLINO!JI$6</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="JG6" s="22" t="str">
         <f>[1]CARTELLINO!JJ$6</f>
-        <v>P</v>
+        <v>m/R</v>
       </c>
       <c r="JH6" s="22" t="str">
         <f>[1]CARTELLINO!JK$6</f>
-        <v>M/R</v>
+        <v>p</v>
       </c>
       <c r="JI6" s="22" t="str">
         <f>[1]CARTELLINO!JL$6</f>
-        <v>N</v>
+        <v>r</v>
       </c>
       <c r="JJ6" s="22" t="str">
         <f>[1]CARTELLINO!JM$6</f>
-        <v>S</v>
+        <v>r</v>
       </c>
       <c r="JK6" s="22" t="str">
         <f>[1]CARTELLINO!JN$6</f>
-        <v>R</v>
+        <v>r</v>
       </c>
       <c r="JL6" s="22" t="str">
         <f>[1]CARTELLINO!JO$6</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="JM6" s="22" t="str">
         <f>[1]CARTELLINO!JP$6</f>
-        <v>m</v>
+        <v>M/R</v>
       </c>
       <c r="JN6" s="22" t="str">
         <f>[1]CARTELLINO!JQ$6</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="JO6" s="22" t="str">
         <f>[1]CARTELLINO!JR$6</f>
@@ -34847,7 +34847,7 @@
       </c>
       <c r="JP6" s="22" t="str">
         <f>[1]CARTELLINO!JS$6</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="JQ6" s="22" t="str">
         <f>[1]CARTELLINO!JT$6</f>
@@ -34895,7 +34895,7 @@
       </c>
       <c r="KB6" s="22" t="str">
         <f>[1]CARTELLINO!KE$6</f>
-        <v>P</v>
+        <v>p</v>
       </c>
       <c r="KC6" s="22" t="str">
         <f>[1]CARTELLINO!KF$6</f>
@@ -34915,7 +34915,7 @@
       </c>
       <c r="KG6" s="22" t="str">
         <f>[1]CARTELLINO!KJ$6</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="KH6" s="22" t="str">
         <f>[1]CARTELLINO!KK$6</f>
@@ -35147,15 +35147,15 @@
       </c>
       <c r="MM6" s="22" t="str">
         <f>[1]CARTELLINO!MP$6</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="MN6" s="22" t="str">
         <f>[1]CARTELLINO!MQ$6</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="MO6" s="22" t="str">
         <f>[1]CARTELLINO!MR$6</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="MP6" s="22" t="str">
         <f>[1]CARTELLINO!MS$6</f>
@@ -35179,7 +35179,7 @@
       </c>
       <c r="MU6" s="22" t="str">
         <f>[1]CARTELLINO!MX$6</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="MV6" s="22" t="str">
         <f>[1]CARTELLINO!MY$6</f>
@@ -36275,25 +36275,25 @@
         <f>[1]CARTELLINO!IC$7</f>
         <v>0</v>
       </c>
-      <c r="IA7" s="46">
+      <c r="IA7" s="46" t="str">
         <f>[1]CARTELLINO!ID$7</f>
-        <v>0</v>
-      </c>
-      <c r="IB7" s="46">
+        <v>f</v>
+      </c>
+      <c r="IB7" s="46" t="str">
         <f>[1]CARTELLINO!IE$7</f>
-        <v>0</v>
-      </c>
-      <c r="IC7" s="46">
+        <v>p</v>
+      </c>
+      <c r="IC7" s="46" t="str">
         <f>[1]CARTELLINO!IF$7</f>
-        <v>0</v>
-      </c>
-      <c r="ID7" s="46">
+        <v>pn</v>
+      </c>
+      <c r="ID7" s="46" t="str">
         <f>[1]CARTELLINO!IG$7</f>
-        <v>0</v>
-      </c>
-      <c r="IE7" s="46">
+        <v>x</v>
+      </c>
+      <c r="IE7" s="46" t="str">
         <f>[1]CARTELLINO!IH$7</f>
-        <v>0</v>
+        <v>f</v>
       </c>
       <c r="IF7" s="46" t="str">
         <f>[1]CARTELLINO!II$7</f>
@@ -38243,11 +38243,11 @@
       </c>
       <c r="HR9" s="24" t="str">
         <f>[1]CARTELLINO!HU$9</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="HS9" s="24" t="str">
         <f>[1]CARTELLINO!HV$9</f>
-        <v>M</v>
+        <v>-</v>
       </c>
       <c r="HT9" s="24" t="str">
         <f>[1]CARTELLINO!HW$9</f>
@@ -38327,7 +38327,7 @@
       </c>
       <c r="IM9" s="24" t="str">
         <f>[1]CARTELLINO!IP$9</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="IN9" s="24" t="str">
         <f>[1]CARTELLINO!IQ$9</f>
@@ -38391,27 +38391,27 @@
       </c>
       <c r="JC9" s="24" t="str">
         <f>[1]CARTELLINO!JF$9</f>
-        <v>m</v>
+        <v>M/R</v>
       </c>
       <c r="JD9" s="24" t="str">
         <f>[1]CARTELLINO!JG$9</f>
-        <v>r</v>
+        <v>N</v>
       </c>
       <c r="JE9" s="24" t="str">
         <f>[1]CARTELLINO!JH$9</f>
-        <v>r</v>
+        <v>S</v>
       </c>
       <c r="JF9" s="24" t="str">
         <f>[1]CARTELLINO!JI$9</f>
-        <v>p</v>
+        <v>R</v>
       </c>
       <c r="JG9" s="24" t="str">
         <f>[1]CARTELLINO!JJ$9</f>
-        <v>m/R</v>
+        <v>p</v>
       </c>
       <c r="JH9" s="24" t="str">
         <f>[1]CARTELLINO!JK$9</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="JI9" s="24" t="str">
         <f>[1]CARTELLINO!JL$9</f>
@@ -38423,35 +38423,35 @@
       </c>
       <c r="JK9" s="24" t="str">
         <f>[1]CARTELLINO!JN$9</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="JL9" s="24" t="str">
         <f>[1]CARTELLINO!JO$9</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="JM9" s="24" t="str">
         <f>[1]CARTELLINO!JP$9</f>
-        <v>M/R</v>
+        <v>P</v>
       </c>
       <c r="JN9" s="24" t="str">
         <f>[1]CARTELLINO!JQ$9</f>
-        <v>N</v>
+        <v>m/R</v>
       </c>
       <c r="JO9" s="24" t="str">
         <f>[1]CARTELLINO!JR$9</f>
-        <v>S</v>
+        <v>m</v>
       </c>
       <c r="JP9" s="24" t="str">
         <f>[1]CARTELLINO!JS$9</f>
-        <v>R</v>
+        <v>p</v>
       </c>
       <c r="JQ9" s="24" t="str">
         <f>[1]CARTELLINO!JT$9</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JR9" s="24" t="str">
         <f>[1]CARTELLINO!JU$9</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JS9" s="24" t="str">
         <f>[1]CARTELLINO!JV$9</f>
@@ -39537,11 +39537,11 @@
       </c>
       <c r="EU10" s="46" t="str">
         <f>[1]CARTELLINO!EX$10</f>
-        <v>pn</v>
+        <v>f</v>
       </c>
       <c r="EV10" s="46" t="str">
         <f>[1]CARTELLINO!EY$10</f>
-        <v>x</v>
+        <v>f</v>
       </c>
       <c r="EW10" s="46">
         <f>[1]CARTELLINO!EZ$10</f>
@@ -39835,13 +39835,13 @@
         <f>[1]CARTELLINO!HT$10</f>
         <v>0</v>
       </c>
-      <c r="HR10" s="46">
+      <c r="HR10" s="46" t="str">
         <f>[1]CARTELLINO!HU$10</f>
-        <v>0</v>
-      </c>
-      <c r="HS10" s="46">
+        <v>p</v>
+      </c>
+      <c r="HS10" s="46" t="str">
         <f>[1]CARTELLINO!HV$10</f>
-        <v>0</v>
+        <v>p</v>
       </c>
       <c r="HT10" s="46">
         <f>[1]CARTELLINO!HW$10</f>
@@ -40015,13 +40015,13 @@
         <f>[1]CARTELLINO!JM$10</f>
         <v>0</v>
       </c>
-      <c r="JK10" s="46">
+      <c r="JK10" s="46" t="str">
         <f>[1]CARTELLINO!JN$10</f>
-        <v>0</v>
-      </c>
-      <c r="JL10" s="46">
+        <v>p</v>
+      </c>
+      <c r="JL10" s="46" t="str">
         <f>[1]CARTELLINO!JO$10</f>
-        <v>0</v>
+        <v>p</v>
       </c>
       <c r="JM10" s="46">
         <f>[1]CARTELLINO!JP$10</f>
@@ -40039,13 +40039,13 @@
         <f>[1]CARTELLINO!JS$10</f>
         <v>0</v>
       </c>
-      <c r="JQ10" s="46" t="str">
+      <c r="JQ10" s="46">
         <f>[1]CARTELLINO!JT$10</f>
-        <v>p</v>
-      </c>
-      <c r="JR10" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="JR10" s="46">
         <f>[1]CARTELLINO!JU$10</f>
-        <v>p</v>
+        <v>0</v>
       </c>
       <c r="JS10" s="46">
         <f>[1]CARTELLINO!JV$10</f>
@@ -41699,7 +41699,7 @@
       </c>
       <c r="GI12" s="25" t="str">
         <f>[1]CARTELLINO!GL$12</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="GJ12" s="25" t="str">
         <f>[1]CARTELLINO!GM$12</f>
@@ -41779,7 +41779,7 @@
       </c>
       <c r="HC12" s="25" t="str">
         <f>[1]CARTELLINO!HF$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="HD12" s="25" t="str">
         <f>[1]CARTELLINO!HG$12</f>
@@ -41863,23 +41863,23 @@
       </c>
       <c r="HX12" s="25" t="str">
         <f>[1]CARTELLINO!IA$12</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="HY12" s="25" t="str">
         <f>[1]CARTELLINO!IB$12</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="HZ12" s="25" t="str">
         <f>[1]CARTELLINO!IC$12</f>
-        <v>p</v>
+        <v>m/R</v>
       </c>
       <c r="IA12" s="25" t="str">
         <f>[1]CARTELLINO!ID$12</f>
-        <v>P</v>
+        <v>p</v>
       </c>
       <c r="IB12" s="25" t="str">
         <f>[1]CARTELLINO!IE$12</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="IC12" s="25" t="str">
         <f>[1]CARTELLINO!IF$12</f>
@@ -41967,31 +41967,31 @@
       </c>
       <c r="IX12" s="25" t="str">
         <f>[1]CARTELLINO!JA$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="IY12" s="25" t="str">
         <f>[1]CARTELLINO!JB$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="IZ12" s="25" t="str">
         <f>[1]CARTELLINO!JC$12</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="JA12" s="25" t="str">
         <f>[1]CARTELLINO!JD$12</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="JB12" s="25" t="str">
         <f>[1]CARTELLINO!JE$12</f>
-        <v>R</v>
+        <v>p</v>
       </c>
       <c r="JC12" s="25" t="str">
         <f>[1]CARTELLINO!JF$12</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JD12" s="25" t="str">
         <f>[1]CARTELLINO!JG$12</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JE12" s="25" t="str">
         <f>[1]CARTELLINO!JH$12</f>
@@ -42027,11 +42027,11 @@
       </c>
       <c r="JM12" s="25" t="str">
         <f>[1]CARTELLINO!JP$12</f>
-        <v>P</v>
+        <v>r</v>
       </c>
       <c r="JN12" s="25" t="str">
         <f>[1]CARTELLINO!JQ$12</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="JO12" s="25" t="str">
         <f>[1]CARTELLINO!JR$12</f>
@@ -42087,19 +42087,19 @@
       </c>
       <c r="KB12" s="25" t="str">
         <f>[1]CARTELLINO!KE$12</f>
-        <v>r</v>
+        <v>-</v>
       </c>
       <c r="KC12" s="25" t="str">
         <f>[1]CARTELLINO!KF$12</f>
-        <v>M/R</v>
+        <v>-</v>
       </c>
       <c r="KD12" s="25" t="str">
         <f>[1]CARTELLINO!KG$12</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="KE12" s="25" t="str">
         <f>[1]CARTELLINO!KH$12</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="KF12" s="25" t="str">
         <f>[1]CARTELLINO!KI$12</f>
@@ -42107,19 +42107,19 @@
       </c>
       <c r="KG12" s="25" t="str">
         <f>[1]CARTELLINO!KJ$12</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="KH12" s="25" t="str">
         <f>[1]CARTELLINO!KK$12</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="KI12" s="25" t="str">
         <f>[1]CARTELLINO!KL$12</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="KJ12" s="25" t="str">
         <f>[1]CARTELLINO!KM$12</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="KK12" s="25" t="str">
         <f>[1]CARTELLINO!KN$12</f>
@@ -43559,33 +43559,33 @@
         <f>[1]CARTELLINO!IZ$13</f>
         <v>0</v>
       </c>
-      <c r="IX13" s="46" t="str">
+      <c r="IX13" s="46">
         <f>[1]CARTELLINO!JA$13</f>
-        <v>f</v>
-      </c>
-      <c r="IY13" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="IY13" s="46">
         <f>[1]CARTELLINO!JB$13</f>
-        <v>f</v>
-      </c>
-      <c r="IZ13" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="IZ13" s="46">
         <f>[1]CARTELLINO!JC$13</f>
-        <v>f</v>
-      </c>
-      <c r="JA13" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="JA13" s="46">
         <f>[1]CARTELLINO!JD$13</f>
-        <v>f</v>
-      </c>
-      <c r="JB13" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="JB13" s="46">
         <f>[1]CARTELLINO!JE$13</f>
-        <v>f</v>
-      </c>
-      <c r="JC13" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="JC13" s="46">
         <f>[1]CARTELLINO!JF$13</f>
-        <v>f</v>
-      </c>
-      <c r="JD13" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="JD13" s="46">
         <f>[1]CARTELLINO!JG$13</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="JE13" s="46">
         <f>[1]CARTELLINO!JH$13</f>
@@ -43679,33 +43679,33 @@
         <f>[1]CARTELLINO!KD$13</f>
         <v>0</v>
       </c>
-      <c r="KB13" s="46">
+      <c r="KB13" s="46" t="str">
         <f>[1]CARTELLINO!KE$13</f>
-        <v>0</v>
-      </c>
-      <c r="KC13" s="46">
+        <v>f</v>
+      </c>
+      <c r="KC13" s="46" t="str">
         <f>[1]CARTELLINO!KF$13</f>
-        <v>0</v>
-      </c>
-      <c r="KD13" s="46">
+        <v>f</v>
+      </c>
+      <c r="KD13" s="46" t="str">
         <f>[1]CARTELLINO!KG$13</f>
-        <v>0</v>
-      </c>
-      <c r="KE13" s="46">
+        <v>f</v>
+      </c>
+      <c r="KE13" s="46" t="str">
         <f>[1]CARTELLINO!KH$13</f>
-        <v>0</v>
-      </c>
-      <c r="KF13" s="46">
+        <v>f</v>
+      </c>
+      <c r="KF13" s="46" t="str">
         <f>[1]CARTELLINO!KI$13</f>
-        <v>0</v>
-      </c>
-      <c r="KG13" s="46">
+        <v>f</v>
+      </c>
+      <c r="KG13" s="46" t="str">
         <f>[1]CARTELLINO!KJ$13</f>
-        <v>0</v>
-      </c>
-      <c r="KH13" s="46">
+        <v>f</v>
+      </c>
+      <c r="KH13" s="46" t="str">
         <f>[1]CARTELLINO!KK$13</f>
-        <v>0</v>
+        <v>f</v>
       </c>
       <c r="KI13" s="46">
         <f>[1]CARTELLINO!KL$13</f>
@@ -45447,7 +45447,7 @@
       </c>
       <c r="HU15" s="26" t="str">
         <f>[1]CARTELLINO!HX$15</f>
-        <v>P</v>
+        <v>r</v>
       </c>
       <c r="HV15" s="26" t="str">
         <f>[1]CARTELLINO!HY$15</f>
@@ -45455,39 +45455,39 @@
       </c>
       <c r="HW15" s="26" t="str">
         <f>[1]CARTELLINO!HZ$15</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="HX15" s="26" t="str">
         <f>[1]CARTELLINO!IA$15</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="HY15" s="26" t="str">
         <f>[1]CARTELLINO!IB$15</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="HZ15" s="26" t="str">
         <f>[1]CARTELLINO!IC$15</f>
-        <v>m/R</v>
+        <v>p</v>
       </c>
       <c r="IA15" s="26" t="str">
         <f>[1]CARTELLINO!ID$15</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="IB15" s="26" t="str">
         <f>[1]CARTELLINO!IE$15</f>
-        <v>r</v>
+        <v>M/R</v>
       </c>
       <c r="IC15" s="26" t="str">
         <f>[1]CARTELLINO!IF$15</f>
-        <v>r</v>
+        <v>N</v>
       </c>
       <c r="ID15" s="26" t="str">
         <f>[1]CARTELLINO!IG$15</f>
-        <v>p</v>
+        <v>S</v>
       </c>
       <c r="IE15" s="26" t="str">
         <f>[1]CARTELLINO!IH$15</f>
-        <v>m</v>
+        <v>R</v>
       </c>
       <c r="IF15" s="26" t="str">
         <f>[1]CARTELLINO!II$15</f>
@@ -48891,7 +48891,7 @@
       </c>
       <c r="GI18" s="27" t="str">
         <f>[1]CARTELLINO!GL$18</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="GJ18" s="27" t="str">
         <f>[1]CARTELLINO!GM$18</f>
@@ -49151,7 +49151,7 @@
       </c>
       <c r="IV18" s="27" t="str">
         <f>[1]CARTELLINO!IY$18</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="IW18" s="27" t="str">
         <f>[1]CARTELLINO!IZ$18</f>
@@ -49163,7 +49163,7 @@
       </c>
       <c r="IY18" s="27" t="str">
         <f>[1]CARTELLINO!JB$18</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="IZ18" s="27" t="str">
         <f>[1]CARTELLINO!JC$18</f>
@@ -52631,7 +52631,7 @@
       </c>
       <c r="HS21" s="28" t="str">
         <f>[1]CARTELLINO!HV$21</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="HT21" s="28" t="str">
         <f>[1]CARTELLINO!HW$21</f>
@@ -52667,7 +52667,7 @@
       </c>
       <c r="IB21" s="28" t="str">
         <f>[1]CARTELLINO!IE$21</f>
-        <v>P</v>
+        <v>r</v>
       </c>
       <c r="IC21" s="28" t="str">
         <f>[1]CARTELLINO!IF$21</f>
@@ -52675,11 +52675,11 @@
       </c>
       <c r="ID21" s="28" t="str">
         <f>[1]CARTELLINO!IG$21</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="IE21" s="28" t="str">
         <f>[1]CARTELLINO!IH$21</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="IF21" s="28" t="str">
         <f>[1]CARTELLINO!II$21</f>
@@ -52703,7 +52703,7 @@
       </c>
       <c r="IK21" s="28" t="str">
         <f>[1]CARTELLINO!IN$21</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="IL21" s="28" t="str">
         <f>[1]CARTELLINO!IO$21</f>
@@ -56215,11 +56215,11 @@
       </c>
       <c r="HP24" s="29" t="str">
         <f>[1]CARTELLINO!HS$24</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="HQ24" s="29" t="str">
         <f>[1]CARTELLINO!HT$24</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="HR24" s="29" t="str">
         <f>[1]CARTELLINO!HU$24</f>
@@ -56227,7 +56227,7 @@
       </c>
       <c r="HS24" s="29" t="str">
         <f>[1]CARTELLINO!HV$24</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="HT24" s="29" t="str">
         <f>[1]CARTELLINO!HW$24</f>
@@ -56319,7 +56319,7 @@
       </c>
       <c r="IP24" s="29" t="str">
         <f>[1]CARTELLINO!IS$24</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="IQ24" s="29" t="str">
         <f>[1]CARTELLINO!IT$24</f>
@@ -56351,7 +56351,7 @@
       </c>
       <c r="IX24" s="29" t="str">
         <f>[1]CARTELLINO!JA$24</f>
-        <v>P</v>
+        <v>r</v>
       </c>
       <c r="IY24" s="29" t="str">
         <f>[1]CARTELLINO!JB$24</f>
@@ -56383,15 +56383,15 @@
       </c>
       <c r="JF24" s="29" t="str">
         <f>[1]CARTELLINO!JI$24</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="JG24" s="29" t="str">
         <f>[1]CARTELLINO!JJ$24</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="JH24" s="29" t="str">
         <f>[1]CARTELLINO!JK$24</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="JI24" s="29" t="str">
         <f>[1]CARTELLINO!JL$24</f>
@@ -56403,7 +56403,7 @@
       </c>
       <c r="JK24" s="29" t="str">
         <f>[1]CARTELLINO!JN$24</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="JL24" s="29" t="str">
         <f>[1]CARTELLINO!JO$24</f>
@@ -56415,15 +56415,15 @@
       </c>
       <c r="JN24" s="29" t="str">
         <f>[1]CARTELLINO!JQ$24</f>
-        <v>p</v>
+        <v>N</v>
       </c>
       <c r="JO24" s="29" t="str">
         <f>[1]CARTELLINO!JR$24</f>
-        <v>m</v>
+        <v>S</v>
       </c>
       <c r="JP24" s="29" t="str">
         <f>[1]CARTELLINO!JS$24</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="JQ24" s="29" t="str">
         <f>[1]CARTELLINO!JT$24</f>
@@ -57807,21 +57807,21 @@
         <f>[1]CARTELLINO!HR$25</f>
         <v>0</v>
       </c>
-      <c r="HP25" s="46">
+      <c r="HP25" s="46" t="str">
         <f>[1]CARTELLINO!HS$25</f>
-        <v>0</v>
-      </c>
-      <c r="HQ25" s="46">
+        <v>pn</v>
+      </c>
+      <c r="HQ25" s="46" t="str">
         <f>[1]CARTELLINO!HT$25</f>
-        <v>0</v>
-      </c>
-      <c r="HR25" s="46">
+        <v>x</v>
+      </c>
+      <c r="HR25" s="46" t="str">
         <f>[1]CARTELLINO!HU$25</f>
-        <v>0</v>
-      </c>
-      <c r="HS25" s="46">
+        <v>f</v>
+      </c>
+      <c r="HS25" s="46" t="str">
         <f>[1]CARTELLINO!HV$25</f>
-        <v>0</v>
+        <v>f</v>
       </c>
       <c r="HT25" s="46">
         <f>[1]CARTELLINO!HW$25</f>
@@ -59947,27 +59947,27 @@
       </c>
       <c r="IX27" s="30" t="str">
         <f>[1]CARTELLINO!JA$27</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="IY27" s="30" t="str">
         <f>[1]CARTELLINO!JB$27</f>
-        <v>m</v>
+        <v>N</v>
       </c>
       <c r="IZ27" s="30" t="str">
         <f>[1]CARTELLINO!JC$27</f>
-        <v>p</v>
+        <v>S</v>
       </c>
       <c r="JA27" s="30" t="str">
         <f>[1]CARTELLINO!JD$27</f>
-        <v>m</v>
+        <v>R</v>
       </c>
       <c r="JB27" s="30" t="str">
         <f>[1]CARTELLINO!JE$27</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="JC27" s="30" t="str">
         <f>[1]CARTELLINO!JF$27</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="JD27" s="30" t="str">
         <f>[1]CARTELLINO!JG$27</f>
@@ -60195,19 +60195,19 @@
       </c>
       <c r="LH27" s="30" t="str">
         <f>[1]CARTELLINO!LK$27</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="LI27" s="30" t="str">
         <f>[1]CARTELLINO!LL$27</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="LJ27" s="30" t="str">
         <f>[1]CARTELLINO!LM$27</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="LK27" s="30" t="str">
         <f>[1]CARTELLINO!LN$27</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="LL27" s="30" t="str">
         <f>[1]CARTELLINO!LO$27</f>
@@ -62743,7 +62743,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="HD29" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>VOLPINI</v>
       </c>
       <c r="HE29" s="63" t="str">
         <v>GHIOTTI</v>
@@ -62812,13 +62812,13 @@
         <v>BIANCHI</v>
       </c>
       <c r="IA29" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="IB29" s="63" t="str">
         <v>MICHELOT.</v>
       </c>
       <c r="IC29" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="ID29" s="63" t="str">
         <v>SARTI</v>
@@ -62893,13 +62893,13 @@
         <v>GHIOTTI</v>
       </c>
       <c r="JB29" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="JC29" s="63" t="str">
         <v>BERARDI</v>
       </c>
       <c r="JD29" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>SARTI</v>
       </c>
       <c r="JE29" s="63" t="str">
         <v>BIANCHI</v>
@@ -62911,10 +62911,10 @@
         <v>FABBRI</v>
       </c>
       <c r="JH29" s="63" t="str">
-        <v>SARTI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="JI29" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="JJ29" s="63" t="str">
         <v>VOLPINI</v>
@@ -62929,10 +62929,10 @@
         <v>BERARDI</v>
       </c>
       <c r="JN29" s="63" t="str">
+        <v>BARBIERI</v>
+      </c>
+      <c r="JO29" s="63" t="str">
         <v>SARTI</v>
-      </c>
-      <c r="JO29" s="63" t="str">
-        <v>VOLPINI</v>
       </c>
       <c r="JP29" s="63" t="str">
         <v>GHIOTTI</v>
@@ -62977,7 +62977,7 @@
         <v>SARTI</v>
       </c>
       <c r="KD29" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="KE29" s="63" t="str">
         <v>BERARDI</v>
@@ -63765,7 +63765,7 @@
         <v>MICHELOT.</v>
       </c>
       <c r="GD30" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="GE30" s="63" t="str">
         <v>FABBRI</v>
@@ -63780,7 +63780,7 @@
         <v>BERARDI</v>
       </c>
       <c r="GI30" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="GJ30" s="63" t="str">
         <v>FABBRI</v>
@@ -63843,7 +63843,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="HD30" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>VOLPINI</v>
       </c>
       <c r="HE30" s="63" t="str">
         <v>GHIOTTI</v>
@@ -63912,13 +63912,13 @@
         <v>BIANCHI</v>
       </c>
       <c r="IA30" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="IB30" s="63" t="str">
         <v>MICHELOT.</v>
       </c>
       <c r="IC30" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="ID30" s="63" t="str">
         <v>SARTI</v>
@@ -63993,13 +63993,13 @@
         <v>GHIOTTI</v>
       </c>
       <c r="JB30" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="JC30" s="63" t="str">
         <v>BERARDI</v>
       </c>
       <c r="JD30" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>SARTI</v>
       </c>
       <c r="JE30" s="63" t="str">
         <v>BIANCHI</v>
@@ -64011,10 +64011,10 @@
         <v>FABBRI</v>
       </c>
       <c r="JH30" s="63" t="str">
-        <v>SARTI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="JI30" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="JJ30" s="63" t="str">
         <v>VOLPINI</v>
@@ -64029,10 +64029,10 @@
         <v>BERARDI</v>
       </c>
       <c r="JN30" s="63" t="str">
+        <v>BARBIERI</v>
+      </c>
+      <c r="JO30" s="63" t="str">
         <v>SARTI</v>
-      </c>
-      <c r="JO30" s="63" t="str">
-        <v>VOLPINI</v>
       </c>
       <c r="JP30" s="63" t="str">
         <v>GHIOTTI</v>
@@ -64077,7 +64077,7 @@
         <v>SARTI</v>
       </c>
       <c r="KD30" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="KE30" s="63" t="str">
         <v>BERARDI</v>
@@ -64940,7 +64940,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="HC31" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>VOLPINI</v>
       </c>
       <c r="HD31" s="63" t="str">
         <v>GHIOTTI</v>
@@ -65009,13 +65009,13 @@
         <v>BIANCHI</v>
       </c>
       <c r="HZ31" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="IA31" s="63" t="str">
         <v>MICHELOT.</v>
       </c>
       <c r="IB31" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="IC31" s="63" t="str">
         <v>SARTI</v>
@@ -65090,13 +65090,13 @@
         <v>GHIOTTI</v>
       </c>
       <c r="JA31" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="JB31" s="63" t="str">
         <v>BERARDI</v>
       </c>
       <c r="JC31" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>SARTI</v>
       </c>
       <c r="JD31" s="63" t="str">
         <v>BIANCHI</v>
@@ -65108,10 +65108,10 @@
         <v>FABBRI</v>
       </c>
       <c r="JG31" s="63" t="str">
-        <v>SARTI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="JH31" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="JI31" s="63" t="str">
         <v>VOLPINI</v>
@@ -65126,10 +65126,10 @@
         <v>BERARDI</v>
       </c>
       <c r="JM31" s="63" t="str">
+        <v>BARBIERI</v>
+      </c>
+      <c r="JN31" s="63" t="str">
         <v>SARTI</v>
-      </c>
-      <c r="JN31" s="63" t="str">
-        <v>VOLPINI</v>
       </c>
       <c r="JO31" s="63" t="str">
         <v>GHIOTTI</v>
@@ -65174,7 +65174,7 @@
         <v>SARTI</v>
       </c>
       <c r="KC31" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="KD31" s="63" t="str">
         <v>BERARDI</v>
@@ -66040,7 +66040,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="HC32" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>VOLPINI</v>
       </c>
       <c r="HD32" s="63" t="str">
         <v>GHIOTTI</v>
@@ -66109,13 +66109,13 @@
         <v>BIANCHI</v>
       </c>
       <c r="HZ32" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="IA32" s="63" t="str">
         <v>MICHELOT.</v>
       </c>
       <c r="IB32" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="IC32" s="63" t="str">
         <v>SARTI</v>
@@ -66190,13 +66190,13 @@
         <v>GHIOTTI</v>
       </c>
       <c r="JA32" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="JB32" s="63" t="str">
         <v>BERARDI</v>
       </c>
       <c r="JC32" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>SARTI</v>
       </c>
       <c r="JD32" s="63" t="str">
         <v>BIANCHI</v>
@@ -66208,10 +66208,10 @@
         <v>FABBRI</v>
       </c>
       <c r="JG32" s="63" t="str">
-        <v>SARTI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="JH32" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="JI32" s="63" t="str">
         <v>VOLPINI</v>
@@ -66226,10 +66226,10 @@
         <v>BERARDI</v>
       </c>
       <c r="JM32" s="63" t="str">
+        <v>BARBIERI</v>
+      </c>
+      <c r="JN32" s="63" t="str">
         <v>SARTI</v>
-      </c>
-      <c r="JN32" s="63" t="str">
-        <v>VOLPINI</v>
       </c>
       <c r="JO32" s="63" t="str">
         <v>GHIOTTI</v>
@@ -66274,7 +66274,7 @@
         <v>SARTI</v>
       </c>
       <c r="KC32" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="KD32" s="63" t="str">
         <v>BERARDI</v>
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,13 +71029,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71044,6 +71037,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{424E6C4F-9423-49A2-A395-3B119757C023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9694687C-FE6A-44C7-8063-FCF0862A96E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="75" windowWidth="28800" windowHeight="15405" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -9811,16 +9811,16 @@
             <v>m</v>
           </cell>
           <cell r="HS6" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="HT6" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="HU6" t="str">
-            <v>R</v>
+            <v>-</v>
           </cell>
           <cell r="HV6" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="HW6" t="str">
             <v>p</v>
@@ -12110,7 +12110,7 @@
             <v>R</v>
           </cell>
           <cell r="GR9" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="GS9" t="str">
             <v>M/R</v>
@@ -16873,13 +16873,13 @@
             <v>M/R</v>
           </cell>
           <cell r="GS15" t="str">
-            <v>N</v>
+            <v>p</v>
           </cell>
           <cell r="GT15" t="str">
-            <v>S</v>
+            <v>m</v>
           </cell>
           <cell r="GU15" t="str">
-            <v>R</v>
+            <v>r</v>
           </cell>
           <cell r="GV15" t="str">
             <v>P</v>
@@ -21720,7 +21720,7 @@
             <v>m/R</v>
           </cell>
           <cell r="HV21" t="str">
-            <v>P</v>
+            <v>p</v>
           </cell>
           <cell r="HW21" t="str">
             <v>m</v>
@@ -23330,16 +23330,16 @@
             <v>f</v>
           </cell>
           <cell r="NF22" t="str">
-            <v>f</v>
+            <v>V</v>
           </cell>
           <cell r="NG22" t="str">
-            <v>f</v>
+            <v>V</v>
           </cell>
           <cell r="NH22" t="str">
-            <v>f</v>
+            <v>V</v>
           </cell>
           <cell r="NI22" t="str">
-            <v>f</v>
+            <v>V</v>
           </cell>
           <cell r="NJ22">
             <v>0</v>
@@ -24010,16 +24010,16 @@
             <v>p</v>
           </cell>
           <cell r="GR24" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="GS24" t="str">
-            <v>p</v>
+            <v>N</v>
           </cell>
           <cell r="GT24" t="str">
-            <v>m</v>
+            <v>S</v>
           </cell>
           <cell r="GU24" t="str">
-            <v>r</v>
+            <v>R</v>
           </cell>
           <cell r="GV24" t="str">
             <v>r</v>
@@ -24091,16 +24091,16 @@
             <v>M/R</v>
           </cell>
           <cell r="HS24" t="str">
-            <v>-</v>
+            <v>N</v>
           </cell>
           <cell r="HT24" t="str">
-            <v>-</v>
+            <v>S</v>
           </cell>
           <cell r="HU24" t="str">
             <v>R</v>
           </cell>
           <cell r="HV24" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="HW24" t="str">
             <v>M/R</v>
@@ -24541,7 +24541,7 @@
             <v>-</v>
           </cell>
           <cell r="NM24" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="NN24" t="str">
             <v>-</v>
@@ -24556,7 +24556,7 @@
             <v>-</v>
           </cell>
           <cell r="NR24" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="NS24" t="str">
             <v>-</v>
@@ -24765,7 +24765,7 @@
             <v>0</v>
           </cell>
           <cell r="BC25">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="BD25">
             <v>0</v>
@@ -25155,7 +25155,7 @@
             <v>0</v>
           </cell>
           <cell r="GC25">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="GD25">
             <v>0</v>
@@ -25280,17 +25280,17 @@
           <cell r="HR25">
             <v>0</v>
           </cell>
-          <cell r="HS25" t="str">
-            <v>pn</v>
-          </cell>
-          <cell r="HT25" t="str">
-            <v>x</v>
-          </cell>
-          <cell r="HU25" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="HV25" t="str">
-            <v>f</v>
+          <cell r="HS25">
+            <v>0</v>
+          </cell>
+          <cell r="HT25">
+            <v>0</v>
+          </cell>
+          <cell r="HU25">
+            <v>0</v>
+          </cell>
+          <cell r="HV25">
+            <v>0</v>
           </cell>
           <cell r="HW25">
             <v>0</v>
@@ -25629,13 +25629,13 @@
             <v>0</v>
           </cell>
           <cell r="ME25" t="str">
-            <v>f</v>
+            <v>F</v>
           </cell>
           <cell r="MF25" t="str">
-            <v>f</v>
+            <v>F</v>
           </cell>
           <cell r="MG25" t="str">
-            <v>f</v>
+            <v>F</v>
           </cell>
           <cell r="MH25" t="str">
             <v>nl</v>
@@ -25713,40 +25713,40 @@
             <v>nl</v>
           </cell>
           <cell r="NG25" t="str">
-            <v>f</v>
+            <v>v</v>
           </cell>
           <cell r="NH25" t="str">
-            <v>f</v>
+            <v>v</v>
           </cell>
           <cell r="NI25" t="str">
-            <v>f</v>
+            <v>v</v>
           </cell>
           <cell r="NJ25" t="str">
-            <v>f</v>
+            <v>v</v>
           </cell>
           <cell r="NK25" t="str">
             <v>nl</v>
           </cell>
           <cell r="NL25" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="NM25">
-            <v>0</v>
-          </cell>
-          <cell r="NN25">
-            <v>0</v>
-          </cell>
-          <cell r="NO25">
-            <v>0</v>
-          </cell>
-          <cell r="NP25">
-            <v>0</v>
-          </cell>
-          <cell r="NQ25">
-            <v>0</v>
-          </cell>
-          <cell r="NR25">
-            <v>0</v>
+            <v>v</v>
+          </cell>
+          <cell r="NM25" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NN25" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NO25" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NP25" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NQ25" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NR25" t="str">
+            <v>v</v>
           </cell>
           <cell r="NS25">
             <v>0</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -34639,19 +34639,19 @@
       </c>
       <c r="HP6" s="22" t="str">
         <f>[1]CARTELLINO!HS$6</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="HQ6" s="22" t="str">
         <f>[1]CARTELLINO!HT$6</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="HR6" s="22" t="str">
         <f>[1]CARTELLINO!HU$6</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="HS6" s="22" t="str">
         <f>[1]CARTELLINO!HV$6</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="HT6" s="22" t="str">
         <f>[1]CARTELLINO!HW$6</f>
@@ -38127,7 +38127,7 @@
       </c>
       <c r="GO9" s="24" t="str">
         <f>[1]CARTELLINO!GR$9</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="GP9" s="24" t="str">
         <f>[1]CARTELLINO!GS$9</f>
@@ -45323,15 +45323,15 @@
       </c>
       <c r="GP15" s="26" t="str">
         <f>[1]CARTELLINO!GS$15</f>
-        <v>N</v>
+        <v>p</v>
       </c>
       <c r="GQ15" s="26" t="str">
         <f>[1]CARTELLINO!GT$15</f>
-        <v>S</v>
+        <v>m</v>
       </c>
       <c r="GR15" s="26" t="str">
         <f>[1]CARTELLINO!GU$15</f>
-        <v>R</v>
+        <v>r</v>
       </c>
       <c r="GS15" s="26" t="str">
         <f>[1]CARTELLINO!GV$15</f>
@@ -52631,7 +52631,7 @@
       </c>
       <c r="HS21" s="28" t="str">
         <f>[1]CARTELLINO!HV$21</f>
-        <v>P</v>
+        <v>p</v>
       </c>
       <c r="HT21" s="28" t="str">
         <f>[1]CARTELLINO!HW$21</f>
@@ -54785,19 +54785,19 @@
       </c>
       <c r="NC22" s="46" t="str">
         <f>[1]CARTELLINO!NF$22</f>
-        <v>f</v>
+        <v>V</v>
       </c>
       <c r="ND22" s="46" t="str">
         <f>[1]CARTELLINO!NG$22</f>
-        <v>f</v>
+        <v>V</v>
       </c>
       <c r="NE22" s="46" t="str">
         <f>[1]CARTELLINO!NH$22</f>
-        <v>f</v>
+        <v>V</v>
       </c>
       <c r="NF22" s="46" t="str">
         <f>[1]CARTELLINO!NI$22</f>
-        <v>f</v>
+        <v>V</v>
       </c>
       <c r="NG22" s="46">
         <f>[1]CARTELLINO!NJ$22</f>
@@ -56107,19 +56107,19 @@
       </c>
       <c r="GO24" s="29" t="str">
         <f>[1]CARTELLINO!GR$24</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="GP24" s="29" t="str">
         <f>[1]CARTELLINO!GS$24</f>
-        <v>p</v>
+        <v>N</v>
       </c>
       <c r="GQ24" s="29" t="str">
         <f>[1]CARTELLINO!GT$24</f>
-        <v>m</v>
+        <v>S</v>
       </c>
       <c r="GR24" s="29" t="str">
         <f>[1]CARTELLINO!GU$24</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="GS24" s="29" t="str">
         <f>[1]CARTELLINO!GV$24</f>
@@ -56215,11 +56215,11 @@
       </c>
       <c r="HP24" s="29" t="str">
         <f>[1]CARTELLINO!HS$24</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="HQ24" s="29" t="str">
         <f>[1]CARTELLINO!HT$24</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="HR24" s="29" t="str">
         <f>[1]CARTELLINO!HU$24</f>
@@ -56227,7 +56227,7 @@
       </c>
       <c r="HS24" s="29" t="str">
         <f>[1]CARTELLINO!HV$24</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="HT24" s="29" t="str">
         <f>[1]CARTELLINO!HW$24</f>
@@ -56815,7 +56815,7 @@
       </c>
       <c r="NJ24" s="29" t="str">
         <f>[1]CARTELLINO!NM$24</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="NK24" s="29" t="str">
         <f>[1]CARTELLINO!NN$24</f>
@@ -56835,7 +56835,7 @@
       </c>
       <c r="NO24" s="29" t="str">
         <f>[1]CARTELLINO!NR$24</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="NP24" s="29" t="str">
         <f>[1]CARTELLINO!NS$24</f>
@@ -57121,7 +57121,7 @@
       </c>
       <c r="AZ25" s="46">
         <f>[1]CARTELLINO!BC$25</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA25" s="46">
         <f>[1]CARTELLINO!BD$25</f>
@@ -57641,7 +57641,7 @@
       </c>
       <c r="FZ25" s="46">
         <f>[1]CARTELLINO!GC$25</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GA25" s="46">
         <f>[1]CARTELLINO!GD$25</f>
@@ -57807,21 +57807,21 @@
         <f>[1]CARTELLINO!HR$25</f>
         <v>0</v>
       </c>
-      <c r="HP25" s="46" t="str">
+      <c r="HP25" s="46">
         <f>[1]CARTELLINO!HS$25</f>
-        <v>pn</v>
-      </c>
-      <c r="HQ25" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="HQ25" s="46">
         <f>[1]CARTELLINO!HT$25</f>
-        <v>x</v>
-      </c>
-      <c r="HR25" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="HR25" s="46">
         <f>[1]CARTELLINO!HU$25</f>
-        <v>f</v>
-      </c>
-      <c r="HS25" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="HS25" s="46">
         <f>[1]CARTELLINO!HV$25</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="HT25" s="46">
         <f>[1]CARTELLINO!HW$25</f>
@@ -58273,15 +58273,15 @@
       </c>
       <c r="MB25" s="46" t="str">
         <f>[1]CARTELLINO!ME$25</f>
-        <v>f</v>
+        <v>F</v>
       </c>
       <c r="MC25" s="46" t="str">
         <f>[1]CARTELLINO!MF$25</f>
-        <v>f</v>
+        <v>F</v>
       </c>
       <c r="MD25" s="46" t="str">
         <f>[1]CARTELLINO!MG$25</f>
-        <v>f</v>
+        <v>F</v>
       </c>
       <c r="ME25" s="46" t="str">
         <f>[1]CARTELLINO!MH$25</f>
@@ -58385,19 +58385,19 @@
       </c>
       <c r="ND25" s="46" t="str">
         <f>[1]CARTELLINO!NG$25</f>
-        <v>f</v>
+        <v>v</v>
       </c>
       <c r="NE25" s="46" t="str">
         <f>[1]CARTELLINO!NH$25</f>
-        <v>f</v>
+        <v>v</v>
       </c>
       <c r="NF25" s="46" t="str">
         <f>[1]CARTELLINO!NI$25</f>
-        <v>f</v>
+        <v>v</v>
       </c>
       <c r="NG25" s="46" t="str">
         <f>[1]CARTELLINO!NJ$25</f>
-        <v>f</v>
+        <v>v</v>
       </c>
       <c r="NH25" s="46" t="str">
         <f>[1]CARTELLINO!NK$25</f>
@@ -58405,31 +58405,31 @@
       </c>
       <c r="NI25" s="46" t="str">
         <f>[1]CARTELLINO!NL$25</f>
-        <v>f</v>
-      </c>
-      <c r="NJ25" s="46">
+        <v>v</v>
+      </c>
+      <c r="NJ25" s="46" t="str">
         <f>[1]CARTELLINO!NM$25</f>
-        <v>0</v>
-      </c>
-      <c r="NK25" s="46">
+        <v>v</v>
+      </c>
+      <c r="NK25" s="46" t="str">
         <f>[1]CARTELLINO!NN$25</f>
-        <v>0</v>
-      </c>
-      <c r="NL25" s="46">
+        <v>v</v>
+      </c>
+      <c r="NL25" s="46" t="str">
         <f>[1]CARTELLINO!NO$25</f>
-        <v>0</v>
-      </c>
-      <c r="NM25" s="46">
+        <v>v</v>
+      </c>
+      <c r="NM25" s="46" t="str">
         <f>[1]CARTELLINO!NP$25</f>
-        <v>0</v>
-      </c>
-      <c r="NN25" s="46">
+        <v>v</v>
+      </c>
+      <c r="NN25" s="46" t="str">
         <f>[1]CARTELLINO!NQ$25</f>
-        <v>0</v>
-      </c>
-      <c r="NO25" s="46">
+        <v>v</v>
+      </c>
+      <c r="NO25" s="46" t="str">
         <f>[1]CARTELLINO!NR$25</f>
-        <v>0</v>
+        <v>v</v>
       </c>
       <c r="NP25" s="46">
         <f>[1]CARTELLINO!NS$25</f>
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,6 +71029,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71037,13 +71044,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9694687C-FE6A-44C7-8063-FCF0862A96E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA453EE0-EBAD-411C-B4DE-1A9BE8B81930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4505,7 +4505,7 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR212" t="str">
-            <v>PAZZAGLIA</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS212" t="str">
             <v>VOLPINI</v>
@@ -7431,13 +7431,13 @@
             <v>P</v>
           </cell>
           <cell r="HR3" t="str">
-            <v>p</v>
+            <v>r</v>
           </cell>
           <cell r="HS3" t="str">
+            <v>P</v>
+          </cell>
+          <cell r="HT3" t="str">
             <v>m</v>
-          </cell>
-          <cell r="HT3" t="str">
-            <v>r</v>
           </cell>
           <cell r="HU3" t="str">
             <v>P</v>
@@ -17089,7 +17089,7 @@
             <v>P</v>
           </cell>
           <cell r="JM15" t="str">
-            <v>M</v>
+            <v>p</v>
           </cell>
           <cell r="JN15" t="str">
             <v>N</v>
@@ -19328,10 +19328,10 @@
             <v>S</v>
           </cell>
           <cell r="HR18" t="str">
-            <v>R</v>
+            <v>p</v>
           </cell>
           <cell r="HS18" t="str">
-            <v>P</v>
+            <v>r</v>
           </cell>
           <cell r="HT18" t="str">
             <v>M/R</v>
@@ -21957,7 +21957,7 @@
             <v>m/R</v>
           </cell>
           <cell r="KW21" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="KX21" t="str">
             <v>m</v>
@@ -24229,10 +24229,10 @@
             <v>p</v>
           </cell>
           <cell r="JM24" t="str">
-            <v>p</v>
+            <v>M</v>
           </cell>
           <cell r="JN24" t="str">
-            <v>m</v>
+            <v>-</v>
           </cell>
           <cell r="JO24" t="str">
             <v>r</v>
@@ -24337,7 +24337,7 @@
             <v>R</v>
           </cell>
           <cell r="KW24" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="KX24" t="str">
             <v>M</v>
@@ -25421,8 +25421,8 @@
           <cell r="JM25">
             <v>0</v>
           </cell>
-          <cell r="JN25">
-            <v>0</v>
+          <cell r="JN25" t="str">
+            <v>p</v>
           </cell>
           <cell r="JO25">
             <v>0</v>
@@ -25526,8 +25526,8 @@
           <cell r="KV25">
             <v>0</v>
           </cell>
-          <cell r="KW25">
-            <v>0</v>
+          <cell r="KW25" t="str">
+            <v>p</v>
           </cell>
           <cell r="KX25">
             <v>0</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -31040,15 +31040,15 @@
       </c>
       <c r="HO3" s="16" t="str">
         <f>[1]CARTELLINO!HR$3</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="HP3" s="16" t="str">
         <f>[1]CARTELLINO!HS$3</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="HQ3" s="16" t="str">
         <f>[1]CARTELLINO!HT$3</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="HR3" s="16" t="str">
         <f>[1]CARTELLINO!HU$3</f>
@@ -45611,7 +45611,7 @@
       </c>
       <c r="JJ15" s="26" t="str">
         <f>[1]CARTELLINO!JM$15</f>
-        <v>M</v>
+        <v>p</v>
       </c>
       <c r="JK15" s="26" t="str">
         <f>[1]CARTELLINO!JN$15</f>
@@ -49019,11 +49019,11 @@
       </c>
       <c r="HO18" s="27" t="str">
         <f>[1]CARTELLINO!HR$18</f>
-        <v>R</v>
+        <v>p</v>
       </c>
       <c r="HP18" s="27" t="str">
         <f>[1]CARTELLINO!HS$18</f>
-        <v>P</v>
+        <v>r</v>
       </c>
       <c r="HQ18" s="27" t="str">
         <f>[1]CARTELLINO!HT$18</f>
@@ -52947,7 +52947,7 @@
       </c>
       <c r="KT21" s="28" t="str">
         <f>[1]CARTELLINO!KW$21</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="KU21" s="28" t="str">
         <f>[1]CARTELLINO!KX$21</f>
@@ -56399,11 +56399,11 @@
       </c>
       <c r="JJ24" s="29" t="str">
         <f>[1]CARTELLINO!JM$24</f>
-        <v>p</v>
+        <v>M</v>
       </c>
       <c r="JK24" s="29" t="str">
         <f>[1]CARTELLINO!JN$24</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="JL24" s="29" t="str">
         <f>[1]CARTELLINO!JO$24</f>
@@ -56543,7 +56543,7 @@
       </c>
       <c r="KT24" s="29" t="str">
         <f>[1]CARTELLINO!KW$24</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="KU24" s="29" t="str">
         <f>[1]CARTELLINO!KX$24</f>
@@ -57995,9 +57995,9 @@
         <f>[1]CARTELLINO!JM$25</f>
         <v>0</v>
       </c>
-      <c r="JK25" s="46">
+      <c r="JK25" s="46" t="str">
         <f>[1]CARTELLINO!JN$25</f>
-        <v>0</v>
+        <v>p</v>
       </c>
       <c r="JL25" s="46">
         <f>[1]CARTELLINO!JO$25</f>
@@ -58135,9 +58135,9 @@
         <f>[1]CARTELLINO!KV$25</f>
         <v>0</v>
       </c>
-      <c r="KT25" s="46">
+      <c r="KT25" s="46" t="str">
         <f>[1]CARTELLINO!KW$25</f>
-        <v>0</v>
+        <v>p</v>
       </c>
       <c r="KU25" s="46">
         <f>[1]CARTELLINO!KX$25</f>
@@ -63825,7 +63825,7 @@
         <v>BERARDI</v>
       </c>
       <c r="GX30" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="GY30" s="63" t="str">
         <v>VOLPINI</v>
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,13 +71029,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71044,6 +71037,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA453EE0-EBAD-411C-B4DE-1A9BE8B81930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E93BA407-C5D3-449F-815F-14D2304718C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="0" yWindow="75" windowWidth="28800" windowHeight="15405" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7392,7 +7392,7 @@
             <v>r</v>
           </cell>
           <cell r="HE3" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="HF3" t="str">
             <v>m</v>
@@ -8581,8 +8581,8 @@
           <cell r="HD4">
             <v>0</v>
           </cell>
-          <cell r="HE4" t="str">
-            <v>nl</v>
+          <cell r="HE4">
+            <v>0</v>
           </cell>
           <cell r="HF4">
             <v>0</v>
@@ -14529,7 +14529,7 @@
             <v>R</v>
           </cell>
           <cell r="HE12" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="HF12" t="str">
             <v>M/R</v>
@@ -15718,8 +15718,8 @@
           <cell r="HD13">
             <v>0</v>
           </cell>
-          <cell r="HE13">
-            <v>0</v>
+          <cell r="HE13" t="str">
+            <v>nl</v>
           </cell>
           <cell r="HF13">
             <v>0</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -30988,7 +30988,7 @@
       </c>
       <c r="HB3" s="16" t="str">
         <f>[1]CARTELLINO!HE$3</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="HC3" s="16" t="str">
         <f>[1]CARTELLINO!HF$3</f>
@@ -32580,9 +32580,9 @@
         <f>[1]CARTELLINO!HD$4</f>
         <v>0</v>
       </c>
-      <c r="HB4" s="43" t="str">
+      <c r="HB4" s="43">
         <f>[1]CARTELLINO!HE$4</f>
-        <v>nl</v>
+        <v>0</v>
       </c>
       <c r="HC4" s="43">
         <f>[1]CARTELLINO!HF$4</f>
@@ -41775,7 +41775,7 @@
       </c>
       <c r="HB12" s="25" t="str">
         <f>[1]CARTELLINO!HE$12</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="HC12" s="25" t="str">
         <f>[1]CARTELLINO!HF$12</f>
@@ -43367,9 +43367,9 @@
         <f>[1]CARTELLINO!HD$13</f>
         <v>0</v>
       </c>
-      <c r="HB13" s="46">
+      <c r="HB13" s="46" t="str">
         <f>[1]CARTELLINO!HE$13</f>
-        <v>0</v>
+        <v>nl</v>
       </c>
       <c r="HC13" s="46">
         <f>[1]CARTELLINO!HF$13</f>
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,6 +71029,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71037,13 +71044,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E93BA407-C5D3-449F-815F-14D2304718C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47DE598C-3B63-4F7D-94DB-A3DDBF3E6BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="75" windowWidth="28800" windowHeight="15405" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4956,18 +4956,18 @@
             <v>SARTI</v>
           </cell>
           <cell r="AS244" t="str">
-            <v>BIANCHI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT244" t="str">
-            <v>BIANCHI</v>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="245">
           <cell r="AQ245" t="str">
-            <v>BIANCHI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR245" t="str">
-            <v>BIANCHI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS245" t="str">
             <v>FABBRI</v>
@@ -4998,18 +4998,18 @@
             <v>GHIOTTI</v>
           </cell>
           <cell r="AS247" t="str">
-            <v>BERARDI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT247" t="str">
-            <v>BERARDI</v>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="248">
           <cell r="AQ248" t="str">
-            <v>BERARDI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR248" t="str">
-            <v>BERARDI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS248" t="str">
             <v>SARTI</v>
@@ -14598,13 +14598,13 @@
             <v>r</v>
           </cell>
           <cell r="IB12" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="IC12" t="str">
             <v>m/R</v>
           </cell>
           <cell r="ID12" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="IE12" t="str">
             <v>m</v>
@@ -16978,13 +16978,13 @@
             <v>p</v>
           </cell>
           <cell r="IB15" t="str">
-            <v>m</v>
+            <v>N</v>
           </cell>
           <cell r="IC15" t="str">
-            <v>p</v>
+            <v>S</v>
           </cell>
           <cell r="ID15" t="str">
-            <v>P</v>
+            <v>R</v>
           </cell>
           <cell r="IE15" t="str">
             <v>M/R</v>
@@ -17146,7 +17146,7 @@
             <v>r</v>
           </cell>
           <cell r="KF15" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="KG15" t="str">
             <v>P</v>
@@ -21738,13 +21738,13 @@
             <v>M/R</v>
           </cell>
           <cell r="IB21" t="str">
-            <v>N</v>
+            <v>p</v>
           </cell>
           <cell r="IC21" t="str">
-            <v>S</v>
+            <v>p</v>
           </cell>
           <cell r="ID21" t="str">
-            <v>R</v>
+            <v>r</v>
           </cell>
           <cell r="IE21" t="str">
             <v>r</v>
@@ -21753,25 +21753,25 @@
             <v>m</v>
           </cell>
           <cell r="IG21" t="str">
+            <v>m/R</v>
+          </cell>
+          <cell r="IH21" t="str">
             <v>p</v>
           </cell>
-          <cell r="IH21" t="str">
+          <cell r="II21" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="IJ21" t="str">
             <v>m</v>
           </cell>
-          <cell r="II21" t="str">
-            <v>P</v>
-          </cell>
-          <cell r="IJ21" t="str">
-            <v>M/R</v>
-          </cell>
           <cell r="IK21" t="str">
-            <v>N</v>
+            <v>p</v>
           </cell>
           <cell r="IL21" t="str">
-            <v>S</v>
+            <v>r</v>
           </cell>
           <cell r="IM21" t="str">
-            <v>R</v>
+            <v>r</v>
           </cell>
           <cell r="IN21" t="str">
             <v>r</v>
@@ -24133,25 +24133,25 @@
             <v>p</v>
           </cell>
           <cell r="IG24" t="str">
-            <v>m/R</v>
+            <v>p</v>
           </cell>
           <cell r="IH24" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="II24" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="IJ24" t="str">
-            <v>m</v>
+            <v>M/R</v>
           </cell>
           <cell r="IK24" t="str">
-            <v>p</v>
+            <v>N</v>
           </cell>
           <cell r="IL24" t="str">
-            <v>r</v>
+            <v>S</v>
           </cell>
           <cell r="IM24" t="str">
-            <v>r</v>
+            <v>R</v>
           </cell>
           <cell r="IN24" t="str">
             <v>P</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -41867,7 +41867,7 @@
       </c>
       <c r="HY12" s="25" t="str">
         <f>[1]CARTELLINO!IB$12</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="HZ12" s="25" t="str">
         <f>[1]CARTELLINO!IC$12</f>
@@ -41875,7 +41875,7 @@
       </c>
       <c r="IA12" s="25" t="str">
         <f>[1]CARTELLINO!ID$12</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="IB12" s="25" t="str">
         <f>[1]CARTELLINO!IE$12</f>
@@ -45463,15 +45463,15 @@
       </c>
       <c r="HY15" s="26" t="str">
         <f>[1]CARTELLINO!IB$15</f>
-        <v>m</v>
+        <v>N</v>
       </c>
       <c r="HZ15" s="26" t="str">
         <f>[1]CARTELLINO!IC$15</f>
-        <v>p</v>
+        <v>S</v>
       </c>
       <c r="IA15" s="26" t="str">
         <f>[1]CARTELLINO!ID$15</f>
-        <v>P</v>
+        <v>R</v>
       </c>
       <c r="IB15" s="26" t="str">
         <f>[1]CARTELLINO!IE$15</f>
@@ -45687,7 +45687,7 @@
       </c>
       <c r="KC15" s="26" t="str">
         <f>[1]CARTELLINO!KF$15</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="KD15" s="26" t="str">
         <f>[1]CARTELLINO!KG$15</f>
@@ -52655,15 +52655,15 @@
       </c>
       <c r="HY21" s="28" t="str">
         <f>[1]CARTELLINO!IB$21</f>
-        <v>N</v>
+        <v>p</v>
       </c>
       <c r="HZ21" s="28" t="str">
         <f>[1]CARTELLINO!IC$21</f>
-        <v>S</v>
+        <v>p</v>
       </c>
       <c r="IA21" s="28" t="str">
         <f>[1]CARTELLINO!ID$21</f>
-        <v>R</v>
+        <v>r</v>
       </c>
       <c r="IB21" s="28" t="str">
         <f>[1]CARTELLINO!IE$21</f>
@@ -52675,31 +52675,31 @@
       </c>
       <c r="ID21" s="28" t="str">
         <f>[1]CARTELLINO!IG$21</f>
-        <v>p</v>
+        <v>m/R</v>
       </c>
       <c r="IE21" s="28" t="str">
         <f>[1]CARTELLINO!IH$21</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="IF21" s="28" t="str">
         <f>[1]CARTELLINO!II$21</f>
-        <v>P</v>
+        <v>p</v>
       </c>
       <c r="IG21" s="28" t="str">
         <f>[1]CARTELLINO!IJ$21</f>
-        <v>M/R</v>
+        <v>m</v>
       </c>
       <c r="IH21" s="28" t="str">
         <f>[1]CARTELLINO!IK$21</f>
-        <v>N</v>
+        <v>p</v>
       </c>
       <c r="II21" s="28" t="str">
         <f>[1]CARTELLINO!IL$21</f>
-        <v>S</v>
+        <v>r</v>
       </c>
       <c r="IJ21" s="28" t="str">
         <f>[1]CARTELLINO!IM$21</f>
-        <v>R</v>
+        <v>r</v>
       </c>
       <c r="IK21" s="28" t="str">
         <f>[1]CARTELLINO!IN$21</f>
@@ -56271,31 +56271,31 @@
       </c>
       <c r="ID24" s="29" t="str">
         <f>[1]CARTELLINO!IG$24</f>
-        <v>m/R</v>
+        <v>p</v>
       </c>
       <c r="IE24" s="29" t="str">
         <f>[1]CARTELLINO!IH$24</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="IF24" s="29" t="str">
         <f>[1]CARTELLINO!II$24</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="IG24" s="29" t="str">
         <f>[1]CARTELLINO!IJ$24</f>
-        <v>m</v>
+        <v>M/R</v>
       </c>
       <c r="IH24" s="29" t="str">
         <f>[1]CARTELLINO!IK$24</f>
-        <v>p</v>
+        <v>N</v>
       </c>
       <c r="II24" s="29" t="str">
         <f>[1]CARTELLINO!IL$24</f>
-        <v>r</v>
+        <v>S</v>
       </c>
       <c r="IJ24" s="29" t="str">
         <f>[1]CARTELLINO!IM$24</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="IK24" s="29" t="str">
         <f>[1]CARTELLINO!IN$24</f>
@@ -62824,7 +62824,7 @@
         <v>SARTI</v>
       </c>
       <c r="IE29" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>BERARDI</v>
       </c>
       <c r="IF29" s="63" t="str">
         <v>FABBRI</v>
@@ -62833,7 +62833,7 @@
         <v>GHIOTTI</v>
       </c>
       <c r="IH29" s="63" t="str">
-        <v>BERARDI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="II29" s="63" t="str">
         <v>SARTI</v>
@@ -63924,7 +63924,7 @@
         <v>SARTI</v>
       </c>
       <c r="IE30" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>BERARDI</v>
       </c>
       <c r="IF30" s="63" t="str">
         <v>FABBRI</v>
@@ -63933,7 +63933,7 @@
         <v>GHIOTTI</v>
       </c>
       <c r="IH30" s="63" t="str">
-        <v>BERARDI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="II30" s="63" t="str">
         <v>SARTI</v>
@@ -65021,7 +65021,7 @@
         <v>SARTI</v>
       </c>
       <c r="ID31" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>BERARDI</v>
       </c>
       <c r="IE31" s="63" t="str">
         <v>FABBRI</v>
@@ -65030,7 +65030,7 @@
         <v>GHIOTTI</v>
       </c>
       <c r="IG31" s="63" t="str">
-        <v>BERARDI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="IH31" s="63" t="str">
         <v>SARTI</v>
@@ -66121,7 +66121,7 @@
         <v>SARTI</v>
       </c>
       <c r="ID32" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>BERARDI</v>
       </c>
       <c r="IE32" s="63" t="str">
         <v>FABBRI</v>
@@ -66130,7 +66130,7 @@
         <v>GHIOTTI</v>
       </c>
       <c r="IG32" s="63" t="str">
-        <v>BERARDI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="IH32" s="63" t="str">
         <v>SARTI</v>
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,13 +71029,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71044,6 +71037,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47DE598C-3B63-4F7D-94DB-A3DDBF3E6BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EBFF550-9578-4FA6-B28B-064E71BADCBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -4533,7 +4533,7 @@
             <v>MICHELOT.</v>
           </cell>
           <cell r="AR214" t="str">
-            <v>MICHELOT.</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS214" t="str">
             <v>FABBRI</v>
@@ -4592,18 +4592,18 @@
             <v>VOLPINI</v>
           </cell>
           <cell r="AS218" t="str">
-            <v>GHIOTTI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT218" t="str">
-            <v>GHIOTTI</v>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="219">
           <cell r="AQ219" t="str">
-            <v>GHIOTTI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR219" t="str">
-            <v>GHIOTTI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS219" t="str">
             <v>FABBRI</v>
@@ -7398,19 +7398,19 @@
             <v>m</v>
           </cell>
           <cell r="HG3" t="str">
-            <v>p</v>
+            <v>m/R</v>
           </cell>
           <cell r="HH3" t="str">
             <v>p</v>
           </cell>
           <cell r="HI3" t="str">
-            <v>N</v>
+            <v>m</v>
           </cell>
           <cell r="HJ3" t="str">
-            <v>S</v>
+            <v>r</v>
           </cell>
           <cell r="HK3" t="str">
-            <v>R</v>
+            <v>m</v>
           </cell>
           <cell r="HL3" t="str">
             <v>P</v>
@@ -9772,19 +9772,19 @@
             <v>M/R</v>
           </cell>
           <cell r="HF6" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="HG6" t="str">
-            <v>m</v>
+            <v>M</v>
           </cell>
           <cell r="HH6" t="str">
-            <v>m</v>
+            <v>N</v>
           </cell>
           <cell r="HI6" t="str">
-            <v>r</v>
+            <v>S</v>
           </cell>
           <cell r="HJ6" t="str">
-            <v>r</v>
+            <v>R</v>
           </cell>
           <cell r="HK6" t="str">
             <v>P</v>
@@ -9811,13 +9811,13 @@
             <v>m</v>
           </cell>
           <cell r="HS6" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="HT6" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="HU6" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="HV6" t="str">
             <v>m</v>
@@ -9826,7 +9826,7 @@
             <v>p</v>
           </cell>
           <cell r="HX6" t="str">
-            <v>m</v>
+            <v>r</v>
           </cell>
           <cell r="HY6" t="str">
             <v>P</v>
@@ -16912,22 +16912,22 @@
             <v>R</v>
           </cell>
           <cell r="HF15" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="HG15" t="str">
-            <v>M/R</v>
+            <v>-</v>
           </cell>
           <cell r="HH15" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="HI15" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="HJ15" t="str">
             <v>R</v>
           </cell>
           <cell r="HK15" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="HL15" t="str">
             <v>m/R</v>
@@ -18101,20 +18101,20 @@
           <cell r="HE16" t="str">
             <v>f</v>
           </cell>
-          <cell r="HF16">
-            <v>0</v>
-          </cell>
-          <cell r="HG16">
-            <v>0</v>
-          </cell>
-          <cell r="HH16">
-            <v>0</v>
-          </cell>
-          <cell r="HI16">
-            <v>0</v>
-          </cell>
-          <cell r="HJ16">
-            <v>0</v>
+          <cell r="HF16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="HG16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="HH16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="HI16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="HJ16" t="str">
+            <v>m</v>
           </cell>
           <cell r="HK16">
             <v>0</v>
@@ -19715,16 +19715,16 @@
             <v>R</v>
           </cell>
           <cell r="MQ18" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="MR18" t="str">
-            <v>M</v>
+            <v>-</v>
           </cell>
           <cell r="MS18" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="MT18" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="MU18" t="str">
             <v>R</v>
@@ -19733,13 +19733,13 @@
             <v>P</v>
           </cell>
           <cell r="MW18" t="str">
-            <v>M</v>
+            <v>M+N</v>
           </cell>
           <cell r="MX18" t="str">
-            <v>N</v>
+            <v>S</v>
           </cell>
           <cell r="MY18" t="str">
-            <v>S</v>
+            <v>R</v>
           </cell>
           <cell r="MZ18" t="str">
             <v>R</v>
@@ -20904,20 +20904,20 @@
           <cell r="MP19">
             <v>0</v>
           </cell>
-          <cell r="MQ19">
-            <v>0</v>
-          </cell>
-          <cell r="MR19">
-            <v>0</v>
-          </cell>
-          <cell r="MS19">
-            <v>0</v>
-          </cell>
-          <cell r="MT19">
-            <v>0</v>
-          </cell>
-          <cell r="MU19">
-            <v>0</v>
+          <cell r="MQ19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="MR19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="MS19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="MT19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="MU19" t="str">
+            <v>f</v>
           </cell>
           <cell r="MV19">
             <v>0</v>
@@ -22113,13 +22113,13 @@
             <v>M</v>
           </cell>
           <cell r="MW21" t="str">
+            <v>R</v>
+          </cell>
+          <cell r="MX21" t="str">
             <v>N</v>
           </cell>
-          <cell r="MX21" t="str">
+          <cell r="MY21" t="str">
             <v>S</v>
-          </cell>
-          <cell r="MY21" t="str">
-            <v>R</v>
           </cell>
           <cell r="MZ21" t="str">
             <v>P</v>
@@ -26441,13 +26441,13 @@
             <v>M/R</v>
           </cell>
           <cell r="HI27" t="str">
-            <v>p</v>
+            <v>N</v>
           </cell>
           <cell r="HJ27" t="str">
-            <v>r</v>
+            <v>S</v>
           </cell>
           <cell r="HK27" t="str">
-            <v>p</v>
+            <v>R</v>
           </cell>
           <cell r="HL27" t="str">
             <v>p</v>
@@ -26855,19 +26855,19 @@
             <v>-</v>
           </cell>
           <cell r="MQ27" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="MR27" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="MS27" t="str">
-            <v>-</v>
+            <v>N</v>
           </cell>
           <cell r="MT27" t="str">
-            <v>-</v>
+            <v>S</v>
           </cell>
           <cell r="MU27" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="MV27" t="str">
             <v>-</v>
@@ -28056,8 +28056,8 @@
           <cell r="MT28">
             <v>0</v>
           </cell>
-          <cell r="MU28" t="str">
-            <v>f</v>
+          <cell r="MU28">
+            <v>0</v>
           </cell>
           <cell r="MV28" t="str">
             <v>f</v>
@@ -30996,7 +30996,7 @@
       </c>
       <c r="HD3" s="16" t="str">
         <f>[1]CARTELLINO!HG$3</f>
-        <v>p</v>
+        <v>m/R</v>
       </c>
       <c r="HE3" s="16" t="str">
         <f>[1]CARTELLINO!HH$3</f>
@@ -31004,15 +31004,15 @@
       </c>
       <c r="HF3" s="16" t="str">
         <f>[1]CARTELLINO!HI$3</f>
-        <v>N</v>
+        <v>m</v>
       </c>
       <c r="HG3" s="16" t="str">
         <f>[1]CARTELLINO!HJ$3</f>
-        <v>S</v>
+        <v>r</v>
       </c>
       <c r="HH3" s="16" t="str">
         <f>[1]CARTELLINO!HK$3</f>
-        <v>R</v>
+        <v>m</v>
       </c>
       <c r="HI3" s="16" t="str">
         <f>[1]CARTELLINO!HL$3</f>
@@ -34587,23 +34587,23 @@
       </c>
       <c r="HC6" s="22" t="str">
         <f>[1]CARTELLINO!HF$6</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="HD6" s="22" t="str">
         <f>[1]CARTELLINO!HG$6</f>
-        <v>m</v>
+        <v>M</v>
       </c>
       <c r="HE6" s="22" t="str">
         <f>[1]CARTELLINO!HH$6</f>
-        <v>m</v>
+        <v>N</v>
       </c>
       <c r="HF6" s="22" t="str">
         <f>[1]CARTELLINO!HI$6</f>
-        <v>r</v>
+        <v>S</v>
       </c>
       <c r="HG6" s="22" t="str">
         <f>[1]CARTELLINO!HJ$6</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="HH6" s="22" t="str">
         <f>[1]CARTELLINO!HK$6</f>
@@ -34639,15 +34639,15 @@
       </c>
       <c r="HP6" s="22" t="str">
         <f>[1]CARTELLINO!HS$6</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="HQ6" s="22" t="str">
         <f>[1]CARTELLINO!HT$6</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="HR6" s="22" t="str">
         <f>[1]CARTELLINO!HU$6</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="HS6" s="22" t="str">
         <f>[1]CARTELLINO!HV$6</f>
@@ -34659,7 +34659,7 @@
       </c>
       <c r="HU6" s="22" t="str">
         <f>[1]CARTELLINO!HX$6</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="HV6" s="22" t="str">
         <f>[1]CARTELLINO!HY$6</f>
@@ -45375,19 +45375,19 @@
       </c>
       <c r="HC15" s="26" t="str">
         <f>[1]CARTELLINO!HF$15</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="HD15" s="26" t="str">
         <f>[1]CARTELLINO!HG$15</f>
-        <v>M/R</v>
+        <v>-</v>
       </c>
       <c r="HE15" s="26" t="str">
         <f>[1]CARTELLINO!HH$15</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="HF15" s="26" t="str">
         <f>[1]CARTELLINO!HI$15</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="HG15" s="26" t="str">
         <f>[1]CARTELLINO!HJ$15</f>
@@ -45395,7 +45395,7 @@
       </c>
       <c r="HH15" s="26" t="str">
         <f>[1]CARTELLINO!HK$15</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="HI15" s="26" t="str">
         <f>[1]CARTELLINO!HL$15</f>
@@ -46967,25 +46967,25 @@
         <f>[1]CARTELLINO!HE$16</f>
         <v>f</v>
       </c>
-      <c r="HC16" s="46">
+      <c r="HC16" s="46" t="str">
         <f>[1]CARTELLINO!HF$16</f>
-        <v>0</v>
-      </c>
-      <c r="HD16" s="46">
+        <v>m</v>
+      </c>
+      <c r="HD16" s="46" t="str">
         <f>[1]CARTELLINO!HG$16</f>
-        <v>0</v>
-      </c>
-      <c r="HE16" s="46">
+        <v>m</v>
+      </c>
+      <c r="HE16" s="46" t="str">
         <f>[1]CARTELLINO!HH$16</f>
-        <v>0</v>
-      </c>
-      <c r="HF16" s="46">
+        <v>m</v>
+      </c>
+      <c r="HF16" s="46" t="str">
         <f>[1]CARTELLINO!HI$16</f>
-        <v>0</v>
-      </c>
-      <c r="HG16" s="46">
+        <v>m</v>
+      </c>
+      <c r="HG16" s="46" t="str">
         <f>[1]CARTELLINO!HJ$16</f>
-        <v>0</v>
+        <v>m</v>
       </c>
       <c r="HH16" s="46">
         <f>[1]CARTELLINO!HK$16</f>
@@ -49535,19 +49535,19 @@
       </c>
       <c r="MN18" s="27" t="str">
         <f>[1]CARTELLINO!MQ$18</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="MO18" s="27" t="str">
         <f>[1]CARTELLINO!MR$18</f>
-        <v>M</v>
+        <v>-</v>
       </c>
       <c r="MP18" s="27" t="str">
         <f>[1]CARTELLINO!MS$18</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="MQ18" s="27" t="str">
         <f>[1]CARTELLINO!MT$18</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="MR18" s="27" t="str">
         <f>[1]CARTELLINO!MU$18</f>
@@ -49559,15 +49559,15 @@
       </c>
       <c r="MT18" s="27" t="str">
         <f>[1]CARTELLINO!MW$18</f>
-        <v>M</v>
+        <v>M+N</v>
       </c>
       <c r="MU18" s="27" t="str">
         <f>[1]CARTELLINO!MX$18</f>
-        <v>N</v>
+        <v>S</v>
       </c>
       <c r="MV18" s="27" t="str">
         <f>[1]CARTELLINO!MY$18</f>
-        <v>S</v>
+        <v>R</v>
       </c>
       <c r="MW18" s="27" t="str">
         <f>[1]CARTELLINO!MZ$18</f>
@@ -51127,25 +51127,25 @@
         <f>[1]CARTELLINO!MP$19</f>
         <v>0</v>
       </c>
-      <c r="MN19" s="46">
+      <c r="MN19" s="46" t="str">
         <f>[1]CARTELLINO!MQ$19</f>
-        <v>0</v>
-      </c>
-      <c r="MO19" s="46">
+        <v>f</v>
+      </c>
+      <c r="MO19" s="46" t="str">
         <f>[1]CARTELLINO!MR$19</f>
-        <v>0</v>
-      </c>
-      <c r="MP19" s="46">
+        <v>f</v>
+      </c>
+      <c r="MP19" s="46" t="str">
         <f>[1]CARTELLINO!MS$19</f>
-        <v>0</v>
-      </c>
-      <c r="MQ19" s="46">
+        <v>f</v>
+      </c>
+      <c r="MQ19" s="46" t="str">
         <f>[1]CARTELLINO!MT$19</f>
-        <v>0</v>
-      </c>
-      <c r="MR19" s="46">
+        <v>f</v>
+      </c>
+      <c r="MR19" s="46" t="str">
         <f>[1]CARTELLINO!MU$19</f>
-        <v>0</v>
+        <v>f</v>
       </c>
       <c r="MS19" s="46">
         <f>[1]CARTELLINO!MV$19</f>
@@ -53155,15 +53155,15 @@
       </c>
       <c r="MT21" s="28" t="str">
         <f>[1]CARTELLINO!MW$21</f>
-        <v>N</v>
+        <v>R</v>
       </c>
       <c r="MU21" s="28" t="str">
         <f>[1]CARTELLINO!MX$21</f>
-        <v>S</v>
+        <v>N</v>
       </c>
       <c r="MV21" s="28" t="str">
         <f>[1]CARTELLINO!MY$21</f>
-        <v>R</v>
+        <v>S</v>
       </c>
       <c r="MW21" s="28" t="str">
         <f>[1]CARTELLINO!MZ$21</f>
@@ -59771,15 +59771,15 @@
       </c>
       <c r="HF27" s="30" t="str">
         <f>[1]CARTELLINO!HI$27</f>
-        <v>p</v>
+        <v>N</v>
       </c>
       <c r="HG27" s="30" t="str">
         <f>[1]CARTELLINO!HJ$27</f>
-        <v>r</v>
+        <v>S</v>
       </c>
       <c r="HH27" s="30" t="str">
         <f>[1]CARTELLINO!HK$27</f>
-        <v>p</v>
+        <v>R</v>
       </c>
       <c r="HI27" s="30" t="str">
         <f>[1]CARTELLINO!HL$27</f>
@@ -60323,23 +60323,23 @@
       </c>
       <c r="MN27" s="30" t="str">
         <f>[1]CARTELLINO!MQ$27</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="MO27" s="30" t="str">
         <f>[1]CARTELLINO!MR$27</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="MP27" s="30" t="str">
         <f>[1]CARTELLINO!MS$27</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="MQ27" s="30" t="str">
         <f>[1]CARTELLINO!MT$27</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="MR27" s="30" t="str">
         <f>[1]CARTELLINO!MU$27</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="MS27" s="30" t="str">
         <f>[1]CARTELLINO!MV$27</f>
@@ -61931,9 +61931,9 @@
         <f>[1]CARTELLINO!MT$28</f>
         <v>0</v>
       </c>
-      <c r="MR28" s="62" t="str">
+      <c r="MR28" s="62">
         <f>[1]CARTELLINO!MU$28</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="MS28" s="62" t="str">
         <f>[1]CARTELLINO!MV$28</f>
@@ -62746,7 +62746,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="HE29" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="HF29" s="63" t="str">
         <v>FABBRI</v>
@@ -63831,7 +63831,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="GZ30" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BERARDI</v>
       </c>
       <c r="HA30" s="63" t="str">
         <v>FABBRI</v>
@@ -63846,7 +63846,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="HE30" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="HF30" s="63" t="str">
         <v>FABBRI</v>
@@ -64943,7 +64943,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="HD31" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="HE31" s="63" t="str">
         <v>FABBRI</v>
@@ -66043,7 +66043,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="HD32" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="HE32" s="63" t="str">
         <v>FABBRI</v>

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EBFF550-9578-4FA6-B28B-064E71BADCBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E6B01E-D6DF-4480-879F-342C15B131A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -10078,7 +10078,7 @@
             <v>R</v>
           </cell>
           <cell r="LD6" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="LE6" t="str">
             <v>M</v>
@@ -11267,8 +11267,8 @@
           <cell r="LC7">
             <v>0</v>
           </cell>
-          <cell r="LD7">
-            <v>0</v>
+          <cell r="LD7" t="str">
+            <v>p</v>
           </cell>
           <cell r="LE7">
             <v>0</v>
@@ -16972,7 +16972,7 @@
             <v>r</v>
           </cell>
           <cell r="HZ15" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="IA15" t="str">
             <v>p</v>
@@ -21978,7 +21978,7 @@
             <v>-</v>
           </cell>
           <cell r="LD21" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="LE21" t="str">
             <v>P</v>
@@ -34995,7 +34995,7 @@
       </c>
       <c r="LA6" s="22" t="str">
         <f>[1]CARTELLINO!LD$6</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="LB6" s="22" t="str">
         <f>[1]CARTELLINO!LE$6</f>
@@ -36587,9 +36587,9 @@
         <f>[1]CARTELLINO!LC$7</f>
         <v>0</v>
       </c>
-      <c r="LA7" s="46">
+      <c r="LA7" s="46" t="str">
         <f>[1]CARTELLINO!LD$7</f>
-        <v>0</v>
+        <v>p</v>
       </c>
       <c r="LB7" s="46">
         <f>[1]CARTELLINO!LE$7</f>
@@ -45455,7 +45455,7 @@
       </c>
       <c r="HW15" s="26" t="str">
         <f>[1]CARTELLINO!HZ$15</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="HX15" s="26" t="str">
         <f>[1]CARTELLINO!IA$15</f>
@@ -52975,7 +52975,7 @@
       </c>
       <c r="LA21" s="28" t="str">
         <f>[1]CARTELLINO!LD$21</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="LB21" s="28" t="str">
         <f>[1]CARTELLINO!LE$21</f>

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E6B01E-D6DF-4480-879F-342C15B131A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9674C4E-3962-471C-90B8-64D2FFC82D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4662,18 +4662,18 @@
             <v>VOLPINI</v>
           </cell>
           <cell r="AS223" t="str">
-            <v>GHIOTTI</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT223" t="str">
-            <v>GHIOTTI</v>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="224">
           <cell r="AQ224" t="str">
-            <v>GHIOTTI</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR224" t="str">
-            <v>GHIOTTI</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS224" t="str">
             <v>PAZZAGLIA</v>
@@ -4690,18 +4690,18 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS225" t="str">
-            <v>BARBIERI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT225" t="str">
-            <v>BARBIERI</v>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="226">
           <cell r="AQ226" t="str">
-            <v>BARBIERI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR226" t="str">
-            <v>BARBIERI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS226" t="str">
             <v>MICHELOT.</v>
@@ -5236,18 +5236,18 @@
             <v>SARTI</v>
           </cell>
           <cell r="AS264" t="str">
-            <v>PAZZAGLIA</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT264" t="str">
-            <v>PAZZAGLIA</v>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="265">
           <cell r="AQ265" t="str">
-            <v>PAZZAGLIA</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR265" t="str">
-            <v>PAZZAGLIA</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS265" t="str">
             <v>BIANCHI</v>
@@ -5278,18 +5278,18 @@
             <v>GHIOTTI</v>
           </cell>
           <cell r="AS267" t="str">
-            <v>VOLPINI</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT267" t="str">
-            <v>VOLPINI</v>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="268">
           <cell r="AQ268" t="str">
-            <v>VOLPINI</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR268" t="str">
-            <v>VOLPINI</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS268" t="str">
             <v>BERARDI</v>
@@ -7404,7 +7404,7 @@
             <v>p</v>
           </cell>
           <cell r="HI3" t="str">
-            <v>m</v>
+            <v>r</v>
           </cell>
           <cell r="HJ3" t="str">
             <v>r</v>
@@ -7506,7 +7506,7 @@
             <v>m</v>
           </cell>
           <cell r="IQ3" t="str">
-            <v>p</v>
+            <v>M</v>
           </cell>
           <cell r="IR3" t="str">
             <v>N</v>
@@ -7536,7 +7536,7 @@
             <v>P</v>
           </cell>
           <cell r="JA3" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="JB3" t="str">
             <v>-</v>
@@ -9790,13 +9790,13 @@
             <v>P</v>
           </cell>
           <cell r="HL6" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="HM6" t="str">
             <v>P</v>
           </cell>
           <cell r="HN6" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="HO6" t="str">
             <v>N</v>
@@ -9922,7 +9922,7 @@
             <v>P</v>
           </cell>
           <cell r="JD6" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JE6" t="str">
             <v>N</v>
@@ -14646,7 +14646,7 @@
             <v>m/R</v>
           </cell>
           <cell r="IR12" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="IS12" t="str">
             <v>r</v>
@@ -14676,13 +14676,13 @@
             <v>p</v>
           </cell>
           <cell r="JB12" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="JC12" t="str">
             <v>p</v>
           </cell>
-          <cell r="JC12" t="str">
+          <cell r="JD12" t="str">
             <v>m</v>
-          </cell>
-          <cell r="JD12" t="str">
-            <v>m/R</v>
           </cell>
           <cell r="JE12" t="str">
             <v>p</v>
@@ -16927,25 +16927,25 @@
             <v>R</v>
           </cell>
           <cell r="HK15" t="str">
-            <v>p</v>
+            <v>-</v>
           </cell>
           <cell r="HL15" t="str">
-            <v>m/R</v>
+            <v>-</v>
           </cell>
           <cell r="HM15" t="str">
-            <v>p</v>
+            <v>-</v>
           </cell>
           <cell r="HN15" t="str">
-            <v>p</v>
+            <v>-</v>
           </cell>
           <cell r="HO15" t="str">
-            <v>m</v>
+            <v>R</v>
           </cell>
           <cell r="HP15" t="str">
-            <v>m</v>
+            <v>-</v>
           </cell>
           <cell r="HQ15" t="str">
-            <v>r</v>
+            <v>-</v>
           </cell>
           <cell r="HR15" t="str">
             <v>-</v>
@@ -16954,25 +16954,25 @@
             <v>-</v>
           </cell>
           <cell r="HT15" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="HU15" t="str">
             <v>-</v>
           </cell>
           <cell r="HV15" t="str">
-            <v>R</v>
+            <v>-</v>
           </cell>
           <cell r="HW15" t="str">
             <v>-</v>
           </cell>
           <cell r="HX15" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="HY15" t="str">
+            <v>R</v>
+          </cell>
+          <cell r="HZ15" t="str">
             <v>r</v>
-          </cell>
-          <cell r="HY15" t="str">
-            <v>r</v>
-          </cell>
-          <cell r="HZ15" t="str">
-            <v>m</v>
           </cell>
           <cell r="IA15" t="str">
             <v>p</v>
@@ -17023,10 +17023,10 @@
             <v>M/R</v>
           </cell>
           <cell r="IQ15" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="IR15" t="str">
             <v>r</v>
-          </cell>
-          <cell r="IR15" t="str">
-            <v>P</v>
           </cell>
           <cell r="IS15" t="str">
             <v>M</v>
@@ -17296,10 +17296,10 @@
             <v>M</v>
           </cell>
           <cell r="MD15" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="ME15" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="MF15" t="str">
             <v>R</v>
@@ -17317,13 +17317,13 @@
             <v>-</v>
           </cell>
           <cell r="MK15" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="ML15" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="MM15" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="MN15" t="str">
             <v>-</v>
@@ -18116,26 +18116,26 @@
           <cell r="HJ16" t="str">
             <v>m</v>
           </cell>
-          <cell r="HK16">
-            <v>0</v>
-          </cell>
-          <cell r="HL16">
-            <v>0</v>
-          </cell>
-          <cell r="HM16">
-            <v>0</v>
-          </cell>
-          <cell r="HN16">
-            <v>0</v>
-          </cell>
-          <cell r="HO16">
-            <v>0</v>
-          </cell>
-          <cell r="HP16">
-            <v>0</v>
-          </cell>
-          <cell r="HQ16">
-            <v>0</v>
+          <cell r="HK16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="HL16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="HM16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="HN16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="HO16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="HP16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="HQ16" t="str">
+            <v>m</v>
           </cell>
           <cell r="HR16" t="str">
             <v>f</v>
@@ -18155,11 +18155,11 @@
           <cell r="HW16" t="str">
             <v>ng</v>
           </cell>
-          <cell r="HX16">
-            <v>0</v>
-          </cell>
-          <cell r="HY16">
-            <v>0</v>
+          <cell r="HX16" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="HY16" t="str">
+            <v>f</v>
           </cell>
           <cell r="HZ16">
             <v>0</v>
@@ -18485,8 +18485,8 @@
           <cell r="MC16">
             <v>0</v>
           </cell>
-          <cell r="MD16">
-            <v>0</v>
+          <cell r="MD16" t="str">
+            <v>f</v>
           </cell>
           <cell r="ME16" t="str">
             <v>f</v>
@@ -18503,11 +18503,11 @@
           <cell r="MI16" t="str">
             <v>f</v>
           </cell>
-          <cell r="MJ16">
-            <v>0</v>
-          </cell>
-          <cell r="MK16">
-            <v>0</v>
+          <cell r="MJ16" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="MK16" t="str">
+            <v>f</v>
           </cell>
           <cell r="ML16">
             <v>0</v>
@@ -19433,10 +19433,10 @@
             <v>p</v>
           </cell>
           <cell r="JA18" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="JB18" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="JC18" t="str">
             <v>-</v>
@@ -21768,7 +21768,7 @@
             <v>p</v>
           </cell>
           <cell r="IL21" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="IM21" t="str">
             <v>r</v>
@@ -21783,10 +21783,10 @@
             <v>p</v>
           </cell>
           <cell r="IQ21" t="str">
-            <v>m</v>
+            <v>-</v>
           </cell>
           <cell r="IR21" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="IS21" t="str">
             <v>r</v>
@@ -22972,11 +22972,11 @@
           <cell r="IP22">
             <v>0</v>
           </cell>
-          <cell r="IQ22">
-            <v>0</v>
-          </cell>
-          <cell r="IR22" t="str">
+          <cell r="IQ22" t="str">
             <v>p</v>
+          </cell>
+          <cell r="IR22">
+            <v>0</v>
           </cell>
           <cell r="IS22">
             <v>0</v>
@@ -26456,7 +26456,7 @@
             <v>m</v>
           </cell>
           <cell r="HN27" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="HO27" t="str">
             <v>p</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -31004,7 +31004,7 @@
       </c>
       <c r="HF3" s="16" t="str">
         <f>[1]CARTELLINO!HI$3</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="HG3" s="16" t="str">
         <f>[1]CARTELLINO!HJ$3</f>
@@ -31140,7 +31140,7 @@
       </c>
       <c r="IN3" s="16" t="str">
         <f>[1]CARTELLINO!IQ$3</f>
-        <v>p</v>
+        <v>M</v>
       </c>
       <c r="IO3" s="16" t="str">
         <f>[1]CARTELLINO!IR$3</f>
@@ -31180,7 +31180,7 @@
       </c>
       <c r="IX3" s="16" t="str">
         <f>[1]CARTELLINO!JA$3</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="IY3" s="16" t="str">
         <f>[1]CARTELLINO!JB$3</f>
@@ -34611,7 +34611,7 @@
       </c>
       <c r="HI6" s="22" t="str">
         <f>[1]CARTELLINO!HL$6</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="HJ6" s="22" t="str">
         <f>[1]CARTELLINO!HM$6</f>
@@ -34619,7 +34619,7 @@
       </c>
       <c r="HK6" s="22" t="str">
         <f>[1]CARTELLINO!HN$6</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="HL6" s="22" t="str">
         <f>[1]CARTELLINO!HO$6</f>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="JA6" s="22" t="str">
         <f>[1]CARTELLINO!JD$6</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="JB6" s="22" t="str">
         <f>[1]CARTELLINO!JE$6</f>
@@ -41931,7 +41931,7 @@
       </c>
       <c r="IO12" s="25" t="str">
         <f>[1]CARTELLINO!IR$12</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="IP12" s="25" t="str">
         <f>[1]CARTELLINO!IS$12</f>
@@ -41971,15 +41971,15 @@
       </c>
       <c r="IY12" s="25" t="str">
         <f>[1]CARTELLINO!JB$12</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="IZ12" s="25" t="str">
         <f>[1]CARTELLINO!JC$12</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="JA12" s="25" t="str">
         <f>[1]CARTELLINO!JD$12</f>
-        <v>m/R</v>
+        <v>m</v>
       </c>
       <c r="JB12" s="25" t="str">
         <f>[1]CARTELLINO!JE$12</f>
@@ -45395,31 +45395,31 @@
       </c>
       <c r="HH15" s="26" t="str">
         <f>[1]CARTELLINO!HK$15</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="HI15" s="26" t="str">
         <f>[1]CARTELLINO!HL$15</f>
-        <v>m/R</v>
+        <v>-</v>
       </c>
       <c r="HJ15" s="26" t="str">
         <f>[1]CARTELLINO!HM$15</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="HK15" s="26" t="str">
         <f>[1]CARTELLINO!HN$15</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="HL15" s="26" t="str">
         <f>[1]CARTELLINO!HO$15</f>
-        <v>m</v>
+        <v>R</v>
       </c>
       <c r="HM15" s="26" t="str">
         <f>[1]CARTELLINO!HP$15</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="HN15" s="26" t="str">
         <f>[1]CARTELLINO!HQ$15</f>
-        <v>r</v>
+        <v>-</v>
       </c>
       <c r="HO15" s="26" t="str">
         <f>[1]CARTELLINO!HR$15</f>
@@ -45431,7 +45431,7 @@
       </c>
       <c r="HQ15" s="26" t="str">
         <f>[1]CARTELLINO!HT$15</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="HR15" s="26" t="str">
         <f>[1]CARTELLINO!HU$15</f>
@@ -45439,7 +45439,7 @@
       </c>
       <c r="HS15" s="26" t="str">
         <f>[1]CARTELLINO!HV$15</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="HT15" s="26" t="str">
         <f>[1]CARTELLINO!HW$15</f>
@@ -45447,15 +45447,15 @@
       </c>
       <c r="HU15" s="26" t="str">
         <f>[1]CARTELLINO!HX$15</f>
-        <v>r</v>
+        <v>-</v>
       </c>
       <c r="HV15" s="26" t="str">
         <f>[1]CARTELLINO!HY$15</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="HW15" s="26" t="str">
         <f>[1]CARTELLINO!HZ$15</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="HX15" s="26" t="str">
         <f>[1]CARTELLINO!IA$15</f>
@@ -45523,11 +45523,11 @@
       </c>
       <c r="IN15" s="26" t="str">
         <f>[1]CARTELLINO!IQ$15</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="IO15" s="26" t="str">
         <f>[1]CARTELLINO!IR$15</f>
-        <v>P</v>
+        <v>r</v>
       </c>
       <c r="IP15" s="26" t="str">
         <f>[1]CARTELLINO!IS$15</f>
@@ -45887,11 +45887,11 @@
       </c>
       <c r="MA15" s="26" t="str">
         <f>[1]CARTELLINO!MD$15</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="MB15" s="26" t="str">
         <f>[1]CARTELLINO!ME$15</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="MC15" s="26" t="str">
         <f>[1]CARTELLINO!MF$15</f>
@@ -45915,15 +45915,15 @@
       </c>
       <c r="MH15" s="26" t="str">
         <f>[1]CARTELLINO!MK$15</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="MI15" s="26" t="str">
         <f>[1]CARTELLINO!ML$15</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="MJ15" s="26" t="str">
         <f>[1]CARTELLINO!MM$15</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="MK15" s="26" t="str">
         <f>[1]CARTELLINO!MN$15</f>
@@ -46987,33 +46987,33 @@
         <f>[1]CARTELLINO!HJ$16</f>
         <v>m</v>
       </c>
-      <c r="HH16" s="46">
+      <c r="HH16" s="46" t="str">
         <f>[1]CARTELLINO!HK$16</f>
-        <v>0</v>
-      </c>
-      <c r="HI16" s="46">
+        <v>m</v>
+      </c>
+      <c r="HI16" s="46" t="str">
         <f>[1]CARTELLINO!HL$16</f>
-        <v>0</v>
-      </c>
-      <c r="HJ16" s="46">
+        <v>m</v>
+      </c>
+      <c r="HJ16" s="46" t="str">
         <f>[1]CARTELLINO!HM$16</f>
-        <v>0</v>
-      </c>
-      <c r="HK16" s="46">
+        <v>m</v>
+      </c>
+      <c r="HK16" s="46" t="str">
         <f>[1]CARTELLINO!HN$16</f>
-        <v>0</v>
-      </c>
-      <c r="HL16" s="46">
+        <v>m</v>
+      </c>
+      <c r="HL16" s="46" t="str">
         <f>[1]CARTELLINO!HO$16</f>
-        <v>0</v>
-      </c>
-      <c r="HM16" s="46">
+        <v>m</v>
+      </c>
+      <c r="HM16" s="46" t="str">
         <f>[1]CARTELLINO!HP$16</f>
-        <v>0</v>
-      </c>
-      <c r="HN16" s="46">
+        <v>m</v>
+      </c>
+      <c r="HN16" s="46" t="str">
         <f>[1]CARTELLINO!HQ$16</f>
-        <v>0</v>
+        <v>m</v>
       </c>
       <c r="HO16" s="46" t="str">
         <f>[1]CARTELLINO!HR$16</f>
@@ -47039,13 +47039,13 @@
         <f>[1]CARTELLINO!HW$16</f>
         <v>ng</v>
       </c>
-      <c r="HU16" s="46">
+      <c r="HU16" s="46" t="str">
         <f>[1]CARTELLINO!HX$16</f>
-        <v>0</v>
-      </c>
-      <c r="HV16" s="46">
+        <v>f</v>
+      </c>
+      <c r="HV16" s="46" t="str">
         <f>[1]CARTELLINO!HY$16</f>
-        <v>0</v>
+        <v>f</v>
       </c>
       <c r="HW16" s="46">
         <f>[1]CARTELLINO!HZ$16</f>
@@ -47479,9 +47479,9 @@
         <f>[1]CARTELLINO!MC$16</f>
         <v>0</v>
       </c>
-      <c r="MA16" s="46">
+      <c r="MA16" s="46" t="str">
         <f>[1]CARTELLINO!MD$16</f>
-        <v>0</v>
+        <v>f</v>
       </c>
       <c r="MB16" s="46" t="str">
         <f>[1]CARTELLINO!ME$16</f>
@@ -47503,13 +47503,13 @@
         <f>[1]CARTELLINO!MI$16</f>
         <v>f</v>
       </c>
-      <c r="MG16" s="46">
+      <c r="MG16" s="46" t="str">
         <f>[1]CARTELLINO!MJ$16</f>
-        <v>0</v>
-      </c>
-      <c r="MH16" s="46">
+        <v>f</v>
+      </c>
+      <c r="MH16" s="46" t="str">
         <f>[1]CARTELLINO!MK$16</f>
-        <v>0</v>
+        <v>f</v>
       </c>
       <c r="MI16" s="46">
         <f>[1]CARTELLINO!ML$16</f>
@@ -49159,11 +49159,11 @@
       </c>
       <c r="IX18" s="27" t="str">
         <f>[1]CARTELLINO!JA$18</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="IY18" s="27" t="str">
         <f>[1]CARTELLINO!JB$18</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="IZ18" s="27" t="str">
         <f>[1]CARTELLINO!JC$18</f>
@@ -52695,7 +52695,7 @@
       </c>
       <c r="II21" s="28" t="str">
         <f>[1]CARTELLINO!IL$21</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="IJ21" s="28" t="str">
         <f>[1]CARTELLINO!IM$21</f>
@@ -52715,11 +52715,11 @@
       </c>
       <c r="IN21" s="28" t="str">
         <f>[1]CARTELLINO!IQ$21</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="IO21" s="28" t="str">
         <f>[1]CARTELLINO!IR$21</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="IP21" s="28" t="str">
         <f>[1]CARTELLINO!IS$21</f>
@@ -54307,13 +54307,13 @@
         <f>[1]CARTELLINO!IP$22</f>
         <v>0</v>
       </c>
-      <c r="IN22" s="46">
+      <c r="IN22" s="46" t="str">
         <f>[1]CARTELLINO!IQ$22</f>
-        <v>0</v>
-      </c>
-      <c r="IO22" s="46" t="str">
+        <v>p</v>
+      </c>
+      <c r="IO22" s="46">
         <f>[1]CARTELLINO!IR$22</f>
-        <v>p</v>
+        <v>0</v>
       </c>
       <c r="IP22" s="46">
         <f>[1]CARTELLINO!IS$22</f>
@@ -59791,7 +59791,7 @@
       </c>
       <c r="HK27" s="30" t="str">
         <f>[1]CARTELLINO!HN$27</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="HL27" s="30" t="str">
         <f>[1]CARTELLINO!HO$27</f>
@@ -62761,13 +62761,13 @@
         <v>VOLPINI</v>
       </c>
       <c r="HJ29" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="HK29" s="63" t="str">
         <v>PAZZAGLIA</v>
       </c>
       <c r="HL29" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>FABBRI</v>
       </c>
       <c r="HM29" s="63" t="str">
         <v>MICHELOT.</v>
@@ -62884,7 +62884,7 @@
         <v>SARTI</v>
       </c>
       <c r="IY29" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="IZ29" s="63" t="str">
         <v>BIANCHI</v>
@@ -62893,7 +62893,7 @@
         <v>GHIOTTI</v>
       </c>
       <c r="JB29" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="JC29" s="63" t="str">
         <v>BERARDI</v>
@@ -63861,13 +63861,13 @@
         <v>VOLPINI</v>
       </c>
       <c r="HJ30" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="HK30" s="63" t="str">
         <v>PAZZAGLIA</v>
       </c>
       <c r="HL30" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>FABBRI</v>
       </c>
       <c r="HM30" s="63" t="str">
         <v>MICHELOT.</v>
@@ -63984,7 +63984,7 @@
         <v>SARTI</v>
       </c>
       <c r="IY30" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="IZ30" s="63" t="str">
         <v>BIANCHI</v>
@@ -63993,7 +63993,7 @@
         <v>GHIOTTI</v>
       </c>
       <c r="JB30" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="JC30" s="63" t="str">
         <v>BERARDI</v>
@@ -64958,13 +64958,13 @@
         <v>VOLPINI</v>
       </c>
       <c r="HI31" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="HJ31" s="63" t="str">
         <v>PAZZAGLIA</v>
       </c>
       <c r="HK31" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>FABBRI</v>
       </c>
       <c r="HL31" s="63" t="str">
         <v>MICHELOT.</v>
@@ -65081,7 +65081,7 @@
         <v>SARTI</v>
       </c>
       <c r="IX31" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="IY31" s="63" t="str">
         <v>BIANCHI</v>
@@ -65090,7 +65090,7 @@
         <v>GHIOTTI</v>
       </c>
       <c r="JA31" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="JB31" s="63" t="str">
         <v>BERARDI</v>
@@ -66058,13 +66058,13 @@
         <v>VOLPINI</v>
       </c>
       <c r="HI32" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="HJ32" s="63" t="str">
         <v>PAZZAGLIA</v>
       </c>
       <c r="HK32" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>FABBRI</v>
       </c>
       <c r="HL32" s="63" t="str">
         <v>MICHELOT.</v>
@@ -66181,7 +66181,7 @@
         <v>SARTI</v>
       </c>
       <c r="IX32" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="IY32" s="63" t="str">
         <v>BIANCHI</v>
@@ -66190,7 +66190,7 @@
         <v>GHIOTTI</v>
       </c>
       <c r="JA32" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="JB32" s="63" t="str">
         <v>BERARDI</v>
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,6 +71029,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71037,13 +71044,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9674C4E-3962-471C-90B8-64D2FFC82D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3249E04-B474-434B-9721-0984FD375CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4690,10 +4690,10 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS225" t="str">
-            <v>FABBRI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT225" t="str">
-            <v>FABBRI</v>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="226">
@@ -21744,7 +21744,7 @@
             <v>p</v>
           </cell>
           <cell r="ID21" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="IE21" t="str">
             <v>r</v>
@@ -21768,7 +21768,7 @@
             <v>p</v>
           </cell>
           <cell r="IL21" t="str">
-            <v>m</v>
+            <v>r</v>
           </cell>
           <cell r="IM21" t="str">
             <v>r</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -52663,7 +52663,7 @@
       </c>
       <c r="IA21" s="28" t="str">
         <f>[1]CARTELLINO!ID$21</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="IB21" s="28" t="str">
         <f>[1]CARTELLINO!IE$21</f>
@@ -52695,7 +52695,7 @@
       </c>
       <c r="II21" s="28" t="str">
         <f>[1]CARTELLINO!IL$21</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="IJ21" s="28" t="str">
         <f>[1]CARTELLINO!IM$21</f>
@@ -64964,7 +64964,7 @@
         <v>PAZZAGLIA</v>
       </c>
       <c r="HK31" s="63" t="str">
-        <v>FABBRI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="HL31" s="63" t="str">
         <v>MICHELOT.</v>
@@ -66064,7 +66064,7 @@
         <v>PAZZAGLIA</v>
       </c>
       <c r="HK32" s="63" t="str">
-        <v>FABBRI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="HL32" s="63" t="str">
         <v>MICHELOT.</v>
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,13 +71029,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71044,6 +71037,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3249E04-B474-434B-9721-0984FD375CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A5AF0A-53BE-4B9C-9F9B-998CEE876F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7455,13 +7455,13 @@
             <v>r</v>
           </cell>
           <cell r="HZ3" t="str">
-            <v>p</v>
+            <v>N</v>
           </cell>
           <cell r="IA3" t="str">
-            <v>m</v>
+            <v>S</v>
           </cell>
           <cell r="IB3" t="str">
-            <v>r</v>
+            <v>R</v>
           </cell>
           <cell r="IC3" t="str">
             <v>r</v>
@@ -19352,13 +19352,13 @@
             <v>M/R</v>
           </cell>
           <cell r="HZ18" t="str">
-            <v>N</v>
+            <v>p</v>
           </cell>
           <cell r="IA18" t="str">
-            <v>S</v>
+            <v>m</v>
           </cell>
           <cell r="IB18" t="str">
-            <v>R</v>
+            <v>r</v>
           </cell>
           <cell r="IC18" t="str">
             <v>P</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -31072,15 +31072,15 @@
       </c>
       <c r="HW3" s="16" t="str">
         <f>[1]CARTELLINO!HZ$3</f>
-        <v>p</v>
+        <v>N</v>
       </c>
       <c r="HX3" s="16" t="str">
         <f>[1]CARTELLINO!IA$3</f>
-        <v>m</v>
+        <v>S</v>
       </c>
       <c r="HY3" s="16" t="str">
         <f>[1]CARTELLINO!IB$3</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="HZ3" s="16" t="str">
         <f>[1]CARTELLINO!IC$3</f>
@@ -49051,15 +49051,15 @@
       </c>
       <c r="HW18" s="27" t="str">
         <f>[1]CARTELLINO!HZ$18</f>
-        <v>N</v>
+        <v>p</v>
       </c>
       <c r="HX18" s="27" t="str">
         <f>[1]CARTELLINO!IA$18</f>
-        <v>S</v>
+        <v>m</v>
       </c>
       <c r="HY18" s="27" t="str">
         <f>[1]CARTELLINO!IB$18</f>
-        <v>R</v>
+        <v>r</v>
       </c>
       <c r="HZ18" s="27" t="str">
         <f>[1]CARTELLINO!IC$18</f>
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,6 +71029,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71037,13 +71044,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A5AF0A-53BE-4B9C-9F9B-998CEE876F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E073241-930C-4C52-86DA-2706F582DB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1645,6 +1645,9 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="8">
+          <cell r="R8" t="str">
+            <v>MAT/R</v>
+          </cell>
           <cell r="AQ8" t="str">
             <v>GHIOTTI</v>
           </cell>
@@ -4900,46 +4903,46 @@
             <v>BIANCHI</v>
           </cell>
           <cell r="AS240" t="str">
-            <v>VOLPINI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT240" t="str">
-            <v>VOLPINI</v>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="241">
           <cell r="AQ241" t="str">
-            <v>VOLPINI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR241" t="str">
-            <v>VOLPINI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS241" t="str">
-            <v>MICHELOT.</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT241" t="str">
-            <v>MICHELOT.</v>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="242">
           <cell r="AQ242" t="str">
-            <v>MICHELOT.</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR242" t="str">
-            <v>MICHELOT.</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS242" t="str">
-            <v>GHIOTTI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT242" t="str">
-            <v>GHIOTTI</v>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="243">
           <cell r="AQ243" t="str">
-            <v>GHIOTTI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR243" t="str">
-            <v>GHIOTTI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS243" t="str">
             <v>SARTI</v>
@@ -4956,18 +4959,18 @@
             <v>SARTI</v>
           </cell>
           <cell r="AS244" t="str">
-            <v>BERARDI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT244" t="str">
-            <v>BERARDI</v>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="245">
           <cell r="AQ245" t="str">
-            <v>BERARDI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR245" t="str">
-            <v>BERARDI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS245" t="str">
             <v>FABBRI</v>
@@ -4984,18 +4987,18 @@
             <v>FABBRI</v>
           </cell>
           <cell r="AS246" t="str">
-            <v>GHIOTTI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT246" t="str">
-            <v>GHIOTTI</v>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="247">
           <cell r="AQ247" t="str">
-            <v>GHIOTTI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR247" t="str">
-            <v>GHIOTTI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS247" t="str">
             <v>BIANCHI</v>
@@ -5054,46 +5057,46 @@
             <v>VOLPINI</v>
           </cell>
           <cell r="AS251" t="str">
-            <v>MICHELOT.</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT251" t="str">
-            <v>MICHELOT.</v>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="252">
           <cell r="AQ252" t="str">
-            <v>MICHELOT.</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR252" t="str">
-            <v>MICHELOT.</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS252" t="str">
-            <v>BERARDI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT252" t="str">
-            <v>BERARDI</v>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="253">
           <cell r="AQ253" t="str">
-            <v>BERARDI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR253" t="str">
-            <v>BERARDI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS253" t="str">
-            <v>GHIOTTI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT253" t="str">
-            <v>GHIOTTI</v>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="254">
           <cell r="AQ254" t="str">
-            <v>GHIOTTI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR254" t="str">
-            <v>GHIOTTI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS254" t="str">
             <v>VOLPINI</v>
@@ -7464,10 +7467,10 @@
             <v>R</v>
           </cell>
           <cell r="IC3" t="str">
-            <v>r</v>
+            <v>P</v>
           </cell>
           <cell r="ID3" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="IE3" t="str">
             <v>P</v>
@@ -7476,7 +7479,7 @@
             <v>P</v>
           </cell>
           <cell r="IG3" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="IH3" t="str">
             <v>N</v>
@@ -7503,10 +7506,10 @@
             <v>R</v>
           </cell>
           <cell r="IP3" t="str">
-            <v>m</v>
+            <v>M/R</v>
           </cell>
           <cell r="IQ3" t="str">
-            <v>M</v>
+            <v>P</v>
           </cell>
           <cell r="IR3" t="str">
             <v>N</v>
@@ -14601,13 +14604,13 @@
             <v>m</v>
           </cell>
           <cell r="IC12" t="str">
-            <v>m/R</v>
+            <v>m</v>
           </cell>
           <cell r="ID12" t="str">
             <v>P</v>
           </cell>
           <cell r="IE12" t="str">
-            <v>m</v>
+            <v>M/R</v>
           </cell>
           <cell r="IF12" t="str">
             <v>-</v>
@@ -14640,7 +14643,7 @@
             <v>r</v>
           </cell>
           <cell r="IP12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="IQ12" t="str">
             <v>m/R</v>
@@ -14649,13 +14652,13 @@
             <v>P</v>
           </cell>
           <cell r="IS12" t="str">
-            <v>r</v>
+            <v>M</v>
           </cell>
           <cell r="IT12" t="str">
             <v>p</v>
           </cell>
           <cell r="IU12" t="str">
-            <v>p</v>
+            <v>r</v>
           </cell>
           <cell r="IV12" t="str">
             <v>P</v>
@@ -15829,8 +15832,8 @@
           <cell r="IO13">
             <v>0</v>
           </cell>
-          <cell r="IP13" t="str">
-            <v>ng</v>
+          <cell r="IP13">
+            <v>0</v>
           </cell>
           <cell r="IQ13">
             <v>0</v>
@@ -16972,73 +16975,73 @@
             <v>R</v>
           </cell>
           <cell r="HZ15" t="str">
-            <v>r</v>
+            <v>-</v>
           </cell>
           <cell r="IA15" t="str">
-            <v>p</v>
+            <v>-</v>
           </cell>
           <cell r="IB15" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="IC15" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="ID15" t="str">
             <v>R</v>
           </cell>
           <cell r="IE15" t="str">
-            <v>M/R</v>
+            <v>-</v>
           </cell>
           <cell r="IF15" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="IG15" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="IH15" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="II15" t="str">
             <v>R</v>
           </cell>
-          <cell r="II15" t="str">
-            <v>m/R</v>
-          </cell>
           <cell r="IJ15" t="str">
-            <v>p</v>
+            <v>-</v>
           </cell>
           <cell r="IK15" t="str">
-            <v>m</v>
+            <v>-</v>
           </cell>
           <cell r="IL15" t="str">
-            <v>r</v>
+            <v>-</v>
           </cell>
           <cell r="IM15" t="str">
-            <v>p</v>
+            <v>-</v>
           </cell>
           <cell r="IN15" t="str">
-            <v>m</v>
+            <v>R</v>
           </cell>
           <cell r="IO15" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="IP15" t="str">
-            <v>M/R</v>
+            <v>-</v>
           </cell>
           <cell r="IQ15" t="str">
-            <v>p</v>
+            <v>-</v>
           </cell>
           <cell r="IR15" t="str">
-            <v>r</v>
+            <v>-</v>
           </cell>
           <cell r="IS15" t="str">
-            <v>M</v>
+            <v>R</v>
           </cell>
           <cell r="IT15" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="IU15" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="IV15" t="str">
-            <v>R</v>
+            <v>-</v>
           </cell>
           <cell r="IW15" t="str">
             <v>P</v>
@@ -18138,97 +18141,97 @@
             <v>m</v>
           </cell>
           <cell r="HR16" t="str">
-            <v>f</v>
+            <v>m</v>
           </cell>
           <cell r="HS16" t="str">
-            <v>f</v>
+            <v>m</v>
           </cell>
           <cell r="HT16" t="str">
-            <v>f</v>
+            <v>m</v>
           </cell>
           <cell r="HU16" t="str">
-            <v>f</v>
+            <v>m</v>
           </cell>
           <cell r="HV16" t="str">
-            <v>f</v>
+            <v>m</v>
           </cell>
           <cell r="HW16" t="str">
-            <v>ng</v>
+            <v>m</v>
           </cell>
           <cell r="HX16" t="str">
-            <v>f</v>
+            <v>m</v>
           </cell>
           <cell r="HY16" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="HZ16">
-            <v>0</v>
-          </cell>
-          <cell r="IA16">
-            <v>0</v>
-          </cell>
-          <cell r="IB16">
-            <v>0</v>
-          </cell>
-          <cell r="IC16">
-            <v>0</v>
-          </cell>
-          <cell r="ID16">
-            <v>0</v>
-          </cell>
-          <cell r="IE16">
-            <v>0</v>
-          </cell>
-          <cell r="IF16">
-            <v>0</v>
-          </cell>
-          <cell r="IG16">
-            <v>0</v>
-          </cell>
-          <cell r="IH16">
-            <v>0</v>
-          </cell>
-          <cell r="II16">
-            <v>0</v>
-          </cell>
-          <cell r="IJ16">
-            <v>0</v>
-          </cell>
-          <cell r="IK16">
-            <v>0</v>
-          </cell>
-          <cell r="IL16">
-            <v>0</v>
-          </cell>
-          <cell r="IM16">
-            <v>0</v>
-          </cell>
-          <cell r="IN16">
-            <v>0</v>
-          </cell>
-          <cell r="IO16">
-            <v>0</v>
-          </cell>
-          <cell r="IP16">
-            <v>0</v>
-          </cell>
-          <cell r="IQ16">
-            <v>0</v>
-          </cell>
-          <cell r="IR16">
-            <v>0</v>
-          </cell>
-          <cell r="IS16">
-            <v>0</v>
-          </cell>
-          <cell r="IT16">
-            <v>0</v>
-          </cell>
-          <cell r="IU16">
-            <v>0</v>
-          </cell>
-          <cell r="IV16">
-            <v>0</v>
+            <v>m</v>
+          </cell>
+          <cell r="HZ16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="IA16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="IB16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="IC16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="ID16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="IE16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="IF16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="IG16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="IH16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="II16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="IJ16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="IK16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="IL16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="IM16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="IN16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="IO16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="IP16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="IQ16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="IR16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="IS16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="IT16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="IU16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="IV16" t="str">
+            <v>m</v>
           </cell>
           <cell r="IW16">
             <v>0</v>
@@ -19358,13 +19361,13 @@
             <v>m</v>
           </cell>
           <cell r="IB18" t="str">
-            <v>r</v>
+            <v>N</v>
           </cell>
           <cell r="IC18" t="str">
-            <v>P</v>
+            <v>S</v>
           </cell>
           <cell r="ID18" t="str">
-            <v>M/R</v>
+            <v>R</v>
           </cell>
           <cell r="IE18" t="str">
             <v>N</v>
@@ -19379,7 +19382,7 @@
             <v>P</v>
           </cell>
           <cell r="II18" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="IJ18" t="str">
             <v>N</v>
@@ -19394,7 +19397,7 @@
             <v>P</v>
           </cell>
           <cell r="IN18" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="IO18" t="str">
             <v>N</v>
@@ -21750,13 +21753,13 @@
             <v>r</v>
           </cell>
           <cell r="IF21" t="str">
-            <v>m</v>
+            <v>N</v>
           </cell>
           <cell r="IG21" t="str">
-            <v>m/R</v>
+            <v>S</v>
           </cell>
           <cell r="IH21" t="str">
-            <v>p</v>
+            <v>R</v>
           </cell>
           <cell r="II21" t="str">
             <v>p</v>
@@ -21774,13 +21777,13 @@
             <v>r</v>
           </cell>
           <cell r="IN21" t="str">
-            <v>r</v>
+            <v>m/R</v>
           </cell>
           <cell r="IO21" t="str">
-            <v>m/R</v>
+            <v>P</v>
           </cell>
           <cell r="IP21" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="IQ21" t="str">
             <v>-</v>
@@ -24157,7 +24160,7 @@
             <v>P</v>
           </cell>
           <cell r="IO24" t="str">
-            <v>p</v>
+            <v>M/R</v>
           </cell>
           <cell r="IP24" t="str">
             <v>N</v>
@@ -24172,13 +24175,13 @@
             <v>P</v>
           </cell>
           <cell r="IT24" t="str">
-            <v>m</v>
+            <v>N</v>
           </cell>
           <cell r="IU24" t="str">
-            <v>r</v>
+            <v>S</v>
           </cell>
           <cell r="IV24" t="str">
-            <v>m</v>
+            <v>R</v>
           </cell>
           <cell r="IW24" t="str">
             <v>p</v>
@@ -26501,7 +26504,7 @@
             <v>P</v>
           </cell>
           <cell r="IC27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="ID27" t="str">
             <v>N</v>
@@ -26543,7 +26546,7 @@
             <v>R</v>
           </cell>
           <cell r="IQ27" t="str">
-            <v>P</v>
+            <v>M</v>
           </cell>
           <cell r="IR27" t="str">
             <v>M/R</v>
@@ -28519,431 +28522,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28956,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -31084,11 +31087,11 @@
       </c>
       <c r="HZ3" s="16" t="str">
         <f>[1]CARTELLINO!IC$3</f>
-        <v>r</v>
+        <v>P</v>
       </c>
       <c r="IA3" s="16" t="str">
         <f>[1]CARTELLINO!ID$3</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="IB3" s="16" t="str">
         <f>[1]CARTELLINO!IE$3</f>
@@ -31100,7 +31103,7 @@
       </c>
       <c r="ID3" s="16" t="str">
         <f>[1]CARTELLINO!IG$3</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="IE3" s="16" t="str">
         <f>[1]CARTELLINO!IH$3</f>
@@ -31136,11 +31139,11 @@
       </c>
       <c r="IM3" s="16" t="str">
         <f>[1]CARTELLINO!IP$3</f>
-        <v>m</v>
+        <v>M/R</v>
       </c>
       <c r="IN3" s="16" t="str">
         <f>[1]CARTELLINO!IQ$3</f>
-        <v>M</v>
+        <v>P</v>
       </c>
       <c r="IO3" s="16" t="str">
         <f>[1]CARTELLINO!IR$3</f>
@@ -41871,7 +41874,7 @@
       </c>
       <c r="HZ12" s="25" t="str">
         <f>[1]CARTELLINO!IC$12</f>
-        <v>m/R</v>
+        <v>m</v>
       </c>
       <c r="IA12" s="25" t="str">
         <f>[1]CARTELLINO!ID$12</f>
@@ -41879,7 +41882,7 @@
       </c>
       <c r="IB12" s="25" t="str">
         <f>[1]CARTELLINO!IE$12</f>
-        <v>m</v>
+        <v>M/R</v>
       </c>
       <c r="IC12" s="25" t="str">
         <f>[1]CARTELLINO!IF$12</f>
@@ -41923,7 +41926,7 @@
       </c>
       <c r="IM12" s="25" t="str">
         <f>[1]CARTELLINO!IP$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="IN12" s="25" t="str">
         <f>[1]CARTELLINO!IQ$12</f>
@@ -41935,7 +41938,7 @@
       </c>
       <c r="IP12" s="25" t="str">
         <f>[1]CARTELLINO!IS$12</f>
-        <v>r</v>
+        <v>M</v>
       </c>
       <c r="IQ12" s="25" t="str">
         <f>[1]CARTELLINO!IT$12</f>
@@ -41943,7 +41946,7 @@
       </c>
       <c r="IR12" s="25" t="str">
         <f>[1]CARTELLINO!IU$12</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="IS12" s="25" t="str">
         <f>[1]CARTELLINO!IV$12</f>
@@ -43515,9 +43518,9 @@
         <f>[1]CARTELLINO!IO$13</f>
         <v>0</v>
       </c>
-      <c r="IM13" s="46" t="str">
+      <c r="IM13" s="46">
         <f>[1]CARTELLINO!IP$13</f>
-        <v>ng</v>
+        <v>0</v>
       </c>
       <c r="IN13" s="46">
         <f>[1]CARTELLINO!IQ$13</f>
@@ -45455,19 +45458,19 @@
       </c>
       <c r="HW15" s="26" t="str">
         <f>[1]CARTELLINO!HZ$15</f>
-        <v>r</v>
+        <v>-</v>
       </c>
       <c r="HX15" s="26" t="str">
         <f>[1]CARTELLINO!IA$15</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="HY15" s="26" t="str">
         <f>[1]CARTELLINO!IB$15</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="HZ15" s="26" t="str">
         <f>[1]CARTELLINO!IC$15</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="IA15" s="26" t="str">
         <f>[1]CARTELLINO!ID$15</f>
@@ -45475,75 +45478,75 @@
       </c>
       <c r="IB15" s="26" t="str">
         <f>[1]CARTELLINO!IE$15</f>
-        <v>M/R</v>
+        <v>-</v>
       </c>
       <c r="IC15" s="26" t="str">
         <f>[1]CARTELLINO!IF$15</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="ID15" s="26" t="str">
         <f>[1]CARTELLINO!IG$15</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="IE15" s="26" t="str">
         <f>[1]CARTELLINO!IH$15</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="IF15" s="26" t="str">
         <f>[1]CARTELLINO!II$15</f>
-        <v>m/R</v>
+        <v>R</v>
       </c>
       <c r="IG15" s="26" t="str">
         <f>[1]CARTELLINO!IJ$15</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="IH15" s="26" t="str">
         <f>[1]CARTELLINO!IK$15</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="II15" s="26" t="str">
         <f>[1]CARTELLINO!IL$15</f>
-        <v>r</v>
+        <v>-</v>
       </c>
       <c r="IJ15" s="26" t="str">
         <f>[1]CARTELLINO!IM$15</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="IK15" s="26" t="str">
         <f>[1]CARTELLINO!IN$15</f>
-        <v>m</v>
+        <v>R</v>
       </c>
       <c r="IL15" s="26" t="str">
         <f>[1]CARTELLINO!IO$15</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="IM15" s="26" t="str">
         <f>[1]CARTELLINO!IP$15</f>
-        <v>M/R</v>
+        <v>-</v>
       </c>
       <c r="IN15" s="26" t="str">
         <f>[1]CARTELLINO!IQ$15</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="IO15" s="26" t="str">
         <f>[1]CARTELLINO!IR$15</f>
-        <v>r</v>
+        <v>-</v>
       </c>
       <c r="IP15" s="26" t="str">
         <f>[1]CARTELLINO!IS$15</f>
-        <v>M</v>
+        <v>R</v>
       </c>
       <c r="IQ15" s="26" t="str">
         <f>[1]CARTELLINO!IT$15</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="IR15" s="26" t="str">
         <f>[1]CARTELLINO!IU$15</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="IS15" s="26" t="str">
         <f>[1]CARTELLINO!IV$15</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="IT15" s="26" t="str">
         <f>[1]CARTELLINO!IW$15</f>
@@ -47017,127 +47020,127 @@
       </c>
       <c r="HO16" s="46" t="str">
         <f>[1]CARTELLINO!HR$16</f>
-        <v>f</v>
+        <v>m</v>
       </c>
       <c r="HP16" s="46" t="str">
         <f>[1]CARTELLINO!HS$16</f>
-        <v>f</v>
+        <v>m</v>
       </c>
       <c r="HQ16" s="46" t="str">
         <f>[1]CARTELLINO!HT$16</f>
-        <v>f</v>
+        <v>m</v>
       </c>
       <c r="HR16" s="46" t="str">
         <f>[1]CARTELLINO!HU$16</f>
-        <v>f</v>
+        <v>m</v>
       </c>
       <c r="HS16" s="46" t="str">
         <f>[1]CARTELLINO!HV$16</f>
-        <v>f</v>
+        <v>m</v>
       </c>
       <c r="HT16" s="46" t="str">
         <f>[1]CARTELLINO!HW$16</f>
-        <v>ng</v>
+        <v>m</v>
       </c>
       <c r="HU16" s="46" t="str">
         <f>[1]CARTELLINO!HX$16</f>
-        <v>f</v>
+        <v>m</v>
       </c>
       <c r="HV16" s="46" t="str">
         <f>[1]CARTELLINO!HY$16</f>
-        <v>f</v>
-      </c>
-      <c r="HW16" s="46">
+        <v>m</v>
+      </c>
+      <c r="HW16" s="46" t="str">
         <f>[1]CARTELLINO!HZ$16</f>
-        <v>0</v>
-      </c>
-      <c r="HX16" s="46">
+        <v>m</v>
+      </c>
+      <c r="HX16" s="46" t="str">
         <f>[1]CARTELLINO!IA$16</f>
-        <v>0</v>
-      </c>
-      <c r="HY16" s="46">
+        <v>m</v>
+      </c>
+      <c r="HY16" s="46" t="str">
         <f>[1]CARTELLINO!IB$16</f>
-        <v>0</v>
-      </c>
-      <c r="HZ16" s="46">
+        <v>m</v>
+      </c>
+      <c r="HZ16" s="46" t="str">
         <f>[1]CARTELLINO!IC$16</f>
-        <v>0</v>
-      </c>
-      <c r="IA16" s="46">
+        <v>m</v>
+      </c>
+      <c r="IA16" s="46" t="str">
         <f>[1]CARTELLINO!ID$16</f>
-        <v>0</v>
-      </c>
-      <c r="IB16" s="46">
+        <v>m</v>
+      </c>
+      <c r="IB16" s="46" t="str">
         <f>[1]CARTELLINO!IE$16</f>
-        <v>0</v>
-      </c>
-      <c r="IC16" s="46">
+        <v>m</v>
+      </c>
+      <c r="IC16" s="46" t="str">
         <f>[1]CARTELLINO!IF$16</f>
-        <v>0</v>
-      </c>
-      <c r="ID16" s="46">
+        <v>m</v>
+      </c>
+      <c r="ID16" s="46" t="str">
         <f>[1]CARTELLINO!IG$16</f>
-        <v>0</v>
-      </c>
-      <c r="IE16" s="46">
+        <v>m</v>
+      </c>
+      <c r="IE16" s="46" t="str">
         <f>[1]CARTELLINO!IH$16</f>
-        <v>0</v>
-      </c>
-      <c r="IF16" s="46">
+        <v>m</v>
+      </c>
+      <c r="IF16" s="46" t="str">
         <f>[1]CARTELLINO!II$16</f>
-        <v>0</v>
-      </c>
-      <c r="IG16" s="46">
+        <v>m</v>
+      </c>
+      <c r="IG16" s="46" t="str">
         <f>[1]CARTELLINO!IJ$16</f>
-        <v>0</v>
-      </c>
-      <c r="IH16" s="46">
+        <v>m</v>
+      </c>
+      <c r="IH16" s="46" t="str">
         <f>[1]CARTELLINO!IK$16</f>
-        <v>0</v>
-      </c>
-      <c r="II16" s="46">
+        <v>m</v>
+      </c>
+      <c r="II16" s="46" t="str">
         <f>[1]CARTELLINO!IL$16</f>
-        <v>0</v>
-      </c>
-      <c r="IJ16" s="46">
+        <v>m</v>
+      </c>
+      <c r="IJ16" s="46" t="str">
         <f>[1]CARTELLINO!IM$16</f>
-        <v>0</v>
-      </c>
-      <c r="IK16" s="46">
+        <v>m</v>
+      </c>
+      <c r="IK16" s="46" t="str">
         <f>[1]CARTELLINO!IN$16</f>
-        <v>0</v>
-      </c>
-      <c r="IL16" s="46">
+        <v>m</v>
+      </c>
+      <c r="IL16" s="46" t="str">
         <f>[1]CARTELLINO!IO$16</f>
-        <v>0</v>
-      </c>
-      <c r="IM16" s="46">
+        <v>m</v>
+      </c>
+      <c r="IM16" s="46" t="str">
         <f>[1]CARTELLINO!IP$16</f>
-        <v>0</v>
-      </c>
-      <c r="IN16" s="46">
+        <v>m</v>
+      </c>
+      <c r="IN16" s="46" t="str">
         <f>[1]CARTELLINO!IQ$16</f>
-        <v>0</v>
-      </c>
-      <c r="IO16" s="46">
+        <v>m</v>
+      </c>
+      <c r="IO16" s="46" t="str">
         <f>[1]CARTELLINO!IR$16</f>
-        <v>0</v>
-      </c>
-      <c r="IP16" s="46">
+        <v>m</v>
+      </c>
+      <c r="IP16" s="46" t="str">
         <f>[1]CARTELLINO!IS$16</f>
-        <v>0</v>
-      </c>
-      <c r="IQ16" s="46">
+        <v>m</v>
+      </c>
+      <c r="IQ16" s="46" t="str">
         <f>[1]CARTELLINO!IT$16</f>
-        <v>0</v>
-      </c>
-      <c r="IR16" s="46">
+        <v>m</v>
+      </c>
+      <c r="IR16" s="46" t="str">
         <f>[1]CARTELLINO!IU$16</f>
-        <v>0</v>
-      </c>
-      <c r="IS16" s="46">
+        <v>m</v>
+      </c>
+      <c r="IS16" s="46" t="str">
         <f>[1]CARTELLINO!IV$16</f>
-        <v>0</v>
+        <v>m</v>
       </c>
       <c r="IT16" s="46">
         <f>[1]CARTELLINO!IW$16</f>
@@ -49059,15 +49062,15 @@
       </c>
       <c r="HY18" s="27" t="str">
         <f>[1]CARTELLINO!IB$18</f>
-        <v>r</v>
+        <v>N</v>
       </c>
       <c r="HZ18" s="27" t="str">
         <f>[1]CARTELLINO!IC$18</f>
-        <v>P</v>
+        <v>S</v>
       </c>
       <c r="IA18" s="27" t="str">
         <f>[1]CARTELLINO!ID$18</f>
-        <v>M/R</v>
+        <v>R</v>
       </c>
       <c r="IB18" s="27" t="str">
         <f>[1]CARTELLINO!IE$18</f>
@@ -49087,7 +49090,7 @@
       </c>
       <c r="IF18" s="27" t="str">
         <f>[1]CARTELLINO!II$18</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="IG18" s="27" t="str">
         <f>[1]CARTELLINO!IJ$18</f>
@@ -49107,7 +49110,7 @@
       </c>
       <c r="IK18" s="27" t="str">
         <f>[1]CARTELLINO!IN$18</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="IL18" s="27" t="str">
         <f>[1]CARTELLINO!IO$18</f>
@@ -52671,15 +52674,15 @@
       </c>
       <c r="IC21" s="28" t="str">
         <f>[1]CARTELLINO!IF$21</f>
-        <v>m</v>
+        <v>N</v>
       </c>
       <c r="ID21" s="28" t="str">
         <f>[1]CARTELLINO!IG$21</f>
-        <v>m/R</v>
+        <v>S</v>
       </c>
       <c r="IE21" s="28" t="str">
         <f>[1]CARTELLINO!IH$21</f>
-        <v>p</v>
+        <v>R</v>
       </c>
       <c r="IF21" s="28" t="str">
         <f>[1]CARTELLINO!II$21</f>
@@ -52703,15 +52706,15 @@
       </c>
       <c r="IK21" s="28" t="str">
         <f>[1]CARTELLINO!IN$21</f>
-        <v>r</v>
+        <v>m/R</v>
       </c>
       <c r="IL21" s="28" t="str">
         <f>[1]CARTELLINO!IO$21</f>
-        <v>m/R</v>
+        <v>P</v>
       </c>
       <c r="IM21" s="28" t="str">
         <f>[1]CARTELLINO!IP$21</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="IN21" s="28" t="str">
         <f>[1]CARTELLINO!IQ$21</f>
@@ -56303,7 +56306,7 @@
       </c>
       <c r="IL24" s="29" t="str">
         <f>[1]CARTELLINO!IO$24</f>
-        <v>p</v>
+        <v>M/R</v>
       </c>
       <c r="IM24" s="29" t="str">
         <f>[1]CARTELLINO!IP$24</f>
@@ -56323,15 +56326,15 @@
       </c>
       <c r="IQ24" s="29" t="str">
         <f>[1]CARTELLINO!IT$24</f>
-        <v>m</v>
+        <v>N</v>
       </c>
       <c r="IR24" s="29" t="str">
         <f>[1]CARTELLINO!IU$24</f>
-        <v>r</v>
+        <v>S</v>
       </c>
       <c r="IS24" s="29" t="str">
         <f>[1]CARTELLINO!IV$24</f>
-        <v>m</v>
+        <v>R</v>
       </c>
       <c r="IT24" s="29" t="str">
         <f>[1]CARTELLINO!IW$24</f>
@@ -59851,7 +59854,7 @@
       </c>
       <c r="HZ27" s="30" t="str">
         <f>[1]CARTELLINO!IC$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="IA27" s="30" t="str">
         <f>[1]CARTELLINO!ID$27</f>
@@ -59907,7 +59910,7 @@
       </c>
       <c r="IN27" s="30" t="str">
         <f>[1]CARTELLINO!IQ$27</f>
-        <v>P</v>
+        <v>M</v>
       </c>
       <c r="IO27" s="30" t="str">
         <f>[1]CARTELLINO!IR$27</f>
@@ -62812,25 +62815,25 @@
         <v>BIANCHI</v>
       </c>
       <c r="IA29" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>FABBRI</v>
       </c>
       <c r="IB29" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IC29" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BERARDI</v>
       </c>
       <c r="ID29" s="63" t="str">
         <v>SARTI</v>
       </c>
       <c r="IE29" s="63" t="str">
-        <v>BERARDI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IF29" s="63" t="str">
         <v>FABBRI</v>
       </c>
       <c r="IG29" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="IH29" s="63" t="str">
         <v>BIANCHI</v>
@@ -62845,13 +62848,13 @@
         <v>VOLPINI</v>
       </c>
       <c r="IL29" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BERARDI</v>
       </c>
       <c r="IM29" s="63" t="str">
-        <v>BERARDI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="IN29" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IO29" s="63" t="str">
         <v>VOLPINI</v>
@@ -63912,25 +63915,25 @@
         <v>BIANCHI</v>
       </c>
       <c r="IA30" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>FABBRI</v>
       </c>
       <c r="IB30" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IC30" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BERARDI</v>
       </c>
       <c r="ID30" s="63" t="str">
         <v>SARTI</v>
       </c>
       <c r="IE30" s="63" t="str">
-        <v>BERARDI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IF30" s="63" t="str">
         <v>FABBRI</v>
       </c>
       <c r="IG30" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="IH30" s="63" t="str">
         <v>BIANCHI</v>
@@ -63945,13 +63948,13 @@
         <v>VOLPINI</v>
       </c>
       <c r="IL30" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BERARDI</v>
       </c>
       <c r="IM30" s="63" t="str">
-        <v>BERARDI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="IN30" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IO30" s="63" t="str">
         <v>VOLPINI</v>
@@ -65009,25 +65012,25 @@
         <v>BIANCHI</v>
       </c>
       <c r="HZ31" s="63" t="str">
+        <v>FABBRI</v>
+      </c>
+      <c r="IA31" s="63" t="str">
+        <v>PAZZAGLIA</v>
+      </c>
+      <c r="IB31" s="63" t="str">
         <v>VOLPINI</v>
-      </c>
-      <c r="IA31" s="63" t="str">
-        <v>MICHELOT.</v>
-      </c>
-      <c r="IB31" s="63" t="str">
-        <v>GHIOTTI</v>
       </c>
       <c r="IC31" s="63" t="str">
         <v>SARTI</v>
       </c>
       <c r="ID31" s="63" t="str">
-        <v>BERARDI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IE31" s="63" t="str">
         <v>FABBRI</v>
       </c>
       <c r="IF31" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="IG31" s="63" t="str">
         <v>BIANCHI</v>
@@ -65042,13 +65045,13 @@
         <v>VOLPINI</v>
       </c>
       <c r="IK31" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BERARDI</v>
       </c>
       <c r="IL31" s="63" t="str">
-        <v>BERARDI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="IM31" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IN31" s="63" t="str">
         <v>VOLPINI</v>
@@ -66109,25 +66112,25 @@
         <v>BIANCHI</v>
       </c>
       <c r="HZ32" s="63" t="str">
+        <v>FABBRI</v>
+      </c>
+      <c r="IA32" s="63" t="str">
+        <v>PAZZAGLIA</v>
+      </c>
+      <c r="IB32" s="63" t="str">
         <v>VOLPINI</v>
-      </c>
-      <c r="IA32" s="63" t="str">
-        <v>MICHELOT.</v>
-      </c>
-      <c r="IB32" s="63" t="str">
-        <v>GHIOTTI</v>
       </c>
       <c r="IC32" s="63" t="str">
         <v>SARTI</v>
       </c>
       <c r="ID32" s="63" t="str">
-        <v>BERARDI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IE32" s="63" t="str">
         <v>FABBRI</v>
       </c>
       <c r="IF32" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="IG32" s="63" t="str">
         <v>BIANCHI</v>
@@ -66142,13 +66145,13 @@
         <v>VOLPINI</v>
       </c>
       <c r="IK32" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BERARDI</v>
       </c>
       <c r="IL32" s="63" t="str">
-        <v>BERARDI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="IM32" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IN32" s="63" t="str">
         <v>VOLPINI</v>
@@ -66531,12 +66534,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,13 +71032,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71044,6 +71040,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E073241-930C-4C52-86DA-2706F582DB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0361A9D-5AD3-4E09-AF78-6AECD84C924F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="0" yWindow="390" windowWidth="28800" windowHeight="15090" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1645,9 +1645,6 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="8">
-          <cell r="R8" t="str">
-            <v>MAT/R</v>
-          </cell>
           <cell r="AQ8" t="str">
             <v>GHIOTTI</v>
           </cell>
@@ -26591,7 +26588,7 @@
             <v>P</v>
           </cell>
           <cell r="JF27" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="JG27" t="str">
             <v>r</v>
@@ -28522,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28956,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -59970,7 +59967,7 @@
       </c>
       <c r="JC27" s="30" t="str">
         <f>[1]CARTELLINO!JF$27</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="JD27" s="30" t="str">
         <f>[1]CARTELLINO!JG$27</f>
@@ -66534,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71032,6 +71029,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71040,13 +71044,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0361A9D-5AD3-4E09-AF78-6AECD84C924F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E7E528-0263-4B0A-B722-82E8EA710C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="390" windowWidth="28800" windowHeight="15090" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1645,6 +1645,9 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="8">
+          <cell r="R8" t="str">
+            <v>MAT/R</v>
+          </cell>
           <cell r="AQ8" t="str">
             <v>GHIOTTI</v>
           </cell>
@@ -12224,10 +12227,10 @@
             <v>-</v>
           </cell>
           <cell r="ID9" t="str">
-            <v>R</v>
+            <v>M</v>
           </cell>
           <cell r="IE9" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="IF9" t="str">
             <v>M/R</v>
@@ -13414,10 +13417,10 @@
             <v>f</v>
           </cell>
           <cell r="ID10" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="IE10" t="str">
-            <v>f</v>
+            <v>x</v>
+          </cell>
+          <cell r="IE10">
+            <v>0</v>
           </cell>
           <cell r="IF10">
             <v>0</v>
@@ -17041,10 +17044,10 @@
             <v>-</v>
           </cell>
           <cell r="IW15" t="str">
-            <v>P</v>
+            <v>R</v>
           </cell>
           <cell r="IX15" t="str">
-            <v>p</v>
+            <v>-</v>
           </cell>
           <cell r="IY15" t="str">
             <v>N</v>
@@ -18230,11 +18233,11 @@
           <cell r="IV16" t="str">
             <v>m</v>
           </cell>
-          <cell r="IW16">
-            <v>0</v>
-          </cell>
-          <cell r="IX16">
-            <v>0</v>
+          <cell r="IW16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="IX16" t="str">
+            <v>m</v>
           </cell>
           <cell r="IY16">
             <v>0</v>
@@ -21744,7 +21747,7 @@
             <v>p</v>
           </cell>
           <cell r="ID21" t="str">
-            <v>m</v>
+            <v>M</v>
           </cell>
           <cell r="IE21" t="str">
             <v>r</v>
@@ -21768,7 +21771,7 @@
             <v>p</v>
           </cell>
           <cell r="IL21" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="IM21" t="str">
             <v>r</v>
@@ -22933,8 +22936,8 @@
           <cell r="IC22">
             <v>0</v>
           </cell>
-          <cell r="ID22">
-            <v>0</v>
+          <cell r="ID22" t="str">
+            <v>x</v>
           </cell>
           <cell r="IE22">
             <v>0</v>
@@ -24181,7 +24184,7 @@
             <v>R</v>
           </cell>
           <cell r="IW24" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="IX24" t="str">
             <v>m/R</v>
@@ -38279,11 +38282,11 @@
       </c>
       <c r="IA9" s="24" t="str">
         <f>[1]CARTELLINO!ID$9</f>
-        <v>R</v>
+        <v>M</v>
       </c>
       <c r="IB9" s="24" t="str">
         <f>[1]CARTELLINO!IE$9</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="IC9" s="24" t="str">
         <f>[1]CARTELLINO!IF$9</f>
@@ -39873,11 +39876,11 @@
       </c>
       <c r="IA10" s="46" t="str">
         <f>[1]CARTELLINO!ID$10</f>
-        <v>f</v>
-      </c>
-      <c r="IB10" s="46" t="str">
+        <v>x</v>
+      </c>
+      <c r="IB10" s="46">
         <f>[1]CARTELLINO!IE$10</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="IC10" s="46">
         <f>[1]CARTELLINO!IF$10</f>
@@ -45547,11 +45550,11 @@
       </c>
       <c r="IT15" s="26" t="str">
         <f>[1]CARTELLINO!IW$15</f>
-        <v>P</v>
+        <v>R</v>
       </c>
       <c r="IU15" s="26" t="str">
         <f>[1]CARTELLINO!IX$15</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="IV15" s="26" t="str">
         <f>[1]CARTELLINO!IY$15</f>
@@ -47139,13 +47142,13 @@
         <f>[1]CARTELLINO!IV$16</f>
         <v>m</v>
       </c>
-      <c r="IT16" s="46">
+      <c r="IT16" s="46" t="str">
         <f>[1]CARTELLINO!IW$16</f>
-        <v>0</v>
-      </c>
-      <c r="IU16" s="46">
+        <v>m</v>
+      </c>
+      <c r="IU16" s="46" t="str">
         <f>[1]CARTELLINO!IX$16</f>
-        <v>0</v>
+        <v>m</v>
       </c>
       <c r="IV16" s="46">
         <f>[1]CARTELLINO!IY$16</f>
@@ -52663,7 +52666,7 @@
       </c>
       <c r="IA21" s="28" t="str">
         <f>[1]CARTELLINO!ID$21</f>
-        <v>m</v>
+        <v>M</v>
       </c>
       <c r="IB21" s="28" t="str">
         <f>[1]CARTELLINO!IE$21</f>
@@ -52695,7 +52698,7 @@
       </c>
       <c r="II21" s="28" t="str">
         <f>[1]CARTELLINO!IL$21</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="IJ21" s="28" t="str">
         <f>[1]CARTELLINO!IM$21</f>
@@ -54255,9 +54258,9 @@
         <f>[1]CARTELLINO!IC$22</f>
         <v>0</v>
       </c>
-      <c r="IA22" s="46">
+      <c r="IA22" s="46" t="str">
         <f>[1]CARTELLINO!ID$22</f>
-        <v>0</v>
+        <v>x</v>
       </c>
       <c r="IB22" s="46">
         <f>[1]CARTELLINO!IE$22</f>
@@ -56335,7 +56338,7 @@
       </c>
       <c r="IT24" s="29" t="str">
         <f>[1]CARTELLINO!IW$24</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="IU24" s="29" t="str">
         <f>[1]CARTELLINO!IX$24</f>

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E7E528-0263-4B0A-B722-82E8EA710C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557C1A06-702B-4170-9E49-3D6482A8E63C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="0" yWindow="390" windowWidth="28800" windowHeight="15090" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1645,9 +1645,6 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="8">
-          <cell r="R8" t="str">
-            <v>MAT/R</v>
-          </cell>
           <cell r="AQ8" t="str">
             <v>GHIOTTI</v>
           </cell>
@@ -4721,7 +4718,7 @@
             <v>MICHELOT.</v>
           </cell>
           <cell r="AS227" t="str">
-            <v>VOLPINI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT227" t="str">
             <v>VOLPINI</v>
@@ -4794,7 +4791,7 @@
             <v>BERARDI</v>
           </cell>
           <cell r="AT232" t="str">
-            <v>BERARDI</v>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="233">
@@ -7470,7 +7467,7 @@
             <v>P</v>
           </cell>
           <cell r="ID3" t="str">
-            <v>m/R</v>
+            <v>M/R</v>
           </cell>
           <cell r="IE3" t="str">
             <v>P</v>
@@ -7842,7 +7839,7 @@
             <v>R</v>
           </cell>
           <cell r="MX3" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="MY3" t="str">
             <v>M</v>
@@ -9031,8 +9028,8 @@
           <cell r="MW4" t="str">
             <v>f</v>
           </cell>
-          <cell r="MX4" t="str">
-            <v>f</v>
+          <cell r="MX4">
+            <v>0</v>
           </cell>
           <cell r="MY4">
             <v>0</v>
@@ -9973,7 +9970,7 @@
             <v>r</v>
           </cell>
           <cell r="JT6" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="JU6" t="str">
             <v>m</v>
@@ -10219,13 +10216,13 @@
             <v>R</v>
           </cell>
           <cell r="MX6" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="MY6" t="str">
-            <v>m</v>
+            <v>-</v>
           </cell>
           <cell r="MZ6" t="str">
-            <v>p</v>
+            <v>-</v>
           </cell>
           <cell r="NA6" t="str">
             <v>-</v>
@@ -11408,14 +11405,14 @@
           <cell r="MW7">
             <v>0</v>
           </cell>
-          <cell r="MX7">
-            <v>0</v>
-          </cell>
-          <cell r="MY7">
-            <v>0</v>
-          </cell>
-          <cell r="MZ7">
-            <v>0</v>
+          <cell r="MX7" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="MY7" t="str">
+            <v>nl</v>
+          </cell>
+          <cell r="MZ7" t="str">
+            <v>nl</v>
           </cell>
           <cell r="NA7">
             <v>0</v>
@@ -12227,7 +12224,7 @@
             <v>-</v>
           </cell>
           <cell r="ID9" t="str">
-            <v>M</v>
+            <v>m</v>
           </cell>
           <cell r="IE9" t="str">
             <v>m</v>
@@ -17044,10 +17041,10 @@
             <v>-</v>
           </cell>
           <cell r="IW15" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="IX15" t="str">
             <v>R</v>
-          </cell>
-          <cell r="IX15" t="str">
-            <v>-</v>
           </cell>
           <cell r="IY15" t="str">
             <v>N</v>
@@ -19679,13 +19676,13 @@
             <v>-</v>
           </cell>
           <cell r="MD18" t="str">
-            <v>-</v>
+            <v>N</v>
           </cell>
           <cell r="ME18" t="str">
-            <v>-</v>
+            <v>S</v>
           </cell>
           <cell r="MF18" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="MG18" t="str">
             <v>P</v>
@@ -21747,7 +21744,7 @@
             <v>p</v>
           </cell>
           <cell r="ID21" t="str">
-            <v>M</v>
+            <v>m</v>
           </cell>
           <cell r="IE21" t="str">
             <v>r</v>
@@ -24253,7 +24250,7 @@
             <v>R</v>
           </cell>
           <cell r="JT24" t="str">
-            <v>P</v>
+            <v>p</v>
           </cell>
           <cell r="JU24" t="str">
             <v>p</v>
@@ -26882,10 +26879,10 @@
             <v>-</v>
           </cell>
           <cell r="MY27" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="MZ27" t="str">
             <v>R</v>
-          </cell>
-          <cell r="MZ27" t="str">
-            <v>-</v>
           </cell>
           <cell r="NA27" t="str">
             <v>-</v>
@@ -28072,10 +28069,10 @@
             <v>f</v>
           </cell>
           <cell r="MY28" t="str">
+            <v>nl</v>
+          </cell>
+          <cell r="MZ28" t="str">
             <v>f</v>
-          </cell>
-          <cell r="MZ28" t="str">
-            <v>nl</v>
           </cell>
           <cell r="NA28" t="str">
             <v>p</v>
@@ -28522,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28956,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -31091,7 +31088,7 @@
       </c>
       <c r="IA3" s="16" t="str">
         <f>[1]CARTELLINO!ID$3</f>
-        <v>m/R</v>
+        <v>M/R</v>
       </c>
       <c r="IB3" s="16" t="str">
         <f>[1]CARTELLINO!IE$3</f>
@@ -31587,7 +31584,7 @@
       </c>
       <c r="MU3" s="16" t="str">
         <f>[1]CARTELLINO!MX$3</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="MV3" s="16" t="str">
         <f>[1]CARTELLINO!MY$3</f>
@@ -33179,9 +33176,9 @@
         <f>[1]CARTELLINO!MW$4</f>
         <v>f</v>
       </c>
-      <c r="MU4" s="43" t="str">
+      <c r="MU4" s="43">
         <f>[1]CARTELLINO!MX$4</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="MV4" s="43">
         <f>[1]CARTELLINO!MY$4</f>
@@ -34854,7 +34851,7 @@
       </c>
       <c r="JQ6" s="22" t="str">
         <f>[1]CARTELLINO!JT$6</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="JR6" s="22" t="str">
         <f>[1]CARTELLINO!JU$6</f>
@@ -35182,15 +35179,15 @@
       </c>
       <c r="MU6" s="22" t="str">
         <f>[1]CARTELLINO!MX$6</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="MV6" s="22" t="str">
         <f>[1]CARTELLINO!MY$6</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="MW6" s="22" t="str">
         <f>[1]CARTELLINO!MZ$6</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="MX6" s="22" t="str">
         <f>[1]CARTELLINO!NA$6</f>
@@ -36774,17 +36771,17 @@
         <f>[1]CARTELLINO!MW$7</f>
         <v>0</v>
       </c>
-      <c r="MU7" s="46">
+      <c r="MU7" s="46" t="str">
         <f>[1]CARTELLINO!MX$7</f>
-        <v>0</v>
-      </c>
-      <c r="MV7" s="46">
+        <v>f</v>
+      </c>
+      <c r="MV7" s="46" t="str">
         <f>[1]CARTELLINO!MY$7</f>
-        <v>0</v>
-      </c>
-      <c r="MW7" s="46">
+        <v>nl</v>
+      </c>
+      <c r="MW7" s="46" t="str">
         <f>[1]CARTELLINO!MZ$7</f>
-        <v>0</v>
+        <v>nl</v>
       </c>
       <c r="MX7" s="46">
         <f>[1]CARTELLINO!NA$7</f>
@@ -38282,7 +38279,7 @@
       </c>
       <c r="IA9" s="24" t="str">
         <f>[1]CARTELLINO!ID$9</f>
-        <v>M</v>
+        <v>m</v>
       </c>
       <c r="IB9" s="24" t="str">
         <f>[1]CARTELLINO!IE$9</f>
@@ -45550,11 +45547,11 @@
       </c>
       <c r="IT15" s="26" t="str">
         <f>[1]CARTELLINO!IW$15</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="IU15" s="26" t="str">
         <f>[1]CARTELLINO!IX$15</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="IV15" s="26" t="str">
         <f>[1]CARTELLINO!IY$15</f>
@@ -49486,15 +49483,15 @@
       </c>
       <c r="MA18" s="27" t="str">
         <f>[1]CARTELLINO!MD$18</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="MB18" s="27" t="str">
         <f>[1]CARTELLINO!ME$18</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="MC18" s="27" t="str">
         <f>[1]CARTELLINO!MF$18</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="MD18" s="27" t="str">
         <f>[1]CARTELLINO!MG$18</f>
@@ -52666,7 +52663,7 @@
       </c>
       <c r="IA21" s="28" t="str">
         <f>[1]CARTELLINO!ID$21</f>
-        <v>M</v>
+        <v>m</v>
       </c>
       <c r="IB21" s="28" t="str">
         <f>[1]CARTELLINO!IE$21</f>
@@ -56430,7 +56427,7 @@
       </c>
       <c r="JQ24" s="29" t="str">
         <f>[1]CARTELLINO!JT$24</f>
-        <v>P</v>
+        <v>p</v>
       </c>
       <c r="JR24" s="29" t="str">
         <f>[1]CARTELLINO!JU$24</f>
@@ -60358,11 +60355,11 @@
       </c>
       <c r="MV27" s="30" t="str">
         <f>[1]CARTELLINO!MY$27</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="MW27" s="30" t="str">
         <f>[1]CARTELLINO!MZ$27</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="MX27" s="30" t="str">
         <f>[1]CARTELLINO!NA$27</f>
@@ -61952,11 +61949,11 @@
       </c>
       <c r="MV28" s="62" t="str">
         <f>[1]CARTELLINO!MY$28</f>
-        <v>f</v>
+        <v>nl</v>
       </c>
       <c r="MW28" s="62" t="str">
         <f>[1]CARTELLINO!MZ$28</f>
-        <v>nl</v>
+        <v>f</v>
       </c>
       <c r="MX28" s="62" t="str">
         <f>[1]CARTELLINO!NA$28</f>
@@ -64973,7 +64970,7 @@
         <v>MICHELOT.</v>
       </c>
       <c r="HM31" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="HN31" s="63" t="str">
         <v>SARTI</v>
@@ -66088,7 +66085,7 @@
         <v>MICHELOT.</v>
       </c>
       <c r="HR32" s="63" t="str">
-        <v>BERARDI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="HS32" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -66534,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71032,13 +71029,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71047,6 +71037,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557C1A06-702B-4170-9E49-3D6482A8E63C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB32F9B3-04B3-4324-AAD7-5736B8F843CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="390" windowWidth="28800" windowHeight="15090" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4903,7 +4903,7 @@
             <v>FABBRI</v>
           </cell>
           <cell r="AT240" t="str">
-            <v>FABBRI</v>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="241">
@@ -4925,7 +4925,7 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR242" t="str">
-            <v>PAZZAGLIA</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS242" t="str">
             <v>VOLPINI</v>
@@ -12323,13 +12323,13 @@
             <v>p</v>
           </cell>
           <cell r="JK9" t="str">
-            <v>m</v>
+            <v>N</v>
           </cell>
           <cell r="JL9" t="str">
-            <v>m</v>
+            <v>S</v>
           </cell>
           <cell r="JM9" t="str">
-            <v>r</v>
+            <v>R</v>
           </cell>
           <cell r="JN9" t="str">
             <v>-</v>
@@ -21843,10 +21843,10 @@
             <v>M</v>
           </cell>
           <cell r="JK21" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="JL21" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="JM21" t="str">
             <v>R</v>
@@ -23032,11 +23032,11 @@
           <cell r="JJ22">
             <v>0</v>
           </cell>
-          <cell r="JK22">
-            <v>0</v>
-          </cell>
-          <cell r="JL22">
-            <v>0</v>
+          <cell r="JK22" t="str">
+            <v>pn</v>
+          </cell>
+          <cell r="JL22" t="str">
+            <v>x</v>
           </cell>
           <cell r="JM22">
             <v>0</v>
@@ -23264,22 +23264,22 @@
             <v>0</v>
           </cell>
           <cell r="MJ22" t="str">
-            <v>f</v>
+            <v>p</v>
           </cell>
           <cell r="MK22" t="str">
-            <v>f</v>
+            <v>pn</v>
           </cell>
           <cell r="ML22" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="MM22" t="str">
-            <v>f</v>
+            <v>x</v>
+          </cell>
+          <cell r="MM22">
+            <v>0</v>
           </cell>
           <cell r="MN22" t="str">
-            <v>f</v>
+            <v>p</v>
           </cell>
           <cell r="MO22" t="str">
-            <v>f</v>
+            <v>p</v>
           </cell>
           <cell r="MP22">
             <v>0</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -38411,15 +38411,15 @@
       </c>
       <c r="JH9" s="24" t="str">
         <f>[1]CARTELLINO!JK$9</f>
-        <v>m</v>
+        <v>N</v>
       </c>
       <c r="JI9" s="24" t="str">
         <f>[1]CARTELLINO!JL$9</f>
-        <v>m</v>
+        <v>S</v>
       </c>
       <c r="JJ9" s="24" t="str">
         <f>[1]CARTELLINO!JM$9</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="JK9" s="24" t="str">
         <f>[1]CARTELLINO!JN$9</f>
@@ -52795,11 +52795,11 @@
       </c>
       <c r="JH21" s="28" t="str">
         <f>[1]CARTELLINO!JK$21</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="JI21" s="28" t="str">
         <f>[1]CARTELLINO!JL$21</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="JJ21" s="28" t="str">
         <f>[1]CARTELLINO!JM$21</f>
@@ -54387,13 +54387,13 @@
         <f>[1]CARTELLINO!JJ$22</f>
         <v>0</v>
       </c>
-      <c r="JH22" s="46">
+      <c r="JH22" s="46" t="str">
         <f>[1]CARTELLINO!JK$22</f>
-        <v>0</v>
-      </c>
-      <c r="JI22" s="46">
+        <v>pn</v>
+      </c>
+      <c r="JI22" s="46" t="str">
         <f>[1]CARTELLINO!JL$22</f>
-        <v>0</v>
+        <v>x</v>
       </c>
       <c r="JJ22" s="46">
         <f>[1]CARTELLINO!JM$22</f>
@@ -54697,27 +54697,27 @@
       </c>
       <c r="MG22" s="46" t="str">
         <f>[1]CARTELLINO!MJ$22</f>
-        <v>f</v>
+        <v>p</v>
       </c>
       <c r="MH22" s="46" t="str">
         <f>[1]CARTELLINO!MK$22</f>
-        <v>f</v>
+        <v>pn</v>
       </c>
       <c r="MI22" s="46" t="str">
         <f>[1]CARTELLINO!ML$22</f>
-        <v>f</v>
-      </c>
-      <c r="MJ22" s="46" t="str">
+        <v>x</v>
+      </c>
+      <c r="MJ22" s="46">
         <f>[1]CARTELLINO!MM$22</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="MK22" s="46" t="str">
         <f>[1]CARTELLINO!MN$22</f>
-        <v>f</v>
+        <v>p</v>
       </c>
       <c r="ML22" s="46" t="str">
         <f>[1]CARTELLINO!MO$22</f>
-        <v>f</v>
+        <v>p</v>
       </c>
       <c r="MM22" s="46">
         <f>[1]CARTELLINO!MP$22</f>
@@ -63915,7 +63915,7 @@
         <v>FABBRI</v>
       </c>
       <c r="IB30" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="IC30" s="63" t="str">
         <v>BERARDI</v>
@@ -66109,7 +66109,7 @@
         <v>BIANCHI</v>
       </c>
       <c r="HZ32" s="63" t="str">
-        <v>FABBRI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IA32" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,6 +71029,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71037,13 +71044,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">
